--- a/NBFC-MF/LoanPortfolio.xlsx
+++ b/NBFC-MF/LoanPortfolio.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="164011"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="3600" windowWidth="15360" windowHeight="4410"/>
+    <workbookView xWindow="0" yWindow="3600" windowWidth="15360" windowHeight="4410" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Portfolio" sheetId="7" r:id="rId1"/>
@@ -63,7 +63,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="247" uniqueCount="130">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="255" uniqueCount="135">
   <si>
     <t>Code</t>
   </si>
@@ -453,6 +453,21 @@
   </si>
   <si>
     <t>grocery expense 1550</t>
+  </si>
+  <si>
+    <t>bomcha marup 6500; interest 5000; phiroi 2000 ; kongba marup 3000</t>
+  </si>
+  <si>
+    <t>224kamala loan 50000</t>
+  </si>
+  <si>
+    <t>wangkhei marup 12000</t>
+  </si>
+  <si>
+    <t>225samila loan 20000; 226sandhyarani loan25000</t>
+  </si>
+  <si>
+    <t>21sept: 5500 payable to aboong</t>
   </si>
 </sst>
 </file>
@@ -1223,6 +1238,7 @@
     <sheetNames>
       <sheetName val="Loan1"/>
       <sheetName val="198"/>
+      <sheetName val="226"/>
     </sheetNames>
     <sheetDataSet>
       <sheetData sheetId="0">
@@ -1310,22 +1326,22 @@
         </row>
         <row r="12">
           <cell r="K12">
-            <v>11</v>
+            <v>17</v>
           </cell>
         </row>
         <row r="13">
           <cell r="K13">
-            <v>8400</v>
+            <v>0</v>
           </cell>
         </row>
         <row r="14">
           <cell r="K14">
-            <v>7840.638844742849</v>
+            <v>9.1336005425546318E-10</v>
           </cell>
         </row>
         <row r="15">
           <cell r="K15">
-            <v>12159.361155257151</v>
+            <v>19999.999999999087</v>
           </cell>
         </row>
         <row r="16">
@@ -1336,6 +1352,63 @@
         <row r="17">
           <cell r="K17">
             <v>46324</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="2">
+        <row r="2">
+          <cell r="K2" t="str">
+            <v>L25000W17-Mutum_Sandhyarani-N226</v>
+          </cell>
+        </row>
+        <row r="3">
+          <cell r="K3" t="str">
+            <v>Mutum_Sandhyarani</v>
+          </cell>
+        </row>
+        <row r="7">
+          <cell r="K7">
+            <v>25000</v>
+          </cell>
+        </row>
+        <row r="9">
+          <cell r="K9">
+            <v>1750</v>
+          </cell>
+        </row>
+        <row r="10">
+          <cell r="K10">
+            <v>17</v>
+          </cell>
+        </row>
+        <row r="12">
+          <cell r="K12">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="13">
+          <cell r="K13">
+            <v>29750</v>
+          </cell>
+        </row>
+        <row r="14">
+          <cell r="K14">
+            <v>29750</v>
+          </cell>
+        </row>
+        <row r="15">
+          <cell r="K15">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="16">
+          <cell r="K16" t="str">
+            <v/>
+          </cell>
+        </row>
+        <row r="17">
+          <cell r="K17" t="str">
+            <v/>
           </cell>
         </row>
       </sheetData>
@@ -1437,22 +1510,22 @@
         </row>
         <row r="12">
           <cell r="K12">
-            <v>4</v>
+            <v>5</v>
           </cell>
         </row>
         <row r="13">
           <cell r="K13">
-            <v>18200</v>
+            <v>16800</v>
           </cell>
         </row>
         <row r="14">
           <cell r="K14">
-            <v>15882.325006125111</v>
+            <v>14800.790431951375</v>
           </cell>
         </row>
         <row r="15">
           <cell r="K15">
-            <v>4117.674993874889</v>
+            <v>5199.2095680486254</v>
           </cell>
         </row>
         <row r="16">
@@ -1807,22 +1880,22 @@
         </row>
         <row r="12">
           <cell r="K12">
-            <v>2</v>
+            <v>3</v>
           </cell>
         </row>
         <row r="13">
           <cell r="K13">
-            <v>30000</v>
+            <v>27000</v>
           </cell>
         </row>
         <row r="14">
           <cell r="K14">
-            <v>25691.656051705635</v>
+            <v>23442.585668039574</v>
           </cell>
         </row>
         <row r="15">
           <cell r="K15">
-            <v>4308.343948294365</v>
+            <v>6557.4143319604264</v>
           </cell>
         </row>
         <row r="16">
@@ -1992,22 +2065,22 @@
         </row>
         <row r="12">
           <cell r="K12">
-            <v>11</v>
+            <v>21</v>
           </cell>
         </row>
         <row r="13">
           <cell r="K13">
-            <v>32700</v>
+            <v>29700</v>
           </cell>
         </row>
         <row r="14">
           <cell r="K14">
-            <v>27691.965326606991</v>
+            <v>25524.137134582503</v>
           </cell>
         </row>
         <row r="15">
           <cell r="K15">
-            <v>2308.0346733930091</v>
+            <v>4475.8628654174972</v>
           </cell>
         </row>
         <row r="16">
@@ -2159,6 +2232,7 @@
     <sheetNames>
       <sheetName val="Loan1"/>
       <sheetName val="197"/>
+      <sheetName val="225"/>
     </sheetNames>
     <sheetDataSet>
       <sheetData sheetId="0">
@@ -2246,22 +2320,22 @@
         </row>
         <row r="12">
           <cell r="K12">
-            <v>11</v>
+            <v>17</v>
           </cell>
         </row>
         <row r="13">
           <cell r="K13">
-            <v>8400</v>
+            <v>0</v>
           </cell>
         </row>
         <row r="14">
           <cell r="K14">
-            <v>7840.638844742849</v>
+            <v>9.1336005425546318E-10</v>
           </cell>
         </row>
         <row r="15">
           <cell r="K15">
-            <v>12159.361155257151</v>
+            <v>19999.999999999087</v>
           </cell>
         </row>
         <row r="16">
@@ -2272,6 +2346,63 @@
         <row r="17">
           <cell r="K17">
             <v>46325</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="2">
+        <row r="2">
+          <cell r="K2" t="str">
+            <v>L20000W17-Lanchenbi_Samila-N225</v>
+          </cell>
+        </row>
+        <row r="3">
+          <cell r="K3" t="str">
+            <v>Lanchenbi_Samila</v>
+          </cell>
+        </row>
+        <row r="7">
+          <cell r="K7">
+            <v>20000</v>
+          </cell>
+        </row>
+        <row r="9">
+          <cell r="K9">
+            <v>1400</v>
+          </cell>
+        </row>
+        <row r="10">
+          <cell r="K10">
+            <v>17</v>
+          </cell>
+        </row>
+        <row r="12">
+          <cell r="K12">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="13">
+          <cell r="K13">
+            <v>23800</v>
+          </cell>
+        </row>
+        <row r="14">
+          <cell r="K14">
+            <v>23800</v>
+          </cell>
+        </row>
+        <row r="15">
+          <cell r="K15">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="16">
+          <cell r="K16" t="str">
+            <v/>
+          </cell>
+        </row>
+        <row r="17">
+          <cell r="K17" t="str">
+            <v/>
           </cell>
         </row>
       </sheetData>
@@ -2374,22 +2505,22 @@
         </row>
         <row r="12">
           <cell r="K12">
-            <v>3</v>
+            <v>4</v>
           </cell>
         </row>
         <row r="13">
           <cell r="K13">
-            <v>9800</v>
+            <v>9100</v>
           </cell>
         </row>
         <row r="14">
           <cell r="K14">
-            <v>8471.2997110135693</v>
+            <v>7941.1625030625555</v>
           </cell>
         </row>
         <row r="15">
           <cell r="K15">
-            <v>1528.7002889864307</v>
+            <v>2058.8374969374445</v>
           </cell>
         </row>
         <row r="16">
@@ -2431,22 +2562,22 @@
         </row>
         <row r="12">
           <cell r="K12">
-            <v>1</v>
+            <v>2</v>
           </cell>
         </row>
         <row r="13">
           <cell r="K13">
-            <v>33600</v>
+            <v>31500</v>
           </cell>
         </row>
         <row r="14">
           <cell r="K14">
-            <v>28501.546862383388</v>
+            <v>26973.047398654715</v>
           </cell>
         </row>
         <row r="15">
           <cell r="K15">
-            <v>1498.4531376166124</v>
+            <v>3026.9526013452851</v>
           </cell>
         </row>
         <row r="16">
@@ -2892,22 +3023,22 @@
         </row>
         <row r="12">
           <cell r="K12">
-            <v>4</v>
+            <v>12</v>
           </cell>
         </row>
         <row r="13">
           <cell r="K13">
-            <v>23200</v>
+            <v>21600</v>
           </cell>
         </row>
         <row r="14">
           <cell r="K14">
-            <v>19446.555966324511</v>
+            <v>18318.802096717634</v>
           </cell>
         </row>
         <row r="15">
           <cell r="K15">
-            <v>553.44403367548875</v>
+            <v>1681.1979032823656</v>
           </cell>
         </row>
         <row r="16">
@@ -2961,22 +3092,22 @@
         </row>
         <row r="12">
           <cell r="K12">
-            <v>14</v>
+            <v>15</v>
           </cell>
         </row>
         <row r="13">
           <cell r="K13">
-            <v>4200</v>
+            <v>2800</v>
           </cell>
         </row>
         <row r="14">
           <cell r="K14">
-            <v>4037.031116629747</v>
+            <v>2717.9798966815056</v>
           </cell>
         </row>
         <row r="15">
           <cell r="K15">
-            <v>15962.968883370253</v>
+            <v>17282.020103318493</v>
           </cell>
         </row>
         <row r="16">
@@ -3099,22 +3230,22 @@
         </row>
         <row r="12">
           <cell r="K12">
-            <v>11</v>
+            <v>13</v>
           </cell>
         </row>
         <row r="13">
           <cell r="K13">
-            <v>12600</v>
+            <v>8400</v>
           </cell>
         </row>
         <row r="14">
           <cell r="K14">
-            <v>11760.958267114203</v>
+            <v>7995.2298277146756</v>
           </cell>
         </row>
         <row r="15">
           <cell r="K15">
-            <v>18239.041732885795</v>
+            <v>22004.770172285323</v>
           </cell>
         </row>
         <row r="16">
@@ -3168,22 +3299,22 @@
         </row>
         <row r="12">
           <cell r="K12">
-            <v>11</v>
+            <v>12</v>
           </cell>
         </row>
         <row r="13">
           <cell r="K13">
-            <v>4200</v>
+            <v>3500</v>
           </cell>
         </row>
         <row r="14">
           <cell r="K14">
-            <v>3920.3194223714245</v>
+            <v>3298.927950640365</v>
           </cell>
         </row>
         <row r="15">
           <cell r="K15">
-            <v>6079.6805776285755</v>
+            <v>6701.0720493596345</v>
           </cell>
         </row>
         <row r="16">
@@ -3237,22 +3368,22 @@
         </row>
         <row r="12">
           <cell r="K12">
-            <v>11</v>
+            <v>13</v>
           </cell>
         </row>
         <row r="13">
           <cell r="K13">
-            <v>8400</v>
+            <v>5600</v>
           </cell>
         </row>
         <row r="14">
           <cell r="K14">
-            <v>7840.638844742849</v>
+            <v>5330.1532184765038</v>
           </cell>
         </row>
         <row r="15">
           <cell r="K15">
-            <v>12159.361155257151</v>
+            <v>14669.846781523496</v>
           </cell>
         </row>
         <row r="16">
@@ -3306,22 +3437,22 @@
         </row>
         <row r="12">
           <cell r="K12">
-            <v>11</v>
+            <v>12</v>
           </cell>
         </row>
         <row r="13">
           <cell r="K13">
-            <v>8400</v>
+            <v>7000</v>
           </cell>
         </row>
         <row r="14">
           <cell r="K14">
-            <v>7840.638844742849</v>
+            <v>6597.85590128073</v>
           </cell>
         </row>
         <row r="15">
           <cell r="K15">
-            <v>12159.361155257151</v>
+            <v>13402.144098719269</v>
           </cell>
         </row>
         <row r="16">
@@ -3375,22 +3506,22 @@
         </row>
         <row r="12">
           <cell r="K12">
-            <v>7</v>
+            <v>9</v>
           </cell>
         </row>
         <row r="13">
           <cell r="K13">
-            <v>70000</v>
+            <v>56000</v>
           </cell>
         </row>
         <row r="14">
           <cell r="K14">
-            <v>62861.13531643273</v>
+            <v>51266.976567526755</v>
           </cell>
         </row>
         <row r="15">
           <cell r="K15">
-            <v>37138.86468356727</v>
+            <v>48733.023432473245</v>
           </cell>
         </row>
         <row r="16">
@@ -3444,22 +3575,22 @@
         </row>
         <row r="12">
           <cell r="K12">
-            <v>7</v>
+            <v>8</v>
           </cell>
         </row>
         <row r="13">
           <cell r="K13">
-            <v>42000</v>
+            <v>37800</v>
           </cell>
         </row>
         <row r="14">
           <cell r="K14">
-            <v>37716.681189859737</v>
+            <v>34272.959564168894</v>
           </cell>
         </row>
         <row r="15">
           <cell r="K15">
-            <v>22283.318810140263</v>
+            <v>25727.040435831106</v>
           </cell>
         </row>
         <row r="16">
@@ -3513,22 +3644,22 @@
         </row>
         <row r="12">
           <cell r="K12">
-            <v>61</v>
+            <v>63</v>
           </cell>
         </row>
         <row r="13">
           <cell r="K13">
-            <v>29500</v>
+            <v>28500</v>
           </cell>
         </row>
         <row r="14">
           <cell r="K14">
-            <v>26910.362742211062</v>
+            <v>26076.674163036809</v>
           </cell>
         </row>
         <row r="15">
           <cell r="K15">
-            <v>23089.637257788938</v>
+            <v>23923.325836963191</v>
           </cell>
         </row>
         <row r="16">
@@ -3582,22 +3713,22 @@
         </row>
         <row r="12">
           <cell r="K12">
-            <v>7</v>
+            <v>8</v>
           </cell>
         </row>
         <row r="13">
           <cell r="K13">
-            <v>14000</v>
+            <v>12600</v>
           </cell>
         </row>
         <row r="14">
           <cell r="K14">
-            <v>12572.227063286609</v>
+            <v>11424.319854722999</v>
           </cell>
         </row>
         <row r="15">
           <cell r="K15">
-            <v>7427.7729367133907</v>
+            <v>8575.6801452770014</v>
           </cell>
         </row>
         <row r="16">
@@ -3651,22 +3782,22 @@
         </row>
         <row r="12">
           <cell r="K12">
-            <v>5</v>
+            <v>7</v>
           </cell>
         </row>
         <row r="13">
           <cell r="K13">
-            <v>84000</v>
+            <v>70000</v>
           </cell>
         </row>
         <row r="14">
           <cell r="K14">
-            <v>74003.952159756635</v>
+            <v>62861.13531643273</v>
           </cell>
         </row>
         <row r="15">
           <cell r="K15">
-            <v>25996.047840243365</v>
+            <v>37138.86468356727</v>
           </cell>
         </row>
         <row r="16">
@@ -3720,22 +3851,22 @@
         </row>
         <row r="12">
           <cell r="K12">
-            <v>26</v>
+            <v>31</v>
           </cell>
         </row>
         <row r="13">
           <cell r="K13">
-            <v>16200</v>
+            <v>14700</v>
           </cell>
         </row>
         <row r="14">
           <cell r="K14">
-            <v>14295.302542559919</v>
+            <v>13117.062707143943</v>
           </cell>
         </row>
         <row r="15">
           <cell r="K15">
-            <v>5704.6974574400811</v>
+            <v>6882.937292856057</v>
           </cell>
         </row>
         <row r="16">
@@ -3858,22 +3989,22 @@
         </row>
         <row r="12">
           <cell r="K12">
-            <v>3</v>
+            <v>4</v>
           </cell>
         </row>
         <row r="13">
           <cell r="K13">
-            <v>19600</v>
+            <v>18200</v>
           </cell>
         </row>
         <row r="14">
           <cell r="K14">
-            <v>16942.599422027139</v>
+            <v>15882.325006125111</v>
           </cell>
         </row>
         <row r="15">
           <cell r="K15">
-            <v>3057.4005779728614</v>
+            <v>4117.674993874889</v>
           </cell>
         </row>
         <row r="16">
@@ -3927,22 +4058,22 @@
         </row>
         <row r="12">
           <cell r="K12">
-            <v>3</v>
+            <v>4</v>
           </cell>
         </row>
         <row r="13">
           <cell r="K13">
-            <v>19600</v>
+            <v>18200</v>
           </cell>
         </row>
         <row r="14">
           <cell r="K14">
-            <v>16942.599422027139</v>
+            <v>15882.325006125111</v>
           </cell>
         </row>
         <row r="15">
           <cell r="K15">
-            <v>3057.4005779728614</v>
+            <v>4117.674993874889</v>
           </cell>
         </row>
         <row r="16">
@@ -3996,22 +4127,22 @@
         </row>
         <row r="12">
           <cell r="K12">
-            <v>2</v>
+            <v>3</v>
           </cell>
         </row>
         <row r="13">
           <cell r="K13">
-            <v>21000</v>
+            <v>19600</v>
           </cell>
         </row>
         <row r="14">
           <cell r="K14">
-            <v>17982.031599103153</v>
+            <v>16942.599422027139</v>
           </cell>
         </row>
         <row r="15">
           <cell r="K15">
-            <v>2017.968400896847</v>
+            <v>3057.4005779728614</v>
           </cell>
         </row>
         <row r="16">
@@ -4065,22 +4196,22 @@
         </row>
         <row r="12">
           <cell r="K12">
-            <v>17</v>
+            <v>24</v>
           </cell>
         </row>
         <row r="13">
           <cell r="K13">
-            <v>18900</v>
+            <v>16800</v>
           </cell>
         </row>
         <row r="14">
           <cell r="K14">
-            <v>16348.408466459945</v>
+            <v>14758.991922004241</v>
           </cell>
         </row>
         <row r="15">
           <cell r="K15">
-            <v>3651.591533540055</v>
+            <v>5241.0080779957589</v>
           </cell>
         </row>
         <row r="16">
@@ -4134,22 +4265,22 @@
         </row>
         <row r="12">
           <cell r="K12">
-            <v>2</v>
+            <v>3</v>
           </cell>
         </row>
         <row r="13">
           <cell r="K13">
-            <v>31500</v>
+            <v>29400</v>
           </cell>
         </row>
         <row r="14">
           <cell r="K14">
-            <v>26973.047398654715</v>
+            <v>25413.899133040686</v>
           </cell>
         </row>
         <row r="15">
           <cell r="K15">
-            <v>3026.9526013452851</v>
+            <v>4586.1008669593139</v>
           </cell>
         </row>
         <row r="16">
@@ -4244,6 +4375,7 @@
       <sheetName val="Loan1"/>
       <sheetName val="188"/>
       <sheetName val="204"/>
+      <sheetName val="224"/>
     </sheetNames>
     <sheetDataSet>
       <sheetData sheetId="0">
@@ -4331,22 +4463,22 @@
         </row>
         <row r="12">
           <cell r="K12">
-            <v>85</v>
+            <v>120</v>
           </cell>
         </row>
         <row r="13">
           <cell r="K13">
-            <v>14000</v>
+            <v>0</v>
           </cell>
         </row>
         <row r="14">
           <cell r="K14">
-            <v>13244.497417797626</v>
+            <v>1.8109176380676217E-9</v>
           </cell>
         </row>
         <row r="15">
           <cell r="K15">
-            <v>26755.502582202374</v>
+            <v>39999.999999998188</v>
           </cell>
         </row>
         <row r="16">
@@ -4388,22 +4520,22 @@
         </row>
         <row r="12">
           <cell r="K12">
-            <v>6</v>
+            <v>7</v>
           </cell>
         </row>
         <row r="13">
           <cell r="K13">
-            <v>15400</v>
+            <v>14000</v>
           </cell>
         </row>
         <row r="14">
           <cell r="K14">
-            <v>13697.569400122526</v>
+            <v>12572.227063286609</v>
           </cell>
         </row>
         <row r="15">
           <cell r="K15">
-            <v>6302.4305998774744</v>
+            <v>7427.7729367133907</v>
           </cell>
         </row>
         <row r="16">
@@ -4414,6 +4546,63 @@
         <row r="17">
           <cell r="K17">
             <v>46360</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="3">
+        <row r="2">
+          <cell r="K2" t="str">
+            <v>L50000D120-Kamala-N224</v>
+          </cell>
+        </row>
+        <row r="3">
+          <cell r="K3" t="str">
+            <v>Kamala</v>
+          </cell>
+        </row>
+        <row r="7">
+          <cell r="K7">
+            <v>50000</v>
+          </cell>
+        </row>
+        <row r="9">
+          <cell r="K9">
+            <v>500</v>
+          </cell>
+        </row>
+        <row r="10">
+          <cell r="K10">
+            <v>120</v>
+          </cell>
+        </row>
+        <row r="12">
+          <cell r="K12">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="13">
+          <cell r="K13">
+            <v>60000</v>
+          </cell>
+        </row>
+        <row r="14">
+          <cell r="K14">
+            <v>60000</v>
+          </cell>
+        </row>
+        <row r="15">
+          <cell r="K15">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="16">
+          <cell r="K16" t="str">
+            <v/>
+          </cell>
+        </row>
+        <row r="17">
+          <cell r="K17" t="str">
+            <v/>
           </cell>
         </row>
       </sheetData>
@@ -4457,22 +4646,22 @@
         </row>
         <row r="12">
           <cell r="K12">
-            <v>4</v>
+            <v>9</v>
           </cell>
         </row>
         <row r="13">
           <cell r="K13">
-            <v>11400</v>
+            <v>10650</v>
           </cell>
         </row>
         <row r="14">
           <cell r="K14">
-            <v>9583.2761230814613</v>
+            <v>9051.3676217399407</v>
           </cell>
         </row>
         <row r="15">
           <cell r="K15">
-            <v>416.72387691853874</v>
+            <v>948.63237826005934</v>
           </cell>
         </row>
         <row r="16">
@@ -4526,32 +4715,32 @@
         </row>
         <row r="12">
           <cell r="K12">
-            <v>0</v>
+            <v>1</v>
           </cell>
         </row>
         <row r="13">
           <cell r="K13">
-            <v>71400</v>
+            <v>67200</v>
           </cell>
         </row>
         <row r="14">
           <cell r="K14">
-            <v>71400</v>
+            <v>57003.093724766775</v>
           </cell>
         </row>
         <row r="15">
           <cell r="K15">
-            <v>0</v>
+            <v>2996.9062752332247</v>
           </cell>
         </row>
         <row r="16">
-          <cell r="K16" t="str">
-            <v/>
+          <cell r="K16">
+            <v>46281</v>
           </cell>
         </row>
         <row r="17">
-          <cell r="K17" t="str">
-            <v/>
+          <cell r="K17">
+            <v>46400</v>
           </cell>
         </row>
       </sheetData>
@@ -5101,22 +5290,22 @@
         </row>
         <row r="12">
           <cell r="K12">
-            <v>105</v>
+            <v>120</v>
           </cell>
         </row>
         <row r="13">
           <cell r="K13">
-            <v>3000</v>
+            <v>0</v>
           </cell>
         </row>
         <row r="14">
           <cell r="K14">
-            <v>2926.5603118846607</v>
+            <v>9.0545881903381087E-10</v>
           </cell>
         </row>
         <row r="15">
           <cell r="K15">
-            <v>17073.439688115341</v>
+            <v>19999.999999999094</v>
           </cell>
         </row>
         <row r="16">
@@ -5228,22 +5417,22 @@
         </row>
         <row r="12">
           <cell r="K12">
-            <v>11</v>
+            <v>12</v>
           </cell>
         </row>
         <row r="13">
           <cell r="K13">
-            <v>75600</v>
+            <v>63000</v>
           </cell>
         </row>
         <row r="14">
           <cell r="K14">
-            <v>70565.749602685508</v>
+            <v>59380.703111526433</v>
           </cell>
         </row>
         <row r="15">
           <cell r="K15">
-            <v>109434.25039731449</v>
+            <v>120619.29688847356</v>
           </cell>
         </row>
         <row r="16">
@@ -5355,22 +5544,22 @@
         </row>
         <row r="12">
           <cell r="K12">
-            <v>9</v>
+            <v>10</v>
           </cell>
         </row>
         <row r="13">
           <cell r="K13">
-            <v>16800</v>
+            <v>14700</v>
           </cell>
         </row>
         <row r="14">
           <cell r="K14">
-            <v>15380.092970258089</v>
+            <v>13588.487859238874</v>
           </cell>
         </row>
         <row r="15">
           <cell r="K15">
-            <v>14619.907029741911</v>
+            <v>16411.512140761126</v>
           </cell>
         </row>
         <row r="16">
@@ -5551,22 +5740,22 @@
         </row>
         <row r="12">
           <cell r="K12">
-            <v>11</v>
+            <v>13</v>
           </cell>
         </row>
         <row r="13">
           <cell r="K13">
-            <v>9800</v>
+            <v>9400</v>
           </cell>
         </row>
         <row r="14">
           <cell r="K14">
-            <v>8432.3044104048531</v>
+            <v>8135.670977686661</v>
           </cell>
         </row>
         <row r="15">
           <cell r="K15">
-            <v>1567.6955895951469</v>
+            <v>1864.329022313339</v>
           </cell>
         </row>
         <row r="16">
@@ -5881,7 +6070,7 @@
       <c r="J1" s="82"/>
       <c r="K1" s="83">
         <f>SUM(J5:J1000)</f>
-        <v>858950</v>
+        <v>850450</v>
       </c>
       <c r="L1" s="84"/>
       <c r="N1" s="78" t="s">
@@ -5890,7 +6079,7 @@
       <c r="O1" s="10"/>
       <c r="P1" s="78">
         <f>SUM(P5:P1000)</f>
-        <v>78600</v>
+        <v>79650</v>
       </c>
     </row>
     <row r="2" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -5903,7 +6092,7 @@
       <c r="J2" s="82"/>
       <c r="K2" s="83">
         <f>SUM(K5:K1000)</f>
-        <v>770232.83311614464</v>
+        <v>768809.71349669166</v>
       </c>
       <c r="L2" s="84"/>
       <c r="M2" s="2"/>
@@ -5967,7 +6156,7 @@
       </c>
       <c r="R4" s="43">
         <f>SUM(R5:R43)</f>
-        <v>258000</v>
+        <v>218000</v>
       </c>
     </row>
     <row r="5" spans="1:18" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -6115,7 +6304,7 @@
       </c>
       <c r="G7" s="19">
         <f t="shared" ref="G7:G17" si="0">IF(H7,H7-I7,"")</f>
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="H7" s="62">
         <f>[3]Loan1!$K$10</f>
@@ -6123,19 +6312,19 @@
       </c>
       <c r="I7" s="62">
         <f>[3]Loan1!$K$12</f>
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="J7" s="15">
         <f>[3]Loan1!$K$13</f>
-        <v>29500</v>
+        <v>28500</v>
       </c>
       <c r="K7" s="15">
         <f>[3]Loan1!$K$14</f>
-        <v>26910.362742211062</v>
+        <v>26076.674163036809</v>
       </c>
       <c r="L7" s="64">
         <f>[3]Loan1!$K$15</f>
-        <v>23089.637257788938</v>
+        <v>23923.325836963191</v>
       </c>
       <c r="M7" s="65">
         <f>[3]Loan1!$K$16</f>
@@ -6214,68 +6403,67 @@
       <c r="R8" s="43"/>
     </row>
     <row r="9" spans="1:18" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="62">
+      <c r="A9" s="41">
         <f t="shared" si="1"/>
         <v>164</v>
       </c>
-      <c r="B9" s="62" t="str">
+      <c r="B9" s="41" t="str">
         <f>[5]Loan1!$K$3</f>
         <v>Sanasam_Sonia</v>
       </c>
-      <c r="C9" s="62" t="s">
+      <c r="C9" s="41" t="s">
         <v>6</v>
       </c>
-      <c r="D9" s="63" t="str">
+      <c r="D9" s="67" t="str">
         <f>[5]Loan1!$K$2</f>
         <v>L20000D120-Sanasam_Sonia-NLoan1</v>
       </c>
-      <c r="E9" s="15">
+      <c r="E9" s="68">
         <f>[5]Loan1!$K$7</f>
         <v>20000</v>
       </c>
-      <c r="F9" s="62">
+      <c r="F9" s="41">
         <f>[5]Loan1!$K$9</f>
         <v>200</v>
       </c>
-      <c r="G9" s="19">
+      <c r="G9" s="41">
         <f t="shared" si="0"/>
-        <v>15</v>
-      </c>
-      <c r="H9" s="62">
+        <v>0</v>
+      </c>
+      <c r="H9" s="41">
         <f>[5]Loan1!$K$10</f>
         <v>120</v>
       </c>
-      <c r="I9" s="62">
+      <c r="I9" s="41">
         <f>[5]Loan1!$K$12</f>
-        <v>105</v>
-      </c>
-      <c r="J9" s="15">
+        <v>120</v>
+      </c>
+      <c r="J9" s="68">
         <f>[5]Loan1!$K$13</f>
-        <v>3000</v>
-      </c>
-      <c r="K9" s="15">
+        <v>0</v>
+      </c>
+      <c r="K9" s="68">
         <f>[5]Loan1!$K$14</f>
-        <v>2926.5603118846607</v>
-      </c>
-      <c r="L9" s="64">
+        <v>9.0545881903381087E-10</v>
+      </c>
+      <c r="L9" s="69">
         <f>[5]Loan1!$K$15</f>
-        <v>17073.439688115341</v>
-      </c>
-      <c r="M9" s="65">
+        <v>19999.999999999094</v>
+      </c>
+      <c r="M9" s="70">
         <f>[5]Loan1!$K$16</f>
         <v>46092</v>
       </c>
-      <c r="N9" s="66">
+      <c r="N9" s="71">
         <f>[5]Loan1!$K$17</f>
         <v>46212</v>
       </c>
-      <c r="P9" s="46"/>
-      <c r="Q9" s="46" t="s">
+      <c r="O9" s="42"/>
+      <c r="P9" s="45"/>
+      <c r="Q9" s="43" t="s">
         <v>32</v>
       </c>
-      <c r="R9" s="46">
-        <v>40000</v>
-      </c>
+      <c r="R9" s="43"/>
     </row>
     <row r="10" spans="1:18" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="41">
@@ -7352,7 +7540,7 @@
       </c>
       <c r="G27" s="19">
         <f t="shared" si="4"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H27" s="62">
         <f>[22]Loan1!$K$10</f>
@@ -7360,19 +7548,19 @@
       </c>
       <c r="I27" s="62">
         <f>[22]Loan1!$K$12</f>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J27" s="15">
         <f>[22]Loan1!$K$13</f>
-        <v>4200</v>
+        <v>2800</v>
       </c>
       <c r="K27" s="15">
         <f>[22]Loan1!$K$14</f>
-        <v>4037.031116629747</v>
+        <v>2717.9798966815056</v>
       </c>
       <c r="L27" s="64">
         <f>[22]Loan1!$K$15</f>
-        <v>15962.968883370253</v>
+        <v>17282.020103318493</v>
       </c>
       <c r="M27" s="65">
         <f>[22]Loan1!$K$16</f>
@@ -7454,67 +7642,64 @@
       <c r="R28" s="43"/>
     </row>
     <row r="29" spans="1:18" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="62">
+      <c r="A29" s="41">
         <f t="shared" si="1"/>
         <v>188</v>
       </c>
-      <c r="B29" s="62" t="str">
+      <c r="B29" s="41" t="str">
         <f>'[4]188'!$K$3</f>
         <v>Kamala</v>
       </c>
-      <c r="C29" s="62" t="s">
+      <c r="C29" s="41" t="s">
         <v>6</v>
       </c>
-      <c r="D29" s="63" t="str">
+      <c r="D29" s="67" t="str">
         <f>'[4]188'!$K$2</f>
         <v>L40000D120-Kamala-N188</v>
       </c>
-      <c r="E29" s="15">
+      <c r="E29" s="68">
         <f>'[4]188'!$K$7</f>
         <v>40000</v>
       </c>
-      <c r="F29" s="62">
+      <c r="F29" s="41">
         <f>'[4]188'!$K$9</f>
         <v>400</v>
       </c>
-      <c r="G29" s="19">
+      <c r="G29" s="41">
         <f t="shared" si="4"/>
-        <v>35</v>
-      </c>
-      <c r="H29" s="62">
+        <v>0</v>
+      </c>
+      <c r="H29" s="41">
         <f>'[4]188'!$K$10</f>
         <v>120</v>
       </c>
-      <c r="I29" s="62">
+      <c r="I29" s="41">
         <f>'[4]188'!$K$12</f>
-        <v>85</v>
-      </c>
-      <c r="J29" s="15">
+        <v>120</v>
+      </c>
+      <c r="J29" s="68">
         <f>'[4]188'!$K$13</f>
-        <v>14000</v>
-      </c>
-      <c r="K29" s="15">
+        <v>0</v>
+      </c>
+      <c r="K29" s="68">
         <f>'[4]188'!$K$14</f>
-        <v>13244.497417797626</v>
-      </c>
-      <c r="L29" s="64">
+        <v>1.8109176380676217E-9</v>
+      </c>
+      <c r="L29" s="69">
         <f>'[4]188'!$K$15</f>
-        <v>26755.502582202374</v>
-      </c>
-      <c r="M29" s="65">
+        <v>39999.999999998188</v>
+      </c>
+      <c r="M29" s="70">
         <f>'[4]188'!$K$16</f>
         <v>46190</v>
       </c>
-      <c r="N29" s="66">
+      <c r="N29" s="71">
         <f>'[4]188'!$K$17</f>
         <v>46310</v>
       </c>
-      <c r="P29" s="46">
-        <f>400*7</f>
-        <v>2800</v>
-      </c>
-      <c r="Q29" s="46"/>
-      <c r="R29" s="46">
+      <c r="O29" s="42"/>
+      <c r="P29" s="45"/>
+      <c r="R29" s="43">
         <v>10000</v>
       </c>
     </row>
@@ -7667,7 +7852,7 @@
       </c>
       <c r="G32" s="19">
         <f t="shared" si="4"/>
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H32" s="19">
         <f>'[24]191'!$K$10</f>
@@ -7675,19 +7860,19 @@
       </c>
       <c r="I32" s="19">
         <f>'[24]191'!$K$12</f>
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="J32" s="18">
         <f>'[24]191'!$K$13</f>
-        <v>12600</v>
+        <v>8400</v>
       </c>
       <c r="K32" s="18">
         <f>'[24]191'!$K$14</f>
-        <v>11760.958267114203</v>
+        <v>7995.2298277146756</v>
       </c>
       <c r="L32" s="73">
         <f>'[24]191'!$K$15</f>
-        <v>18239.041732885795</v>
+        <v>22004.770172285323</v>
       </c>
       <c r="M32" s="74">
         <f>'[24]191'!$K$16</f>
@@ -7731,7 +7916,7 @@
       </c>
       <c r="G33" s="19">
         <f t="shared" si="4"/>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H33" s="62">
         <f>'[25]192'!$K$10</f>
@@ -7739,19 +7924,19 @@
       </c>
       <c r="I33" s="62">
         <f>'[25]192'!$K$12</f>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J33" s="15">
         <f>'[25]192'!$K$13</f>
-        <v>4200</v>
+        <v>3500</v>
       </c>
       <c r="K33" s="15">
         <f>'[25]192'!$K$14</f>
-        <v>3920.3194223714245</v>
+        <v>3298.927950640365</v>
       </c>
       <c r="L33" s="64">
         <f>'[25]192'!$K$15</f>
-        <v>6079.6805776285755</v>
+        <v>6701.0720493596345</v>
       </c>
       <c r="M33" s="65">
         <f>'[25]192'!$K$16</f>
@@ -7792,7 +7977,7 @@
       </c>
       <c r="G34" s="19">
         <f t="shared" si="4"/>
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H34" s="19">
         <f>'[26]193'!$K$10</f>
@@ -7800,19 +7985,19 @@
       </c>
       <c r="I34" s="19">
         <f>'[26]193'!$K$12</f>
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="J34" s="18">
         <f>'[26]193'!$K$13</f>
-        <v>8400</v>
+        <v>5600</v>
       </c>
       <c r="K34" s="18">
         <f>'[26]193'!$K$14</f>
-        <v>7840.638844742849</v>
+        <v>5330.1532184765038</v>
       </c>
       <c r="L34" s="73">
         <f>'[26]193'!$K$15</f>
-        <v>12159.361155257151</v>
+        <v>14669.846781523496</v>
       </c>
       <c r="M34" s="74">
         <f>'[26]193'!$K$16</f>
@@ -7853,7 +8038,7 @@
       </c>
       <c r="G35" s="19">
         <f t="shared" si="4"/>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H35" s="62">
         <f>'[27]194'!$K$10</f>
@@ -7861,19 +8046,19 @@
       </c>
       <c r="I35" s="62">
         <f>'[27]194'!$K$12</f>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J35" s="15">
         <f>'[27]194'!$K$13</f>
-        <v>8400</v>
+        <v>7000</v>
       </c>
       <c r="K35" s="15">
         <f>'[27]194'!$K$14</f>
-        <v>7840.638844742849</v>
+        <v>6597.85590128073</v>
       </c>
       <c r="L35" s="64">
         <f>'[27]194'!$K$15</f>
-        <v>12159.361155257151</v>
+        <v>13402.144098719269</v>
       </c>
       <c r="M35" s="65">
         <f>'[27]194'!$K$16</f>
@@ -7917,7 +8102,7 @@
       </c>
       <c r="G36" s="19">
         <f t="shared" si="4"/>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H36" s="19">
         <f>'[6]195'!$K$10</f>
@@ -7925,19 +8110,19 @@
       </c>
       <c r="I36" s="19">
         <f>'[6]195'!$K$12</f>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J36" s="18">
         <f>'[6]195'!$K$13</f>
-        <v>75600</v>
+        <v>63000</v>
       </c>
       <c r="K36" s="18">
         <f>'[6]195'!$K$14</f>
-        <v>70565.749602685508</v>
+        <v>59380.703111526433</v>
       </c>
       <c r="L36" s="73">
         <f>'[6]195'!$K$15</f>
-        <v>109434.25039731449</v>
+        <v>120619.29688847356</v>
       </c>
       <c r="M36" s="74">
         <f>'[6]195'!$K$16</f>
@@ -8012,125 +8197,125 @@
         <v>700</v>
       </c>
     </row>
-    <row r="38" spans="1:18" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="19">
+    <row r="38" spans="1:18" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="41">
         <f t="shared" si="1"/>
         <v>197</v>
       </c>
-      <c r="B38" s="19" t="str">
+      <c r="B38" s="41" t="str">
         <f>'[16]197'!$K$3</f>
         <v>Lanchenbi_Samila</v>
       </c>
-      <c r="C38" s="19" t="s">
+      <c r="C38" s="41" t="s">
         <v>6</v>
       </c>
-      <c r="D38" s="72" t="str">
+      <c r="D38" s="67" t="str">
         <f>'[16]197'!$K$2</f>
         <v>L20000W17-Lanchenbi_Samila-N197</v>
       </c>
-      <c r="E38" s="18">
+      <c r="E38" s="68">
         <f>'[16]197'!$K$7</f>
         <v>20000</v>
       </c>
-      <c r="F38" s="19">
+      <c r="F38" s="41">
         <f>'[16]197'!$K$9</f>
         <v>1400</v>
       </c>
-      <c r="G38" s="19">
+      <c r="G38" s="41">
         <f t="shared" si="4"/>
-        <v>6</v>
-      </c>
-      <c r="H38" s="19">
+        <v>0</v>
+      </c>
+      <c r="H38" s="41">
         <f>'[16]197'!$K$10</f>
         <v>17</v>
       </c>
-      <c r="I38" s="19">
+      <c r="I38" s="41">
         <f>'[16]197'!$K$12</f>
-        <v>11</v>
-      </c>
-      <c r="J38" s="18">
+        <v>17</v>
+      </c>
+      <c r="J38" s="68">
         <f>'[16]197'!$K$13</f>
-        <v>8400</v>
-      </c>
-      <c r="K38" s="18">
+        <v>0</v>
+      </c>
+      <c r="K38" s="68">
         <f>'[16]197'!$K$14</f>
-        <v>7840.638844742849</v>
-      </c>
-      <c r="L38" s="73">
+        <v>9.1336005425546318E-10</v>
+      </c>
+      <c r="L38" s="69">
         <f>'[16]197'!$K$15</f>
-        <v>12159.361155257151</v>
-      </c>
-      <c r="M38" s="74">
+        <v>19999.999999999087</v>
+      </c>
+      <c r="M38" s="70">
         <f>'[16]197'!$K$16</f>
         <v>46206</v>
       </c>
-      <c r="N38" s="75">
+      <c r="N38" s="71">
         <f>'[16]197'!$K$17</f>
         <v>46325</v>
       </c>
-      <c r="P38" s="43">
-        <v>1400</v>
-      </c>
-    </row>
-    <row r="39" spans="1:18" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="62">
+      <c r="O38" s="42"/>
+      <c r="P38" s="45"/>
+      <c r="R38" s="43"/>
+    </row>
+    <row r="39" spans="1:18" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="41">
         <f t="shared" si="1"/>
         <v>198</v>
       </c>
-      <c r="B39" s="62" t="str">
+      <c r="B39" s="41" t="str">
         <f>'[10]198'!$K$3</f>
         <v>Mutum_Sandhyarani</v>
       </c>
-      <c r="C39" s="62" t="s">
+      <c r="C39" s="41" t="s">
         <v>6</v>
       </c>
-      <c r="D39" s="63" t="str">
+      <c r="D39" s="67" t="str">
         <f>'[10]198'!$K$2</f>
         <v>L20000W17-Mutum_Sandhyarani-N198</v>
       </c>
-      <c r="E39" s="15">
+      <c r="E39" s="68">
         <f>'[10]198'!$K$7</f>
         <v>20000</v>
       </c>
-      <c r="F39" s="62">
+      <c r="F39" s="41">
         <f>'[10]198'!$K$9</f>
         <v>1400</v>
       </c>
-      <c r="G39" s="19">
+      <c r="G39" s="41">
         <f t="shared" si="4"/>
-        <v>6</v>
-      </c>
-      <c r="H39" s="62">
+        <v>0</v>
+      </c>
+      <c r="H39" s="41">
         <f>'[10]198'!$K$10</f>
         <v>17</v>
       </c>
-      <c r="I39" s="62">
+      <c r="I39" s="41">
         <f>'[10]198'!$K$12</f>
-        <v>11</v>
-      </c>
-      <c r="J39" s="15">
+        <v>17</v>
+      </c>
+      <c r="J39" s="68">
         <f>'[10]198'!$K$13</f>
-        <v>8400</v>
-      </c>
-      <c r="K39" s="15">
+        <v>0</v>
+      </c>
+      <c r="K39" s="68">
         <f>'[10]198'!$K$14</f>
-        <v>7840.638844742849</v>
-      </c>
-      <c r="L39" s="64">
+        <v>9.1336005425546318E-10</v>
+      </c>
+      <c r="L39" s="69">
         <f>'[10]198'!$K$15</f>
-        <v>12159.361155257151</v>
-      </c>
-      <c r="M39" s="65">
+        <v>19999.999999999087</v>
+      </c>
+      <c r="M39" s="70">
         <f>'[10]198'!$K$16</f>
         <v>46205</v>
       </c>
-      <c r="N39" s="66">
+      <c r="N39" s="71">
         <f>'[10]198'!$K$17</f>
         <v>46324</v>
       </c>
-      <c r="P39" s="43">
-        <v>1400</v>
-      </c>
+      <c r="O39" s="42"/>
+      <c r="P39" s="45"/>
+      <c r="R39" s="43"/>
     </row>
     <row r="40" spans="1:18" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="41">
@@ -8218,7 +8403,7 @@
       </c>
       <c r="G41" s="19">
         <f t="shared" si="4"/>
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H41" s="62">
         <f>'[7]200'!$K$10</f>
@@ -8226,19 +8411,19 @@
       </c>
       <c r="I41" s="62">
         <f>'[7]200'!$K$12</f>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J41" s="15">
         <f>'[7]200'!$K$13</f>
-        <v>16800</v>
+        <v>14700</v>
       </c>
       <c r="K41" s="15">
         <f>'[7]200'!$K$14</f>
-        <v>15380.092970258089</v>
+        <v>13588.487859238874</v>
       </c>
       <c r="L41" s="64">
         <f>'[7]200'!$K$15</f>
-        <v>14619.907029741911</v>
+        <v>16411.512140761126</v>
       </c>
       <c r="M41" s="65">
         <f>'[7]200'!$K$16</f>
@@ -8278,7 +8463,7 @@
       </c>
       <c r="G42" s="19">
         <f t="shared" si="4"/>
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="H42" s="19">
         <f>'[28]195'!$K$10</f>
@@ -8286,19 +8471,19 @@
       </c>
       <c r="I42" s="19">
         <f>'[28]195'!$K$12</f>
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="J42" s="18">
         <f>'[28]195'!$K$13</f>
-        <v>70000</v>
+        <v>56000</v>
       </c>
       <c r="K42" s="18">
         <f>'[28]195'!$K$14</f>
-        <v>62861.13531643273</v>
+        <v>51266.976567526755</v>
       </c>
       <c r="L42" s="73">
         <f>'[28]195'!$K$15</f>
-        <v>37138.86468356727</v>
+        <v>48733.023432473245</v>
       </c>
       <c r="M42" s="74">
         <f>'[28]195'!$K$16</f>
@@ -8338,7 +8523,7 @@
       </c>
       <c r="G43" s="19">
         <f t="shared" si="4"/>
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H43" s="62">
         <f>'[29]202'!$K$10</f>
@@ -8346,19 +8531,19 @@
       </c>
       <c r="I43" s="62">
         <f>'[29]202'!$K$12</f>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J43" s="15">
         <f>'[29]202'!$K$13</f>
-        <v>42000</v>
+        <v>37800</v>
       </c>
       <c r="K43" s="15">
         <f>'[29]202'!$K$14</f>
-        <v>37716.681189859737</v>
+        <v>34272.959564168894</v>
       </c>
       <c r="L43" s="64">
         <f>'[29]202'!$K$15</f>
-        <v>22283.318810140263</v>
+        <v>25727.040435831106</v>
       </c>
       <c r="M43" s="65">
         <f>'[29]202'!$K$16</f>
@@ -8398,7 +8583,7 @@
       </c>
       <c r="G44" s="19">
         <f t="shared" si="4"/>
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H44" s="36">
         <f>'[30]203'!$K$10</f>
@@ -8406,19 +8591,19 @@
       </c>
       <c r="I44" s="36">
         <f>'[30]203'!$K$12</f>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J44" s="39">
         <f>'[30]203'!$K$13</f>
-        <v>14000</v>
+        <v>12600</v>
       </c>
       <c r="K44" s="39">
         <f>'[30]203'!$K$14</f>
-        <v>12572.227063286609</v>
+        <v>11424.319854722999</v>
       </c>
       <c r="L44" s="40">
         <f>'[30]203'!$K$15</f>
-        <v>7427.7729367133907</v>
+        <v>8575.6801452770014</v>
       </c>
       <c r="M44" s="20">
         <f>'[30]203'!$K$16</f>
@@ -8458,7 +8643,7 @@
       </c>
       <c r="G45" s="19">
         <f t="shared" si="4"/>
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H45" s="33">
         <f>'[4]204'!$K$10</f>
@@ -8466,19 +8651,19 @@
       </c>
       <c r="I45" s="33">
         <f>'[4]204'!$K$12</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J45" s="35">
         <f>'[4]204'!$K$13</f>
-        <v>15400</v>
+        <v>14000</v>
       </c>
       <c r="K45" s="35">
         <f>'[4]204'!$K$14</f>
-        <v>13697.569400122526</v>
+        <v>12572.227063286609</v>
       </c>
       <c r="L45" s="37">
         <f>'[4]204'!$K$15</f>
-        <v>6302.4305998774744</v>
+        <v>7427.7729367133907</v>
       </c>
       <c r="M45" s="22">
         <f>'[4]204'!$K$16</f>
@@ -8518,7 +8703,7 @@
       </c>
       <c r="G46" s="19">
         <f t="shared" si="4"/>
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H46" s="36">
         <f>'[31]205'!$K$10</f>
@@ -8526,19 +8711,19 @@
       </c>
       <c r="I46" s="36">
         <f>'[31]205'!$K$12</f>
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J46" s="39">
         <f>'[31]205'!$K$13</f>
-        <v>84000</v>
+        <v>70000</v>
       </c>
       <c r="K46" s="39">
         <f>'[31]205'!$K$14</f>
-        <v>74003.952159756635</v>
+        <v>62861.13531643273</v>
       </c>
       <c r="L46" s="40">
         <f>'[31]205'!$K$15</f>
-        <v>25996.047840243365</v>
+        <v>37138.86468356727</v>
       </c>
       <c r="M46" s="20">
         <f>'[31]205'!$K$16</f>
@@ -8578,7 +8763,7 @@
       </c>
       <c r="G47" s="19">
         <f t="shared" si="4"/>
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="H47" s="33">
         <f>'[9]206'!$K$10</f>
@@ -8586,19 +8771,19 @@
       </c>
       <c r="I47" s="33">
         <f>'[9]206'!$K$12</f>
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="J47" s="35">
         <f>'[9]206'!$K$13</f>
-        <v>9800</v>
+        <v>9400</v>
       </c>
       <c r="K47" s="35">
         <f>'[9]206'!$K$14</f>
-        <v>8432.3044104048531</v>
+        <v>8135.670977686661</v>
       </c>
       <c r="L47" s="37">
         <f>'[9]206'!$K$15</f>
-        <v>1567.6955895951469</v>
+        <v>1864.329022313339</v>
       </c>
       <c r="M47" s="22">
         <f>'[9]206'!$K$16</f>
@@ -8635,7 +8820,7 @@
       </c>
       <c r="G48" s="19">
         <f t="shared" si="4"/>
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="H48" s="36">
         <f>'[32]207'!$K$10</f>
@@ -8643,19 +8828,19 @@
       </c>
       <c r="I48" s="36">
         <f>'[32]207'!$K$12</f>
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="J48" s="39">
         <f>'[32]207'!$K$13</f>
-        <v>16200</v>
+        <v>14700</v>
       </c>
       <c r="K48" s="39">
         <f>'[32]207'!$K$14</f>
-        <v>14295.302542559919</v>
+        <v>13117.062707143943</v>
       </c>
       <c r="L48" s="40">
         <f>'[32]207'!$K$15</f>
-        <v>5704.6974574400811</v>
+        <v>6882.937292856057</v>
       </c>
       <c r="M48" s="20">
         <f>'[32]207'!$K$16</f>
@@ -8815,7 +9000,7 @@
       </c>
       <c r="G51" s="19">
         <f t="shared" si="4"/>
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H51" s="33">
         <f>'[11]210'!$K$10</f>
@@ -8823,19 +9008,19 @@
       </c>
       <c r="I51" s="33">
         <f>'[11]210'!$K$12</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J51" s="35">
         <f>'[11]210'!$K$13</f>
-        <v>18200</v>
+        <v>16800</v>
       </c>
       <c r="K51" s="35">
         <f>'[11]210'!$K$14</f>
-        <v>15882.325006125111</v>
+        <v>14800.790431951375</v>
       </c>
       <c r="L51" s="37">
         <f>'[11]210'!$K$15</f>
-        <v>4117.674993874889</v>
+        <v>5199.2095680486254</v>
       </c>
       <c r="M51" s="22">
         <f>'[11]210'!$K$16</f>
@@ -8875,7 +9060,7 @@
       </c>
       <c r="G52" s="19">
         <f t="shared" si="4"/>
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H52" s="36">
         <f>'[34]211'!$K$10</f>
@@ -8883,19 +9068,19 @@
       </c>
       <c r="I52" s="36">
         <f>'[34]211'!$K$12</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J52" s="39">
         <f>'[34]211'!$K$13</f>
-        <v>19600</v>
+        <v>18200</v>
       </c>
       <c r="K52" s="39">
         <f>'[34]211'!$K$14</f>
-        <v>16942.599422027139</v>
+        <v>15882.325006125111</v>
       </c>
       <c r="L52" s="40">
         <f>'[34]211'!$K$15</f>
-        <v>3057.4005779728614</v>
+        <v>4117.674993874889</v>
       </c>
       <c r="M52" s="20">
         <f>'[34]211'!$K$16</f>
@@ -8935,7 +9120,7 @@
       </c>
       <c r="G53" s="19">
         <f t="shared" si="4"/>
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H53" s="33">
         <f>'[35]212'!$K$10</f>
@@ -8943,19 +9128,19 @@
       </c>
       <c r="I53" s="33">
         <f>'[35]212'!$K$12</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J53" s="35">
         <f>'[35]212'!$K$13</f>
-        <v>19600</v>
+        <v>18200</v>
       </c>
       <c r="K53" s="35">
         <f>'[35]212'!$K$14</f>
-        <v>16942.599422027139</v>
+        <v>15882.325006125111</v>
       </c>
       <c r="L53" s="37">
         <f>'[35]212'!$K$15</f>
-        <v>3057.4005779728614</v>
+        <v>4117.674993874889</v>
       </c>
       <c r="M53" s="22">
         <f>'[35]212'!$K$16</f>
@@ -8995,7 +9180,7 @@
       </c>
       <c r="G54" s="19">
         <f t="shared" si="4"/>
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H54" s="36">
         <f>'[17]213'!$K$10</f>
@@ -9003,19 +9188,19 @@
       </c>
       <c r="I54" s="36">
         <f>'[17]213'!$K$12</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J54" s="39">
         <f>'[17]213'!$K$13</f>
-        <v>9800</v>
+        <v>9100</v>
       </c>
       <c r="K54" s="39">
         <f>'[17]213'!$K$14</f>
-        <v>8471.2997110135693</v>
+        <v>7941.1625030625555</v>
       </c>
       <c r="L54" s="40">
         <f>'[17]213'!$K$15</f>
-        <v>1528.7002889864307</v>
+        <v>2058.8374969374445</v>
       </c>
       <c r="M54" s="20">
         <f>'[17]213'!$K$16</f>
@@ -9055,7 +9240,7 @@
       </c>
       <c r="G55" s="19">
         <f t="shared" si="4"/>
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H55" s="33">
         <f>'[36]214'!$K$10</f>
@@ -9063,19 +9248,19 @@
       </c>
       <c r="I55" s="33">
         <f>'[36]214'!$K$12</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J55" s="35">
         <f>'[36]214'!$K$13</f>
-        <v>21000</v>
+        <v>19600</v>
       </c>
       <c r="K55" s="35">
         <f>'[36]214'!$K$14</f>
-        <v>17982.031599103153</v>
+        <v>16942.599422027139</v>
       </c>
       <c r="L55" s="37">
         <f>'[36]214'!$K$15</f>
-        <v>2017.968400896847</v>
+        <v>3057.4005779728614</v>
       </c>
       <c r="M55" s="22">
         <f>'[36]214'!$K$16</f>
@@ -9115,7 +9300,7 @@
       </c>
       <c r="G56" s="19">
         <f t="shared" si="4"/>
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="H56" s="36">
         <f>'[37]215'!$K$10</f>
@@ -9123,19 +9308,19 @@
       </c>
       <c r="I56" s="36">
         <f>'[37]215'!$K$12</f>
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="J56" s="39">
         <f>'[37]215'!$K$13</f>
-        <v>18900</v>
+        <v>16800</v>
       </c>
       <c r="K56" s="39">
         <f>'[37]215'!$K$14</f>
-        <v>16348.408466459945</v>
+        <v>14758.991922004241</v>
       </c>
       <c r="L56" s="40">
         <f>'[37]215'!$K$15</f>
-        <v>3651.591533540055</v>
+        <v>5241.0080779957589</v>
       </c>
       <c r="M56" s="20">
         <f>'[37]215'!$K$16</f>
@@ -9175,7 +9360,7 @@
       </c>
       <c r="G57" s="19">
         <f t="shared" si="4"/>
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H57" s="33">
         <f>'[13]216'!$K$10</f>
@@ -9183,19 +9368,19 @@
       </c>
       <c r="I57" s="33">
         <f>'[13]216'!$K$12</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J57" s="35">
         <f>'[13]216'!$K$13</f>
-        <v>30000</v>
+        <v>27000</v>
       </c>
       <c r="K57" s="35">
         <f>'[13]216'!$K$14</f>
-        <v>25691.656051705635</v>
+        <v>23442.585668039574</v>
       </c>
       <c r="L57" s="37">
         <f>'[13]216'!$K$15</f>
-        <v>4308.343948294365</v>
+        <v>6557.4143319604264</v>
       </c>
       <c r="M57" s="22">
         <f>'[13]216'!$K$16</f>
@@ -9235,7 +9420,7 @@
       </c>
       <c r="G58" s="19">
         <f t="shared" si="4"/>
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H58" s="36">
         <f>'[38]217'!$K$10</f>
@@ -9243,19 +9428,19 @@
       </c>
       <c r="I58" s="36">
         <f>'[38]217'!$K$12</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J58" s="39">
         <f>'[38]217'!$K$13</f>
-        <v>31500</v>
+        <v>29400</v>
       </c>
       <c r="K58" s="39">
         <f>'[38]217'!$K$14</f>
-        <v>26973.047398654715</v>
+        <v>25413.899133040686</v>
       </c>
       <c r="L58" s="40">
         <f>'[38]217'!$K$15</f>
-        <v>3026.9526013452851</v>
+        <v>4586.1008669593139</v>
       </c>
       <c r="M58" s="20">
         <f>'[38]217'!$K$16</f>
@@ -9295,7 +9480,7 @@
       </c>
       <c r="G59" s="19">
         <f t="shared" si="4"/>
-        <v>109</v>
+        <v>99</v>
       </c>
       <c r="H59" s="33">
         <f>'[14]218'!$K$10</f>
@@ -9303,19 +9488,19 @@
       </c>
       <c r="I59" s="33">
         <f>'[14]218'!$K$12</f>
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="J59" s="35">
         <f>'[14]218'!$K$13</f>
-        <v>32700</v>
+        <v>29700</v>
       </c>
       <c r="K59" s="35">
         <f>'[14]218'!$K$14</f>
-        <v>27691.965326606991</v>
+        <v>25524.137134582503</v>
       </c>
       <c r="L59" s="37">
         <f>'[14]218'!$K$15</f>
-        <v>2308.0346733930091</v>
+        <v>4475.8628654174972</v>
       </c>
       <c r="M59" s="22">
         <f>'[14]218'!$K$16</f>
@@ -9355,7 +9540,7 @@
       </c>
       <c r="G60" s="19">
         <f t="shared" si="4"/>
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H60" s="36">
         <f>'[17]219'!$K$10</f>
@@ -9363,19 +9548,19 @@
       </c>
       <c r="I60" s="36">
         <f>'[17]219'!$K$12</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J60" s="39">
         <f>'[17]219'!$K$13</f>
-        <v>33600</v>
+        <v>31500</v>
       </c>
       <c r="K60" s="39">
         <f>'[17]219'!$K$14</f>
-        <v>28501.546862383388</v>
+        <v>26973.047398654715</v>
       </c>
       <c r="L60" s="40">
         <f>'[17]219'!$K$15</f>
-        <v>1498.4531376166124</v>
+        <v>3026.9526013452851</v>
       </c>
       <c r="M60" s="20">
         <f>'[17]219'!$K$16</f>
@@ -9475,7 +9660,7 @@
       </c>
       <c r="G62" s="19">
         <f t="shared" si="4"/>
-        <v>116</v>
+        <v>108</v>
       </c>
       <c r="H62" s="36">
         <f>'[21]221'!$K$10</f>
@@ -9483,19 +9668,19 @@
       </c>
       <c r="I62" s="36">
         <f>'[21]221'!$K$12</f>
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="J62" s="39">
         <f>'[21]221'!$K$13</f>
-        <v>23200</v>
+        <v>21600</v>
       </c>
       <c r="K62" s="39">
         <f>'[21]221'!$K$14</f>
-        <v>19446.555966324511</v>
+        <v>18318.802096717634</v>
       </c>
       <c r="L62" s="40">
         <f>'[21]221'!$K$15</f>
-        <v>553.44403367548875</v>
+        <v>1681.1979032823656</v>
       </c>
       <c r="M62" s="20">
         <f>'[21]221'!$K$16</f>
@@ -9535,7 +9720,7 @@
       </c>
       <c r="G63" s="19">
         <f t="shared" si="4"/>
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="H63" s="33">
         <f>'[40]222'!$K$10</f>
@@ -9543,19 +9728,19 @@
       </c>
       <c r="I63" s="33">
         <f>'[40]222'!$K$12</f>
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="J63" s="35">
         <f>'[40]222'!$K$13</f>
-        <v>11400</v>
+        <v>10650</v>
       </c>
       <c r="K63" s="35">
         <f>'[40]222'!$K$14</f>
-        <v>9583.2761230814613</v>
+        <v>9051.3676217399407</v>
       </c>
       <c r="L63" s="37">
         <f>'[40]222'!$K$15</f>
-        <v>416.72387691853874</v>
+        <v>948.63237826005934</v>
       </c>
       <c r="M63" s="22">
         <f>'[40]222'!$K$16</f>
@@ -9595,7 +9780,7 @@
       </c>
       <c r="G64" s="19">
         <f t="shared" si="4"/>
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H64" s="36">
         <f>'[41]223'!$K$10</f>
@@ -9603,99 +9788,213 @@
       </c>
       <c r="I64" s="36">
         <f>'[41]223'!$K$12</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J64" s="39">
         <f>'[41]223'!$K$13</f>
-        <v>71400</v>
+        <v>67200</v>
       </c>
       <c r="K64" s="39">
         <f>'[41]223'!$K$14</f>
-        <v>71400</v>
+        <v>57003.093724766775</v>
       </c>
       <c r="L64" s="40">
         <f>'[41]223'!$K$15</f>
-        <v>0</v>
-      </c>
-      <c r="M64" s="20" t="str">
+        <v>2996.9062752332247</v>
+      </c>
+      <c r="M64" s="20">
         <f>'[41]223'!$K$16</f>
-        <v/>
-      </c>
-      <c r="N64" s="21" t="str">
+        <v>46281</v>
+      </c>
+      <c r="N64" s="21">
         <f>'[41]223'!$K$17</f>
-        <v/>
+        <v>46400</v>
       </c>
       <c r="P64" s="43">
         <v>4200</v>
       </c>
     </row>
-    <row r="65" spans="1:14" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:16" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A65" s="33">
         <f t="shared" si="1"/>
         <v>224</v>
       </c>
-      <c r="B65" s="33"/>
-      <c r="C65" s="33"/>
-      <c r="D65" s="34"/>
-      <c r="E65" s="35"/>
-      <c r="F65" s="33"/>
-      <c r="G65" s="19" t="str">
+      <c r="B65" s="33" t="str">
+        <f>'[4]224'!$K$3</f>
+        <v>Kamala</v>
+      </c>
+      <c r="C65" s="33" t="s">
+        <v>6</v>
+      </c>
+      <c r="D65" s="34" t="str">
+        <f>'[4]224'!$K$2</f>
+        <v>L50000D120-Kamala-N224</v>
+      </c>
+      <c r="E65" s="35">
+        <f>'[4]224'!$K$7</f>
+        <v>50000</v>
+      </c>
+      <c r="F65" s="33">
+        <f>'[4]224'!$K$9</f>
+        <v>500</v>
+      </c>
+      <c r="G65" s="19">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H65" s="33"/>
-      <c r="I65" s="33"/>
-      <c r="J65" s="35"/>
-      <c r="K65" s="35"/>
-      <c r="L65" s="37"/>
-      <c r="M65" s="22"/>
-      <c r="N65" s="23"/>
-    </row>
-    <row r="66" spans="1:14" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
+        <v>120</v>
+      </c>
+      <c r="H65" s="33">
+        <f>'[4]224'!$K$10</f>
+        <v>120</v>
+      </c>
+      <c r="I65" s="33">
+        <f>'[4]224'!$K$12</f>
+        <v>0</v>
+      </c>
+      <c r="J65" s="35">
+        <f>'[4]224'!$K$13</f>
+        <v>60000</v>
+      </c>
+      <c r="K65" s="35">
+        <f>'[4]224'!$K$14</f>
+        <v>60000</v>
+      </c>
+      <c r="L65" s="37">
+        <f>'[4]224'!$K$15</f>
+        <v>0</v>
+      </c>
+      <c r="M65" s="22" t="str">
+        <f>'[4]224'!$K$16</f>
+        <v/>
+      </c>
+      <c r="N65" s="23" t="str">
+        <f>'[4]224'!$K$17</f>
+        <v/>
+      </c>
+      <c r="P65" s="43">
+        <v>3500</v>
+      </c>
+    </row>
+    <row r="66" spans="1:16" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A66" s="36">
         <f t="shared" si="1"/>
         <v>225</v>
       </c>
-      <c r="B66" s="36"/>
-      <c r="C66" s="36"/>
-      <c r="D66" s="38"/>
-      <c r="E66" s="39"/>
-      <c r="F66" s="36"/>
-      <c r="G66" s="19" t="str">
+      <c r="B66" s="36" t="str">
+        <f>'[16]225'!$K$3</f>
+        <v>Lanchenbi_Samila</v>
+      </c>
+      <c r="C66" s="36" t="s">
+        <v>6</v>
+      </c>
+      <c r="D66" s="38" t="str">
+        <f>'[16]225'!$K$2</f>
+        <v>L20000W17-Lanchenbi_Samila-N225</v>
+      </c>
+      <c r="E66" s="39">
+        <f>'[16]225'!$K$7</f>
+        <v>20000</v>
+      </c>
+      <c r="F66" s="36">
+        <f>'[16]225'!$K$9</f>
+        <v>1400</v>
+      </c>
+      <c r="G66" s="19">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H66" s="36"/>
-      <c r="I66" s="36"/>
-      <c r="J66" s="39"/>
-      <c r="K66" s="39"/>
-      <c r="L66" s="40"/>
-      <c r="M66" s="20"/>
-      <c r="N66" s="21"/>
-    </row>
-    <row r="67" spans="1:14" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
+        <v>17</v>
+      </c>
+      <c r="H66" s="36">
+        <f>'[16]225'!$K$10</f>
+        <v>17</v>
+      </c>
+      <c r="I66" s="36">
+        <f>'[16]225'!$K$12</f>
+        <v>0</v>
+      </c>
+      <c r="J66" s="39">
+        <f>'[16]225'!$K$13</f>
+        <v>23800</v>
+      </c>
+      <c r="K66" s="39">
+        <f>'[16]225'!$K$14</f>
+        <v>23800</v>
+      </c>
+      <c r="L66" s="40">
+        <f>'[16]225'!$K$15</f>
+        <v>0</v>
+      </c>
+      <c r="M66" s="20" t="str">
+        <f>'[16]225'!$K$16</f>
+        <v/>
+      </c>
+      <c r="N66" s="21" t="str">
+        <f>'[16]225'!$K$17</f>
+        <v/>
+      </c>
+      <c r="P66" s="43">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="67" spans="1:16" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A67" s="33">
         <f t="shared" si="1"/>
         <v>226</v>
       </c>
-      <c r="B67" s="33"/>
-      <c r="C67" s="33"/>
-      <c r="D67" s="34"/>
-      <c r="E67" s="35"/>
-      <c r="F67" s="33"/>
-      <c r="G67" s="19" t="str">
+      <c r="B67" s="33" t="str">
+        <f>'[10]226'!$K$3</f>
+        <v>Mutum_Sandhyarani</v>
+      </c>
+      <c r="C67" s="33" t="s">
+        <v>6</v>
+      </c>
+      <c r="D67" s="34" t="str">
+        <f>'[10]226'!$K$2</f>
+        <v>L25000W17-Mutum_Sandhyarani-N226</v>
+      </c>
+      <c r="E67" s="35">
+        <f>'[10]226'!$K$7</f>
+        <v>25000</v>
+      </c>
+      <c r="F67" s="33">
+        <f>'[10]226'!$K$9</f>
+        <v>1750</v>
+      </c>
+      <c r="G67" s="19">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H67" s="33"/>
-      <c r="I67" s="33"/>
-      <c r="J67" s="35"/>
-      <c r="K67" s="35"/>
-      <c r="L67" s="37"/>
-      <c r="M67" s="22"/>
-      <c r="N67" s="23"/>
-    </row>
-    <row r="68" spans="1:14" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
+        <v>17</v>
+      </c>
+      <c r="H67" s="33">
+        <f>'[10]226'!$K$10</f>
+        <v>17</v>
+      </c>
+      <c r="I67" s="33">
+        <f>'[10]226'!$K$12</f>
+        <v>0</v>
+      </c>
+      <c r="J67" s="35">
+        <f>'[10]226'!$K$13</f>
+        <v>29750</v>
+      </c>
+      <c r="K67" s="35">
+        <f>'[10]226'!$K$14</f>
+        <v>29750</v>
+      </c>
+      <c r="L67" s="37">
+        <f>'[10]226'!$K$15</f>
+        <v>0</v>
+      </c>
+      <c r="M67" s="22" t="str">
+        <f>'[10]226'!$K$16</f>
+        <v/>
+      </c>
+      <c r="N67" s="23" t="str">
+        <f>'[10]226'!$K$17</f>
+        <v/>
+      </c>
+      <c r="P67" s="43">
+        <v>1750</v>
+      </c>
+    </row>
+    <row r="68" spans="1:16" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A68" s="36">
         <f t="shared" si="1"/>
         <v>227</v>
@@ -9717,7 +10016,7 @@
       <c r="M68" s="20"/>
       <c r="N68" s="21"/>
     </row>
-    <row r="69" spans="1:14" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:16" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A69" s="33">
         <f t="shared" si="1"/>
         <v>228</v>
@@ -9739,7 +10038,7 @@
       <c r="M69" s="22"/>
       <c r="N69" s="23"/>
     </row>
-    <row r="70" spans="1:14" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:16" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A70" s="36">
         <f t="shared" si="1"/>
         <v>229</v>
@@ -9761,7 +10060,7 @@
       <c r="M70" s="20"/>
       <c r="N70" s="21"/>
     </row>
-    <row r="71" spans="1:14" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:16" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A71" s="33">
         <f t="shared" si="1"/>
         <v>230</v>
@@ -9783,7 +10082,7 @@
       <c r="M71" s="22"/>
       <c r="N71" s="23"/>
     </row>
-    <row r="72" spans="1:14" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:16" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A72" s="36">
         <f t="shared" ref="A72:A135" si="5">A71+1</f>
         <v>231</v>
@@ -9805,7 +10104,7 @@
       <c r="M72" s="20"/>
       <c r="N72" s="21"/>
     </row>
-    <row r="73" spans="1:14" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:16" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A73" s="33">
         <f t="shared" si="5"/>
         <v>232</v>
@@ -9827,7 +10126,7 @@
       <c r="M73" s="22"/>
       <c r="N73" s="23"/>
     </row>
-    <row r="74" spans="1:14" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:16" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A74" s="36">
         <f t="shared" si="5"/>
         <v>233</v>
@@ -9849,7 +10148,7 @@
       <c r="M74" s="20"/>
       <c r="N74" s="21"/>
     </row>
-    <row r="75" spans="1:14" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:16" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A75" s="33">
         <f t="shared" si="5"/>
         <v>234</v>
@@ -9871,7 +10170,7 @@
       <c r="M75" s="22"/>
       <c r="N75" s="23"/>
     </row>
-    <row r="76" spans="1:14" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:16" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A76" s="36">
         <f t="shared" si="5"/>
         <v>235</v>
@@ -9893,7 +10192,7 @@
       <c r="M76" s="20"/>
       <c r="N76" s="21"/>
     </row>
-    <row r="77" spans="1:14" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:16" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A77" s="33">
         <f t="shared" si="5"/>
         <v>236</v>
@@ -9915,7 +10214,7 @@
       <c r="M77" s="22"/>
       <c r="N77" s="23"/>
     </row>
-    <row r="78" spans="1:14" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:16" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A78" s="36">
         <f t="shared" si="5"/>
         <v>237</v>
@@ -9937,7 +10236,7 @@
       <c r="M78" s="20"/>
       <c r="N78" s="21"/>
     </row>
-    <row r="79" spans="1:14" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:16" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A79" s="33">
         <f t="shared" si="5"/>
         <v>238</v>
@@ -9959,7 +10258,7 @@
       <c r="M79" s="22"/>
       <c r="N79" s="23"/>
     </row>
-    <row r="80" spans="1:14" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:16" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A80" s="36">
         <f t="shared" si="5"/>
         <v>239</v>
@@ -18624,7 +18923,7 @@
     <mergeCell ref="H1:J1"/>
     <mergeCell ref="K1:L1"/>
   </mergeCells>
-  <dataValidations disablePrompts="1" count="1">
+  <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C5:C472">
       <formula1>"Active, Closed"</formula1>
     </dataValidation>
@@ -18639,7 +18938,7 @@
   <dimension ref="A1:P111"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="21.42578125" style="1" customWidth="1"/>
+    <col min="1" max="1" width="23.5703125" style="1" customWidth="1"/>
     <col min="2" max="2" width="15.5703125" style="1" customWidth="1"/>
     <col min="3" max="4" width="18.85546875" style="1" customWidth="1"/>
     <col min="5" max="5" width="16.42578125" style="1" customWidth="1"/>
@@ -22230,81 +22529,245 @@
       <c r="P73" s="9"/>
     </row>
     <row r="74" spans="1:16" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A74" s="11"/>
-      <c r="B74" s="14" t="str">
+      <c r="A74" s="11">
+        <v>46283</v>
+      </c>
+      <c r="B74" s="14" t="e">
         <f>IF(A74&lt;&gt;"",
     SUMIFS([42]FinancingJournal!$E:$E,
            [42]FinancingJournal!$C:$C,"Capital Injection",
            [42]FinancingJournal!$A:$A,"&lt;="&amp;A74),
     "")</f>
-        <v/>
-      </c>
-      <c r="C74" s="15"/>
-      <c r="D74" s="15"/>
-      <c r="E74" s="15"/>
-      <c r="F74" s="26"/>
-      <c r="G74" s="26"/>
-      <c r="H74" s="26"/>
-      <c r="I74" s="26"/>
-      <c r="J74" s="31"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="C74" s="15" t="e">
+        <f>IF(A74&lt;&gt;"",
+    SUMIFS([42]InvestingJournal!$F:$F,
+           [42]InvestingJournal!$C:$C,"Izra Advance",
+           [42]InvestingJournal!$A:$A,"&lt;="&amp;A74)
+    +
+    SUMIFS([42]InvestingJournal!$F:$F,
+           [42]InvestingJournal!$C:$C,"Investment to Unit",
+           [42]InvestingJournal!$A:$A,"&lt;="&amp;A74),
+    "")</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="D74" s="15" t="e">
+        <f>IF(A74&lt;&gt;"",
+    SUMIFS([42]InvestingJournal!$F:$F,
+           [42]InvestingJournal!$C:$C,"Loan Advance",
+           [42]InvestingJournal!$A:$A,"&lt;="&amp;A74),
+    "")</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="E74" s="15" t="e">
+        <f>IF(A74&lt;&gt;"",
+    SUMIFS([42]FinancingJournal!$E:$E,
+           [42]FinancingJournal!$C:$C,"Borrowing",
+           [42]FinancingJournal!$A:$A,"&lt;="&amp;A74)
+    +
+    SUMIFS([42]FinancingJournal!$E:$E,
+           [42]FinancingJournal!$C:$C,"Withdrawal",
+           [42]FinancingJournal!$A:$A,"&lt;="&amp;A74),
+    "")</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="F74" s="26">
+        <v>1139946</v>
+      </c>
+      <c r="G74" s="26">
+        <v>141576</v>
+      </c>
+      <c r="H74" s="26">
+        <v>776100</v>
+      </c>
+      <c r="I74" s="26">
+        <v>689099.64753996639</v>
+      </c>
+      <c r="J74" s="31" t="s">
+        <v>130</v>
+      </c>
     </row>
     <row r="75" spans="1:16" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A75" s="16"/>
-      <c r="B75" s="17" t="str">
+      <c r="A75" s="16">
+        <v>46283</v>
+      </c>
+      <c r="B75" s="17" t="e">
         <f>IF(A75&lt;&gt;"",
     SUMIFS([42]FinancingJournal!$E:$E,
            [42]FinancingJournal!$C:$C,"Capital Injection",
            [42]FinancingJournal!$A:$A,"&lt;="&amp;A75),
     "")</f>
-        <v/>
-      </c>
-      <c r="C75" s="18"/>
-      <c r="D75" s="18"/>
-      <c r="E75" s="18"/>
-      <c r="F75" s="29"/>
-      <c r="G75" s="29"/>
-      <c r="H75" s="29"/>
-      <c r="I75" s="29"/>
-      <c r="J75" s="32"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="C75" s="18" t="e">
+        <f>IF(A75&lt;&gt;"",
+    SUMIFS([42]InvestingJournal!$F:$F,
+           [42]InvestingJournal!$C:$C,"Izra Advance",
+           [42]InvestingJournal!$A:$A,"&lt;="&amp;A75)
+    +
+    SUMIFS([42]InvestingJournal!$F:$F,
+           [42]InvestingJournal!$C:$C,"Investment to Unit",
+           [42]InvestingJournal!$A:$A,"&lt;="&amp;A75),
+    "")</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="D75" s="18" t="e">
+        <f>IF(A75&lt;&gt;"",
+    SUMIFS([42]InvestingJournal!$F:$F,
+           [42]InvestingJournal!$C:$C,"Loan Advance",
+           [42]InvestingJournal!$A:$A,"&lt;="&amp;A75),
+    "")</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="E75" s="18" t="e">
+        <f>IF(A75&lt;&gt;"",
+    SUMIFS([42]FinancingJournal!$E:$E,
+           [42]FinancingJournal!$C:$C,"Borrowing",
+           [42]FinancingJournal!$A:$A,"&lt;="&amp;A75)
+    +
+    SUMIFS([42]FinancingJournal!$E:$E,
+           [42]FinancingJournal!$C:$C,"Withdrawal",
+           [42]FinancingJournal!$A:$A,"&lt;="&amp;A75),
+    "")</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="F75" s="29">
+        <v>1149946</v>
+      </c>
+      <c r="G75" s="29">
+        <v>91576</v>
+      </c>
+      <c r="H75" s="29">
+        <v>836100</v>
+      </c>
+      <c r="I75" s="29">
+        <v>749099.64753996639</v>
+      </c>
+      <c r="J75" s="32" t="s">
+        <v>131</v>
+      </c>
       <c r="P75" s="9"/>
     </row>
     <row r="76" spans="1:16" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A76" s="11"/>
-      <c r="B76" s="14" t="str">
+      <c r="A76" s="11">
+        <v>46286</v>
+      </c>
+      <c r="B76" s="14" t="e">
         <f>IF(A76&lt;&gt;"",
     SUMIFS([42]FinancingJournal!$E:$E,
            [42]FinancingJournal!$C:$C,"Capital Injection",
            [42]FinancingJournal!$A:$A,"&lt;="&amp;A76),
     "")</f>
-        <v/>
-      </c>
-      <c r="C76" s="15"/>
-      <c r="D76" s="15"/>
-      <c r="E76" s="15"/>
-      <c r="F76" s="26"/>
-      <c r="G76" s="26"/>
-      <c r="H76" s="26"/>
-      <c r="I76" s="26"/>
-      <c r="J76" s="31"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="C76" s="15" t="e">
+        <f>IF(A76&lt;&gt;"",
+    SUMIFS([42]InvestingJournal!$F:$F,
+           [42]InvestingJournal!$C:$C,"Izra Advance",
+           [42]InvestingJournal!$A:$A,"&lt;="&amp;A76)
+    +
+    SUMIFS([42]InvestingJournal!$F:$F,
+           [42]InvestingJournal!$C:$C,"Investment to Unit",
+           [42]InvestingJournal!$A:$A,"&lt;="&amp;A76),
+    "")</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="D76" s="15" t="e">
+        <f>IF(A76&lt;&gt;"",
+    SUMIFS([42]InvestingJournal!$F:$F,
+           [42]InvestingJournal!$C:$C,"Loan Advance",
+           [42]InvestingJournal!$A:$A,"&lt;="&amp;A76),
+    "")</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="E76" s="15" t="e">
+        <f>IF(A76&lt;&gt;"",
+    SUMIFS([42]FinancingJournal!$E:$E,
+           [42]FinancingJournal!$C:$C,"Borrowing",
+           [42]FinancingJournal!$A:$A,"&lt;="&amp;A76)
+    +
+    SUMIFS([42]FinancingJournal!$E:$E,
+           [42]FinancingJournal!$C:$C,"Withdrawal",
+           [42]FinancingJournal!$A:$A,"&lt;="&amp;A76),
+    "")</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="F76" s="26">
+        <v>1137946</v>
+      </c>
+      <c r="G76" s="26">
+        <v>118776</v>
+      </c>
+      <c r="H76" s="26">
+        <v>796900</v>
+      </c>
+      <c r="I76" s="26">
+        <v>715259.71349669166</v>
+      </c>
+      <c r="J76" s="31" t="s">
+        <v>132</v>
+      </c>
     </row>
     <row r="77" spans="1:16" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A77" s="16"/>
-      <c r="B77" s="17" t="str">
+      <c r="A77" s="16">
+        <v>46286</v>
+      </c>
+      <c r="B77" s="17" t="e">
         <f>IF(A77&lt;&gt;"",
     SUMIFS([42]FinancingJournal!$E:$E,
            [42]FinancingJournal!$C:$C,"Capital Injection",
            [42]FinancingJournal!$A:$A,"&lt;="&amp;A77),
     "")</f>
-        <v/>
-      </c>
-      <c r="C77" s="18"/>
-      <c r="D77" s="18"/>
-      <c r="E77" s="18"/>
-      <c r="F77" s="29"/>
-      <c r="G77" s="29"/>
-      <c r="H77" s="29"/>
-      <c r="I77" s="29"/>
-      <c r="J77" s="32"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="C77" s="18" t="e">
+        <f>IF(A77&lt;&gt;"",
+    SUMIFS([42]InvestingJournal!$F:$F,
+           [42]InvestingJournal!$C:$C,"Izra Advance",
+           [42]InvestingJournal!$A:$A,"&lt;="&amp;A77)
+    +
+    SUMIFS([42]InvestingJournal!$F:$F,
+           [42]InvestingJournal!$C:$C,"Investment to Unit",
+           [42]InvestingJournal!$A:$A,"&lt;="&amp;A77),
+    "")</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="D77" s="18" t="e">
+        <f>IF(A77&lt;&gt;"",
+    SUMIFS([42]InvestingJournal!$F:$F,
+           [42]InvestingJournal!$C:$C,"Loan Advance",
+           [42]InvestingJournal!$A:$A,"&lt;="&amp;A77),
+    "")</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="E77" s="18" t="e">
+        <f>IF(A77&lt;&gt;"",
+    SUMIFS([42]FinancingJournal!$E:$E,
+           [42]FinancingJournal!$C:$C,"Borrowing",
+           [42]FinancingJournal!$A:$A,"&lt;="&amp;A77)
+    +
+    SUMIFS([42]FinancingJournal!$E:$E,
+           [42]FinancingJournal!$C:$C,"Withdrawal",
+           [42]FinancingJournal!$A:$A,"&lt;="&amp;A77),
+    "")</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="F77" s="29">
+        <v>1146496</v>
+      </c>
+      <c r="G77" s="29">
+        <v>73776</v>
+      </c>
+      <c r="H77" s="29">
+        <v>850450</v>
+      </c>
+      <c r="I77" s="29">
+        <v>768809.71349669166</v>
+      </c>
+      <c r="J77" s="32" t="s">
+        <v>133</v>
+      </c>
       <c r="P77" s="9"/>
     </row>
     <row r="78" spans="1:16" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -22317,14 +22780,45 @@
     "")</f>
         <v/>
       </c>
-      <c r="C78" s="15"/>
-      <c r="D78" s="15"/>
-      <c r="E78" s="15"/>
+      <c r="C78" s="15" t="str">
+        <f>IF(A78&lt;&gt;"",
+    SUMIFS([42]InvestingJournal!$F:$F,
+           [42]InvestingJournal!$C:$C,"Izra Advance",
+           [42]InvestingJournal!$A:$A,"&lt;="&amp;A78)
+    +
+    SUMIFS([42]InvestingJournal!$F:$F,
+           [42]InvestingJournal!$C:$C,"Investment to Unit",
+           [42]InvestingJournal!$A:$A,"&lt;="&amp;A78),
+    "")</f>
+        <v/>
+      </c>
+      <c r="D78" s="15" t="str">
+        <f>IF(A78&lt;&gt;"",
+    SUMIFS([42]InvestingJournal!$F:$F,
+           [42]InvestingJournal!$C:$C,"Loan Advance",
+           [42]InvestingJournal!$A:$A,"&lt;="&amp;A78),
+    "")</f>
+        <v/>
+      </c>
+      <c r="E78" s="15" t="str">
+        <f>IF(A78&lt;&gt;"",
+    SUMIFS([42]FinancingJournal!$E:$E,
+           [42]FinancingJournal!$C:$C,"Borrowing",
+           [42]FinancingJournal!$A:$A,"&lt;="&amp;A78)
+    +
+    SUMIFS([42]FinancingJournal!$E:$E,
+           [42]FinancingJournal!$C:$C,"Withdrawal",
+           [42]FinancingJournal!$A:$A,"&lt;="&amp;A78),
+    "")</f>
+        <v/>
+      </c>
       <c r="F78" s="26"/>
       <c r="G78" s="26"/>
       <c r="H78" s="26"/>
       <c r="I78" s="26"/>
-      <c r="J78" s="31"/>
+      <c r="J78" s="31" t="s">
+        <v>134</v>
+      </c>
     </row>
     <row r="79" spans="1:16" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A79" s="16"/>
@@ -22336,9 +22830,38 @@
     "")</f>
         <v/>
       </c>
-      <c r="C79" s="18"/>
-      <c r="D79" s="18"/>
-      <c r="E79" s="18"/>
+      <c r="C79" s="18" t="str">
+        <f>IF(A79&lt;&gt;"",
+    SUMIFS([42]InvestingJournal!$F:$F,
+           [42]InvestingJournal!$C:$C,"Izra Advance",
+           [42]InvestingJournal!$A:$A,"&lt;="&amp;A79)
+    +
+    SUMIFS([42]InvestingJournal!$F:$F,
+           [42]InvestingJournal!$C:$C,"Investment to Unit",
+           [42]InvestingJournal!$A:$A,"&lt;="&amp;A79),
+    "")</f>
+        <v/>
+      </c>
+      <c r="D79" s="18" t="str">
+        <f>IF(A79&lt;&gt;"",
+    SUMIFS([42]InvestingJournal!$F:$F,
+           [42]InvestingJournal!$C:$C,"Loan Advance",
+           [42]InvestingJournal!$A:$A,"&lt;="&amp;A79),
+    "")</f>
+        <v/>
+      </c>
+      <c r="E79" s="18" t="str">
+        <f>IF(A79&lt;&gt;"",
+    SUMIFS([42]FinancingJournal!$E:$E,
+           [42]FinancingJournal!$C:$C,"Borrowing",
+           [42]FinancingJournal!$A:$A,"&lt;="&amp;A79)
+    +
+    SUMIFS([42]FinancingJournal!$E:$E,
+           [42]FinancingJournal!$C:$C,"Withdrawal",
+           [42]FinancingJournal!$A:$A,"&lt;="&amp;A79),
+    "")</f>
+        <v/>
+      </c>
       <c r="F79" s="29"/>
       <c r="G79" s="29"/>
       <c r="H79" s="29"/>
@@ -22356,9 +22879,38 @@
     "")</f>
         <v/>
       </c>
-      <c r="C80" s="15"/>
-      <c r="D80" s="15"/>
-      <c r="E80" s="15"/>
+      <c r="C80" s="15" t="str">
+        <f>IF(A80&lt;&gt;"",
+    SUMIFS([42]InvestingJournal!$F:$F,
+           [42]InvestingJournal!$C:$C,"Izra Advance",
+           [42]InvestingJournal!$A:$A,"&lt;="&amp;A80)
+    +
+    SUMIFS([42]InvestingJournal!$F:$F,
+           [42]InvestingJournal!$C:$C,"Investment to Unit",
+           [42]InvestingJournal!$A:$A,"&lt;="&amp;A80),
+    "")</f>
+        <v/>
+      </c>
+      <c r="D80" s="15" t="str">
+        <f>IF(A80&lt;&gt;"",
+    SUMIFS([42]InvestingJournal!$F:$F,
+           [42]InvestingJournal!$C:$C,"Loan Advance",
+           [42]InvestingJournal!$A:$A,"&lt;="&amp;A80),
+    "")</f>
+        <v/>
+      </c>
+      <c r="E80" s="15" t="str">
+        <f>IF(A80&lt;&gt;"",
+    SUMIFS([42]FinancingJournal!$E:$E,
+           [42]FinancingJournal!$C:$C,"Borrowing",
+           [42]FinancingJournal!$A:$A,"&lt;="&amp;A80)
+    +
+    SUMIFS([42]FinancingJournal!$E:$E,
+           [42]FinancingJournal!$C:$C,"Withdrawal",
+           [42]FinancingJournal!$A:$A,"&lt;="&amp;A80),
+    "")</f>
+        <v/>
+      </c>
       <c r="F80" s="26"/>
       <c r="G80" s="26"/>
       <c r="H80" s="26"/>
@@ -22375,9 +22927,38 @@
     "")</f>
         <v/>
       </c>
-      <c r="C81" s="18"/>
-      <c r="D81" s="18"/>
-      <c r="E81" s="18"/>
+      <c r="C81" s="18" t="str">
+        <f>IF(A81&lt;&gt;"",
+    SUMIFS([42]InvestingJournal!$F:$F,
+           [42]InvestingJournal!$C:$C,"Izra Advance",
+           [42]InvestingJournal!$A:$A,"&lt;="&amp;A81)
+    +
+    SUMIFS([42]InvestingJournal!$F:$F,
+           [42]InvestingJournal!$C:$C,"Investment to Unit",
+           [42]InvestingJournal!$A:$A,"&lt;="&amp;A81),
+    "")</f>
+        <v/>
+      </c>
+      <c r="D81" s="18" t="str">
+        <f>IF(A81&lt;&gt;"",
+    SUMIFS([42]InvestingJournal!$F:$F,
+           [42]InvestingJournal!$C:$C,"Loan Advance",
+           [42]InvestingJournal!$A:$A,"&lt;="&amp;A81),
+    "")</f>
+        <v/>
+      </c>
+      <c r="E81" s="18" t="str">
+        <f>IF(A81&lt;&gt;"",
+    SUMIFS([42]FinancingJournal!$E:$E,
+           [42]FinancingJournal!$C:$C,"Borrowing",
+           [42]FinancingJournal!$A:$A,"&lt;="&amp;A81)
+    +
+    SUMIFS([42]FinancingJournal!$E:$E,
+           [42]FinancingJournal!$C:$C,"Withdrawal",
+           [42]FinancingJournal!$A:$A,"&lt;="&amp;A81),
+    "")</f>
+        <v/>
+      </c>
       <c r="F81" s="29"/>
       <c r="G81" s="29"/>
       <c r="H81" s="29"/>
@@ -22395,9 +22976,38 @@
     "")</f>
         <v/>
       </c>
-      <c r="C82" s="15"/>
-      <c r="D82" s="15"/>
-      <c r="E82" s="15"/>
+      <c r="C82" s="15" t="str">
+        <f>IF(A82&lt;&gt;"",
+    SUMIFS([42]InvestingJournal!$F:$F,
+           [42]InvestingJournal!$C:$C,"Izra Advance",
+           [42]InvestingJournal!$A:$A,"&lt;="&amp;A82)
+    +
+    SUMIFS([42]InvestingJournal!$F:$F,
+           [42]InvestingJournal!$C:$C,"Investment to Unit",
+           [42]InvestingJournal!$A:$A,"&lt;="&amp;A82),
+    "")</f>
+        <v/>
+      </c>
+      <c r="D82" s="15" t="str">
+        <f>IF(A82&lt;&gt;"",
+    SUMIFS([42]InvestingJournal!$F:$F,
+           [42]InvestingJournal!$C:$C,"Loan Advance",
+           [42]InvestingJournal!$A:$A,"&lt;="&amp;A82),
+    "")</f>
+        <v/>
+      </c>
+      <c r="E82" s="15" t="str">
+        <f>IF(A82&lt;&gt;"",
+    SUMIFS([42]FinancingJournal!$E:$E,
+           [42]FinancingJournal!$C:$C,"Borrowing",
+           [42]FinancingJournal!$A:$A,"&lt;="&amp;A82)
+    +
+    SUMIFS([42]FinancingJournal!$E:$E,
+           [42]FinancingJournal!$C:$C,"Withdrawal",
+           [42]FinancingJournal!$A:$A,"&lt;="&amp;A82),
+    "")</f>
+        <v/>
+      </c>
       <c r="F82" s="26"/>
       <c r="G82" s="26"/>
       <c r="H82" s="26"/>
@@ -22414,9 +23024,38 @@
     "")</f>
         <v/>
       </c>
-      <c r="C83" s="18"/>
-      <c r="D83" s="18"/>
-      <c r="E83" s="18"/>
+      <c r="C83" s="18" t="str">
+        <f>IF(A83&lt;&gt;"",
+    SUMIFS([42]InvestingJournal!$F:$F,
+           [42]InvestingJournal!$C:$C,"Izra Advance",
+           [42]InvestingJournal!$A:$A,"&lt;="&amp;A83)
+    +
+    SUMIFS([42]InvestingJournal!$F:$F,
+           [42]InvestingJournal!$C:$C,"Investment to Unit",
+           [42]InvestingJournal!$A:$A,"&lt;="&amp;A83),
+    "")</f>
+        <v/>
+      </c>
+      <c r="D83" s="18" t="str">
+        <f>IF(A83&lt;&gt;"",
+    SUMIFS([42]InvestingJournal!$F:$F,
+           [42]InvestingJournal!$C:$C,"Loan Advance",
+           [42]InvestingJournal!$A:$A,"&lt;="&amp;A83),
+    "")</f>
+        <v/>
+      </c>
+      <c r="E83" s="18" t="str">
+        <f>IF(A83&lt;&gt;"",
+    SUMIFS([42]FinancingJournal!$E:$E,
+           [42]FinancingJournal!$C:$C,"Borrowing",
+           [42]FinancingJournal!$A:$A,"&lt;="&amp;A83)
+    +
+    SUMIFS([42]FinancingJournal!$E:$E,
+           [42]FinancingJournal!$C:$C,"Withdrawal",
+           [42]FinancingJournal!$A:$A,"&lt;="&amp;A83),
+    "")</f>
+        <v/>
+      </c>
       <c r="F83" s="29"/>
       <c r="G83" s="29"/>
       <c r="H83" s="29"/>
@@ -22434,9 +23073,38 @@
     "")</f>
         <v/>
       </c>
-      <c r="C84" s="15"/>
-      <c r="D84" s="15"/>
-      <c r="E84" s="15"/>
+      <c r="C84" s="15" t="str">
+        <f>IF(A84&lt;&gt;"",
+    SUMIFS([42]InvestingJournal!$F:$F,
+           [42]InvestingJournal!$C:$C,"Izra Advance",
+           [42]InvestingJournal!$A:$A,"&lt;="&amp;A84)
+    +
+    SUMIFS([42]InvestingJournal!$F:$F,
+           [42]InvestingJournal!$C:$C,"Investment to Unit",
+           [42]InvestingJournal!$A:$A,"&lt;="&amp;A84),
+    "")</f>
+        <v/>
+      </c>
+      <c r="D84" s="15" t="str">
+        <f>IF(A84&lt;&gt;"",
+    SUMIFS([42]InvestingJournal!$F:$F,
+           [42]InvestingJournal!$C:$C,"Loan Advance",
+           [42]InvestingJournal!$A:$A,"&lt;="&amp;A84),
+    "")</f>
+        <v/>
+      </c>
+      <c r="E84" s="15" t="str">
+        <f>IF(A84&lt;&gt;"",
+    SUMIFS([42]FinancingJournal!$E:$E,
+           [42]FinancingJournal!$C:$C,"Borrowing",
+           [42]FinancingJournal!$A:$A,"&lt;="&amp;A84)
+    +
+    SUMIFS([42]FinancingJournal!$E:$E,
+           [42]FinancingJournal!$C:$C,"Withdrawal",
+           [42]FinancingJournal!$A:$A,"&lt;="&amp;A84),
+    "")</f>
+        <v/>
+      </c>
       <c r="F84" s="26"/>
       <c r="G84" s="26"/>
       <c r="H84" s="26"/>
@@ -22453,9 +23121,38 @@
     "")</f>
         <v/>
       </c>
-      <c r="C85" s="18"/>
-      <c r="D85" s="18"/>
-      <c r="E85" s="18"/>
+      <c r="C85" s="18" t="str">
+        <f>IF(A85&lt;&gt;"",
+    SUMIFS([42]InvestingJournal!$F:$F,
+           [42]InvestingJournal!$C:$C,"Izra Advance",
+           [42]InvestingJournal!$A:$A,"&lt;="&amp;A85)
+    +
+    SUMIFS([42]InvestingJournal!$F:$F,
+           [42]InvestingJournal!$C:$C,"Investment to Unit",
+           [42]InvestingJournal!$A:$A,"&lt;="&amp;A85),
+    "")</f>
+        <v/>
+      </c>
+      <c r="D85" s="18" t="str">
+        <f>IF(A85&lt;&gt;"",
+    SUMIFS([42]InvestingJournal!$F:$F,
+           [42]InvestingJournal!$C:$C,"Loan Advance",
+           [42]InvestingJournal!$A:$A,"&lt;="&amp;A85),
+    "")</f>
+        <v/>
+      </c>
+      <c r="E85" s="18" t="str">
+        <f>IF(A85&lt;&gt;"",
+    SUMIFS([42]FinancingJournal!$E:$E,
+           [42]FinancingJournal!$C:$C,"Borrowing",
+           [42]FinancingJournal!$A:$A,"&lt;="&amp;A85)
+    +
+    SUMIFS([42]FinancingJournal!$E:$E,
+           [42]FinancingJournal!$C:$C,"Withdrawal",
+           [42]FinancingJournal!$A:$A,"&lt;="&amp;A85),
+    "")</f>
+        <v/>
+      </c>
       <c r="F85" s="29"/>
       <c r="G85" s="29"/>
       <c r="H85" s="29"/>
@@ -22473,9 +23170,38 @@
     "")</f>
         <v/>
       </c>
-      <c r="C86" s="15"/>
-      <c r="D86" s="15"/>
-      <c r="E86" s="15"/>
+      <c r="C86" s="15" t="str">
+        <f>IF(A86&lt;&gt;"",
+    SUMIFS([42]InvestingJournal!$F:$F,
+           [42]InvestingJournal!$C:$C,"Izra Advance",
+           [42]InvestingJournal!$A:$A,"&lt;="&amp;A86)
+    +
+    SUMIFS([42]InvestingJournal!$F:$F,
+           [42]InvestingJournal!$C:$C,"Investment to Unit",
+           [42]InvestingJournal!$A:$A,"&lt;="&amp;A86),
+    "")</f>
+        <v/>
+      </c>
+      <c r="D86" s="15" t="str">
+        <f>IF(A86&lt;&gt;"",
+    SUMIFS([42]InvestingJournal!$F:$F,
+           [42]InvestingJournal!$C:$C,"Loan Advance",
+           [42]InvestingJournal!$A:$A,"&lt;="&amp;A86),
+    "")</f>
+        <v/>
+      </c>
+      <c r="E86" s="15" t="str">
+        <f>IF(A86&lt;&gt;"",
+    SUMIFS([42]FinancingJournal!$E:$E,
+           [42]FinancingJournal!$C:$C,"Borrowing",
+           [42]FinancingJournal!$A:$A,"&lt;="&amp;A86)
+    +
+    SUMIFS([42]FinancingJournal!$E:$E,
+           [42]FinancingJournal!$C:$C,"Withdrawal",
+           [42]FinancingJournal!$A:$A,"&lt;="&amp;A86),
+    "")</f>
+        <v/>
+      </c>
       <c r="F86" s="26"/>
       <c r="G86" s="26"/>
       <c r="H86" s="26"/>
@@ -22492,9 +23218,38 @@
     "")</f>
         <v/>
       </c>
-      <c r="C87" s="18"/>
-      <c r="D87" s="18"/>
-      <c r="E87" s="18"/>
+      <c r="C87" s="18" t="str">
+        <f>IF(A87&lt;&gt;"",
+    SUMIFS([42]InvestingJournal!$F:$F,
+           [42]InvestingJournal!$C:$C,"Izra Advance",
+           [42]InvestingJournal!$A:$A,"&lt;="&amp;A87)
+    +
+    SUMIFS([42]InvestingJournal!$F:$F,
+           [42]InvestingJournal!$C:$C,"Investment to Unit",
+           [42]InvestingJournal!$A:$A,"&lt;="&amp;A87),
+    "")</f>
+        <v/>
+      </c>
+      <c r="D87" s="18" t="str">
+        <f>IF(A87&lt;&gt;"",
+    SUMIFS([42]InvestingJournal!$F:$F,
+           [42]InvestingJournal!$C:$C,"Loan Advance",
+           [42]InvestingJournal!$A:$A,"&lt;="&amp;A87),
+    "")</f>
+        <v/>
+      </c>
+      <c r="E87" s="18" t="str">
+        <f>IF(A87&lt;&gt;"",
+    SUMIFS([42]FinancingJournal!$E:$E,
+           [42]FinancingJournal!$C:$C,"Borrowing",
+           [42]FinancingJournal!$A:$A,"&lt;="&amp;A87)
+    +
+    SUMIFS([42]FinancingJournal!$E:$E,
+           [42]FinancingJournal!$C:$C,"Withdrawal",
+           [42]FinancingJournal!$A:$A,"&lt;="&amp;A87),
+    "")</f>
+        <v/>
+      </c>
       <c r="F87" s="29"/>
       <c r="G87" s="29"/>
       <c r="H87" s="29"/>
@@ -22512,9 +23267,38 @@
     "")</f>
         <v/>
       </c>
-      <c r="C88" s="15"/>
-      <c r="D88" s="15"/>
-      <c r="E88" s="15"/>
+      <c r="C88" s="15" t="str">
+        <f>IF(A88&lt;&gt;"",
+    SUMIFS([42]InvestingJournal!$F:$F,
+           [42]InvestingJournal!$C:$C,"Izra Advance",
+           [42]InvestingJournal!$A:$A,"&lt;="&amp;A88)
+    +
+    SUMIFS([42]InvestingJournal!$F:$F,
+           [42]InvestingJournal!$C:$C,"Investment to Unit",
+           [42]InvestingJournal!$A:$A,"&lt;="&amp;A88),
+    "")</f>
+        <v/>
+      </c>
+      <c r="D88" s="15" t="str">
+        <f>IF(A88&lt;&gt;"",
+    SUMIFS([42]InvestingJournal!$F:$F,
+           [42]InvestingJournal!$C:$C,"Loan Advance",
+           [42]InvestingJournal!$A:$A,"&lt;="&amp;A88),
+    "")</f>
+        <v/>
+      </c>
+      <c r="E88" s="15" t="str">
+        <f>IF(A88&lt;&gt;"",
+    SUMIFS([42]FinancingJournal!$E:$E,
+           [42]FinancingJournal!$C:$C,"Borrowing",
+           [42]FinancingJournal!$A:$A,"&lt;="&amp;A88)
+    +
+    SUMIFS([42]FinancingJournal!$E:$E,
+           [42]FinancingJournal!$C:$C,"Withdrawal",
+           [42]FinancingJournal!$A:$A,"&lt;="&amp;A88),
+    "")</f>
+        <v/>
+      </c>
       <c r="F88" s="26"/>
       <c r="G88" s="26"/>
       <c r="H88" s="26"/>
@@ -22531,9 +23315,38 @@
     "")</f>
         <v/>
       </c>
-      <c r="C89" s="18"/>
-      <c r="D89" s="18"/>
-      <c r="E89" s="18"/>
+      <c r="C89" s="18" t="str">
+        <f>IF(A89&lt;&gt;"",
+    SUMIFS([42]InvestingJournal!$F:$F,
+           [42]InvestingJournal!$C:$C,"Izra Advance",
+           [42]InvestingJournal!$A:$A,"&lt;="&amp;A89)
+    +
+    SUMIFS([42]InvestingJournal!$F:$F,
+           [42]InvestingJournal!$C:$C,"Investment to Unit",
+           [42]InvestingJournal!$A:$A,"&lt;="&amp;A89),
+    "")</f>
+        <v/>
+      </c>
+      <c r="D89" s="18" t="str">
+        <f>IF(A89&lt;&gt;"",
+    SUMIFS([42]InvestingJournal!$F:$F,
+           [42]InvestingJournal!$C:$C,"Loan Advance",
+           [42]InvestingJournal!$A:$A,"&lt;="&amp;A89),
+    "")</f>
+        <v/>
+      </c>
+      <c r="E89" s="18" t="str">
+        <f>IF(A89&lt;&gt;"",
+    SUMIFS([42]FinancingJournal!$E:$E,
+           [42]FinancingJournal!$C:$C,"Borrowing",
+           [42]FinancingJournal!$A:$A,"&lt;="&amp;A89)
+    +
+    SUMIFS([42]FinancingJournal!$E:$E,
+           [42]FinancingJournal!$C:$C,"Withdrawal",
+           [42]FinancingJournal!$A:$A,"&lt;="&amp;A89),
+    "")</f>
+        <v/>
+      </c>
       <c r="F89" s="29"/>
       <c r="G89" s="29"/>
       <c r="H89" s="29"/>
@@ -22551,9 +23364,38 @@
     "")</f>
         <v/>
       </c>
-      <c r="C90" s="15"/>
-      <c r="D90" s="15"/>
-      <c r="E90" s="15"/>
+      <c r="C90" s="15" t="str">
+        <f>IF(A90&lt;&gt;"",
+    SUMIFS([42]InvestingJournal!$F:$F,
+           [42]InvestingJournal!$C:$C,"Izra Advance",
+           [42]InvestingJournal!$A:$A,"&lt;="&amp;A90)
+    +
+    SUMIFS([42]InvestingJournal!$F:$F,
+           [42]InvestingJournal!$C:$C,"Investment to Unit",
+           [42]InvestingJournal!$A:$A,"&lt;="&amp;A90),
+    "")</f>
+        <v/>
+      </c>
+      <c r="D90" s="15" t="str">
+        <f>IF(A90&lt;&gt;"",
+    SUMIFS([42]InvestingJournal!$F:$F,
+           [42]InvestingJournal!$C:$C,"Loan Advance",
+           [42]InvestingJournal!$A:$A,"&lt;="&amp;A90),
+    "")</f>
+        <v/>
+      </c>
+      <c r="E90" s="15" t="str">
+        <f>IF(A90&lt;&gt;"",
+    SUMIFS([42]FinancingJournal!$E:$E,
+           [42]FinancingJournal!$C:$C,"Borrowing",
+           [42]FinancingJournal!$A:$A,"&lt;="&amp;A90)
+    +
+    SUMIFS([42]FinancingJournal!$E:$E,
+           [42]FinancingJournal!$C:$C,"Withdrawal",
+           [42]FinancingJournal!$A:$A,"&lt;="&amp;A90),
+    "")</f>
+        <v/>
+      </c>
       <c r="F90" s="26"/>
       <c r="G90" s="26"/>
       <c r="H90" s="26"/>
@@ -22570,9 +23412,38 @@
     "")</f>
         <v/>
       </c>
-      <c r="C91" s="18"/>
-      <c r="D91" s="18"/>
-      <c r="E91" s="18"/>
+      <c r="C91" s="18" t="str">
+        <f>IF(A91&lt;&gt;"",
+    SUMIFS([42]InvestingJournal!$F:$F,
+           [42]InvestingJournal!$C:$C,"Izra Advance",
+           [42]InvestingJournal!$A:$A,"&lt;="&amp;A91)
+    +
+    SUMIFS([42]InvestingJournal!$F:$F,
+           [42]InvestingJournal!$C:$C,"Investment to Unit",
+           [42]InvestingJournal!$A:$A,"&lt;="&amp;A91),
+    "")</f>
+        <v/>
+      </c>
+      <c r="D91" s="18" t="str">
+        <f>IF(A91&lt;&gt;"",
+    SUMIFS([42]InvestingJournal!$F:$F,
+           [42]InvestingJournal!$C:$C,"Loan Advance",
+           [42]InvestingJournal!$A:$A,"&lt;="&amp;A91),
+    "")</f>
+        <v/>
+      </c>
+      <c r="E91" s="18" t="str">
+        <f>IF(A91&lt;&gt;"",
+    SUMIFS([42]FinancingJournal!$E:$E,
+           [42]FinancingJournal!$C:$C,"Borrowing",
+           [42]FinancingJournal!$A:$A,"&lt;="&amp;A91)
+    +
+    SUMIFS([42]FinancingJournal!$E:$E,
+           [42]FinancingJournal!$C:$C,"Withdrawal",
+           [42]FinancingJournal!$A:$A,"&lt;="&amp;A91),
+    "")</f>
+        <v/>
+      </c>
       <c r="F91" s="29"/>
       <c r="G91" s="29"/>
       <c r="H91" s="29"/>
@@ -22590,9 +23461,38 @@
     "")</f>
         <v/>
       </c>
-      <c r="C92" s="15"/>
-      <c r="D92" s="15"/>
-      <c r="E92" s="15"/>
+      <c r="C92" s="15" t="str">
+        <f>IF(A92&lt;&gt;"",
+    SUMIFS([42]InvestingJournal!$F:$F,
+           [42]InvestingJournal!$C:$C,"Izra Advance",
+           [42]InvestingJournal!$A:$A,"&lt;="&amp;A92)
+    +
+    SUMIFS([42]InvestingJournal!$F:$F,
+           [42]InvestingJournal!$C:$C,"Investment to Unit",
+           [42]InvestingJournal!$A:$A,"&lt;="&amp;A92),
+    "")</f>
+        <v/>
+      </c>
+      <c r="D92" s="15" t="str">
+        <f>IF(A92&lt;&gt;"",
+    SUMIFS([42]InvestingJournal!$F:$F,
+           [42]InvestingJournal!$C:$C,"Loan Advance",
+           [42]InvestingJournal!$A:$A,"&lt;="&amp;A92),
+    "")</f>
+        <v/>
+      </c>
+      <c r="E92" s="15" t="str">
+        <f>IF(A92&lt;&gt;"",
+    SUMIFS([42]FinancingJournal!$E:$E,
+           [42]FinancingJournal!$C:$C,"Borrowing",
+           [42]FinancingJournal!$A:$A,"&lt;="&amp;A92)
+    +
+    SUMIFS([42]FinancingJournal!$E:$E,
+           [42]FinancingJournal!$C:$C,"Withdrawal",
+           [42]FinancingJournal!$A:$A,"&lt;="&amp;A92),
+    "")</f>
+        <v/>
+      </c>
       <c r="F92" s="26"/>
       <c r="G92" s="26"/>
       <c r="H92" s="26"/>
@@ -22609,9 +23509,38 @@
     "")</f>
         <v/>
       </c>
-      <c r="C93" s="18"/>
-      <c r="D93" s="18"/>
-      <c r="E93" s="18"/>
+      <c r="C93" s="18" t="str">
+        <f>IF(A93&lt;&gt;"",
+    SUMIFS([42]InvestingJournal!$F:$F,
+           [42]InvestingJournal!$C:$C,"Izra Advance",
+           [42]InvestingJournal!$A:$A,"&lt;="&amp;A93)
+    +
+    SUMIFS([42]InvestingJournal!$F:$F,
+           [42]InvestingJournal!$C:$C,"Investment to Unit",
+           [42]InvestingJournal!$A:$A,"&lt;="&amp;A93),
+    "")</f>
+        <v/>
+      </c>
+      <c r="D93" s="18" t="str">
+        <f>IF(A93&lt;&gt;"",
+    SUMIFS([42]InvestingJournal!$F:$F,
+           [42]InvestingJournal!$C:$C,"Loan Advance",
+           [42]InvestingJournal!$A:$A,"&lt;="&amp;A93),
+    "")</f>
+        <v/>
+      </c>
+      <c r="E93" s="18" t="str">
+        <f>IF(A93&lt;&gt;"",
+    SUMIFS([42]FinancingJournal!$E:$E,
+           [42]FinancingJournal!$C:$C,"Borrowing",
+           [42]FinancingJournal!$A:$A,"&lt;="&amp;A93)
+    +
+    SUMIFS([42]FinancingJournal!$E:$E,
+           [42]FinancingJournal!$C:$C,"Withdrawal",
+           [42]FinancingJournal!$A:$A,"&lt;="&amp;A93),
+    "")</f>
+        <v/>
+      </c>
       <c r="F93" s="29"/>
       <c r="G93" s="29"/>
       <c r="H93" s="29"/>
@@ -22629,9 +23558,38 @@
     "")</f>
         <v/>
       </c>
-      <c r="C94" s="15"/>
-      <c r="D94" s="15"/>
-      <c r="E94" s="15"/>
+      <c r="C94" s="15" t="str">
+        <f>IF(A94&lt;&gt;"",
+    SUMIFS([42]InvestingJournal!$F:$F,
+           [42]InvestingJournal!$C:$C,"Izra Advance",
+           [42]InvestingJournal!$A:$A,"&lt;="&amp;A94)
+    +
+    SUMIFS([42]InvestingJournal!$F:$F,
+           [42]InvestingJournal!$C:$C,"Investment to Unit",
+           [42]InvestingJournal!$A:$A,"&lt;="&amp;A94),
+    "")</f>
+        <v/>
+      </c>
+      <c r="D94" s="15" t="str">
+        <f>IF(A94&lt;&gt;"",
+    SUMIFS([42]InvestingJournal!$F:$F,
+           [42]InvestingJournal!$C:$C,"Loan Advance",
+           [42]InvestingJournal!$A:$A,"&lt;="&amp;A94),
+    "")</f>
+        <v/>
+      </c>
+      <c r="E94" s="15" t="str">
+        <f>IF(A94&lt;&gt;"",
+    SUMIFS([42]FinancingJournal!$E:$E,
+           [42]FinancingJournal!$C:$C,"Borrowing",
+           [42]FinancingJournal!$A:$A,"&lt;="&amp;A94)
+    +
+    SUMIFS([42]FinancingJournal!$E:$E,
+           [42]FinancingJournal!$C:$C,"Withdrawal",
+           [42]FinancingJournal!$A:$A,"&lt;="&amp;A94),
+    "")</f>
+        <v/>
+      </c>
       <c r="F94" s="26"/>
       <c r="G94" s="26"/>
       <c r="H94" s="26"/>
@@ -22648,9 +23606,38 @@
     "")</f>
         <v/>
       </c>
-      <c r="C95" s="18"/>
-      <c r="D95" s="18"/>
-      <c r="E95" s="18"/>
+      <c r="C95" s="18" t="str">
+        <f>IF(A95&lt;&gt;"",
+    SUMIFS([42]InvestingJournal!$F:$F,
+           [42]InvestingJournal!$C:$C,"Izra Advance",
+           [42]InvestingJournal!$A:$A,"&lt;="&amp;A95)
+    +
+    SUMIFS([42]InvestingJournal!$F:$F,
+           [42]InvestingJournal!$C:$C,"Investment to Unit",
+           [42]InvestingJournal!$A:$A,"&lt;="&amp;A95),
+    "")</f>
+        <v/>
+      </c>
+      <c r="D95" s="18" t="str">
+        <f>IF(A95&lt;&gt;"",
+    SUMIFS([42]InvestingJournal!$F:$F,
+           [42]InvestingJournal!$C:$C,"Loan Advance",
+           [42]InvestingJournal!$A:$A,"&lt;="&amp;A95),
+    "")</f>
+        <v/>
+      </c>
+      <c r="E95" s="18" t="str">
+        <f>IF(A95&lt;&gt;"",
+    SUMIFS([42]FinancingJournal!$E:$E,
+           [42]FinancingJournal!$C:$C,"Borrowing",
+           [42]FinancingJournal!$A:$A,"&lt;="&amp;A95)
+    +
+    SUMIFS([42]FinancingJournal!$E:$E,
+           [42]FinancingJournal!$C:$C,"Withdrawal",
+           [42]FinancingJournal!$A:$A,"&lt;="&amp;A95),
+    "")</f>
+        <v/>
+      </c>
       <c r="F95" s="29"/>
       <c r="G95" s="29"/>
       <c r="H95" s="29"/>
@@ -22668,9 +23655,38 @@
     "")</f>
         <v/>
       </c>
-      <c r="C96" s="15"/>
-      <c r="D96" s="15"/>
-      <c r="E96" s="15"/>
+      <c r="C96" s="15" t="str">
+        <f>IF(A96&lt;&gt;"",
+    SUMIFS([42]InvestingJournal!$F:$F,
+           [42]InvestingJournal!$C:$C,"Izra Advance",
+           [42]InvestingJournal!$A:$A,"&lt;="&amp;A96)
+    +
+    SUMIFS([42]InvestingJournal!$F:$F,
+           [42]InvestingJournal!$C:$C,"Investment to Unit",
+           [42]InvestingJournal!$A:$A,"&lt;="&amp;A96),
+    "")</f>
+        <v/>
+      </c>
+      <c r="D96" s="15" t="str">
+        <f>IF(A96&lt;&gt;"",
+    SUMIFS([42]InvestingJournal!$F:$F,
+           [42]InvestingJournal!$C:$C,"Loan Advance",
+           [42]InvestingJournal!$A:$A,"&lt;="&amp;A96),
+    "")</f>
+        <v/>
+      </c>
+      <c r="E96" s="15" t="str">
+        <f>IF(A96&lt;&gt;"",
+    SUMIFS([42]FinancingJournal!$E:$E,
+           [42]FinancingJournal!$C:$C,"Borrowing",
+           [42]FinancingJournal!$A:$A,"&lt;="&amp;A96)
+    +
+    SUMIFS([42]FinancingJournal!$E:$E,
+           [42]FinancingJournal!$C:$C,"Withdrawal",
+           [42]FinancingJournal!$A:$A,"&lt;="&amp;A96),
+    "")</f>
+        <v/>
+      </c>
       <c r="F96" s="26"/>
       <c r="G96" s="26"/>
       <c r="H96" s="26"/>
@@ -22687,9 +23703,38 @@
     "")</f>
         <v/>
       </c>
-      <c r="C97" s="18"/>
-      <c r="D97" s="18"/>
-      <c r="E97" s="18"/>
+      <c r="C97" s="18" t="str">
+        <f>IF(A97&lt;&gt;"",
+    SUMIFS([42]InvestingJournal!$F:$F,
+           [42]InvestingJournal!$C:$C,"Izra Advance",
+           [42]InvestingJournal!$A:$A,"&lt;="&amp;A97)
+    +
+    SUMIFS([42]InvestingJournal!$F:$F,
+           [42]InvestingJournal!$C:$C,"Investment to Unit",
+           [42]InvestingJournal!$A:$A,"&lt;="&amp;A97),
+    "")</f>
+        <v/>
+      </c>
+      <c r="D97" s="18" t="str">
+        <f>IF(A97&lt;&gt;"",
+    SUMIFS([42]InvestingJournal!$F:$F,
+           [42]InvestingJournal!$C:$C,"Loan Advance",
+           [42]InvestingJournal!$A:$A,"&lt;="&amp;A97),
+    "")</f>
+        <v/>
+      </c>
+      <c r="E97" s="18" t="str">
+        <f>IF(A97&lt;&gt;"",
+    SUMIFS([42]FinancingJournal!$E:$E,
+           [42]FinancingJournal!$C:$C,"Borrowing",
+           [42]FinancingJournal!$A:$A,"&lt;="&amp;A97)
+    +
+    SUMIFS([42]FinancingJournal!$E:$E,
+           [42]FinancingJournal!$C:$C,"Withdrawal",
+           [42]FinancingJournal!$A:$A,"&lt;="&amp;A97),
+    "")</f>
+        <v/>
+      </c>
       <c r="F97" s="29"/>
       <c r="G97" s="29"/>
       <c r="H97" s="29"/>
@@ -22707,9 +23752,38 @@
     "")</f>
         <v/>
       </c>
-      <c r="C98" s="15"/>
-      <c r="D98" s="15"/>
-      <c r="E98" s="15"/>
+      <c r="C98" s="15" t="str">
+        <f>IF(A98&lt;&gt;"",
+    SUMIFS([42]InvestingJournal!$F:$F,
+           [42]InvestingJournal!$C:$C,"Izra Advance",
+           [42]InvestingJournal!$A:$A,"&lt;="&amp;A98)
+    +
+    SUMIFS([42]InvestingJournal!$F:$F,
+           [42]InvestingJournal!$C:$C,"Investment to Unit",
+           [42]InvestingJournal!$A:$A,"&lt;="&amp;A98),
+    "")</f>
+        <v/>
+      </c>
+      <c r="D98" s="15" t="str">
+        <f>IF(A98&lt;&gt;"",
+    SUMIFS([42]InvestingJournal!$F:$F,
+           [42]InvestingJournal!$C:$C,"Loan Advance",
+           [42]InvestingJournal!$A:$A,"&lt;="&amp;A98),
+    "")</f>
+        <v/>
+      </c>
+      <c r="E98" s="15" t="str">
+        <f>IF(A98&lt;&gt;"",
+    SUMIFS([42]FinancingJournal!$E:$E,
+           [42]FinancingJournal!$C:$C,"Borrowing",
+           [42]FinancingJournal!$A:$A,"&lt;="&amp;A98)
+    +
+    SUMIFS([42]FinancingJournal!$E:$E,
+           [42]FinancingJournal!$C:$C,"Withdrawal",
+           [42]FinancingJournal!$A:$A,"&lt;="&amp;A98),
+    "")</f>
+        <v/>
+      </c>
       <c r="F98" s="26"/>
       <c r="G98" s="26"/>
       <c r="H98" s="26"/>
@@ -22726,9 +23800,38 @@
     "")</f>
         <v/>
       </c>
-      <c r="C99" s="18"/>
-      <c r="D99" s="18"/>
-      <c r="E99" s="18"/>
+      <c r="C99" s="18" t="str">
+        <f>IF(A99&lt;&gt;"",
+    SUMIFS([42]InvestingJournal!$F:$F,
+           [42]InvestingJournal!$C:$C,"Izra Advance",
+           [42]InvestingJournal!$A:$A,"&lt;="&amp;A99)
+    +
+    SUMIFS([42]InvestingJournal!$F:$F,
+           [42]InvestingJournal!$C:$C,"Investment to Unit",
+           [42]InvestingJournal!$A:$A,"&lt;="&amp;A99),
+    "")</f>
+        <v/>
+      </c>
+      <c r="D99" s="18" t="str">
+        <f>IF(A99&lt;&gt;"",
+    SUMIFS([42]InvestingJournal!$F:$F,
+           [42]InvestingJournal!$C:$C,"Loan Advance",
+           [42]InvestingJournal!$A:$A,"&lt;="&amp;A99),
+    "")</f>
+        <v/>
+      </c>
+      <c r="E99" s="18" t="str">
+        <f>IF(A99&lt;&gt;"",
+    SUMIFS([42]FinancingJournal!$E:$E,
+           [42]FinancingJournal!$C:$C,"Borrowing",
+           [42]FinancingJournal!$A:$A,"&lt;="&amp;A99)
+    +
+    SUMIFS([42]FinancingJournal!$E:$E,
+           [42]FinancingJournal!$C:$C,"Withdrawal",
+           [42]FinancingJournal!$A:$A,"&lt;="&amp;A99),
+    "")</f>
+        <v/>
+      </c>
       <c r="F99" s="29"/>
       <c r="G99" s="29"/>
       <c r="H99" s="29"/>
@@ -22746,9 +23849,38 @@
     "")</f>
         <v/>
       </c>
-      <c r="C100" s="15"/>
-      <c r="D100" s="15"/>
-      <c r="E100" s="15"/>
+      <c r="C100" s="15" t="str">
+        <f>IF(A100&lt;&gt;"",
+    SUMIFS([42]InvestingJournal!$F:$F,
+           [42]InvestingJournal!$C:$C,"Izra Advance",
+           [42]InvestingJournal!$A:$A,"&lt;="&amp;A100)
+    +
+    SUMIFS([42]InvestingJournal!$F:$F,
+           [42]InvestingJournal!$C:$C,"Investment to Unit",
+           [42]InvestingJournal!$A:$A,"&lt;="&amp;A100),
+    "")</f>
+        <v/>
+      </c>
+      <c r="D100" s="15" t="str">
+        <f>IF(A100&lt;&gt;"",
+    SUMIFS([42]InvestingJournal!$F:$F,
+           [42]InvestingJournal!$C:$C,"Loan Advance",
+           [42]InvestingJournal!$A:$A,"&lt;="&amp;A100),
+    "")</f>
+        <v/>
+      </c>
+      <c r="E100" s="15" t="str">
+        <f>IF(A100&lt;&gt;"",
+    SUMIFS([42]FinancingJournal!$E:$E,
+           [42]FinancingJournal!$C:$C,"Borrowing",
+           [42]FinancingJournal!$A:$A,"&lt;="&amp;A100)
+    +
+    SUMIFS([42]FinancingJournal!$E:$E,
+           [42]FinancingJournal!$C:$C,"Withdrawal",
+           [42]FinancingJournal!$A:$A,"&lt;="&amp;A100),
+    "")</f>
+        <v/>
+      </c>
       <c r="F100" s="26"/>
       <c r="G100" s="26"/>
       <c r="H100" s="26"/>

--- a/NBFC-MF/LoanPortfolio.xlsx
+++ b/NBFC-MF/LoanPortfolio.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="164011"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="3600" windowWidth="15360" windowHeight="4410" activeTab="1"/>
+    <workbookView xWindow="0" yWindow="3600" windowWidth="15360" windowHeight="4410"/>
   </bookViews>
   <sheets>
     <sheet name="Portfolio" sheetId="7" r:id="rId1"/>
@@ -54,6 +54,7 @@
     <externalReference r:id="rId43"/>
     <externalReference r:id="rId44"/>
     <externalReference r:id="rId45"/>
+    <externalReference r:id="rId46"/>
   </externalReferences>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Portfolio!$A$4:$N$472</definedName>
@@ -63,7 +64,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="255" uniqueCount="135">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="260" uniqueCount="138">
   <si>
     <t>Code</t>
   </si>
@@ -468,6 +469,15 @@
   </si>
   <si>
     <t>21sept: 5500 payable to aboong</t>
+  </si>
+  <si>
+    <t>227tina loan 10000; 228Gomti loan 30000</t>
+  </si>
+  <si>
+    <t>snacks+paper 1050; chahi din 2450</t>
+  </si>
+  <si>
+    <t>229ichal loan30000</t>
   </si>
 </sst>
 </file>
@@ -1383,32 +1393,32 @@
         </row>
         <row r="12">
           <cell r="K12">
-            <v>0</v>
+            <v>1</v>
           </cell>
         </row>
         <row r="13">
           <cell r="K13">
-            <v>29750</v>
+            <v>28000</v>
           </cell>
         </row>
         <row r="14">
           <cell r="K14">
-            <v>29750</v>
+            <v>23751.28905198615</v>
           </cell>
         </row>
         <row r="15">
           <cell r="K15">
-            <v>0</v>
+            <v>1248.7109480138497</v>
           </cell>
         </row>
         <row r="16">
-          <cell r="K16" t="str">
-            <v/>
+          <cell r="K16">
+            <v>46287</v>
           </cell>
         </row>
         <row r="17">
-          <cell r="K17" t="str">
-            <v/>
+          <cell r="K17">
+            <v>46406</v>
           </cell>
         </row>
       </sheetData>
@@ -1510,22 +1520,22 @@
         </row>
         <row r="12">
           <cell r="K12">
-            <v>5</v>
+            <v>6</v>
           </cell>
         </row>
         <row r="13">
           <cell r="K13">
-            <v>16800</v>
+            <v>15400</v>
           </cell>
         </row>
         <row r="14">
           <cell r="K14">
-            <v>14800.790431951375</v>
+            <v>13697.569400122526</v>
           </cell>
         </row>
         <row r="15">
           <cell r="K15">
-            <v>5199.2095680486254</v>
+            <v>6302.4305998774744</v>
           </cell>
         </row>
         <row r="16">
@@ -1637,22 +1647,22 @@
         </row>
         <row r="12">
           <cell r="K12">
-            <v>13</v>
+            <v>14</v>
           </cell>
         </row>
         <row r="13">
           <cell r="K13">
-            <v>2800</v>
+            <v>2100</v>
           </cell>
         </row>
         <row r="14">
           <cell r="K14">
-            <v>2665.0766092382519</v>
+            <v>2018.5155583148735</v>
           </cell>
         </row>
         <row r="15">
           <cell r="K15">
-            <v>7334.9233907617481</v>
+            <v>7981.4844416851265</v>
           </cell>
         </row>
         <row r="16">
@@ -1880,22 +1890,22 @@
         </row>
         <row r="12">
           <cell r="K12">
-            <v>3</v>
+            <v>4</v>
           </cell>
         </row>
         <row r="13">
           <cell r="K13">
-            <v>27000</v>
+            <v>24000</v>
           </cell>
         </row>
         <row r="14">
           <cell r="K14">
-            <v>23442.585668039574</v>
+            <v>21127.778238971867</v>
           </cell>
         </row>
         <row r="15">
           <cell r="K15">
-            <v>6557.4143319604264</v>
+            <v>8872.2217610281332</v>
           </cell>
         </row>
         <row r="16">
@@ -2065,22 +2075,22 @@
         </row>
         <row r="12">
           <cell r="K12">
-            <v>21</v>
+            <v>29</v>
           </cell>
         </row>
         <row r="13">
           <cell r="K13">
-            <v>29700</v>
+            <v>27300</v>
           </cell>
         </row>
         <row r="14">
           <cell r="K14">
-            <v>25524.137134582503</v>
+            <v>23740.683254256033</v>
           </cell>
         </row>
         <row r="15">
           <cell r="K15">
-            <v>4475.8628654174972</v>
+            <v>6259.3167457439667</v>
           </cell>
         </row>
         <row r="16">
@@ -2377,32 +2387,32 @@
         </row>
         <row r="12">
           <cell r="K12">
-            <v>0</v>
+            <v>1</v>
           </cell>
         </row>
         <row r="13">
           <cell r="K13">
-            <v>23800</v>
+            <v>22400</v>
           </cell>
         </row>
         <row r="14">
           <cell r="K14">
-            <v>23800</v>
+            <v>19001.031241588931</v>
           </cell>
         </row>
         <row r="15">
           <cell r="K15">
-            <v>0</v>
+            <v>998.96875841106885</v>
           </cell>
         </row>
         <row r="16">
-          <cell r="K16" t="str">
-            <v/>
+          <cell r="K16">
+            <v>46290</v>
           </cell>
         </row>
         <row r="17">
-          <cell r="K17" t="str">
-            <v/>
+          <cell r="K17">
+            <v>46409</v>
           </cell>
         </row>
       </sheetData>
@@ -2505,22 +2515,22 @@
         </row>
         <row r="12">
           <cell r="K12">
-            <v>4</v>
+            <v>5</v>
           </cell>
         </row>
         <row r="13">
           <cell r="K13">
-            <v>9100</v>
+            <v>8400</v>
           </cell>
         </row>
         <row r="14">
           <cell r="K14">
-            <v>7941.1625030625555</v>
+            <v>7400.3952159756873</v>
           </cell>
         </row>
         <row r="15">
           <cell r="K15">
-            <v>2058.8374969374445</v>
+            <v>2599.6047840243127</v>
           </cell>
         </row>
         <row r="16">
@@ -2562,22 +2572,22 @@
         </row>
         <row r="12">
           <cell r="K12">
-            <v>2</v>
+            <v>3</v>
           </cell>
         </row>
         <row r="13">
           <cell r="K13">
-            <v>31500</v>
+            <v>29400</v>
           </cell>
         </row>
         <row r="14">
           <cell r="K14">
-            <v>26973.047398654715</v>
+            <v>25413.899133040686</v>
           </cell>
         </row>
         <row r="15">
           <cell r="K15">
-            <v>3026.9526013452851</v>
+            <v>4586.1008669593139</v>
           </cell>
         </row>
         <row r="16">
@@ -3023,22 +3033,22 @@
         </row>
         <row r="12">
           <cell r="K12">
-            <v>12</v>
+            <v>20</v>
           </cell>
         </row>
         <row r="13">
           <cell r="K13">
-            <v>21600</v>
+            <v>20000</v>
           </cell>
         </row>
         <row r="14">
           <cell r="K14">
-            <v>18318.802096717634</v>
+            <v>17162.643827501808</v>
           </cell>
         </row>
         <row r="15">
           <cell r="K15">
-            <v>1681.1979032823656</v>
+            <v>2837.3561724981919</v>
           </cell>
         </row>
         <row r="16">
@@ -3062,6 +3072,7 @@
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="Loan1"/>
+      <sheetName val="228"/>
     </sheetNames>
     <sheetDataSet>
       <sheetData sheetId="0">
@@ -3092,22 +3103,22 @@
         </row>
         <row r="12">
           <cell r="K12">
-            <v>15</v>
+            <v>17</v>
           </cell>
         </row>
         <row r="13">
           <cell r="K13">
-            <v>2800</v>
+            <v>0</v>
           </cell>
         </row>
         <row r="14">
           <cell r="K14">
-            <v>2717.9798966815056</v>
+            <v>9.1336005425546318E-10</v>
           </cell>
         </row>
         <row r="15">
           <cell r="K15">
-            <v>17282.020103318493</v>
+            <v>19999.999999999087</v>
           </cell>
         </row>
         <row r="16">
@@ -3118,6 +3129,63 @@
         <row r="17">
           <cell r="K17">
             <v>46304</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1">
+        <row r="2">
+          <cell r="K2" t="str">
+            <v>L30000W17-L_Gomti-N228</v>
+          </cell>
+        </row>
+        <row r="3">
+          <cell r="K3" t="str">
+            <v>L_Gomti</v>
+          </cell>
+        </row>
+        <row r="7">
+          <cell r="K7">
+            <v>30000</v>
+          </cell>
+        </row>
+        <row r="9">
+          <cell r="K9">
+            <v>2100</v>
+          </cell>
+        </row>
+        <row r="10">
+          <cell r="K10">
+            <v>17</v>
+          </cell>
+        </row>
+        <row r="12">
+          <cell r="K12">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="13">
+          <cell r="K13">
+            <v>35700</v>
+          </cell>
+        </row>
+        <row r="14">
+          <cell r="K14">
+            <v>35700</v>
+          </cell>
+        </row>
+        <row r="15">
+          <cell r="K15">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="16">
+          <cell r="K16" t="str">
+            <v/>
+          </cell>
+        </row>
+        <row r="17">
+          <cell r="K17" t="str">
+            <v/>
           </cell>
         </row>
       </sheetData>
@@ -3161,22 +3229,22 @@
         </row>
         <row r="12">
           <cell r="K12">
-            <v>13</v>
+            <v>14</v>
           </cell>
         </row>
         <row r="13">
           <cell r="K13">
-            <v>2800</v>
+            <v>2100</v>
           </cell>
         </row>
         <row r="14">
           <cell r="K14">
-            <v>2665.0766092382519</v>
+            <v>2018.5155583148735</v>
           </cell>
         </row>
         <row r="15">
           <cell r="K15">
-            <v>7334.9233907617481</v>
+            <v>7981.4844416851265</v>
           </cell>
         </row>
         <row r="16">
@@ -3230,22 +3298,22 @@
         </row>
         <row r="12">
           <cell r="K12">
-            <v>13</v>
+            <v>14</v>
           </cell>
         </row>
         <row r="13">
           <cell r="K13">
-            <v>8400</v>
+            <v>6300</v>
           </cell>
         </row>
         <row r="14">
           <cell r="K14">
-            <v>7995.2298277146756</v>
+            <v>6055.5466749445368</v>
           </cell>
         </row>
         <row r="15">
           <cell r="K15">
-            <v>22004.770172285323</v>
+            <v>23944.453325055463</v>
           </cell>
         </row>
         <row r="16">
@@ -3299,22 +3367,22 @@
         </row>
         <row r="12">
           <cell r="K12">
-            <v>12</v>
+            <v>13</v>
           </cell>
         </row>
         <row r="13">
           <cell r="K13">
-            <v>3500</v>
+            <v>2800</v>
           </cell>
         </row>
         <row r="14">
           <cell r="K14">
-            <v>3298.927950640365</v>
+            <v>2665.0766092382519</v>
           </cell>
         </row>
         <row r="15">
           <cell r="K15">
-            <v>6701.0720493596345</v>
+            <v>7334.9233907617481</v>
           </cell>
         </row>
         <row r="16">
@@ -3407,6 +3475,7 @@
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="194"/>
+      <sheetName val="229"/>
     </sheetNames>
     <sheetDataSet>
       <sheetData sheetId="0">
@@ -3437,22 +3506,22 @@
         </row>
         <row r="12">
           <cell r="K12">
-            <v>12</v>
+            <v>17</v>
           </cell>
         </row>
         <row r="13">
           <cell r="K13">
-            <v>7000</v>
+            <v>0</v>
           </cell>
         </row>
         <row r="14">
           <cell r="K14">
-            <v>6597.85590128073</v>
+            <v>9.1336005425546318E-10</v>
           </cell>
         </row>
         <row r="15">
           <cell r="K15">
-            <v>13402.144098719269</v>
+            <v>19999.999999999087</v>
           </cell>
         </row>
         <row r="16">
@@ -3463,6 +3532,63 @@
         <row r="17">
           <cell r="K17">
             <v>46321</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1">
+        <row r="2">
+          <cell r="K2" t="str">
+            <v>L30000W17-Salam_Echal-N229</v>
+          </cell>
+        </row>
+        <row r="3">
+          <cell r="K3" t="str">
+            <v>Salam_Echal</v>
+          </cell>
+        </row>
+        <row r="7">
+          <cell r="K7">
+            <v>30000</v>
+          </cell>
+        </row>
+        <row r="9">
+          <cell r="K9">
+            <v>2100</v>
+          </cell>
+        </row>
+        <row r="10">
+          <cell r="K10">
+            <v>17</v>
+          </cell>
+        </row>
+        <row r="12">
+          <cell r="K12">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="13">
+          <cell r="K13">
+            <v>35700</v>
+          </cell>
+        </row>
+        <row r="14">
+          <cell r="K14">
+            <v>35700</v>
+          </cell>
+        </row>
+        <row r="15">
+          <cell r="K15">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="16">
+          <cell r="K16" t="str">
+            <v/>
+          </cell>
+        </row>
+        <row r="17">
+          <cell r="K17" t="str">
+            <v/>
           </cell>
         </row>
       </sheetData>
@@ -3506,22 +3632,22 @@
         </row>
         <row r="12">
           <cell r="K12">
-            <v>9</v>
+            <v>10</v>
           </cell>
         </row>
         <row r="13">
           <cell r="K13">
-            <v>56000</v>
+            <v>49000</v>
           </cell>
         </row>
         <row r="14">
           <cell r="K14">
-            <v>51266.976567526755</v>
+            <v>45294.959530796019</v>
           </cell>
         </row>
         <row r="15">
           <cell r="K15">
-            <v>48733.023432473245</v>
+            <v>54705.040469203981</v>
           </cell>
         </row>
         <row r="16">
@@ -3575,22 +3701,22 @@
         </row>
         <row r="12">
           <cell r="K12">
-            <v>8</v>
+            <v>9</v>
           </cell>
         </row>
         <row r="13">
           <cell r="K13">
-            <v>37800</v>
+            <v>33600</v>
           </cell>
         </row>
         <row r="14">
           <cell r="K14">
-            <v>34272.959564168894</v>
+            <v>30760.185940516178</v>
           </cell>
         </row>
         <row r="15">
           <cell r="K15">
-            <v>25727.040435831106</v>
+            <v>29239.814059483822</v>
           </cell>
         </row>
         <row r="16">
@@ -3644,22 +3770,22 @@
         </row>
         <row r="12">
           <cell r="K12">
-            <v>63</v>
+            <v>66</v>
           </cell>
         </row>
         <row r="13">
           <cell r="K13">
-            <v>28500</v>
+            <v>27000</v>
           </cell>
         </row>
         <row r="14">
           <cell r="K14">
-            <v>26076.674163036809</v>
+            <v>24816.380037149793</v>
           </cell>
         </row>
         <row r="15">
           <cell r="K15">
-            <v>23923.325836963191</v>
+            <v>25183.619962850207</v>
           </cell>
         </row>
         <row r="16">
@@ -3713,22 +3839,22 @@
         </row>
         <row r="12">
           <cell r="K12">
-            <v>8</v>
+            <v>9</v>
           </cell>
         </row>
         <row r="13">
           <cell r="K13">
-            <v>12600</v>
+            <v>11200</v>
           </cell>
         </row>
         <row r="14">
           <cell r="K14">
-            <v>11424.319854722999</v>
+            <v>10253.395313505431</v>
           </cell>
         </row>
         <row r="15">
           <cell r="K15">
-            <v>8575.6801452770014</v>
+            <v>9746.6046864945693</v>
           </cell>
         </row>
         <row r="16">
@@ -3782,22 +3908,22 @@
         </row>
         <row r="12">
           <cell r="K12">
-            <v>7</v>
+            <v>8</v>
           </cell>
         </row>
         <row r="13">
           <cell r="K13">
-            <v>70000</v>
+            <v>63000</v>
           </cell>
         </row>
         <row r="14">
           <cell r="K14">
-            <v>62861.13531643273</v>
+            <v>57121.599273614636</v>
           </cell>
         </row>
         <row r="15">
           <cell r="K15">
-            <v>37138.86468356727</v>
+            <v>42878.400726385364</v>
           </cell>
         </row>
         <row r="16">
@@ -3851,22 +3977,22 @@
         </row>
         <row r="12">
           <cell r="K12">
-            <v>31</v>
+            <v>33</v>
           </cell>
         </row>
         <row r="13">
           <cell r="K13">
-            <v>14700</v>
+            <v>14100</v>
           </cell>
         </row>
         <row r="14">
           <cell r="K14">
-            <v>13117.062707143943</v>
+            <v>12638.053512615395</v>
           </cell>
         </row>
         <row r="15">
           <cell r="K15">
-            <v>6882.937292856057</v>
+            <v>7361.9464873846046</v>
           </cell>
         </row>
         <row r="16">
@@ -3920,22 +4046,22 @@
         </row>
         <row r="12">
           <cell r="K12">
-            <v>5</v>
+            <v>6</v>
           </cell>
         </row>
         <row r="13">
           <cell r="K13">
-            <v>16800</v>
+            <v>15400</v>
           </cell>
         </row>
         <row r="14">
           <cell r="K14">
-            <v>14800.790431951375</v>
+            <v>13697.569400122526</v>
           </cell>
         </row>
         <row r="15">
           <cell r="K15">
-            <v>5199.2095680486254</v>
+            <v>6302.4305998774744</v>
           </cell>
         </row>
         <row r="16">
@@ -3989,22 +4115,22 @@
         </row>
         <row r="12">
           <cell r="K12">
-            <v>4</v>
+            <v>6</v>
           </cell>
         </row>
         <row r="13">
           <cell r="K13">
-            <v>18200</v>
+            <v>15400</v>
           </cell>
         </row>
         <row r="14">
           <cell r="K14">
-            <v>15882.325006125111</v>
+            <v>13697.569400122526</v>
           </cell>
         </row>
         <row r="15">
           <cell r="K15">
-            <v>4117.674993874889</v>
+            <v>6302.4305998774744</v>
           </cell>
         </row>
         <row r="16">
@@ -4058,22 +4184,22 @@
         </row>
         <row r="12">
           <cell r="K12">
-            <v>4</v>
+            <v>6</v>
           </cell>
         </row>
         <row r="13">
           <cell r="K13">
-            <v>18200</v>
+            <v>15400</v>
           </cell>
         </row>
         <row r="14">
           <cell r="K14">
-            <v>15882.325006125111</v>
+            <v>13697.569400122526</v>
           </cell>
         </row>
         <row r="15">
           <cell r="K15">
-            <v>4117.674993874889</v>
+            <v>6302.4305998774744</v>
           </cell>
         </row>
         <row r="16">
@@ -4127,22 +4253,22 @@
         </row>
         <row r="12">
           <cell r="K12">
-            <v>3</v>
+            <v>5</v>
           </cell>
         </row>
         <row r="13">
           <cell r="K13">
-            <v>19600</v>
+            <v>16800</v>
           </cell>
         </row>
         <row r="14">
           <cell r="K14">
-            <v>16942.599422027139</v>
+            <v>14800.790431951375</v>
           </cell>
         </row>
         <row r="15">
           <cell r="K15">
-            <v>3057.4005779728614</v>
+            <v>5199.2095680486254</v>
           </cell>
         </row>
         <row r="16">
@@ -4196,22 +4322,22 @@
         </row>
         <row r="12">
           <cell r="K12">
-            <v>24</v>
+            <v>35</v>
           </cell>
         </row>
         <row r="13">
           <cell r="K13">
-            <v>16800</v>
+            <v>13500</v>
           </cell>
         </row>
         <row r="14">
           <cell r="K14">
-            <v>14758.991922004241</v>
+            <v>12154.574982735843</v>
           </cell>
         </row>
         <row r="15">
           <cell r="K15">
-            <v>5241.0080779957589</v>
+            <v>7845.4250172641568</v>
           </cell>
         </row>
         <row r="16">
@@ -4265,22 +4391,22 @@
         </row>
         <row r="12">
           <cell r="K12">
-            <v>3</v>
+            <v>4</v>
           </cell>
         </row>
         <row r="13">
           <cell r="K13">
-            <v>29400</v>
+            <v>27300</v>
           </cell>
         </row>
         <row r="14">
           <cell r="K14">
-            <v>25413.899133040686</v>
+            <v>23823.487509187638</v>
           </cell>
         </row>
         <row r="15">
           <cell r="K15">
-            <v>4586.1008669593139</v>
+            <v>6176.5124908123616</v>
           </cell>
         </row>
         <row r="16">
@@ -4334,22 +4460,22 @@
         </row>
         <row r="12">
           <cell r="K12">
-            <v>2</v>
+            <v>3</v>
           </cell>
         </row>
         <row r="13">
           <cell r="K13">
-            <v>5250</v>
+            <v>4900</v>
           </cell>
         </row>
         <row r="14">
           <cell r="K14">
-            <v>4495.5078997757882</v>
+            <v>4235.6498555067847</v>
           </cell>
         </row>
         <row r="15">
           <cell r="K15">
-            <v>504.49210022421175</v>
+            <v>764.35014449321534</v>
           </cell>
         </row>
         <row r="16">
@@ -4520,22 +4646,22 @@
         </row>
         <row r="12">
           <cell r="K12">
-            <v>7</v>
+            <v>8</v>
           </cell>
         </row>
         <row r="13">
           <cell r="K13">
-            <v>14000</v>
+            <v>12600</v>
           </cell>
         </row>
         <row r="14">
           <cell r="K14">
-            <v>12572.227063286609</v>
+            <v>11424.319854722999</v>
           </cell>
         </row>
         <row r="15">
           <cell r="K15">
-            <v>7427.7729367133907</v>
+            <v>8575.6801452770014</v>
           </cell>
         </row>
         <row r="16">
@@ -4577,32 +4703,32 @@
         </row>
         <row r="12">
           <cell r="K12">
-            <v>0</v>
+            <v>5</v>
           </cell>
         </row>
         <row r="13">
           <cell r="K13">
-            <v>60000</v>
+            <v>57500</v>
           </cell>
         </row>
         <row r="14">
           <cell r="K14">
-            <v>60000</v>
+            <v>48267.790199566742</v>
           </cell>
         </row>
         <row r="15">
           <cell r="K15">
-            <v>0</v>
+            <v>1732.2098004332584</v>
           </cell>
         </row>
         <row r="16">
-          <cell r="K16" t="str">
-            <v/>
+          <cell r="K16">
+            <v>46288</v>
           </cell>
         </row>
         <row r="17">
-          <cell r="K17" t="str">
-            <v/>
+          <cell r="K17">
+            <v>46408</v>
           </cell>
         </row>
       </sheetData>
@@ -4646,22 +4772,22 @@
         </row>
         <row r="12">
           <cell r="K12">
-            <v>9</v>
+            <v>12</v>
           </cell>
         </row>
         <row r="13">
           <cell r="K13">
-            <v>10650</v>
+            <v>10200</v>
           </cell>
         </row>
         <row r="14">
           <cell r="K14">
-            <v>9051.3676217399407</v>
+            <v>8726.2439243020872</v>
           </cell>
         </row>
         <row r="15">
           <cell r="K15">
-            <v>948.63237826005934</v>
+            <v>1273.7560756979128</v>
           </cell>
         </row>
         <row r="16">
@@ -4715,22 +4841,22 @@
         </row>
         <row r="12">
           <cell r="K12">
-            <v>1</v>
+            <v>2</v>
           </cell>
         </row>
         <row r="13">
           <cell r="K13">
-            <v>67200</v>
+            <v>63000</v>
           </cell>
         </row>
         <row r="14">
           <cell r="K14">
-            <v>57003.093724766775</v>
+            <v>53946.09479730943</v>
           </cell>
         </row>
         <row r="15">
           <cell r="K15">
-            <v>2996.9062752332247</v>
+            <v>6053.9052026905701</v>
           </cell>
         </row>
         <row r="16">
@@ -4750,6 +4876,75 @@
 </file>
 
 <file path=xl/externalLinks/externalLink42.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="227"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="K2" t="str">
+            <v>L10000D120-Tina_devi-N227</v>
+          </cell>
+        </row>
+        <row r="3">
+          <cell r="K3" t="str">
+            <v>Tina_devi</v>
+          </cell>
+        </row>
+        <row r="7">
+          <cell r="K7">
+            <v>10000</v>
+          </cell>
+        </row>
+        <row r="9">
+          <cell r="K9">
+            <v>100</v>
+          </cell>
+        </row>
+        <row r="10">
+          <cell r="K10">
+            <v>120</v>
+          </cell>
+        </row>
+        <row r="12">
+          <cell r="K12">
+            <v>4</v>
+          </cell>
+        </row>
+        <row r="13">
+          <cell r="K13">
+            <v>11600</v>
+          </cell>
+        </row>
+        <row r="14">
+          <cell r="K14">
+            <v>9723.2779831622556</v>
+          </cell>
+        </row>
+        <row r="15">
+          <cell r="K15">
+            <v>276.72201683774438</v>
+          </cell>
+        </row>
+        <row r="16">
+          <cell r="K16">
+            <v>46291</v>
+          </cell>
+        </row>
+        <row r="17">
+          <cell r="K17">
+            <v>46411</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink43.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
@@ -5417,22 +5612,22 @@
         </row>
         <row r="12">
           <cell r="K12">
-            <v>12</v>
+            <v>13</v>
           </cell>
         </row>
         <row r="13">
           <cell r="K13">
-            <v>63000</v>
+            <v>50400</v>
           </cell>
         </row>
         <row r="14">
           <cell r="K14">
-            <v>59380.703111526433</v>
+            <v>47971.378966288386</v>
           </cell>
         </row>
         <row r="15">
           <cell r="K15">
-            <v>120619.29688847356</v>
+            <v>132028.62103371162</v>
           </cell>
         </row>
         <row r="16">
@@ -5544,22 +5739,22 @@
         </row>
         <row r="12">
           <cell r="K12">
-            <v>10</v>
+            <v>11</v>
           </cell>
         </row>
         <row r="13">
           <cell r="K13">
-            <v>14700</v>
+            <v>12600</v>
           </cell>
         </row>
         <row r="14">
           <cell r="K14">
-            <v>13588.487859238874</v>
+            <v>11760.958267114203</v>
           </cell>
         </row>
         <row r="15">
           <cell r="K15">
-            <v>16411.512140761126</v>
+            <v>18239.041732885795</v>
           </cell>
         </row>
         <row r="16">
@@ -5740,22 +5935,22 @@
         </row>
         <row r="12">
           <cell r="K12">
-            <v>13</v>
+            <v>14</v>
           </cell>
         </row>
         <row r="13">
           <cell r="K13">
-            <v>9400</v>
+            <v>9200</v>
           </cell>
         </row>
         <row r="14">
           <cell r="K14">
-            <v>8135.670977686661</v>
+            <v>7985.9771926857193</v>
           </cell>
         </row>
         <row r="15">
           <cell r="K15">
-            <v>1864.329022313339</v>
+            <v>2014.0228073142807</v>
           </cell>
         </row>
         <row r="16">
@@ -6070,7 +6265,7 @@
       <c r="J1" s="82"/>
       <c r="K1" s="83">
         <f>SUM(J5:J1000)</f>
-        <v>850450</v>
+        <v>844400</v>
       </c>
       <c r="L1" s="84"/>
       <c r="N1" s="78" t="s">
@@ -6079,7 +6274,7 @@
       <c r="O1" s="10"/>
       <c r="P1" s="78">
         <f>SUM(P5:P1000)</f>
-        <v>79650</v>
+        <v>81750</v>
       </c>
     </row>
     <row r="2" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -6092,7 +6287,7 @@
       <c r="J2" s="82"/>
       <c r="K2" s="83">
         <f>SUM(K5:K1000)</f>
-        <v>768809.71349669166</v>
+        <v>757642.69365391904</v>
       </c>
       <c r="L2" s="84"/>
       <c r="M2" s="2"/>
@@ -6156,7 +6351,7 @@
       </c>
       <c r="R4" s="43">
         <f>SUM(R5:R43)</f>
-        <v>218000</v>
+        <v>208000</v>
       </c>
     </row>
     <row r="5" spans="1:18" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -6304,7 +6499,7 @@
       </c>
       <c r="G7" s="19">
         <f t="shared" ref="G7:G17" si="0">IF(H7,H7-I7,"")</f>
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="H7" s="62">
         <f>[3]Loan1!$K$10</f>
@@ -6312,19 +6507,19 @@
       </c>
       <c r="I7" s="62">
         <f>[3]Loan1!$K$12</f>
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="J7" s="15">
         <f>[3]Loan1!$K$13</f>
-        <v>28500</v>
+        <v>27000</v>
       </c>
       <c r="K7" s="15">
         <f>[3]Loan1!$K$14</f>
-        <v>26076.674163036809</v>
+        <v>24816.380037149793</v>
       </c>
       <c r="L7" s="64">
         <f>[3]Loan1!$K$15</f>
-        <v>23923.325836963191</v>
+        <v>25183.619962850207</v>
       </c>
       <c r="M7" s="65">
         <f>[3]Loan1!$K$16</f>
@@ -7515,70 +7710,64 @@
       </c>
     </row>
     <row r="27" spans="1:18" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="62">
+      <c r="A27" s="41">
         <f t="shared" si="1"/>
         <v>186</v>
       </c>
-      <c r="B27" s="62" t="str">
+      <c r="B27" s="41" t="str">
         <f>[22]Loan1!$K$3</f>
         <v>L_Gomti</v>
       </c>
-      <c r="C27" s="62" t="s">
+      <c r="C27" s="41" t="s">
         <v>6</v>
       </c>
-      <c r="D27" s="63" t="str">
+      <c r="D27" s="67" t="str">
         <f>[22]Loan1!$K$2</f>
         <v>L20000W17-L_Gomti-NLoan1</v>
       </c>
-      <c r="E27" s="15">
+      <c r="E27" s="68">
         <f>[22]Loan1!$K$7</f>
         <v>20000</v>
       </c>
-      <c r="F27" s="62">
+      <c r="F27" s="41">
         <f>[22]Loan1!$K$9</f>
         <v>1400</v>
       </c>
-      <c r="G27" s="19">
+      <c r="G27" s="41">
         <f t="shared" si="4"/>
-        <v>2</v>
-      </c>
-      <c r="H27" s="62">
+        <v>0</v>
+      </c>
+      <c r="H27" s="41">
         <f>[22]Loan1!$K$10</f>
         <v>17</v>
       </c>
-      <c r="I27" s="62">
+      <c r="I27" s="41">
         <f>[22]Loan1!$K$12</f>
-        <v>15</v>
-      </c>
-      <c r="J27" s="15">
+        <v>17</v>
+      </c>
+      <c r="J27" s="68">
         <f>[22]Loan1!$K$13</f>
-        <v>2800</v>
-      </c>
-      <c r="K27" s="15">
+        <v>0</v>
+      </c>
+      <c r="K27" s="68">
         <f>[22]Loan1!$K$14</f>
-        <v>2717.9798966815056</v>
-      </c>
-      <c r="L27" s="64">
+        <v>9.1336005425546318E-10</v>
+      </c>
+      <c r="L27" s="69">
         <f>[22]Loan1!$K$15</f>
-        <v>17282.020103318493</v>
-      </c>
-      <c r="M27" s="65">
+        <v>19999.999999999087</v>
+      </c>
+      <c r="M27" s="70">
         <f>[22]Loan1!$K$16</f>
         <v>46185</v>
       </c>
-      <c r="N27" s="66">
+      <c r="N27" s="71">
         <f>[22]Loan1!$K$17</f>
         <v>46304</v>
       </c>
-      <c r="P27" s="46">
-        <v>1400</v>
-      </c>
-      <c r="Q27" s="46" t="s">
-        <v>32</v>
-      </c>
-      <c r="R27" s="46">
-        <v>10000</v>
-      </c>
+      <c r="O27" s="42"/>
+      <c r="P27" s="45"/>
+      <c r="R27" s="43"/>
     </row>
     <row r="28" spans="1:18" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="19">
@@ -7606,7 +7795,7 @@
       </c>
       <c r="G28" s="19">
         <f t="shared" si="4"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H28" s="19">
         <f>'[23]187'!$K$10</f>
@@ -7614,19 +7803,19 @@
       </c>
       <c r="I28" s="19">
         <f>'[23]187'!$K$12</f>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J28" s="18">
         <f>'[23]187'!$K$13</f>
-        <v>2800</v>
+        <v>2100</v>
       </c>
       <c r="K28" s="18">
         <f>'[23]187'!$K$14</f>
-        <v>2665.0766092382519</v>
+        <v>2018.5155583148735</v>
       </c>
       <c r="L28" s="73">
         <f>'[23]187'!$K$15</f>
-        <v>7334.9233907617481</v>
+        <v>7981.4844416851265</v>
       </c>
       <c r="M28" s="74">
         <f>'[23]187'!$K$16</f>
@@ -7791,7 +7980,7 @@
       </c>
       <c r="G31" s="19">
         <f t="shared" si="4"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H31" s="62">
         <f>'[12]190'!$K$10</f>
@@ -7799,19 +7988,19 @@
       </c>
       <c r="I31" s="62">
         <f>'[12]190'!$K$12</f>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J31" s="15">
         <f>'[12]190'!$K$13</f>
-        <v>2800</v>
+        <v>2100</v>
       </c>
       <c r="K31" s="15">
         <f>'[12]190'!$K$14</f>
-        <v>2665.0766092382519</v>
+        <v>2018.5155583148735</v>
       </c>
       <c r="L31" s="64">
         <f>'[12]190'!$K$15</f>
-        <v>7334.9233907617481</v>
+        <v>7981.4844416851265</v>
       </c>
       <c r="M31" s="65">
         <f>'[12]190'!$K$16</f>
@@ -7852,7 +8041,7 @@
       </c>
       <c r="G32" s="19">
         <f t="shared" si="4"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H32" s="19">
         <f>'[24]191'!$K$10</f>
@@ -7860,19 +8049,19 @@
       </c>
       <c r="I32" s="19">
         <f>'[24]191'!$K$12</f>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J32" s="18">
         <f>'[24]191'!$K$13</f>
-        <v>8400</v>
+        <v>6300</v>
       </c>
       <c r="K32" s="18">
         <f>'[24]191'!$K$14</f>
-        <v>7995.2298277146756</v>
+        <v>6055.5466749445368</v>
       </c>
       <c r="L32" s="73">
         <f>'[24]191'!$K$15</f>
-        <v>22004.770172285323</v>
+        <v>23944.453325055463</v>
       </c>
       <c r="M32" s="74">
         <f>'[24]191'!$K$16</f>
@@ -7916,7 +8105,7 @@
       </c>
       <c r="G33" s="19">
         <f t="shared" si="4"/>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H33" s="62">
         <f>'[25]192'!$K$10</f>
@@ -7924,19 +8113,19 @@
       </c>
       <c r="I33" s="62">
         <f>'[25]192'!$K$12</f>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J33" s="15">
         <f>'[25]192'!$K$13</f>
-        <v>3500</v>
+        <v>2800</v>
       </c>
       <c r="K33" s="15">
         <f>'[25]192'!$K$14</f>
-        <v>3298.927950640365</v>
+        <v>2665.0766092382519</v>
       </c>
       <c r="L33" s="64">
         <f>'[25]192'!$K$15</f>
-        <v>6701.0720493596345</v>
+        <v>7334.9233907617481</v>
       </c>
       <c r="M33" s="65">
         <f>'[25]192'!$K$16</f>
@@ -8013,66 +8202,64 @@
       <c r="R34" s="43"/>
     </row>
     <row r="35" spans="1:18" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="62">
+      <c r="A35" s="41">
         <f t="shared" si="1"/>
         <v>194</v>
       </c>
-      <c r="B35" s="62" t="str">
+      <c r="B35" s="41" t="str">
         <f>'[27]194'!$K$3</f>
         <v>Salam_Echal</v>
       </c>
-      <c r="C35" s="62" t="s">
+      <c r="C35" s="41" t="s">
         <v>6</v>
       </c>
-      <c r="D35" s="63" t="str">
-        <f>'[27]194'!$K$2</f>
+      <c r="D35" s="67" t="str">
+        <f ca="1">'[27]194'!$K$2</f>
         <v>L20000W17-Salam_Echal-N194</v>
       </c>
-      <c r="E35" s="15">
+      <c r="E35" s="68">
         <f>'[27]194'!$K$7</f>
         <v>20000</v>
       </c>
-      <c r="F35" s="62">
+      <c r="F35" s="41">
         <f>'[27]194'!$K$9</f>
         <v>1400</v>
       </c>
-      <c r="G35" s="19">
+      <c r="G35" s="41">
         <f t="shared" si="4"/>
-        <v>5</v>
-      </c>
-      <c r="H35" s="62">
+        <v>0</v>
+      </c>
+      <c r="H35" s="41">
         <f>'[27]194'!$K$10</f>
         <v>17</v>
       </c>
-      <c r="I35" s="62">
+      <c r="I35" s="41">
         <f>'[27]194'!$K$12</f>
-        <v>12</v>
-      </c>
-      <c r="J35" s="15">
+        <v>17</v>
+      </c>
+      <c r="J35" s="68">
         <f>'[27]194'!$K$13</f>
-        <v>7000</v>
-      </c>
-      <c r="K35" s="15">
+        <v>0</v>
+      </c>
+      <c r="K35" s="68">
         <f>'[27]194'!$K$14</f>
-        <v>6597.85590128073</v>
-      </c>
-      <c r="L35" s="64">
+        <v>9.1336005425546318E-10</v>
+      </c>
+      <c r="L35" s="69">
         <f>'[27]194'!$K$15</f>
-        <v>13402.144098719269</v>
-      </c>
-      <c r="M35" s="65">
+        <v>19999.999999999087</v>
+      </c>
+      <c r="M35" s="70">
         <f>'[27]194'!$K$16</f>
         <v>46202</v>
       </c>
-      <c r="N35" s="66">
+      <c r="N35" s="71">
         <f>'[27]194'!$K$17</f>
         <v>46321</v>
       </c>
-      <c r="P35" s="46">
-        <v>1400</v>
-      </c>
-      <c r="Q35" s="46"/>
-      <c r="R35" s="46">
+      <c r="O35" s="42"/>
+      <c r="P35" s="45"/>
+      <c r="R35" s="43">
         <v>20000</v>
       </c>
     </row>
@@ -8102,7 +8289,7 @@
       </c>
       <c r="G36" s="19">
         <f t="shared" si="4"/>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H36" s="19">
         <f>'[6]195'!$K$10</f>
@@ -8110,19 +8297,19 @@
       </c>
       <c r="I36" s="19">
         <f>'[6]195'!$K$12</f>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J36" s="18">
         <f>'[6]195'!$K$13</f>
-        <v>63000</v>
+        <v>50400</v>
       </c>
       <c r="K36" s="18">
         <f>'[6]195'!$K$14</f>
-        <v>59380.703111526433</v>
+        <v>47971.378966288386</v>
       </c>
       <c r="L36" s="73">
         <f>'[6]195'!$K$15</f>
-        <v>120619.29688847356</v>
+        <v>132028.62103371162</v>
       </c>
       <c r="M36" s="74">
         <f>'[6]195'!$K$16</f>
@@ -8403,7 +8590,7 @@
       </c>
       <c r="G41" s="19">
         <f t="shared" si="4"/>
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H41" s="62">
         <f>'[7]200'!$K$10</f>
@@ -8411,19 +8598,19 @@
       </c>
       <c r="I41" s="62">
         <f>'[7]200'!$K$12</f>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J41" s="15">
         <f>'[7]200'!$K$13</f>
-        <v>14700</v>
+        <v>12600</v>
       </c>
       <c r="K41" s="15">
         <f>'[7]200'!$K$14</f>
-        <v>13588.487859238874</v>
+        <v>11760.958267114203</v>
       </c>
       <c r="L41" s="64">
         <f>'[7]200'!$K$15</f>
-        <v>16411.512140761126</v>
+        <v>18239.041732885795</v>
       </c>
       <c r="M41" s="65">
         <f>'[7]200'!$K$16</f>
@@ -8463,7 +8650,7 @@
       </c>
       <c r="G42" s="19">
         <f t="shared" si="4"/>
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H42" s="19">
         <f>'[28]195'!$K$10</f>
@@ -8471,19 +8658,19 @@
       </c>
       <c r="I42" s="19">
         <f>'[28]195'!$K$12</f>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J42" s="18">
         <f>'[28]195'!$K$13</f>
-        <v>56000</v>
+        <v>49000</v>
       </c>
       <c r="K42" s="18">
         <f>'[28]195'!$K$14</f>
-        <v>51266.976567526755</v>
+        <v>45294.959530796019</v>
       </c>
       <c r="L42" s="73">
         <f>'[28]195'!$K$15</f>
-        <v>48733.023432473245</v>
+        <v>54705.040469203981</v>
       </c>
       <c r="M42" s="74">
         <f>'[28]195'!$K$16</f>
@@ -8523,7 +8710,7 @@
       </c>
       <c r="G43" s="19">
         <f t="shared" si="4"/>
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H43" s="62">
         <f>'[29]202'!$K$10</f>
@@ -8531,19 +8718,19 @@
       </c>
       <c r="I43" s="62">
         <f>'[29]202'!$K$12</f>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J43" s="15">
         <f>'[29]202'!$K$13</f>
-        <v>37800</v>
+        <v>33600</v>
       </c>
       <c r="K43" s="15">
         <f>'[29]202'!$K$14</f>
-        <v>34272.959564168894</v>
+        <v>30760.185940516178</v>
       </c>
       <c r="L43" s="64">
         <f>'[29]202'!$K$15</f>
-        <v>25727.040435831106</v>
+        <v>29239.814059483822</v>
       </c>
       <c r="M43" s="65">
         <f>'[29]202'!$K$16</f>
@@ -8583,7 +8770,7 @@
       </c>
       <c r="G44" s="19">
         <f t="shared" si="4"/>
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H44" s="36">
         <f>'[30]203'!$K$10</f>
@@ -8591,19 +8778,19 @@
       </c>
       <c r="I44" s="36">
         <f>'[30]203'!$K$12</f>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J44" s="39">
         <f>'[30]203'!$K$13</f>
-        <v>12600</v>
+        <v>11200</v>
       </c>
       <c r="K44" s="39">
         <f>'[30]203'!$K$14</f>
-        <v>11424.319854722999</v>
+        <v>10253.395313505431</v>
       </c>
       <c r="L44" s="40">
         <f>'[30]203'!$K$15</f>
-        <v>8575.6801452770014</v>
+        <v>9746.6046864945693</v>
       </c>
       <c r="M44" s="20">
         <f>'[30]203'!$K$16</f>
@@ -8643,7 +8830,7 @@
       </c>
       <c r="G45" s="19">
         <f t="shared" si="4"/>
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H45" s="33">
         <f>'[4]204'!$K$10</f>
@@ -8651,19 +8838,19 @@
       </c>
       <c r="I45" s="33">
         <f>'[4]204'!$K$12</f>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J45" s="35">
         <f>'[4]204'!$K$13</f>
-        <v>14000</v>
+        <v>12600</v>
       </c>
       <c r="K45" s="35">
         <f>'[4]204'!$K$14</f>
-        <v>12572.227063286609</v>
+        <v>11424.319854722999</v>
       </c>
       <c r="L45" s="37">
         <f>'[4]204'!$K$15</f>
-        <v>7427.7729367133907</v>
+        <v>8575.6801452770014</v>
       </c>
       <c r="M45" s="22">
         <f>'[4]204'!$K$16</f>
@@ -8703,7 +8890,7 @@
       </c>
       <c r="G46" s="19">
         <f t="shared" si="4"/>
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H46" s="36">
         <f>'[31]205'!$K$10</f>
@@ -8711,19 +8898,19 @@
       </c>
       <c r="I46" s="36">
         <f>'[31]205'!$K$12</f>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J46" s="39">
         <f>'[31]205'!$K$13</f>
-        <v>70000</v>
+        <v>63000</v>
       </c>
       <c r="K46" s="39">
         <f>'[31]205'!$K$14</f>
-        <v>62861.13531643273</v>
+        <v>57121.599273614636</v>
       </c>
       <c r="L46" s="40">
         <f>'[31]205'!$K$15</f>
-        <v>37138.86468356727</v>
+        <v>42878.400726385364</v>
       </c>
       <c r="M46" s="20">
         <f>'[31]205'!$K$16</f>
@@ -8763,7 +8950,7 @@
       </c>
       <c r="G47" s="19">
         <f t="shared" si="4"/>
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="H47" s="33">
         <f>'[9]206'!$K$10</f>
@@ -8771,19 +8958,19 @@
       </c>
       <c r="I47" s="33">
         <f>'[9]206'!$K$12</f>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J47" s="35">
         <f>'[9]206'!$K$13</f>
-        <v>9400</v>
+        <v>9200</v>
       </c>
       <c r="K47" s="35">
         <f>'[9]206'!$K$14</f>
-        <v>8135.670977686661</v>
+        <v>7985.9771926857193</v>
       </c>
       <c r="L47" s="37">
         <f>'[9]206'!$K$15</f>
-        <v>1864.329022313339</v>
+        <v>2014.0228073142807</v>
       </c>
       <c r="M47" s="22">
         <f>'[9]206'!$K$16</f>
@@ -8820,7 +9007,7 @@
       </c>
       <c r="G48" s="19">
         <f t="shared" si="4"/>
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="H48" s="36">
         <f>'[32]207'!$K$10</f>
@@ -8828,19 +9015,19 @@
       </c>
       <c r="I48" s="36">
         <f>'[32]207'!$K$12</f>
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="J48" s="39">
         <f>'[32]207'!$K$13</f>
-        <v>14700</v>
+        <v>14100</v>
       </c>
       <c r="K48" s="39">
         <f>'[32]207'!$K$14</f>
-        <v>13117.062707143943</v>
+        <v>12638.053512615395</v>
       </c>
       <c r="L48" s="40">
         <f>'[32]207'!$K$15</f>
-        <v>6882.937292856057</v>
+        <v>7361.9464873846046</v>
       </c>
       <c r="M48" s="20">
         <f>'[32]207'!$K$16</f>
@@ -8880,7 +9067,7 @@
       </c>
       <c r="G49" s="19">
         <f t="shared" si="4"/>
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H49" s="33">
         <f>'[33]208'!$K$10</f>
@@ -8888,19 +9075,19 @@
       </c>
       <c r="I49" s="33">
         <f>'[33]208'!$K$12</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J49" s="35">
         <f>'[33]208'!$K$13</f>
-        <v>16800</v>
+        <v>15400</v>
       </c>
       <c r="K49" s="35">
         <f>'[33]208'!$K$14</f>
-        <v>14800.790431951375</v>
+        <v>13697.569400122526</v>
       </c>
       <c r="L49" s="37">
         <f>'[33]208'!$K$15</f>
-        <v>5199.2095680486254</v>
+        <v>6302.4305998774744</v>
       </c>
       <c r="M49" s="22">
         <f>'[33]208'!$K$16</f>
@@ -9000,7 +9187,7 @@
       </c>
       <c r="G51" s="19">
         <f t="shared" si="4"/>
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H51" s="33">
         <f>'[11]210'!$K$10</f>
@@ -9008,19 +9195,19 @@
       </c>
       <c r="I51" s="33">
         <f>'[11]210'!$K$12</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J51" s="35">
         <f>'[11]210'!$K$13</f>
-        <v>16800</v>
+        <v>15400</v>
       </c>
       <c r="K51" s="35">
         <f>'[11]210'!$K$14</f>
-        <v>14800.790431951375</v>
+        <v>13697.569400122526</v>
       </c>
       <c r="L51" s="37">
         <f>'[11]210'!$K$15</f>
-        <v>5199.2095680486254</v>
+        <v>6302.4305998774744</v>
       </c>
       <c r="M51" s="22">
         <f>'[11]210'!$K$16</f>
@@ -9060,7 +9247,7 @@
       </c>
       <c r="G52" s="19">
         <f t="shared" si="4"/>
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="H52" s="36">
         <f>'[34]211'!$K$10</f>
@@ -9068,19 +9255,19 @@
       </c>
       <c r="I52" s="36">
         <f>'[34]211'!$K$12</f>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J52" s="39">
         <f>'[34]211'!$K$13</f>
-        <v>18200</v>
+        <v>15400</v>
       </c>
       <c r="K52" s="39">
         <f>'[34]211'!$K$14</f>
-        <v>15882.325006125111</v>
+        <v>13697.569400122526</v>
       </c>
       <c r="L52" s="40">
         <f>'[34]211'!$K$15</f>
-        <v>4117.674993874889</v>
+        <v>6302.4305998774744</v>
       </c>
       <c r="M52" s="20">
         <f>'[34]211'!$K$16</f>
@@ -9120,7 +9307,7 @@
       </c>
       <c r="G53" s="19">
         <f t="shared" si="4"/>
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="H53" s="33">
         <f>'[35]212'!$K$10</f>
@@ -9128,19 +9315,19 @@
       </c>
       <c r="I53" s="33">
         <f>'[35]212'!$K$12</f>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J53" s="35">
         <f>'[35]212'!$K$13</f>
-        <v>18200</v>
+        <v>15400</v>
       </c>
       <c r="K53" s="35">
         <f>'[35]212'!$K$14</f>
-        <v>15882.325006125111</v>
+        <v>13697.569400122526</v>
       </c>
       <c r="L53" s="37">
         <f>'[35]212'!$K$15</f>
-        <v>4117.674993874889</v>
+        <v>6302.4305998774744</v>
       </c>
       <c r="M53" s="22">
         <f>'[35]212'!$K$16</f>
@@ -9180,7 +9367,7 @@
       </c>
       <c r="G54" s="19">
         <f t="shared" si="4"/>
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H54" s="36">
         <f>'[17]213'!$K$10</f>
@@ -9188,19 +9375,19 @@
       </c>
       <c r="I54" s="36">
         <f>'[17]213'!$K$12</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J54" s="39">
         <f>'[17]213'!$K$13</f>
-        <v>9100</v>
+        <v>8400</v>
       </c>
       <c r="K54" s="39">
         <f>'[17]213'!$K$14</f>
-        <v>7941.1625030625555</v>
+        <v>7400.3952159756873</v>
       </c>
       <c r="L54" s="40">
         <f>'[17]213'!$K$15</f>
-        <v>2058.8374969374445</v>
+        <v>2599.6047840243127</v>
       </c>
       <c r="M54" s="20">
         <f>'[17]213'!$K$16</f>
@@ -9240,7 +9427,7 @@
       </c>
       <c r="G55" s="19">
         <f t="shared" si="4"/>
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H55" s="33">
         <f>'[36]214'!$K$10</f>
@@ -9248,19 +9435,19 @@
       </c>
       <c r="I55" s="33">
         <f>'[36]214'!$K$12</f>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J55" s="35">
         <f>'[36]214'!$K$13</f>
-        <v>19600</v>
+        <v>16800</v>
       </c>
       <c r="K55" s="35">
         <f>'[36]214'!$K$14</f>
-        <v>16942.599422027139</v>
+        <v>14800.790431951375</v>
       </c>
       <c r="L55" s="37">
         <f>'[36]214'!$K$15</f>
-        <v>3057.4005779728614</v>
+        <v>5199.2095680486254</v>
       </c>
       <c r="M55" s="22">
         <f>'[36]214'!$K$16</f>
@@ -9300,7 +9487,7 @@
       </c>
       <c r="G56" s="19">
         <f t="shared" si="4"/>
-        <v>56</v>
+        <v>45</v>
       </c>
       <c r="H56" s="36">
         <f>'[37]215'!$K$10</f>
@@ -9308,19 +9495,19 @@
       </c>
       <c r="I56" s="36">
         <f>'[37]215'!$K$12</f>
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="J56" s="39">
         <f>'[37]215'!$K$13</f>
-        <v>16800</v>
+        <v>13500</v>
       </c>
       <c r="K56" s="39">
         <f>'[37]215'!$K$14</f>
-        <v>14758.991922004241</v>
+        <v>12154.574982735843</v>
       </c>
       <c r="L56" s="40">
         <f>'[37]215'!$K$15</f>
-        <v>5241.0080779957589</v>
+        <v>7845.4250172641568</v>
       </c>
       <c r="M56" s="20">
         <f>'[37]215'!$K$16</f>
@@ -9360,7 +9547,7 @@
       </c>
       <c r="G57" s="19">
         <f t="shared" si="4"/>
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H57" s="33">
         <f>'[13]216'!$K$10</f>
@@ -9368,19 +9555,19 @@
       </c>
       <c r="I57" s="33">
         <f>'[13]216'!$K$12</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J57" s="35">
         <f>'[13]216'!$K$13</f>
-        <v>27000</v>
+        <v>24000</v>
       </c>
       <c r="K57" s="35">
         <f>'[13]216'!$K$14</f>
-        <v>23442.585668039574</v>
+        <v>21127.778238971867</v>
       </c>
       <c r="L57" s="37">
         <f>'[13]216'!$K$15</f>
-        <v>6557.4143319604264</v>
+        <v>8872.2217610281332</v>
       </c>
       <c r="M57" s="22">
         <f>'[13]216'!$K$16</f>
@@ -9420,7 +9607,7 @@
       </c>
       <c r="G58" s="19">
         <f t="shared" si="4"/>
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H58" s="36">
         <f>'[38]217'!$K$10</f>
@@ -9428,19 +9615,19 @@
       </c>
       <c r="I58" s="36">
         <f>'[38]217'!$K$12</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J58" s="39">
         <f>'[38]217'!$K$13</f>
-        <v>29400</v>
+        <v>27300</v>
       </c>
       <c r="K58" s="39">
         <f>'[38]217'!$K$14</f>
-        <v>25413.899133040686</v>
+        <v>23823.487509187638</v>
       </c>
       <c r="L58" s="40">
         <f>'[38]217'!$K$15</f>
-        <v>4586.1008669593139</v>
+        <v>6176.5124908123616</v>
       </c>
       <c r="M58" s="20">
         <f>'[38]217'!$K$16</f>
@@ -9480,7 +9667,7 @@
       </c>
       <c r="G59" s="19">
         <f t="shared" si="4"/>
-        <v>99</v>
+        <v>91</v>
       </c>
       <c r="H59" s="33">
         <f>'[14]218'!$K$10</f>
@@ -9488,19 +9675,19 @@
       </c>
       <c r="I59" s="33">
         <f>'[14]218'!$K$12</f>
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="J59" s="35">
         <f>'[14]218'!$K$13</f>
-        <v>29700</v>
+        <v>27300</v>
       </c>
       <c r="K59" s="35">
         <f>'[14]218'!$K$14</f>
-        <v>25524.137134582503</v>
+        <v>23740.683254256033</v>
       </c>
       <c r="L59" s="37">
         <f>'[14]218'!$K$15</f>
-        <v>4475.8628654174972</v>
+        <v>6259.3167457439667</v>
       </c>
       <c r="M59" s="22">
         <f>'[14]218'!$K$16</f>
@@ -9540,7 +9727,7 @@
       </c>
       <c r="G60" s="19">
         <f t="shared" si="4"/>
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H60" s="36">
         <f>'[17]219'!$K$10</f>
@@ -9548,19 +9735,19 @@
       </c>
       <c r="I60" s="36">
         <f>'[17]219'!$K$12</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J60" s="39">
         <f>'[17]219'!$K$13</f>
-        <v>31500</v>
+        <v>29400</v>
       </c>
       <c r="K60" s="39">
         <f>'[17]219'!$K$14</f>
-        <v>26973.047398654715</v>
+        <v>25413.899133040686</v>
       </c>
       <c r="L60" s="40">
         <f>'[17]219'!$K$15</f>
-        <v>3026.9526013452851</v>
+        <v>4586.1008669593139</v>
       </c>
       <c r="M60" s="20">
         <f>'[17]219'!$K$16</f>
@@ -9600,7 +9787,7 @@
       </c>
       <c r="G61" s="19">
         <f t="shared" si="4"/>
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H61" s="33">
         <f>'[39]220'!$K$10</f>
@@ -9608,19 +9795,19 @@
       </c>
       <c r="I61" s="33">
         <f>'[39]220'!$K$12</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J61" s="35">
         <f>'[39]220'!$K$13</f>
-        <v>5250</v>
+        <v>4900</v>
       </c>
       <c r="K61" s="35">
         <f>'[39]220'!$K$14</f>
-        <v>4495.5078997757882</v>
+        <v>4235.6498555067847</v>
       </c>
       <c r="L61" s="37">
         <f>'[39]220'!$K$15</f>
-        <v>504.49210022421175</v>
+        <v>764.35014449321534</v>
       </c>
       <c r="M61" s="22">
         <f>'[39]220'!$K$16</f>
@@ -9660,7 +9847,7 @@
       </c>
       <c r="G62" s="19">
         <f t="shared" si="4"/>
-        <v>108</v>
+        <v>100</v>
       </c>
       <c r="H62" s="36">
         <f>'[21]221'!$K$10</f>
@@ -9668,19 +9855,19 @@
       </c>
       <c r="I62" s="36">
         <f>'[21]221'!$K$12</f>
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="J62" s="39">
         <f>'[21]221'!$K$13</f>
-        <v>21600</v>
+        <v>20000</v>
       </c>
       <c r="K62" s="39">
         <f>'[21]221'!$K$14</f>
-        <v>18318.802096717634</v>
+        <v>17162.643827501808</v>
       </c>
       <c r="L62" s="40">
         <f>'[21]221'!$K$15</f>
-        <v>1681.1979032823656</v>
+        <v>2837.3561724981919</v>
       </c>
       <c r="M62" s="20">
         <f>'[21]221'!$K$16</f>
@@ -9720,7 +9907,7 @@
       </c>
       <c r="G63" s="19">
         <f t="shared" si="4"/>
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="H63" s="33">
         <f>'[40]222'!$K$10</f>
@@ -9728,19 +9915,19 @@
       </c>
       <c r="I63" s="33">
         <f>'[40]222'!$K$12</f>
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="J63" s="35">
         <f>'[40]222'!$K$13</f>
-        <v>10650</v>
+        <v>10200</v>
       </c>
       <c r="K63" s="35">
         <f>'[40]222'!$K$14</f>
-        <v>9051.3676217399407</v>
+        <v>8726.2439243020872</v>
       </c>
       <c r="L63" s="37">
         <f>'[40]222'!$K$15</f>
-        <v>948.63237826005934</v>
+        <v>1273.7560756979128</v>
       </c>
       <c r="M63" s="22">
         <f>'[40]222'!$K$16</f>
@@ -9780,7 +9967,7 @@
       </c>
       <c r="G64" s="19">
         <f t="shared" si="4"/>
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H64" s="36">
         <f>'[41]223'!$K$10</f>
@@ -9788,19 +9975,19 @@
       </c>
       <c r="I64" s="36">
         <f>'[41]223'!$K$12</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J64" s="39">
         <f>'[41]223'!$K$13</f>
-        <v>67200</v>
+        <v>63000</v>
       </c>
       <c r="K64" s="39">
         <f>'[41]223'!$K$14</f>
-        <v>57003.093724766775</v>
+        <v>53946.09479730943</v>
       </c>
       <c r="L64" s="40">
         <f>'[41]223'!$K$15</f>
-        <v>2996.9062752332247</v>
+        <v>6053.9052026905701</v>
       </c>
       <c r="M64" s="20">
         <f>'[41]223'!$K$16</f>
@@ -9840,7 +10027,7 @@
       </c>
       <c r="G65" s="19">
         <f t="shared" si="4"/>
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="H65" s="33">
         <f>'[4]224'!$K$10</f>
@@ -9848,27 +10035,27 @@
       </c>
       <c r="I65" s="33">
         <f>'[4]224'!$K$12</f>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J65" s="35">
         <f>'[4]224'!$K$13</f>
-        <v>60000</v>
+        <v>57500</v>
       </c>
       <c r="K65" s="35">
         <f>'[4]224'!$K$14</f>
-        <v>60000</v>
+        <v>48267.790199566742</v>
       </c>
       <c r="L65" s="37">
         <f>'[4]224'!$K$15</f>
-        <v>0</v>
-      </c>
-      <c r="M65" s="22" t="str">
+        <v>1732.2098004332584</v>
+      </c>
+      <c r="M65" s="22">
         <f>'[4]224'!$K$16</f>
-        <v/>
-      </c>
-      <c r="N65" s="23" t="str">
+        <v>46288</v>
+      </c>
+      <c r="N65" s="23">
         <f>'[4]224'!$K$17</f>
-        <v/>
+        <v>46408</v>
       </c>
       <c r="P65" s="43">
         <v>3500</v>
@@ -9900,7 +10087,7 @@
       </c>
       <c r="G66" s="19">
         <f t="shared" si="4"/>
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H66" s="36">
         <f>'[16]225'!$K$10</f>
@@ -9908,27 +10095,27 @@
       </c>
       <c r="I66" s="36">
         <f>'[16]225'!$K$12</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J66" s="39">
         <f>'[16]225'!$K$13</f>
-        <v>23800</v>
+        <v>22400</v>
       </c>
       <c r="K66" s="39">
         <f>'[16]225'!$K$14</f>
-        <v>23800</v>
+        <v>19001.031241588931</v>
       </c>
       <c r="L66" s="40">
         <f>'[16]225'!$K$15</f>
-        <v>0</v>
-      </c>
-      <c r="M66" s="20" t="str">
+        <v>998.96875841106885</v>
+      </c>
+      <c r="M66" s="20">
         <f>'[16]225'!$K$16</f>
-        <v/>
-      </c>
-      <c r="N66" s="21" t="str">
+        <v>46290</v>
+      </c>
+      <c r="N66" s="21">
         <f>'[16]225'!$K$17</f>
-        <v/>
+        <v>46409</v>
       </c>
       <c r="P66" s="43">
         <v>1400</v>
@@ -9960,7 +10147,7 @@
       </c>
       <c r="G67" s="19">
         <f t="shared" si="4"/>
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H67" s="33">
         <f>'[10]226'!$K$10</f>
@@ -9968,27 +10155,27 @@
       </c>
       <c r="I67" s="33">
         <f>'[10]226'!$K$12</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J67" s="35">
         <f>'[10]226'!$K$13</f>
-        <v>29750</v>
+        <v>28000</v>
       </c>
       <c r="K67" s="35">
         <f>'[10]226'!$K$14</f>
-        <v>29750</v>
+        <v>23751.28905198615</v>
       </c>
       <c r="L67" s="37">
         <f>'[10]226'!$K$15</f>
-        <v>0</v>
-      </c>
-      <c r="M67" s="22" t="str">
+        <v>1248.7109480138497</v>
+      </c>
+      <c r="M67" s="22">
         <f>'[10]226'!$K$16</f>
-        <v/>
-      </c>
-      <c r="N67" s="23" t="str">
+        <v>46287</v>
+      </c>
+      <c r="N67" s="23">
         <f>'[10]226'!$K$17</f>
-        <v/>
+        <v>46406</v>
       </c>
       <c r="P67" s="43">
         <v>1750</v>
@@ -9999,66 +10186,180 @@
         <f t="shared" si="1"/>
         <v>227</v>
       </c>
-      <c r="B68" s="36"/>
-      <c r="C68" s="36"/>
-      <c r="D68" s="38"/>
-      <c r="E68" s="39"/>
-      <c r="F68" s="36"/>
-      <c r="G68" s="19" t="str">
+      <c r="B68" s="36" t="str">
+        <f>'[42]227'!$K$3</f>
+        <v>Tina_devi</v>
+      </c>
+      <c r="C68" s="36" t="s">
+        <v>6</v>
+      </c>
+      <c r="D68" s="38" t="str">
+        <f>'[42]227'!$K$2</f>
+        <v>L10000D120-Tina_devi-N227</v>
+      </c>
+      <c r="E68" s="39">
+        <f>'[42]227'!$K$7</f>
+        <v>10000</v>
+      </c>
+      <c r="F68" s="36">
+        <f>'[42]227'!$K$9</f>
+        <v>100</v>
+      </c>
+      <c r="G68" s="19">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H68" s="36"/>
-      <c r="I68" s="36"/>
-      <c r="J68" s="39"/>
-      <c r="K68" s="39"/>
-      <c r="L68" s="40"/>
-      <c r="M68" s="20"/>
-      <c r="N68" s="21"/>
+        <v>116</v>
+      </c>
+      <c r="H68" s="36">
+        <f>'[42]227'!$K$10</f>
+        <v>120</v>
+      </c>
+      <c r="I68" s="36">
+        <f>'[42]227'!$K$12</f>
+        <v>4</v>
+      </c>
+      <c r="J68" s="39">
+        <f>'[42]227'!$K$13</f>
+        <v>11600</v>
+      </c>
+      <c r="K68" s="39">
+        <f>'[42]227'!$K$14</f>
+        <v>9723.2779831622556</v>
+      </c>
+      <c r="L68" s="40">
+        <f>'[42]227'!$K$15</f>
+        <v>276.72201683774438</v>
+      </c>
+      <c r="M68" s="20">
+        <f>'[42]227'!$K$16</f>
+        <v>46291</v>
+      </c>
+      <c r="N68" s="21">
+        <f>'[42]227'!$K$17</f>
+        <v>46411</v>
+      </c>
+      <c r="P68" s="43">
+        <v>700</v>
+      </c>
     </row>
     <row r="69" spans="1:16" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A69" s="33">
         <f t="shared" si="1"/>
         <v>228</v>
       </c>
-      <c r="B69" s="33"/>
-      <c r="C69" s="33"/>
-      <c r="D69" s="34"/>
-      <c r="E69" s="35"/>
-      <c r="F69" s="33"/>
-      <c r="G69" s="19" t="str">
+      <c r="B69" s="33" t="str">
+        <f>'[22]228'!$K$3</f>
+        <v>L_Gomti</v>
+      </c>
+      <c r="C69" s="33" t="s">
+        <v>6</v>
+      </c>
+      <c r="D69" s="34" t="str">
+        <f>'[22]228'!$K$2</f>
+        <v>L30000W17-L_Gomti-N228</v>
+      </c>
+      <c r="E69" s="35">
+        <f>'[22]228'!$K$7</f>
+        <v>30000</v>
+      </c>
+      <c r="F69" s="33">
+        <f>'[22]228'!$K$9</f>
+        <v>2100</v>
+      </c>
+      <c r="G69" s="19">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H69" s="33"/>
-      <c r="I69" s="33"/>
-      <c r="J69" s="35"/>
-      <c r="K69" s="35"/>
-      <c r="L69" s="37"/>
-      <c r="M69" s="22"/>
-      <c r="N69" s="23"/>
+        <v>17</v>
+      </c>
+      <c r="H69" s="33">
+        <f>'[22]228'!$K$10</f>
+        <v>17</v>
+      </c>
+      <c r="I69" s="33">
+        <f>'[22]228'!$K$12</f>
+        <v>0</v>
+      </c>
+      <c r="J69" s="35">
+        <f>'[22]228'!$K$13</f>
+        <v>35700</v>
+      </c>
+      <c r="K69" s="35">
+        <f>'[22]228'!$K$14</f>
+        <v>35700</v>
+      </c>
+      <c r="L69" s="37">
+        <f>'[22]228'!$K$15</f>
+        <v>0</v>
+      </c>
+      <c r="M69" s="22" t="str">
+        <f>'[22]228'!$K$16</f>
+        <v/>
+      </c>
+      <c r="N69" s="23" t="str">
+        <f>'[22]228'!$K$17</f>
+        <v/>
+      </c>
+      <c r="P69" s="43">
+        <v>2100</v>
+      </c>
     </row>
     <row r="70" spans="1:16" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A70" s="36">
         <f t="shared" si="1"/>
         <v>229</v>
       </c>
-      <c r="B70" s="36"/>
-      <c r="C70" s="36"/>
-      <c r="D70" s="38"/>
-      <c r="E70" s="39"/>
-      <c r="F70" s="36"/>
-      <c r="G70" s="19" t="str">
+      <c r="B70" s="36" t="str">
+        <f>'[27]229'!$K$3</f>
+        <v>Salam_Echal</v>
+      </c>
+      <c r="C70" s="36" t="s">
+        <v>6</v>
+      </c>
+      <c r="D70" s="38" t="str">
+        <f ca="1">'[27]229'!$K$2</f>
+        <v>L30000W17-Salam_Echal-N229</v>
+      </c>
+      <c r="E70" s="39">
+        <f>'[27]229'!$K$7</f>
+        <v>30000</v>
+      </c>
+      <c r="F70" s="36">
+        <f>'[27]229'!$K$9</f>
+        <v>2100</v>
+      </c>
+      <c r="G70" s="19">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H70" s="36"/>
-      <c r="I70" s="36"/>
-      <c r="J70" s="39"/>
-      <c r="K70" s="39"/>
-      <c r="L70" s="40"/>
-      <c r="M70" s="20"/>
-      <c r="N70" s="21"/>
+        <v>17</v>
+      </c>
+      <c r="H70" s="36">
+        <f>'[27]229'!$K$10</f>
+        <v>17</v>
+      </c>
+      <c r="I70" s="36">
+        <f>'[27]229'!$K$12</f>
+        <v>0</v>
+      </c>
+      <c r="J70" s="39">
+        <f>'[27]229'!$K$13</f>
+        <v>35700</v>
+      </c>
+      <c r="K70" s="39">
+        <f>'[27]229'!$K$14</f>
+        <v>35700</v>
+      </c>
+      <c r="L70" s="40">
+        <f>'[27]229'!$K$15</f>
+        <v>0</v>
+      </c>
+      <c r="M70" s="20" t="str">
+        <f>'[27]229'!$K$16</f>
+        <v/>
+      </c>
+      <c r="N70" s="21" t="str">
+        <f>'[27]229'!$K$17</f>
+        <v/>
+      </c>
+      <c r="P70" s="43">
+        <v>2100</v>
+      </c>
     </row>
     <row r="71" spans="1:16" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A71" s="33">
@@ -18987,37 +19288,37 @@
       </c>
       <c r="B2" s="14" t="e">
         <f>IF(A2&lt;&gt;"",
-    SUMIFS([42]FinancingJournal!$E:$E,
-           [42]FinancingJournal!$C:$C,"Capital Injection",
-           [42]FinancingJournal!$A:$A,"&lt;="&amp;A2),
+    SUMIFS([43]FinancingJournal!$E:$E,
+           [43]FinancingJournal!$C:$C,"Capital Injection",
+           [43]FinancingJournal!$A:$A,"&lt;="&amp;A2),
     "")</f>
         <v>#VALUE!</v>
       </c>
       <c r="C2" s="15" t="e">
         <f>IF(A2&lt;&gt;"",
-    SUMIFS([42]InvestingJournal!$F:$F,
-           [42]InvestingJournal!$C:$C,"Izra Advance",
-           [42]InvestingJournal!$A:$A,"&lt;="&amp;A2),
+    SUMIFS([43]InvestingJournal!$F:$F,
+           [43]InvestingJournal!$C:$C,"Izra Advance",
+           [43]InvestingJournal!$A:$A,"&lt;="&amp;A2),
     "")</f>
         <v>#VALUE!</v>
       </c>
       <c r="D2" s="15" t="e">
         <f>IF(A2&lt;&gt;"",
-    SUMIFS([42]InvestingJournal!$F:$F,
-           [42]InvestingJournal!$C:$C,"Loan Advance",
-           [42]InvestingJournal!$A:$A,"&lt;="&amp;A2),
+    SUMIFS([43]InvestingJournal!$F:$F,
+           [43]InvestingJournal!$C:$C,"Loan Advance",
+           [43]InvestingJournal!$A:$A,"&lt;="&amp;A2),
     "")</f>
         <v>#VALUE!</v>
       </c>
       <c r="E2" s="15" t="e">
         <f>IF(A2&lt;&gt;"",
-    SUMIFS([42]FinancingJournal!$E:$E,
-           [42]FinancingJournal!$C:$C,"Borrowing",
-           [42]FinancingJournal!$A:$A,"&lt;="&amp;A2)
+    SUMIFS([43]FinancingJournal!$E:$E,
+           [43]FinancingJournal!$C:$C,"Borrowing",
+           [43]FinancingJournal!$A:$A,"&lt;="&amp;A2)
     +
-    SUMIFS([42]FinancingJournal!$E:$E,
-           [42]FinancingJournal!$C:$C,"Withdrawal",
-           [42]FinancingJournal!$A:$A,"&lt;="&amp;A2),
+    SUMIFS([43]FinancingJournal!$E:$E,
+           [43]FinancingJournal!$C:$C,"Withdrawal",
+           [43]FinancingJournal!$A:$A,"&lt;="&amp;A2),
     "")</f>
         <v>#VALUE!</v>
       </c>
@@ -19043,37 +19344,37 @@
       </c>
       <c r="B3" s="17" t="e">
         <f>IF(A3&lt;&gt;"",
-    SUMIFS([42]FinancingJournal!$E:$E,
-           [42]FinancingJournal!$C:$C,"Capital Injection",
-           [42]FinancingJournal!$A:$A,"&lt;="&amp;A3),
+    SUMIFS([43]FinancingJournal!$E:$E,
+           [43]FinancingJournal!$C:$C,"Capital Injection",
+           [43]FinancingJournal!$A:$A,"&lt;="&amp;A3),
     "")</f>
         <v>#VALUE!</v>
       </c>
       <c r="C3" s="18" t="e">
         <f>IF(A3&lt;&gt;"",
-    SUMIFS([42]InvestingJournal!$F:$F,
-           [42]InvestingJournal!$C:$C,"Izra Advance",
-           [42]InvestingJournal!$A:$A,"&lt;="&amp;A3),
+    SUMIFS([43]InvestingJournal!$F:$F,
+           [43]InvestingJournal!$C:$C,"Izra Advance",
+           [43]InvestingJournal!$A:$A,"&lt;="&amp;A3),
     "")</f>
         <v>#VALUE!</v>
       </c>
       <c r="D3" s="18" t="e">
         <f>IF(A3&lt;&gt;"",
-    SUMIFS([42]InvestingJournal!$F:$F,
-           [42]InvestingJournal!$C:$C,"Loan Advance",
-           [42]InvestingJournal!$A:$A,"&lt;="&amp;A3),
+    SUMIFS([43]InvestingJournal!$F:$F,
+           [43]InvestingJournal!$C:$C,"Loan Advance",
+           [43]InvestingJournal!$A:$A,"&lt;="&amp;A3),
     "")</f>
         <v>#VALUE!</v>
       </c>
       <c r="E3" s="18" t="e">
         <f>IF(A3&lt;&gt;"",
-    SUMIFS([42]FinancingJournal!$E:$E,
-           [42]FinancingJournal!$C:$C,"Borrowing",
-           [42]FinancingJournal!$A:$A,"&lt;="&amp;A3)
+    SUMIFS([43]FinancingJournal!$E:$E,
+           [43]FinancingJournal!$C:$C,"Borrowing",
+           [43]FinancingJournal!$A:$A,"&lt;="&amp;A3)
     +
-    SUMIFS([42]FinancingJournal!$E:$E,
-           [42]FinancingJournal!$C:$C,"Withdrawal",
-           [42]FinancingJournal!$A:$A,"&lt;="&amp;A3),
+    SUMIFS([43]FinancingJournal!$E:$E,
+           [43]FinancingJournal!$C:$C,"Withdrawal",
+           [43]FinancingJournal!$A:$A,"&lt;="&amp;A3),
     "")</f>
         <v>#VALUE!</v>
       </c>
@@ -19098,37 +19399,37 @@
       </c>
       <c r="B4" s="14" t="e">
         <f>IF(A4&lt;&gt;"",
-    SUMIFS([42]FinancingJournal!$E:$E,
-           [42]FinancingJournal!$C:$C,"Capital Injection",
-           [42]FinancingJournal!$A:$A,"&lt;="&amp;A4),
+    SUMIFS([43]FinancingJournal!$E:$E,
+           [43]FinancingJournal!$C:$C,"Capital Injection",
+           [43]FinancingJournal!$A:$A,"&lt;="&amp;A4),
     "")</f>
         <v>#VALUE!</v>
       </c>
       <c r="C4" s="15" t="e">
         <f>IF(A4&lt;&gt;"",
-    SUMIFS([42]InvestingJournal!$F:$F,
-           [42]InvestingJournal!$C:$C,"Izra Advance",
-           [42]InvestingJournal!$A:$A,"&lt;="&amp;A4),
+    SUMIFS([43]InvestingJournal!$F:$F,
+           [43]InvestingJournal!$C:$C,"Izra Advance",
+           [43]InvestingJournal!$A:$A,"&lt;="&amp;A4),
     "")</f>
         <v>#VALUE!</v>
       </c>
       <c r="D4" s="15" t="e">
         <f>IF(A4&lt;&gt;"",
-    SUMIFS([42]InvestingJournal!$F:$F,
-           [42]InvestingJournal!$C:$C,"Loan Advance",
-           [42]InvestingJournal!$A:$A,"&lt;="&amp;A4),
+    SUMIFS([43]InvestingJournal!$F:$F,
+           [43]InvestingJournal!$C:$C,"Loan Advance",
+           [43]InvestingJournal!$A:$A,"&lt;="&amp;A4),
     "")</f>
         <v>#VALUE!</v>
       </c>
       <c r="E4" s="15" t="e">
         <f>IF(A4&lt;&gt;"",
-    SUMIFS([42]FinancingJournal!$E:$E,
-           [42]FinancingJournal!$C:$C,"Borrowing",
-           [42]FinancingJournal!$A:$A,"&lt;="&amp;A4)
+    SUMIFS([43]FinancingJournal!$E:$E,
+           [43]FinancingJournal!$C:$C,"Borrowing",
+           [43]FinancingJournal!$A:$A,"&lt;="&amp;A4)
     +
-    SUMIFS([42]FinancingJournal!$E:$E,
-           [42]FinancingJournal!$C:$C,"Withdrawal",
-           [42]FinancingJournal!$A:$A,"&lt;="&amp;A4),
+    SUMIFS([43]FinancingJournal!$E:$E,
+           [43]FinancingJournal!$C:$C,"Withdrawal",
+           [43]FinancingJournal!$A:$A,"&lt;="&amp;A4),
     "")</f>
         <v>#VALUE!</v>
       </c>
@@ -19154,37 +19455,37 @@
       </c>
       <c r="B5" s="17" t="e">
         <f>IF(A5&lt;&gt;"",
-    SUMIFS([42]FinancingJournal!$E:$E,
-           [42]FinancingJournal!$C:$C,"Capital Injection",
-           [42]FinancingJournal!$A:$A,"&lt;="&amp;A5),
+    SUMIFS([43]FinancingJournal!$E:$E,
+           [43]FinancingJournal!$C:$C,"Capital Injection",
+           [43]FinancingJournal!$A:$A,"&lt;="&amp;A5),
     "")</f>
         <v>#VALUE!</v>
       </c>
       <c r="C5" s="18" t="e">
         <f>IF(A5&lt;&gt;"",
-    SUMIFS([42]InvestingJournal!$F:$F,
-           [42]InvestingJournal!$C:$C,"Izra Advance",
-           [42]InvestingJournal!$A:$A,"&lt;="&amp;A5),
+    SUMIFS([43]InvestingJournal!$F:$F,
+           [43]InvestingJournal!$C:$C,"Izra Advance",
+           [43]InvestingJournal!$A:$A,"&lt;="&amp;A5),
     "")</f>
         <v>#VALUE!</v>
       </c>
       <c r="D5" s="18" t="e">
         <f>IF(A5&lt;&gt;"",
-    SUMIFS([42]InvestingJournal!$F:$F,
-           [42]InvestingJournal!$C:$C,"Loan Advance",
-           [42]InvestingJournal!$A:$A,"&lt;="&amp;A5),
+    SUMIFS([43]InvestingJournal!$F:$F,
+           [43]InvestingJournal!$C:$C,"Loan Advance",
+           [43]InvestingJournal!$A:$A,"&lt;="&amp;A5),
     "")</f>
         <v>#VALUE!</v>
       </c>
       <c r="E5" s="18" t="e">
         <f>IF(A5&lt;&gt;"",
-    SUMIFS([42]FinancingJournal!$E:$E,
-           [42]FinancingJournal!$C:$C,"Borrowing",
-           [42]FinancingJournal!$A:$A,"&lt;="&amp;A5)
+    SUMIFS([43]FinancingJournal!$E:$E,
+           [43]FinancingJournal!$C:$C,"Borrowing",
+           [43]FinancingJournal!$A:$A,"&lt;="&amp;A5)
     +
-    SUMIFS([42]FinancingJournal!$E:$E,
-           [42]FinancingJournal!$C:$C,"Withdrawal",
-           [42]FinancingJournal!$A:$A,"&lt;="&amp;A5),
+    SUMIFS([43]FinancingJournal!$E:$E,
+           [43]FinancingJournal!$C:$C,"Withdrawal",
+           [43]FinancingJournal!$A:$A,"&lt;="&amp;A5),
     "")</f>
         <v>#VALUE!</v>
       </c>
@@ -19209,37 +19510,37 @@
       </c>
       <c r="B6" s="14" t="e">
         <f>IF(A6&lt;&gt;"",
-    SUMIFS([42]FinancingJournal!$E:$E,
-           [42]FinancingJournal!$C:$C,"Capital Injection",
-           [42]FinancingJournal!$A:$A,"&lt;="&amp;A6),
+    SUMIFS([43]FinancingJournal!$E:$E,
+           [43]FinancingJournal!$C:$C,"Capital Injection",
+           [43]FinancingJournal!$A:$A,"&lt;="&amp;A6),
     "")</f>
         <v>#VALUE!</v>
       </c>
       <c r="C6" s="15" t="e">
         <f>IF(A6&lt;&gt;"",
-    SUMIFS([42]InvestingJournal!$F:$F,
-           [42]InvestingJournal!$C:$C,"Izra Advance",
-           [42]InvestingJournal!$A:$A,"&lt;="&amp;A6),
+    SUMIFS([43]InvestingJournal!$F:$F,
+           [43]InvestingJournal!$C:$C,"Izra Advance",
+           [43]InvestingJournal!$A:$A,"&lt;="&amp;A6),
     "")</f>
         <v>#VALUE!</v>
       </c>
       <c r="D6" s="15" t="e">
         <f>IF(A6&lt;&gt;"",
-    SUMIFS([42]InvestingJournal!$F:$F,
-           [42]InvestingJournal!$C:$C,"Loan Advance",
-           [42]InvestingJournal!$A:$A,"&lt;="&amp;A6),
+    SUMIFS([43]InvestingJournal!$F:$F,
+           [43]InvestingJournal!$C:$C,"Loan Advance",
+           [43]InvestingJournal!$A:$A,"&lt;="&amp;A6),
     "")</f>
         <v>#VALUE!</v>
       </c>
       <c r="E6" s="15" t="e">
         <f>IF(A6&lt;&gt;"",
-    SUMIFS([42]FinancingJournal!$E:$E,
-           [42]FinancingJournal!$C:$C,"Borrowing",
-           [42]FinancingJournal!$A:$A,"&lt;="&amp;A6)
+    SUMIFS([43]FinancingJournal!$E:$E,
+           [43]FinancingJournal!$C:$C,"Borrowing",
+           [43]FinancingJournal!$A:$A,"&lt;="&amp;A6)
     +
-    SUMIFS([42]FinancingJournal!$E:$E,
-           [42]FinancingJournal!$C:$C,"Withdrawal",
-           [42]FinancingJournal!$A:$A,"&lt;="&amp;A6),
+    SUMIFS([43]FinancingJournal!$E:$E,
+           [43]FinancingJournal!$C:$C,"Withdrawal",
+           [43]FinancingJournal!$A:$A,"&lt;="&amp;A6),
     "")</f>
         <v>#VALUE!</v>
       </c>
@@ -19265,37 +19566,37 @@
       </c>
       <c r="B7" s="17" t="e">
         <f>IF(A7&lt;&gt;"",
-    SUMIFS([42]FinancingJournal!$E:$E,
-           [42]FinancingJournal!$C:$C,"Capital Injection",
-           [42]FinancingJournal!$A:$A,"&lt;="&amp;A7),
+    SUMIFS([43]FinancingJournal!$E:$E,
+           [43]FinancingJournal!$C:$C,"Capital Injection",
+           [43]FinancingJournal!$A:$A,"&lt;="&amp;A7),
     "")</f>
         <v>#VALUE!</v>
       </c>
       <c r="C7" s="18" t="e">
         <f>IF(A7&lt;&gt;"",
-    SUMIFS([42]InvestingJournal!$F:$F,
-           [42]InvestingJournal!$C:$C,"Izra Advance",
-           [42]InvestingJournal!$A:$A,"&lt;="&amp;A7),
+    SUMIFS([43]InvestingJournal!$F:$F,
+           [43]InvestingJournal!$C:$C,"Izra Advance",
+           [43]InvestingJournal!$A:$A,"&lt;="&amp;A7),
     "")</f>
         <v>#VALUE!</v>
       </c>
       <c r="D7" s="18" t="e">
         <f>IF(A7&lt;&gt;"",
-    SUMIFS([42]InvestingJournal!$F:$F,
-           [42]InvestingJournal!$C:$C,"Loan Advance",
-           [42]InvestingJournal!$A:$A,"&lt;="&amp;A7),
+    SUMIFS([43]InvestingJournal!$F:$F,
+           [43]InvestingJournal!$C:$C,"Loan Advance",
+           [43]InvestingJournal!$A:$A,"&lt;="&amp;A7),
     "")</f>
         <v>#VALUE!</v>
       </c>
       <c r="E7" s="18" t="e">
         <f>IF(A7&lt;&gt;"",
-    SUMIFS([42]FinancingJournal!$E:$E,
-           [42]FinancingJournal!$C:$C,"Borrowing",
-           [42]FinancingJournal!$A:$A,"&lt;="&amp;A7)
+    SUMIFS([43]FinancingJournal!$E:$E,
+           [43]FinancingJournal!$C:$C,"Borrowing",
+           [43]FinancingJournal!$A:$A,"&lt;="&amp;A7)
     +
-    SUMIFS([42]FinancingJournal!$E:$E,
-           [42]FinancingJournal!$C:$C,"Withdrawal",
-           [42]FinancingJournal!$A:$A,"&lt;="&amp;A7),
+    SUMIFS([43]FinancingJournal!$E:$E,
+           [43]FinancingJournal!$C:$C,"Withdrawal",
+           [43]FinancingJournal!$A:$A,"&lt;="&amp;A7),
     "")</f>
         <v>#VALUE!</v>
       </c>
@@ -19322,37 +19623,37 @@
       </c>
       <c r="B8" s="14" t="e">
         <f>IF(A8&lt;&gt;"",
-    SUMIFS([42]FinancingJournal!$E:$E,
-           [42]FinancingJournal!$C:$C,"Capital Injection",
-           [42]FinancingJournal!$A:$A,"&lt;="&amp;A8),
+    SUMIFS([43]FinancingJournal!$E:$E,
+           [43]FinancingJournal!$C:$C,"Capital Injection",
+           [43]FinancingJournal!$A:$A,"&lt;="&amp;A8),
     "")</f>
         <v>#VALUE!</v>
       </c>
       <c r="C8" s="15" t="e">
         <f>IF(A8&lt;&gt;"",
-    SUMIFS([42]InvestingJournal!$F:$F,
-           [42]InvestingJournal!$C:$C,"Izra Advance",
-           [42]InvestingJournal!$A:$A,"&lt;="&amp;A8),
+    SUMIFS([43]InvestingJournal!$F:$F,
+           [43]InvestingJournal!$C:$C,"Izra Advance",
+           [43]InvestingJournal!$A:$A,"&lt;="&amp;A8),
     "")</f>
         <v>#VALUE!</v>
       </c>
       <c r="D8" s="15" t="e">
         <f>IF(A8&lt;&gt;"",
-    SUMIFS([42]InvestingJournal!$F:$F,
-           [42]InvestingJournal!$C:$C,"Loan Advance",
-           [42]InvestingJournal!$A:$A,"&lt;="&amp;A8),
+    SUMIFS([43]InvestingJournal!$F:$F,
+           [43]InvestingJournal!$C:$C,"Loan Advance",
+           [43]InvestingJournal!$A:$A,"&lt;="&amp;A8),
     "")</f>
         <v>#VALUE!</v>
       </c>
       <c r="E8" s="15" t="e">
         <f>IF(A8&lt;&gt;"",
-    SUMIFS([42]FinancingJournal!$E:$E,
-           [42]FinancingJournal!$C:$C,"Borrowing",
-           [42]FinancingJournal!$A:$A,"&lt;="&amp;A8)
+    SUMIFS([43]FinancingJournal!$E:$E,
+           [43]FinancingJournal!$C:$C,"Borrowing",
+           [43]FinancingJournal!$A:$A,"&lt;="&amp;A8)
     +
-    SUMIFS([42]FinancingJournal!$E:$E,
-           [42]FinancingJournal!$C:$C,"Withdrawal",
-           [42]FinancingJournal!$A:$A,"&lt;="&amp;A8),
+    SUMIFS([43]FinancingJournal!$E:$E,
+           [43]FinancingJournal!$C:$C,"Withdrawal",
+           [43]FinancingJournal!$A:$A,"&lt;="&amp;A8),
     "")</f>
         <v>#VALUE!</v>
       </c>
@@ -19376,37 +19677,37 @@
       </c>
       <c r="B9" s="17" t="e">
         <f>IF(A9&lt;&gt;"",
-    SUMIFS([42]FinancingJournal!$E:$E,
-           [42]FinancingJournal!$C:$C,"Capital Injection",
-           [42]FinancingJournal!$A:$A,"&lt;="&amp;A9),
+    SUMIFS([43]FinancingJournal!$E:$E,
+           [43]FinancingJournal!$C:$C,"Capital Injection",
+           [43]FinancingJournal!$A:$A,"&lt;="&amp;A9),
     "")</f>
         <v>#VALUE!</v>
       </c>
       <c r="C9" s="18" t="e">
         <f>IF(A9&lt;&gt;"",
-    SUMIFS([42]InvestingJournal!$F:$F,
-           [42]InvestingJournal!$C:$C,"Izra Advance",
-           [42]InvestingJournal!$A:$A,"&lt;="&amp;A9),
+    SUMIFS([43]InvestingJournal!$F:$F,
+           [43]InvestingJournal!$C:$C,"Izra Advance",
+           [43]InvestingJournal!$A:$A,"&lt;="&amp;A9),
     "")</f>
         <v>#VALUE!</v>
       </c>
       <c r="D9" s="18" t="e">
         <f>IF(A9&lt;&gt;"",
-    SUMIFS([42]InvestingJournal!$F:$F,
-           [42]InvestingJournal!$C:$C,"Loan Advance",
-           [42]InvestingJournal!$A:$A,"&lt;="&amp;A9),
+    SUMIFS([43]InvestingJournal!$F:$F,
+           [43]InvestingJournal!$C:$C,"Loan Advance",
+           [43]InvestingJournal!$A:$A,"&lt;="&amp;A9),
     "")</f>
         <v>#VALUE!</v>
       </c>
       <c r="E9" s="18" t="e">
         <f>IF(A9&lt;&gt;"",
-    SUMIFS([42]FinancingJournal!$E:$E,
-           [42]FinancingJournal!$C:$C,"Borrowing",
-           [42]FinancingJournal!$A:$A,"&lt;="&amp;A9)
+    SUMIFS([43]FinancingJournal!$E:$E,
+           [43]FinancingJournal!$C:$C,"Borrowing",
+           [43]FinancingJournal!$A:$A,"&lt;="&amp;A9)
     +
-    SUMIFS([42]FinancingJournal!$E:$E,
-           [42]FinancingJournal!$C:$C,"Withdrawal",
-           [42]FinancingJournal!$A:$A,"&lt;="&amp;A9),
+    SUMIFS([43]FinancingJournal!$E:$E,
+           [43]FinancingJournal!$C:$C,"Withdrawal",
+           [43]FinancingJournal!$A:$A,"&lt;="&amp;A9),
     "")</f>
         <v>#VALUE!</v>
       </c>
@@ -19433,37 +19734,37 @@
       </c>
       <c r="B10" s="14" t="e">
         <f>IF(A10&lt;&gt;"",
-    SUMIFS([42]FinancingJournal!$E:$E,
-           [42]FinancingJournal!$C:$C,"Capital Injection",
-           [42]FinancingJournal!$A:$A,"&lt;="&amp;A10),
+    SUMIFS([43]FinancingJournal!$E:$E,
+           [43]FinancingJournal!$C:$C,"Capital Injection",
+           [43]FinancingJournal!$A:$A,"&lt;="&amp;A10),
     "")</f>
         <v>#VALUE!</v>
       </c>
       <c r="C10" s="15" t="e">
         <f>IF(A10&lt;&gt;"",
-    SUMIFS([42]InvestingJournal!$F:$F,
-           [42]InvestingJournal!$C:$C,"Izra Advance",
-           [42]InvestingJournal!$A:$A,"&lt;="&amp;A10),
+    SUMIFS([43]InvestingJournal!$F:$F,
+           [43]InvestingJournal!$C:$C,"Izra Advance",
+           [43]InvestingJournal!$A:$A,"&lt;="&amp;A10),
     "")</f>
         <v>#VALUE!</v>
       </c>
       <c r="D10" s="15" t="e">
         <f>IF(A10&lt;&gt;"",
-    SUMIFS([42]InvestingJournal!$F:$F,
-           [42]InvestingJournal!$C:$C,"Loan Advance",
-           [42]InvestingJournal!$A:$A,"&lt;="&amp;A10),
+    SUMIFS([43]InvestingJournal!$F:$F,
+           [43]InvestingJournal!$C:$C,"Loan Advance",
+           [43]InvestingJournal!$A:$A,"&lt;="&amp;A10),
     "")</f>
         <v>#VALUE!</v>
       </c>
       <c r="E10" s="15" t="e">
         <f>IF(A10&lt;&gt;"",
-    SUMIFS([42]FinancingJournal!$E:$E,
-           [42]FinancingJournal!$C:$C,"Borrowing",
-           [42]FinancingJournal!$A:$A,"&lt;="&amp;A10)
+    SUMIFS([43]FinancingJournal!$E:$E,
+           [43]FinancingJournal!$C:$C,"Borrowing",
+           [43]FinancingJournal!$A:$A,"&lt;="&amp;A10)
     +
-    SUMIFS([42]FinancingJournal!$E:$E,
-           [42]FinancingJournal!$C:$C,"Withdrawal",
-           [42]FinancingJournal!$A:$A,"&lt;="&amp;A10),
+    SUMIFS([43]FinancingJournal!$E:$E,
+           [43]FinancingJournal!$C:$C,"Withdrawal",
+           [43]FinancingJournal!$A:$A,"&lt;="&amp;A10),
     "")</f>
         <v>#VALUE!</v>
       </c>
@@ -19489,37 +19790,37 @@
       </c>
       <c r="B11" s="17" t="e">
         <f>IF(A11&lt;&gt;"",
-    SUMIFS([42]FinancingJournal!$E:$E,
-           [42]FinancingJournal!$C:$C,"Capital Injection",
-           [42]FinancingJournal!$A:$A,"&lt;="&amp;A11),
+    SUMIFS([43]FinancingJournal!$E:$E,
+           [43]FinancingJournal!$C:$C,"Capital Injection",
+           [43]FinancingJournal!$A:$A,"&lt;="&amp;A11),
     "")</f>
         <v>#VALUE!</v>
       </c>
       <c r="C11" s="18" t="e">
         <f>IF(A11&lt;&gt;"",
-    SUMIFS([42]InvestingJournal!$F:$F,
-           [42]InvestingJournal!$C:$C,"Izra Advance",
-           [42]InvestingJournal!$A:$A,"&lt;="&amp;A11),
+    SUMIFS([43]InvestingJournal!$F:$F,
+           [43]InvestingJournal!$C:$C,"Izra Advance",
+           [43]InvestingJournal!$A:$A,"&lt;="&amp;A11),
     "")</f>
         <v>#VALUE!</v>
       </c>
       <c r="D11" s="18" t="e">
         <f>IF(A11&lt;&gt;"",
-    SUMIFS([42]InvestingJournal!$F:$F,
-           [42]InvestingJournal!$C:$C,"Loan Advance",
-           [42]InvestingJournal!$A:$A,"&lt;="&amp;A11),
+    SUMIFS([43]InvestingJournal!$F:$F,
+           [43]InvestingJournal!$C:$C,"Loan Advance",
+           [43]InvestingJournal!$A:$A,"&lt;="&amp;A11),
     "")</f>
         <v>#VALUE!</v>
       </c>
       <c r="E11" s="18" t="e">
         <f>IF(A11&lt;&gt;"",
-    SUMIFS([42]FinancingJournal!$E:$E,
-           [42]FinancingJournal!$C:$C,"Borrowing",
-           [42]FinancingJournal!$A:$A,"&lt;="&amp;A11)
+    SUMIFS([43]FinancingJournal!$E:$E,
+           [43]FinancingJournal!$C:$C,"Borrowing",
+           [43]FinancingJournal!$A:$A,"&lt;="&amp;A11)
     +
-    SUMIFS([42]FinancingJournal!$E:$E,
-           [42]FinancingJournal!$C:$C,"Withdrawal",
-           [42]FinancingJournal!$A:$A,"&lt;="&amp;A11),
+    SUMIFS([43]FinancingJournal!$E:$E,
+           [43]FinancingJournal!$C:$C,"Withdrawal",
+           [43]FinancingJournal!$A:$A,"&lt;="&amp;A11),
     "")</f>
         <v>#VALUE!</v>
       </c>
@@ -19544,37 +19845,37 @@
       </c>
       <c r="B12" s="14" t="e">
         <f>IF(A12&lt;&gt;"",
-    SUMIFS([42]FinancingJournal!$E:$E,
-           [42]FinancingJournal!$C:$C,"Capital Injection",
-           [42]FinancingJournal!$A:$A,"&lt;="&amp;A12),
+    SUMIFS([43]FinancingJournal!$E:$E,
+           [43]FinancingJournal!$C:$C,"Capital Injection",
+           [43]FinancingJournal!$A:$A,"&lt;="&amp;A12),
     "")</f>
         <v>#VALUE!</v>
       </c>
       <c r="C12" s="15" t="e">
         <f>IF(A12&lt;&gt;"",
-    SUMIFS([42]InvestingJournal!$F:$F,
-           [42]InvestingJournal!$C:$C,"Izra Advance",
-           [42]InvestingJournal!$A:$A,"&lt;="&amp;A12),
+    SUMIFS([43]InvestingJournal!$F:$F,
+           [43]InvestingJournal!$C:$C,"Izra Advance",
+           [43]InvestingJournal!$A:$A,"&lt;="&amp;A12),
     "")</f>
         <v>#VALUE!</v>
       </c>
       <c r="D12" s="15" t="e">
         <f>IF(A12&lt;&gt;"",
-    SUMIFS([42]InvestingJournal!$F:$F,
-           [42]InvestingJournal!$C:$C,"Loan Advance",
-           [42]InvestingJournal!$A:$A,"&lt;="&amp;A12),
+    SUMIFS([43]InvestingJournal!$F:$F,
+           [43]InvestingJournal!$C:$C,"Loan Advance",
+           [43]InvestingJournal!$A:$A,"&lt;="&amp;A12),
     "")</f>
         <v>#VALUE!</v>
       </c>
       <c r="E12" s="15" t="e">
         <f>IF(A12&lt;&gt;"",
-    SUMIFS([42]FinancingJournal!$E:$E,
-           [42]FinancingJournal!$C:$C,"Borrowing",
-           [42]FinancingJournal!$A:$A,"&lt;="&amp;A12)
+    SUMIFS([43]FinancingJournal!$E:$E,
+           [43]FinancingJournal!$C:$C,"Borrowing",
+           [43]FinancingJournal!$A:$A,"&lt;="&amp;A12)
     +
-    SUMIFS([42]FinancingJournal!$E:$E,
-           [42]FinancingJournal!$C:$C,"Withdrawal",
-           [42]FinancingJournal!$A:$A,"&lt;="&amp;A12),
+    SUMIFS([43]FinancingJournal!$E:$E,
+           [43]FinancingJournal!$C:$C,"Withdrawal",
+           [43]FinancingJournal!$A:$A,"&lt;="&amp;A12),
     "")</f>
         <v>#VALUE!</v>
       </c>
@@ -19600,37 +19901,37 @@
       </c>
       <c r="B13" s="17" t="e">
         <f>IF(A13&lt;&gt;"",
-    SUMIFS([42]FinancingJournal!$E:$E,
-           [42]FinancingJournal!$C:$C,"Capital Injection",
-           [42]FinancingJournal!$A:$A,"&lt;="&amp;A13),
+    SUMIFS([43]FinancingJournal!$E:$E,
+           [43]FinancingJournal!$C:$C,"Capital Injection",
+           [43]FinancingJournal!$A:$A,"&lt;="&amp;A13),
     "")</f>
         <v>#VALUE!</v>
       </c>
       <c r="C13" s="18" t="e">
         <f>IF(A13&lt;&gt;"",
-    SUMIFS([42]InvestingJournal!$F:$F,
-           [42]InvestingJournal!$C:$C,"Izra Advance",
-           [42]InvestingJournal!$A:$A,"&lt;="&amp;A13),
+    SUMIFS([43]InvestingJournal!$F:$F,
+           [43]InvestingJournal!$C:$C,"Izra Advance",
+           [43]InvestingJournal!$A:$A,"&lt;="&amp;A13),
     "")</f>
         <v>#VALUE!</v>
       </c>
       <c r="D13" s="18" t="e">
         <f>IF(A13&lt;&gt;"",
-    SUMIFS([42]InvestingJournal!$F:$F,
-           [42]InvestingJournal!$C:$C,"Loan Advance",
-           [42]InvestingJournal!$A:$A,"&lt;="&amp;A13),
+    SUMIFS([43]InvestingJournal!$F:$F,
+           [43]InvestingJournal!$C:$C,"Loan Advance",
+           [43]InvestingJournal!$A:$A,"&lt;="&amp;A13),
     "")</f>
         <v>#VALUE!</v>
       </c>
       <c r="E13" s="18" t="e">
         <f>IF(A13&lt;&gt;"",
-    SUMIFS([42]FinancingJournal!$E:$E,
-           [42]FinancingJournal!$C:$C,"Borrowing",
-           [42]FinancingJournal!$A:$A,"&lt;="&amp;A13)
+    SUMIFS([43]FinancingJournal!$E:$E,
+           [43]FinancingJournal!$C:$C,"Borrowing",
+           [43]FinancingJournal!$A:$A,"&lt;="&amp;A13)
     +
-    SUMIFS([42]FinancingJournal!$E:$E,
-           [42]FinancingJournal!$C:$C,"Withdrawal",
-           [42]FinancingJournal!$A:$A,"&lt;="&amp;A13),
+    SUMIFS([43]FinancingJournal!$E:$E,
+           [43]FinancingJournal!$C:$C,"Withdrawal",
+           [43]FinancingJournal!$A:$A,"&lt;="&amp;A13),
     "")</f>
         <v>#VALUE!</v>
       </c>
@@ -19655,37 +19956,37 @@
       </c>
       <c r="B14" s="14" t="e">
         <f>IF(A14&lt;&gt;"",
-    SUMIFS([42]FinancingJournal!$E:$E,
-           [42]FinancingJournal!$C:$C,"Capital Injection",
-           [42]FinancingJournal!$A:$A,"&lt;="&amp;A14),
+    SUMIFS([43]FinancingJournal!$E:$E,
+           [43]FinancingJournal!$C:$C,"Capital Injection",
+           [43]FinancingJournal!$A:$A,"&lt;="&amp;A14),
     "")</f>
         <v>#VALUE!</v>
       </c>
       <c r="C14" s="15" t="e">
         <f>IF(A14&lt;&gt;"",
-    SUMIFS([42]InvestingJournal!$F:$F,
-           [42]InvestingJournal!$C:$C,"Izra Advance",
-           [42]InvestingJournal!$A:$A,"&lt;="&amp;A14),
+    SUMIFS([43]InvestingJournal!$F:$F,
+           [43]InvestingJournal!$C:$C,"Izra Advance",
+           [43]InvestingJournal!$A:$A,"&lt;="&amp;A14),
     "")</f>
         <v>#VALUE!</v>
       </c>
       <c r="D14" s="15" t="e">
         <f>IF(A14&lt;&gt;"",
-    SUMIFS([42]InvestingJournal!$F:$F,
-           [42]InvestingJournal!$C:$C,"Loan Advance",
-           [42]InvestingJournal!$A:$A,"&lt;="&amp;A14),
+    SUMIFS([43]InvestingJournal!$F:$F,
+           [43]InvestingJournal!$C:$C,"Loan Advance",
+           [43]InvestingJournal!$A:$A,"&lt;="&amp;A14),
     "")</f>
         <v>#VALUE!</v>
       </c>
       <c r="E14" s="15" t="e">
         <f>IF(A14&lt;&gt;"",
-    SUMIFS([42]FinancingJournal!$E:$E,
-           [42]FinancingJournal!$C:$C,"Borrowing",
-           [42]FinancingJournal!$A:$A,"&lt;="&amp;A14)
+    SUMIFS([43]FinancingJournal!$E:$E,
+           [43]FinancingJournal!$C:$C,"Borrowing",
+           [43]FinancingJournal!$A:$A,"&lt;="&amp;A14)
     +
-    SUMIFS([42]FinancingJournal!$E:$E,
-           [42]FinancingJournal!$C:$C,"Withdrawal",
-           [42]FinancingJournal!$A:$A,"&lt;="&amp;A14),
+    SUMIFS([43]FinancingJournal!$E:$E,
+           [43]FinancingJournal!$C:$C,"Withdrawal",
+           [43]FinancingJournal!$A:$A,"&lt;="&amp;A14),
     "")</f>
         <v>#VALUE!</v>
       </c>
@@ -19711,37 +20012,37 @@
       </c>
       <c r="B15" s="17" t="e">
         <f>IF(A15&lt;&gt;"",
-    SUMIFS([42]FinancingJournal!$E:$E,
-           [42]FinancingJournal!$C:$C,"Capital Injection",
-           [42]FinancingJournal!$A:$A,"&lt;="&amp;A15),
+    SUMIFS([43]FinancingJournal!$E:$E,
+           [43]FinancingJournal!$C:$C,"Capital Injection",
+           [43]FinancingJournal!$A:$A,"&lt;="&amp;A15),
     "")</f>
         <v>#VALUE!</v>
       </c>
       <c r="C15" s="18" t="e">
         <f>IF(A15&lt;&gt;"",
-    SUMIFS([42]InvestingJournal!$F:$F,
-           [42]InvestingJournal!$C:$C,"Izra Advance",
-           [42]InvestingJournal!$A:$A,"&lt;="&amp;A15),
+    SUMIFS([43]InvestingJournal!$F:$F,
+           [43]InvestingJournal!$C:$C,"Izra Advance",
+           [43]InvestingJournal!$A:$A,"&lt;="&amp;A15),
     "")</f>
         <v>#VALUE!</v>
       </c>
       <c r="D15" s="18" t="e">
         <f>IF(A15&lt;&gt;"",
-    SUMIFS([42]InvestingJournal!$F:$F,
-           [42]InvestingJournal!$C:$C,"Loan Advance",
-           [42]InvestingJournal!$A:$A,"&lt;="&amp;A15),
+    SUMIFS([43]InvestingJournal!$F:$F,
+           [43]InvestingJournal!$C:$C,"Loan Advance",
+           [43]InvestingJournal!$A:$A,"&lt;="&amp;A15),
     "")</f>
         <v>#VALUE!</v>
       </c>
       <c r="E15" s="18" t="e">
         <f>IF(A15&lt;&gt;"",
-    SUMIFS([42]FinancingJournal!$E:$E,
-           [42]FinancingJournal!$C:$C,"Borrowing",
-           [42]FinancingJournal!$A:$A,"&lt;="&amp;A15)
+    SUMIFS([43]FinancingJournal!$E:$E,
+           [43]FinancingJournal!$C:$C,"Borrowing",
+           [43]FinancingJournal!$A:$A,"&lt;="&amp;A15)
     +
-    SUMIFS([42]FinancingJournal!$E:$E,
-           [42]FinancingJournal!$C:$C,"Withdrawal",
-           [42]FinancingJournal!$A:$A,"&lt;="&amp;A15),
+    SUMIFS([43]FinancingJournal!$E:$E,
+           [43]FinancingJournal!$C:$C,"Withdrawal",
+           [43]FinancingJournal!$A:$A,"&lt;="&amp;A15),
     "")</f>
         <v>#VALUE!</v>
       </c>
@@ -19766,37 +20067,37 @@
       </c>
       <c r="B16" s="14" t="e">
         <f>IF(A16&lt;&gt;"",
-    SUMIFS([42]FinancingJournal!$E:$E,
-           [42]FinancingJournal!$C:$C,"Capital Injection",
-           [42]FinancingJournal!$A:$A,"&lt;="&amp;A16),
+    SUMIFS([43]FinancingJournal!$E:$E,
+           [43]FinancingJournal!$C:$C,"Capital Injection",
+           [43]FinancingJournal!$A:$A,"&lt;="&amp;A16),
     "")</f>
         <v>#VALUE!</v>
       </c>
       <c r="C16" s="15" t="e">
         <f>IF(A16&lt;&gt;"",
-    SUMIFS([42]InvestingJournal!$F:$F,
-           [42]InvestingJournal!$C:$C,"Izra Advance",
-           [42]InvestingJournal!$A:$A,"&lt;="&amp;A16),
+    SUMIFS([43]InvestingJournal!$F:$F,
+           [43]InvestingJournal!$C:$C,"Izra Advance",
+           [43]InvestingJournal!$A:$A,"&lt;="&amp;A16),
     "")</f>
         <v>#VALUE!</v>
       </c>
       <c r="D16" s="15" t="e">
         <f>IF(A16&lt;&gt;"",
-    SUMIFS([42]InvestingJournal!$F:$F,
-           [42]InvestingJournal!$C:$C,"Loan Advance",
-           [42]InvestingJournal!$A:$A,"&lt;="&amp;A16),
+    SUMIFS([43]InvestingJournal!$F:$F,
+           [43]InvestingJournal!$C:$C,"Loan Advance",
+           [43]InvestingJournal!$A:$A,"&lt;="&amp;A16),
     "")</f>
         <v>#VALUE!</v>
       </c>
       <c r="E16" s="15" t="e">
         <f>IF(A16&lt;&gt;"",
-    SUMIFS([42]FinancingJournal!$E:$E,
-           [42]FinancingJournal!$C:$C,"Borrowing",
-           [42]FinancingJournal!$A:$A,"&lt;="&amp;A16)
+    SUMIFS([43]FinancingJournal!$E:$E,
+           [43]FinancingJournal!$C:$C,"Borrowing",
+           [43]FinancingJournal!$A:$A,"&lt;="&amp;A16)
     +
-    SUMIFS([42]FinancingJournal!$E:$E,
-           [42]FinancingJournal!$C:$C,"Withdrawal",
-           [42]FinancingJournal!$A:$A,"&lt;="&amp;A16),
+    SUMIFS([43]FinancingJournal!$E:$E,
+           [43]FinancingJournal!$C:$C,"Withdrawal",
+           [43]FinancingJournal!$A:$A,"&lt;="&amp;A16),
     "")</f>
         <v>#VALUE!</v>
       </c>
@@ -19822,37 +20123,37 @@
       </c>
       <c r="B17" s="17" t="e">
         <f>IF(A17&lt;&gt;"",
-    SUMIFS([42]FinancingJournal!$E:$E,
-           [42]FinancingJournal!$C:$C,"Capital Injection",
-           [42]FinancingJournal!$A:$A,"&lt;="&amp;A17),
+    SUMIFS([43]FinancingJournal!$E:$E,
+           [43]FinancingJournal!$C:$C,"Capital Injection",
+           [43]FinancingJournal!$A:$A,"&lt;="&amp;A17),
     "")</f>
         <v>#VALUE!</v>
       </c>
       <c r="C17" s="18" t="e">
         <f>IF(A17&lt;&gt;"",
-    SUMIFS([42]InvestingJournal!$F:$F,
-           [42]InvestingJournal!$C:$C,"Izra Advance",
-           [42]InvestingJournal!$A:$A,"&lt;="&amp;A17),
+    SUMIFS([43]InvestingJournal!$F:$F,
+           [43]InvestingJournal!$C:$C,"Izra Advance",
+           [43]InvestingJournal!$A:$A,"&lt;="&amp;A17),
     "")</f>
         <v>#VALUE!</v>
       </c>
       <c r="D17" s="18" t="e">
         <f>IF(A17&lt;&gt;"",
-    SUMIFS([42]InvestingJournal!$F:$F,
-           [42]InvestingJournal!$C:$C,"Loan Advance",
-           [42]InvestingJournal!$A:$A,"&lt;="&amp;A17),
+    SUMIFS([43]InvestingJournal!$F:$F,
+           [43]InvestingJournal!$C:$C,"Loan Advance",
+           [43]InvestingJournal!$A:$A,"&lt;="&amp;A17),
     "")</f>
         <v>#VALUE!</v>
       </c>
       <c r="E17" s="18" t="e">
         <f>IF(A17&lt;&gt;"",
-    SUMIFS([42]FinancingJournal!$E:$E,
-           [42]FinancingJournal!$C:$C,"Borrowing",
-           [42]FinancingJournal!$A:$A,"&lt;="&amp;A17)
+    SUMIFS([43]FinancingJournal!$E:$E,
+           [43]FinancingJournal!$C:$C,"Borrowing",
+           [43]FinancingJournal!$A:$A,"&lt;="&amp;A17)
     +
-    SUMIFS([42]FinancingJournal!$E:$E,
-           [42]FinancingJournal!$C:$C,"Withdrawal",
-           [42]FinancingJournal!$A:$A,"&lt;="&amp;A17),
+    SUMIFS([43]FinancingJournal!$E:$E,
+           [43]FinancingJournal!$C:$C,"Withdrawal",
+           [43]FinancingJournal!$A:$A,"&lt;="&amp;A17),
     "")</f>
         <v>#VALUE!</v>
       </c>
@@ -19879,37 +20180,37 @@
       </c>
       <c r="B18" s="14" t="e">
         <f>IF(A18&lt;&gt;"",
-    SUMIFS([42]FinancingJournal!$E:$E,
-           [42]FinancingJournal!$C:$C,"Capital Injection",
-           [42]FinancingJournal!$A:$A,"&lt;="&amp;A18),
+    SUMIFS([43]FinancingJournal!$E:$E,
+           [43]FinancingJournal!$C:$C,"Capital Injection",
+           [43]FinancingJournal!$A:$A,"&lt;="&amp;A18),
     "")</f>
         <v>#VALUE!</v>
       </c>
       <c r="C18" s="15" t="e">
         <f>IF(A18&lt;&gt;"",
-    SUMIFS([42]InvestingJournal!$F:$F,
-           [42]InvestingJournal!$C:$C,"Izra Advance",
-           [42]InvestingJournal!$A:$A,"&lt;="&amp;A18),
+    SUMIFS([43]InvestingJournal!$F:$F,
+           [43]InvestingJournal!$C:$C,"Izra Advance",
+           [43]InvestingJournal!$A:$A,"&lt;="&amp;A18),
     "")</f>
         <v>#VALUE!</v>
       </c>
       <c r="D18" s="15" t="e">
         <f>IF(A18&lt;&gt;"",
-    SUMIFS([42]InvestingJournal!$F:$F,
-           [42]InvestingJournal!$C:$C,"Loan Advance",
-           [42]InvestingJournal!$A:$A,"&lt;="&amp;A18),
+    SUMIFS([43]InvestingJournal!$F:$F,
+           [43]InvestingJournal!$C:$C,"Loan Advance",
+           [43]InvestingJournal!$A:$A,"&lt;="&amp;A18),
     "")</f>
         <v>#VALUE!</v>
       </c>
       <c r="E18" s="15" t="e">
         <f>IF(A18&lt;&gt;"",
-    SUMIFS([42]FinancingJournal!$E:$E,
-           [42]FinancingJournal!$C:$C,"Borrowing",
-           [42]FinancingJournal!$A:$A,"&lt;="&amp;A18)
+    SUMIFS([43]FinancingJournal!$E:$E,
+           [43]FinancingJournal!$C:$C,"Borrowing",
+           [43]FinancingJournal!$A:$A,"&lt;="&amp;A18)
     +
-    SUMIFS([42]FinancingJournal!$E:$E,
-           [42]FinancingJournal!$C:$C,"Withdrawal",
-           [42]FinancingJournal!$A:$A,"&lt;="&amp;A18),
+    SUMIFS([43]FinancingJournal!$E:$E,
+           [43]FinancingJournal!$C:$C,"Withdrawal",
+           [43]FinancingJournal!$A:$A,"&lt;="&amp;A18),
     "")</f>
         <v>#VALUE!</v>
       </c>
@@ -19935,37 +20236,37 @@
       </c>
       <c r="B19" s="17" t="e">
         <f>IF(A19&lt;&gt;"",
-    SUMIFS([42]FinancingJournal!$E:$E,
-           [42]FinancingJournal!$C:$C,"Capital Injection",
-           [42]FinancingJournal!$A:$A,"&lt;="&amp;A19),
+    SUMIFS([43]FinancingJournal!$E:$E,
+           [43]FinancingJournal!$C:$C,"Capital Injection",
+           [43]FinancingJournal!$A:$A,"&lt;="&amp;A19),
     "")</f>
         <v>#VALUE!</v>
       </c>
       <c r="C19" s="18" t="e">
         <f>IF(A19&lt;&gt;"",
-    SUMIFS([42]InvestingJournal!$F:$F,
-           [42]InvestingJournal!$C:$C,"Izra Advance",
-           [42]InvestingJournal!$A:$A,"&lt;="&amp;A19),
+    SUMIFS([43]InvestingJournal!$F:$F,
+           [43]InvestingJournal!$C:$C,"Izra Advance",
+           [43]InvestingJournal!$A:$A,"&lt;="&amp;A19),
     "")</f>
         <v>#VALUE!</v>
       </c>
       <c r="D19" s="18" t="e">
         <f>IF(A19&lt;&gt;"",
-    SUMIFS([42]InvestingJournal!$F:$F,
-           [42]InvestingJournal!$C:$C,"Loan Advance",
-           [42]InvestingJournal!$A:$A,"&lt;="&amp;A19),
+    SUMIFS([43]InvestingJournal!$F:$F,
+           [43]InvestingJournal!$C:$C,"Loan Advance",
+           [43]InvestingJournal!$A:$A,"&lt;="&amp;A19),
     "")</f>
         <v>#VALUE!</v>
       </c>
       <c r="E19" s="18" t="e">
         <f>IF(A19&lt;&gt;"",
-    SUMIFS([42]FinancingJournal!$E:$E,
-           [42]FinancingJournal!$C:$C,"Borrowing",
-           [42]FinancingJournal!$A:$A,"&lt;="&amp;A19)
+    SUMIFS([43]FinancingJournal!$E:$E,
+           [43]FinancingJournal!$C:$C,"Borrowing",
+           [43]FinancingJournal!$A:$A,"&lt;="&amp;A19)
     +
-    SUMIFS([42]FinancingJournal!$E:$E,
-           [42]FinancingJournal!$C:$C,"Withdrawal",
-           [42]FinancingJournal!$A:$A,"&lt;="&amp;A19),
+    SUMIFS([43]FinancingJournal!$E:$E,
+           [43]FinancingJournal!$C:$C,"Withdrawal",
+           [43]FinancingJournal!$A:$A,"&lt;="&amp;A19),
     "")</f>
         <v>#VALUE!</v>
       </c>
@@ -19990,37 +20291,37 @@
       </c>
       <c r="B20" s="14" t="e">
         <f>IF(A20&lt;&gt;"",
-    SUMIFS([42]FinancingJournal!$E:$E,
-           [42]FinancingJournal!$C:$C,"Capital Injection",
-           [42]FinancingJournal!$A:$A,"&lt;="&amp;A20),
+    SUMIFS([43]FinancingJournal!$E:$E,
+           [43]FinancingJournal!$C:$C,"Capital Injection",
+           [43]FinancingJournal!$A:$A,"&lt;="&amp;A20),
     "")</f>
         <v>#VALUE!</v>
       </c>
       <c r="C20" s="15" t="e">
         <f>IF(A20&lt;&gt;"",
-    SUMIFS([42]InvestingJournal!$F:$F,
-           [42]InvestingJournal!$C:$C,"Izra Advance",
-           [42]InvestingJournal!$A:$A,"&lt;="&amp;A20),
+    SUMIFS([43]InvestingJournal!$F:$F,
+           [43]InvestingJournal!$C:$C,"Izra Advance",
+           [43]InvestingJournal!$A:$A,"&lt;="&amp;A20),
     "")</f>
         <v>#VALUE!</v>
       </c>
       <c r="D20" s="15" t="e">
         <f>IF(A20&lt;&gt;"",
-    SUMIFS([42]InvestingJournal!$F:$F,
-           [42]InvestingJournal!$C:$C,"Loan Advance",
-           [42]InvestingJournal!$A:$A,"&lt;="&amp;A20),
+    SUMIFS([43]InvestingJournal!$F:$F,
+           [43]InvestingJournal!$C:$C,"Loan Advance",
+           [43]InvestingJournal!$A:$A,"&lt;="&amp;A20),
     "")</f>
         <v>#VALUE!</v>
       </c>
       <c r="E20" s="15" t="e">
         <f>IF(A20&lt;&gt;"",
-    SUMIFS([42]FinancingJournal!$E:$E,
-           [42]FinancingJournal!$C:$C,"Borrowing",
-           [42]FinancingJournal!$A:$A,"&lt;="&amp;A20)
+    SUMIFS([43]FinancingJournal!$E:$E,
+           [43]FinancingJournal!$C:$C,"Borrowing",
+           [43]FinancingJournal!$A:$A,"&lt;="&amp;A20)
     +
-    SUMIFS([42]FinancingJournal!$E:$E,
-           [42]FinancingJournal!$C:$C,"Withdrawal",
-           [42]FinancingJournal!$A:$A,"&lt;="&amp;A20),
+    SUMIFS([43]FinancingJournal!$E:$E,
+           [43]FinancingJournal!$C:$C,"Withdrawal",
+           [43]FinancingJournal!$A:$A,"&lt;="&amp;A20),
     "")</f>
         <v>#VALUE!</v>
       </c>
@@ -20046,37 +20347,37 @@
       </c>
       <c r="B21" s="17" t="e">
         <f>IF(A21&lt;&gt;"",
-    SUMIFS([42]FinancingJournal!$E:$E,
-           [42]FinancingJournal!$C:$C,"Capital Injection",
-           [42]FinancingJournal!$A:$A,"&lt;="&amp;A21),
+    SUMIFS([43]FinancingJournal!$E:$E,
+           [43]FinancingJournal!$C:$C,"Capital Injection",
+           [43]FinancingJournal!$A:$A,"&lt;="&amp;A21),
     "")</f>
         <v>#VALUE!</v>
       </c>
       <c r="C21" s="18" t="e">
         <f>IF(A21&lt;&gt;"",
-    SUMIFS([42]InvestingJournal!$F:$F,
-           [42]InvestingJournal!$C:$C,"Izra Advance",
-           [42]InvestingJournal!$A:$A,"&lt;="&amp;A21),
+    SUMIFS([43]InvestingJournal!$F:$F,
+           [43]InvestingJournal!$C:$C,"Izra Advance",
+           [43]InvestingJournal!$A:$A,"&lt;="&amp;A21),
     "")</f>
         <v>#VALUE!</v>
       </c>
       <c r="D21" s="18" t="e">
         <f>IF(A21&lt;&gt;"",
-    SUMIFS([42]InvestingJournal!$F:$F,
-           [42]InvestingJournal!$C:$C,"Loan Advance",
-           [42]InvestingJournal!$A:$A,"&lt;="&amp;A21),
+    SUMIFS([43]InvestingJournal!$F:$F,
+           [43]InvestingJournal!$C:$C,"Loan Advance",
+           [43]InvestingJournal!$A:$A,"&lt;="&amp;A21),
     "")</f>
         <v>#VALUE!</v>
       </c>
       <c r="E21" s="18" t="e">
         <f>IF(A21&lt;&gt;"",
-    SUMIFS([42]FinancingJournal!$E:$E,
-           [42]FinancingJournal!$C:$C,"Borrowing",
-           [42]FinancingJournal!$A:$A,"&lt;="&amp;A21)
+    SUMIFS([43]FinancingJournal!$E:$E,
+           [43]FinancingJournal!$C:$C,"Borrowing",
+           [43]FinancingJournal!$A:$A,"&lt;="&amp;A21)
     +
-    SUMIFS([42]FinancingJournal!$E:$E,
-           [42]FinancingJournal!$C:$C,"Withdrawal",
-           [42]FinancingJournal!$A:$A,"&lt;="&amp;A21),
+    SUMIFS([43]FinancingJournal!$E:$E,
+           [43]FinancingJournal!$C:$C,"Withdrawal",
+           [43]FinancingJournal!$A:$A,"&lt;="&amp;A21),
     "")</f>
         <v>#VALUE!</v>
       </c>
@@ -20101,37 +20402,37 @@
       </c>
       <c r="B22" s="14" t="e">
         <f>IF(A22&lt;&gt;"",
-    SUMIFS([42]FinancingJournal!$E:$E,
-           [42]FinancingJournal!$C:$C,"Capital Injection",
-           [42]FinancingJournal!$A:$A,"&lt;="&amp;A22),
+    SUMIFS([43]FinancingJournal!$E:$E,
+           [43]FinancingJournal!$C:$C,"Capital Injection",
+           [43]FinancingJournal!$A:$A,"&lt;="&amp;A22),
     "")</f>
         <v>#VALUE!</v>
       </c>
       <c r="C22" s="15" t="e">
         <f>IF(A22&lt;&gt;"",
-    SUMIFS([42]InvestingJournal!$F:$F,
-           [42]InvestingJournal!$C:$C,"Izra Advance",
-           [42]InvestingJournal!$A:$A,"&lt;="&amp;A22),
+    SUMIFS([43]InvestingJournal!$F:$F,
+           [43]InvestingJournal!$C:$C,"Izra Advance",
+           [43]InvestingJournal!$A:$A,"&lt;="&amp;A22),
     "")</f>
         <v>#VALUE!</v>
       </c>
       <c r="D22" s="15" t="e">
         <f>IF(A22&lt;&gt;"",
-    SUMIFS([42]InvestingJournal!$F:$F,
-           [42]InvestingJournal!$C:$C,"Loan Advance",
-           [42]InvestingJournal!$A:$A,"&lt;="&amp;A22),
+    SUMIFS([43]InvestingJournal!$F:$F,
+           [43]InvestingJournal!$C:$C,"Loan Advance",
+           [43]InvestingJournal!$A:$A,"&lt;="&amp;A22),
     "")</f>
         <v>#VALUE!</v>
       </c>
       <c r="E22" s="15" t="e">
         <f>IF(A22&lt;&gt;"",
-    SUMIFS([42]FinancingJournal!$E:$E,
-           [42]FinancingJournal!$C:$C,"Borrowing",
-           [42]FinancingJournal!$A:$A,"&lt;="&amp;A22)
+    SUMIFS([43]FinancingJournal!$E:$E,
+           [43]FinancingJournal!$C:$C,"Borrowing",
+           [43]FinancingJournal!$A:$A,"&lt;="&amp;A22)
     +
-    SUMIFS([42]FinancingJournal!$E:$E,
-           [42]FinancingJournal!$C:$C,"Withdrawal",
-           [42]FinancingJournal!$A:$A,"&lt;="&amp;A22),
+    SUMIFS([43]FinancingJournal!$E:$E,
+           [43]FinancingJournal!$C:$C,"Withdrawal",
+           [43]FinancingJournal!$A:$A,"&lt;="&amp;A22),
     "")</f>
         <v>#VALUE!</v>
       </c>
@@ -20157,37 +20458,37 @@
       </c>
       <c r="B23" s="17" t="e">
         <f>IF(A23&lt;&gt;"",
-    SUMIFS([42]FinancingJournal!$E:$E,
-           [42]FinancingJournal!$C:$C,"Capital Injection",
-           [42]FinancingJournal!$A:$A,"&lt;="&amp;A23),
+    SUMIFS([43]FinancingJournal!$E:$E,
+           [43]FinancingJournal!$C:$C,"Capital Injection",
+           [43]FinancingJournal!$A:$A,"&lt;="&amp;A23),
     "")</f>
         <v>#VALUE!</v>
       </c>
       <c r="C23" s="18" t="e">
         <f>IF(A23&lt;&gt;"",
-    SUMIFS([42]InvestingJournal!$F:$F,
-           [42]InvestingJournal!$C:$C,"Izra Advance",
-           [42]InvestingJournal!$A:$A,"&lt;="&amp;A23),
+    SUMIFS([43]InvestingJournal!$F:$F,
+           [43]InvestingJournal!$C:$C,"Izra Advance",
+           [43]InvestingJournal!$A:$A,"&lt;="&amp;A23),
     "")</f>
         <v>#VALUE!</v>
       </c>
       <c r="D23" s="18" t="e">
         <f>IF(A23&lt;&gt;"",
-    SUMIFS([42]InvestingJournal!$F:$F,
-           [42]InvestingJournal!$C:$C,"Loan Advance",
-           [42]InvestingJournal!$A:$A,"&lt;="&amp;A23),
+    SUMIFS([43]InvestingJournal!$F:$F,
+           [43]InvestingJournal!$C:$C,"Loan Advance",
+           [43]InvestingJournal!$A:$A,"&lt;="&amp;A23),
     "")</f>
         <v>#VALUE!</v>
       </c>
       <c r="E23" s="18" t="e">
         <f>IF(A23&lt;&gt;"",
-    SUMIFS([42]FinancingJournal!$E:$E,
-           [42]FinancingJournal!$C:$C,"Borrowing",
-           [42]FinancingJournal!$A:$A,"&lt;="&amp;A23)
+    SUMIFS([43]FinancingJournal!$E:$E,
+           [43]FinancingJournal!$C:$C,"Borrowing",
+           [43]FinancingJournal!$A:$A,"&lt;="&amp;A23)
     +
-    SUMIFS([42]FinancingJournal!$E:$E,
-           [42]FinancingJournal!$C:$C,"Withdrawal",
-           [42]FinancingJournal!$A:$A,"&lt;="&amp;A23),
+    SUMIFS([43]FinancingJournal!$E:$E,
+           [43]FinancingJournal!$C:$C,"Withdrawal",
+           [43]FinancingJournal!$A:$A,"&lt;="&amp;A23),
     "")</f>
         <v>#VALUE!</v>
       </c>
@@ -20214,37 +20515,37 @@
       </c>
       <c r="B24" s="14" t="e">
         <f>IF(A24&lt;&gt;"",
-    SUMIFS([42]FinancingJournal!$E:$E,
-           [42]FinancingJournal!$C:$C,"Capital Injection",
-           [42]FinancingJournal!$A:$A,"&lt;="&amp;A24),
+    SUMIFS([43]FinancingJournal!$E:$E,
+           [43]FinancingJournal!$C:$C,"Capital Injection",
+           [43]FinancingJournal!$A:$A,"&lt;="&amp;A24),
     "")</f>
         <v>#VALUE!</v>
       </c>
       <c r="C24" s="15" t="e">
         <f>IF(A24&lt;&gt;"",
-    SUMIFS([42]InvestingJournal!$F:$F,
-           [42]InvestingJournal!$C:$C,"Izra Advance",
-           [42]InvestingJournal!$A:$A,"&lt;="&amp;A24),
+    SUMIFS([43]InvestingJournal!$F:$F,
+           [43]InvestingJournal!$C:$C,"Izra Advance",
+           [43]InvestingJournal!$A:$A,"&lt;="&amp;A24),
     "")</f>
         <v>#VALUE!</v>
       </c>
       <c r="D24" s="15" t="e">
         <f>IF(A24&lt;&gt;"",
-    SUMIFS([42]InvestingJournal!$F:$F,
-           [42]InvestingJournal!$C:$C,"Loan Advance",
-           [42]InvestingJournal!$A:$A,"&lt;="&amp;A24),
+    SUMIFS([43]InvestingJournal!$F:$F,
+           [43]InvestingJournal!$C:$C,"Loan Advance",
+           [43]InvestingJournal!$A:$A,"&lt;="&amp;A24),
     "")</f>
         <v>#VALUE!</v>
       </c>
       <c r="E24" s="15" t="e">
         <f>IF(A24&lt;&gt;"",
-    SUMIFS([42]FinancingJournal!$E:$E,
-           [42]FinancingJournal!$C:$C,"Borrowing",
-           [42]FinancingJournal!$A:$A,"&lt;="&amp;A24)
+    SUMIFS([43]FinancingJournal!$E:$E,
+           [43]FinancingJournal!$C:$C,"Borrowing",
+           [43]FinancingJournal!$A:$A,"&lt;="&amp;A24)
     +
-    SUMIFS([42]FinancingJournal!$E:$E,
-           [42]FinancingJournal!$C:$C,"Withdrawal",
-           [42]FinancingJournal!$A:$A,"&lt;="&amp;A24),
+    SUMIFS([43]FinancingJournal!$E:$E,
+           [43]FinancingJournal!$C:$C,"Withdrawal",
+           [43]FinancingJournal!$A:$A,"&lt;="&amp;A24),
     "")</f>
         <v>#VALUE!</v>
       </c>
@@ -20268,37 +20569,37 @@
       </c>
       <c r="B25" s="17" t="e">
         <f>IF(A25&lt;&gt;"",
-    SUMIFS([42]FinancingJournal!$E:$E,
-           [42]FinancingJournal!$C:$C,"Capital Injection",
-           [42]FinancingJournal!$A:$A,"&lt;="&amp;A25),
+    SUMIFS([43]FinancingJournal!$E:$E,
+           [43]FinancingJournal!$C:$C,"Capital Injection",
+           [43]FinancingJournal!$A:$A,"&lt;="&amp;A25),
     "")</f>
         <v>#VALUE!</v>
       </c>
       <c r="C25" s="18" t="e">
         <f>IF(A25&lt;&gt;"",
-    SUMIFS([42]InvestingJournal!$F:$F,
-           [42]InvestingJournal!$C:$C,"Izra Advance",
-           [42]InvestingJournal!$A:$A,"&lt;="&amp;A25),
+    SUMIFS([43]InvestingJournal!$F:$F,
+           [43]InvestingJournal!$C:$C,"Izra Advance",
+           [43]InvestingJournal!$A:$A,"&lt;="&amp;A25),
     "")</f>
         <v>#VALUE!</v>
       </c>
       <c r="D25" s="18" t="e">
         <f>IF(A25&lt;&gt;"",
-    SUMIFS([42]InvestingJournal!$F:$F,
-           [42]InvestingJournal!$C:$C,"Loan Advance",
-           [42]InvestingJournal!$A:$A,"&lt;="&amp;A25),
+    SUMIFS([43]InvestingJournal!$F:$F,
+           [43]InvestingJournal!$C:$C,"Loan Advance",
+           [43]InvestingJournal!$A:$A,"&lt;="&amp;A25),
     "")</f>
         <v>#VALUE!</v>
       </c>
       <c r="E25" s="18" t="e">
         <f>IF(A25&lt;&gt;"",
-    SUMIFS([42]FinancingJournal!$E:$E,
-           [42]FinancingJournal!$C:$C,"Borrowing",
-           [42]FinancingJournal!$A:$A,"&lt;="&amp;A25)
+    SUMIFS([43]FinancingJournal!$E:$E,
+           [43]FinancingJournal!$C:$C,"Borrowing",
+           [43]FinancingJournal!$A:$A,"&lt;="&amp;A25)
     +
-    SUMIFS([42]FinancingJournal!$E:$E,
-           [42]FinancingJournal!$C:$C,"Withdrawal",
-           [42]FinancingJournal!$A:$A,"&lt;="&amp;A25),
+    SUMIFS([43]FinancingJournal!$E:$E,
+           [43]FinancingJournal!$C:$C,"Withdrawal",
+           [43]FinancingJournal!$A:$A,"&lt;="&amp;A25),
     "")</f>
         <v>#VALUE!</v>
       </c>
@@ -20325,37 +20626,37 @@
       </c>
       <c r="B26" s="14" t="e">
         <f>IF(A26&lt;&gt;"",
-    SUMIFS([42]FinancingJournal!$E:$E,
-           [42]FinancingJournal!$C:$C,"Capital Injection",
-           [42]FinancingJournal!$A:$A,"&lt;="&amp;A26),
+    SUMIFS([43]FinancingJournal!$E:$E,
+           [43]FinancingJournal!$C:$C,"Capital Injection",
+           [43]FinancingJournal!$A:$A,"&lt;="&amp;A26),
     "")</f>
         <v>#VALUE!</v>
       </c>
       <c r="C26" s="15" t="e">
         <f>IF(A26&lt;&gt;"",
-    SUMIFS([42]InvestingJournal!$F:$F,
-           [42]InvestingJournal!$C:$C,"Izra Advance",
-           [42]InvestingJournal!$A:$A,"&lt;="&amp;A26),
+    SUMIFS([43]InvestingJournal!$F:$F,
+           [43]InvestingJournal!$C:$C,"Izra Advance",
+           [43]InvestingJournal!$A:$A,"&lt;="&amp;A26),
     "")</f>
         <v>#VALUE!</v>
       </c>
       <c r="D26" s="15" t="e">
         <f>IF(A26&lt;&gt;"",
-    SUMIFS([42]InvestingJournal!$F:$F,
-           [42]InvestingJournal!$C:$C,"Loan Advance",
-           [42]InvestingJournal!$A:$A,"&lt;="&amp;A26),
+    SUMIFS([43]InvestingJournal!$F:$F,
+           [43]InvestingJournal!$C:$C,"Loan Advance",
+           [43]InvestingJournal!$A:$A,"&lt;="&amp;A26),
     "")</f>
         <v>#VALUE!</v>
       </c>
       <c r="E26" s="15" t="e">
         <f>IF(A26&lt;&gt;"",
-    SUMIFS([42]FinancingJournal!$E:$E,
-           [42]FinancingJournal!$C:$C,"Borrowing",
-           [42]FinancingJournal!$A:$A,"&lt;="&amp;A26)
+    SUMIFS([43]FinancingJournal!$E:$E,
+           [43]FinancingJournal!$C:$C,"Borrowing",
+           [43]FinancingJournal!$A:$A,"&lt;="&amp;A26)
     +
-    SUMIFS([42]FinancingJournal!$E:$E,
-           [42]FinancingJournal!$C:$C,"Withdrawal",
-           [42]FinancingJournal!$A:$A,"&lt;="&amp;A26),
+    SUMIFS([43]FinancingJournal!$E:$E,
+           [43]FinancingJournal!$C:$C,"Withdrawal",
+           [43]FinancingJournal!$A:$A,"&lt;="&amp;A26),
     "")</f>
         <v>#VALUE!</v>
       </c>
@@ -20381,37 +20682,37 @@
       </c>
       <c r="B27" s="17" t="e">
         <f>IF(A27&lt;&gt;"",
-    SUMIFS([42]FinancingJournal!$E:$E,
-           [42]FinancingJournal!$C:$C,"Capital Injection",
-           [42]FinancingJournal!$A:$A,"&lt;="&amp;A27),
+    SUMIFS([43]FinancingJournal!$E:$E,
+           [43]FinancingJournal!$C:$C,"Capital Injection",
+           [43]FinancingJournal!$A:$A,"&lt;="&amp;A27),
     "")</f>
         <v>#VALUE!</v>
       </c>
       <c r="C27" s="18" t="e">
         <f>IF(A27&lt;&gt;"",
-    SUMIFS([42]InvestingJournal!$F:$F,
-           [42]InvestingJournal!$C:$C,"Izra Advance",
-           [42]InvestingJournal!$A:$A,"&lt;="&amp;A27),
+    SUMIFS([43]InvestingJournal!$F:$F,
+           [43]InvestingJournal!$C:$C,"Izra Advance",
+           [43]InvestingJournal!$A:$A,"&lt;="&amp;A27),
     "")</f>
         <v>#VALUE!</v>
       </c>
       <c r="D27" s="18" t="e">
         <f>IF(A27&lt;&gt;"",
-    SUMIFS([42]InvestingJournal!$F:$F,
-           [42]InvestingJournal!$C:$C,"Loan Advance",
-           [42]InvestingJournal!$A:$A,"&lt;="&amp;A27),
+    SUMIFS([43]InvestingJournal!$F:$F,
+           [43]InvestingJournal!$C:$C,"Loan Advance",
+           [43]InvestingJournal!$A:$A,"&lt;="&amp;A27),
     "")</f>
         <v>#VALUE!</v>
       </c>
       <c r="E27" s="18" t="e">
         <f>IF(A27&lt;&gt;"",
-    SUMIFS([42]FinancingJournal!$E:$E,
-           [42]FinancingJournal!$C:$C,"Borrowing",
-           [42]FinancingJournal!$A:$A,"&lt;="&amp;A27)
+    SUMIFS([43]FinancingJournal!$E:$E,
+           [43]FinancingJournal!$C:$C,"Borrowing",
+           [43]FinancingJournal!$A:$A,"&lt;="&amp;A27)
     +
-    SUMIFS([42]FinancingJournal!$E:$E,
-           [42]FinancingJournal!$C:$C,"Withdrawal",
-           [42]FinancingJournal!$A:$A,"&lt;="&amp;A27),
+    SUMIFS([43]FinancingJournal!$E:$E,
+           [43]FinancingJournal!$C:$C,"Withdrawal",
+           [43]FinancingJournal!$A:$A,"&lt;="&amp;A27),
     "")</f>
         <v>#VALUE!</v>
       </c>
@@ -20438,37 +20739,37 @@
       </c>
       <c r="B28" s="14" t="e">
         <f>IF(A28&lt;&gt;"",
-    SUMIFS([42]FinancingJournal!$E:$E,
-           [42]FinancingJournal!$C:$C,"Capital Injection",
-           [42]FinancingJournal!$A:$A,"&lt;="&amp;A28),
+    SUMIFS([43]FinancingJournal!$E:$E,
+           [43]FinancingJournal!$C:$C,"Capital Injection",
+           [43]FinancingJournal!$A:$A,"&lt;="&amp;A28),
     "")</f>
         <v>#VALUE!</v>
       </c>
       <c r="C28" s="15" t="e">
         <f>IF(A28&lt;&gt;"",
-    SUMIFS([42]InvestingJournal!$F:$F,
-           [42]InvestingJournal!$C:$C,"Izra Advance",
-           [42]InvestingJournal!$A:$A,"&lt;="&amp;A28),
+    SUMIFS([43]InvestingJournal!$F:$F,
+           [43]InvestingJournal!$C:$C,"Izra Advance",
+           [43]InvestingJournal!$A:$A,"&lt;="&amp;A28),
     "")</f>
         <v>#VALUE!</v>
       </c>
       <c r="D28" s="15" t="e">
         <f>IF(A28&lt;&gt;"",
-    SUMIFS([42]InvestingJournal!$F:$F,
-           [42]InvestingJournal!$C:$C,"Loan Advance",
-           [42]InvestingJournal!$A:$A,"&lt;="&amp;A28),
+    SUMIFS([43]InvestingJournal!$F:$F,
+           [43]InvestingJournal!$C:$C,"Loan Advance",
+           [43]InvestingJournal!$A:$A,"&lt;="&amp;A28),
     "")</f>
         <v>#VALUE!</v>
       </c>
       <c r="E28" s="15" t="e">
         <f>IF(A28&lt;&gt;"",
-    SUMIFS([42]FinancingJournal!$E:$E,
-           [42]FinancingJournal!$C:$C,"Borrowing",
-           [42]FinancingJournal!$A:$A,"&lt;="&amp;A28)
+    SUMIFS([43]FinancingJournal!$E:$E,
+           [43]FinancingJournal!$C:$C,"Borrowing",
+           [43]FinancingJournal!$A:$A,"&lt;="&amp;A28)
     +
-    SUMIFS([42]FinancingJournal!$E:$E,
-           [42]FinancingJournal!$C:$C,"Withdrawal",
-           [42]FinancingJournal!$A:$A,"&lt;="&amp;A28),
+    SUMIFS([43]FinancingJournal!$E:$E,
+           [43]FinancingJournal!$C:$C,"Withdrawal",
+           [43]FinancingJournal!$A:$A,"&lt;="&amp;A28),
     "")</f>
         <v>#VALUE!</v>
       </c>
@@ -20494,37 +20795,37 @@
       </c>
       <c r="B29" s="17" t="e">
         <f>IF(A29&lt;&gt;"",
-    SUMIFS([42]FinancingJournal!$E:$E,
-           [42]FinancingJournal!$C:$C,"Capital Injection",
-           [42]FinancingJournal!$A:$A,"&lt;="&amp;A29),
+    SUMIFS([43]FinancingJournal!$E:$E,
+           [43]FinancingJournal!$C:$C,"Capital Injection",
+           [43]FinancingJournal!$A:$A,"&lt;="&amp;A29),
     "")</f>
         <v>#VALUE!</v>
       </c>
       <c r="C29" s="18" t="e">
         <f>IF(A29&lt;&gt;"",
-    SUMIFS([42]InvestingJournal!$F:$F,
-           [42]InvestingJournal!$C:$C,"Izra Advance",
-           [42]InvestingJournal!$A:$A,"&lt;="&amp;A29),
+    SUMIFS([43]InvestingJournal!$F:$F,
+           [43]InvestingJournal!$C:$C,"Izra Advance",
+           [43]InvestingJournal!$A:$A,"&lt;="&amp;A29),
     "")</f>
         <v>#VALUE!</v>
       </c>
       <c r="D29" s="18" t="e">
         <f>IF(A29&lt;&gt;"",
-    SUMIFS([42]InvestingJournal!$F:$F,
-           [42]InvestingJournal!$C:$C,"Loan Advance",
-           [42]InvestingJournal!$A:$A,"&lt;="&amp;A29),
+    SUMIFS([43]InvestingJournal!$F:$F,
+           [43]InvestingJournal!$C:$C,"Loan Advance",
+           [43]InvestingJournal!$A:$A,"&lt;="&amp;A29),
     "")</f>
         <v>#VALUE!</v>
       </c>
       <c r="E29" s="18" t="e">
         <f>IF(A29&lt;&gt;"",
-    SUMIFS([42]FinancingJournal!$E:$E,
-           [42]FinancingJournal!$C:$C,"Borrowing",
-           [42]FinancingJournal!$A:$A,"&lt;="&amp;A29)
+    SUMIFS([43]FinancingJournal!$E:$E,
+           [43]FinancingJournal!$C:$C,"Borrowing",
+           [43]FinancingJournal!$A:$A,"&lt;="&amp;A29)
     +
-    SUMIFS([42]FinancingJournal!$E:$E,
-           [42]FinancingJournal!$C:$C,"Withdrawal",
-           [42]FinancingJournal!$A:$A,"&lt;="&amp;A29),
+    SUMIFS([43]FinancingJournal!$E:$E,
+           [43]FinancingJournal!$C:$C,"Withdrawal",
+           [43]FinancingJournal!$A:$A,"&lt;="&amp;A29),
     "")</f>
         <v>#VALUE!</v>
       </c>
@@ -20551,9 +20852,9 @@
       </c>
       <c r="B30" s="14" t="e">
         <f>IF(A30&lt;&gt;"",
-    SUMIFS([42]FinancingJournal!$E:$E,
-           [42]FinancingJournal!$C:$C,"Capital Injection",
-           [42]FinancingJournal!$A:$A,"&lt;="&amp;A30),
+    SUMIFS([43]FinancingJournal!$E:$E,
+           [43]FinancingJournal!$C:$C,"Capital Injection",
+           [43]FinancingJournal!$A:$A,"&lt;="&amp;A30),
     "")</f>
         <v>#VALUE!</v>
       </c>
@@ -20562,9 +20863,9 @@
       </c>
       <c r="D30" s="15" t="e">
         <f>IF(A30&lt;&gt;"",
-    SUMIFS([42]InvestingJournal!$F:$F,
-           [42]InvestingJournal!$C:$C,"Loan Advance",
-           [42]InvestingJournal!$A:$A,"&lt;="&amp;A30),
+    SUMIFS([43]InvestingJournal!$F:$F,
+           [43]InvestingJournal!$C:$C,"Loan Advance",
+           [43]InvestingJournal!$A:$A,"&lt;="&amp;A30),
     "")</f>
         <v>#VALUE!</v>
       </c>
@@ -20593,9 +20894,9 @@
       </c>
       <c r="B31" s="17" t="e">
         <f>IF(A31&lt;&gt;"",
-    SUMIFS([42]FinancingJournal!$E:$E,
-           [42]FinancingJournal!$C:$C,"Capital Injection",
-           [42]FinancingJournal!$A:$A,"&lt;="&amp;A31),
+    SUMIFS([43]FinancingJournal!$E:$E,
+           [43]FinancingJournal!$C:$C,"Capital Injection",
+           [43]FinancingJournal!$A:$A,"&lt;="&amp;A31),
     "")</f>
         <v>#VALUE!</v>
       </c>
@@ -20604,9 +20905,9 @@
       </c>
       <c r="D31" s="18" t="e">
         <f>IF(A31&lt;&gt;"",
-    SUMIFS([42]InvestingJournal!$F:$F,
-           [42]InvestingJournal!$C:$C,"Loan Advance",
-           [42]InvestingJournal!$A:$A,"&lt;="&amp;A31),
+    SUMIFS([43]InvestingJournal!$F:$F,
+           [43]InvestingJournal!$C:$C,"Loan Advance",
+           [43]InvestingJournal!$A:$A,"&lt;="&amp;A31),
     "")</f>
         <v>#VALUE!</v>
       </c>
@@ -20636,25 +20937,25 @@
       </c>
       <c r="B32" s="14" t="e">
         <f>IF(A32&lt;&gt;"",
-    SUMIFS([42]FinancingJournal!$E:$E,
-           [42]FinancingJournal!$C:$C,"Capital Injection",
-           [42]FinancingJournal!$A:$A,"&lt;="&amp;A32),
+    SUMIFS([43]FinancingJournal!$E:$E,
+           [43]FinancingJournal!$C:$C,"Capital Injection",
+           [43]FinancingJournal!$A:$A,"&lt;="&amp;A32),
     "")</f>
         <v>#VALUE!</v>
       </c>
       <c r="C32" s="15" t="e">
         <f>IF(A32&lt;&gt;"",
-    SUMIFS([42]InvestingJournal!$F:$F,
-           [42]InvestingJournal!$C:$C,"Izra Advance",
-           [42]InvestingJournal!$A:$A,"&lt;="&amp;A32),
+    SUMIFS([43]InvestingJournal!$F:$F,
+           [43]InvestingJournal!$C:$C,"Izra Advance",
+           [43]InvestingJournal!$A:$A,"&lt;="&amp;A32),
     "")</f>
         <v>#VALUE!</v>
       </c>
       <c r="D32" s="15" t="e">
         <f>IF(A32&lt;&gt;"",
-    SUMIFS([42]InvestingJournal!$F:$F,
-           [42]InvestingJournal!$C:$C,"Loan Advance",
-           [42]InvestingJournal!$A:$A,"&lt;="&amp;A32),
+    SUMIFS([43]InvestingJournal!$F:$F,
+           [43]InvestingJournal!$C:$C,"Loan Advance",
+           [43]InvestingJournal!$A:$A,"&lt;="&amp;A32),
     "")</f>
         <v>#VALUE!</v>
       </c>
@@ -20683,37 +20984,37 @@
       </c>
       <c r="B33" s="17" t="e">
         <f>IF(A33&lt;&gt;"",
-    SUMIFS([42]FinancingJournal!$E:$E,
-           [42]FinancingJournal!$C:$C,"Capital Injection",
-           [42]FinancingJournal!$A:$A,"&lt;="&amp;A33),
+    SUMIFS([43]FinancingJournal!$E:$E,
+           [43]FinancingJournal!$C:$C,"Capital Injection",
+           [43]FinancingJournal!$A:$A,"&lt;="&amp;A33),
     "")</f>
         <v>#VALUE!</v>
       </c>
       <c r="C33" s="18" t="e">
         <f>IF(A33&lt;&gt;"",
-    SUMIFS([42]InvestingJournal!$F:$F,
-           [42]InvestingJournal!$C:$C,"Izra Advance",
-           [42]InvestingJournal!$A:$A,"&lt;="&amp;A33),
+    SUMIFS([43]InvestingJournal!$F:$F,
+           [43]InvestingJournal!$C:$C,"Izra Advance",
+           [43]InvestingJournal!$A:$A,"&lt;="&amp;A33),
     "")</f>
         <v>#VALUE!</v>
       </c>
       <c r="D33" s="18" t="e">
         <f>IF(A33&lt;&gt;"",
-    SUMIFS([42]InvestingJournal!$F:$F,
-           [42]InvestingJournal!$C:$C,"Loan Advance",
-           [42]InvestingJournal!$A:$A,"&lt;="&amp;A33),
+    SUMIFS([43]InvestingJournal!$F:$F,
+           [43]InvestingJournal!$C:$C,"Loan Advance",
+           [43]InvestingJournal!$A:$A,"&lt;="&amp;A33),
     "")</f>
         <v>#VALUE!</v>
       </c>
       <c r="E33" s="18" t="e">
         <f>IF(A33&lt;&gt;"",
-    SUMIFS([42]FinancingJournal!$E:$E,
-           [42]FinancingJournal!$C:$C,"Borrowing",
-           [42]FinancingJournal!$A:$A,"&lt;="&amp;A33)
+    SUMIFS([43]FinancingJournal!$E:$E,
+           [43]FinancingJournal!$C:$C,"Borrowing",
+           [43]FinancingJournal!$A:$A,"&lt;="&amp;A33)
     +
-    SUMIFS([42]FinancingJournal!$E:$E,
-           [42]FinancingJournal!$C:$C,"Withdrawal",
-           [42]FinancingJournal!$A:$A,"&lt;="&amp;A33),
+    SUMIFS([43]FinancingJournal!$E:$E,
+           [43]FinancingJournal!$C:$C,"Withdrawal",
+           [43]FinancingJournal!$A:$A,"&lt;="&amp;A33),
     "")</f>
         <v>#VALUE!</v>
       </c>
@@ -20740,37 +21041,37 @@
       </c>
       <c r="B34" s="14" t="e">
         <f>IF(A34&lt;&gt;"",
-    SUMIFS([42]FinancingJournal!$E:$E,
-           [42]FinancingJournal!$C:$C,"Capital Injection",
-           [42]FinancingJournal!$A:$A,"&lt;="&amp;A34),
+    SUMIFS([43]FinancingJournal!$E:$E,
+           [43]FinancingJournal!$C:$C,"Capital Injection",
+           [43]FinancingJournal!$A:$A,"&lt;="&amp;A34),
     "")</f>
         <v>#VALUE!</v>
       </c>
       <c r="C34" s="15" t="e">
         <f>IF(A34&lt;&gt;"",
-    SUMIFS([42]InvestingJournal!$F:$F,
-           [42]InvestingJournal!$C:$C,"Izra Advance",
-           [42]InvestingJournal!$A:$A,"&lt;="&amp;A34),
+    SUMIFS([43]InvestingJournal!$F:$F,
+           [43]InvestingJournal!$C:$C,"Izra Advance",
+           [43]InvestingJournal!$A:$A,"&lt;="&amp;A34),
     "")</f>
         <v>#VALUE!</v>
       </c>
       <c r="D34" s="15" t="e">
         <f>IF(A34&lt;&gt;"",
-    SUMIFS([42]InvestingJournal!$F:$F,
-           [42]InvestingJournal!$C:$C,"Loan Advance",
-           [42]InvestingJournal!$A:$A,"&lt;="&amp;A34),
+    SUMIFS([43]InvestingJournal!$F:$F,
+           [43]InvestingJournal!$C:$C,"Loan Advance",
+           [43]InvestingJournal!$A:$A,"&lt;="&amp;A34),
     "")</f>
         <v>#VALUE!</v>
       </c>
       <c r="E34" s="15" t="e">
         <f>IF(A34&lt;&gt;"",
-    SUMIFS([42]FinancingJournal!$E:$E,
-           [42]FinancingJournal!$C:$C,"Borrowing",
-           [42]FinancingJournal!$A:$A,"&lt;="&amp;A34)
+    SUMIFS([43]FinancingJournal!$E:$E,
+           [43]FinancingJournal!$C:$C,"Borrowing",
+           [43]FinancingJournal!$A:$A,"&lt;="&amp;A34)
     +
-    SUMIFS([42]FinancingJournal!$E:$E,
-           [42]FinancingJournal!$C:$C,"Withdrawal",
-           [42]FinancingJournal!$A:$A,"&lt;="&amp;A34),
+    SUMIFS([43]FinancingJournal!$E:$E,
+           [43]FinancingJournal!$C:$C,"Withdrawal",
+           [43]FinancingJournal!$A:$A,"&lt;="&amp;A34),
     "")</f>
         <v>#VALUE!</v>
       </c>
@@ -20796,37 +21097,37 @@
       </c>
       <c r="B35" s="17" t="e">
         <f>IF(A35&lt;&gt;"",
-    SUMIFS([42]FinancingJournal!$E:$E,
-           [42]FinancingJournal!$C:$C,"Capital Injection",
-           [42]FinancingJournal!$A:$A,"&lt;="&amp;A35),
+    SUMIFS([43]FinancingJournal!$E:$E,
+           [43]FinancingJournal!$C:$C,"Capital Injection",
+           [43]FinancingJournal!$A:$A,"&lt;="&amp;A35),
     "")</f>
         <v>#VALUE!</v>
       </c>
       <c r="C35" s="18" t="e">
         <f>IF(A35&lt;&gt;"",
-    SUMIFS([42]InvestingJournal!$F:$F,
-           [42]InvestingJournal!$C:$C,"Izra Advance",
-           [42]InvestingJournal!$A:$A,"&lt;="&amp;A35),
+    SUMIFS([43]InvestingJournal!$F:$F,
+           [43]InvestingJournal!$C:$C,"Izra Advance",
+           [43]InvestingJournal!$A:$A,"&lt;="&amp;A35),
     "")</f>
         <v>#VALUE!</v>
       </c>
       <c r="D35" s="18" t="e">
         <f>IF(A35&lt;&gt;"",
-    SUMIFS([42]InvestingJournal!$F:$F,
-           [42]InvestingJournal!$C:$C,"Loan Advance",
-           [42]InvestingJournal!$A:$A,"&lt;="&amp;A35),
+    SUMIFS([43]InvestingJournal!$F:$F,
+           [43]InvestingJournal!$C:$C,"Loan Advance",
+           [43]InvestingJournal!$A:$A,"&lt;="&amp;A35),
     "")</f>
         <v>#VALUE!</v>
       </c>
       <c r="E35" s="18" t="e">
         <f>IF(A35&lt;&gt;"",
-    SUMIFS([42]FinancingJournal!$E:$E,
-           [42]FinancingJournal!$C:$C,"Borrowing",
-           [42]FinancingJournal!$A:$A,"&lt;="&amp;A35)
+    SUMIFS([43]FinancingJournal!$E:$E,
+           [43]FinancingJournal!$C:$C,"Borrowing",
+           [43]FinancingJournal!$A:$A,"&lt;="&amp;A35)
     +
-    SUMIFS([42]FinancingJournal!$E:$E,
-           [42]FinancingJournal!$C:$C,"Withdrawal",
-           [42]FinancingJournal!$A:$A,"&lt;="&amp;A35),
+    SUMIFS([43]FinancingJournal!$E:$E,
+           [43]FinancingJournal!$C:$C,"Withdrawal",
+           [43]FinancingJournal!$A:$A,"&lt;="&amp;A35),
     "")</f>
         <v>#VALUE!</v>
       </c>
@@ -20853,37 +21154,37 @@
       </c>
       <c r="B36" s="14" t="e">
         <f>IF(A36&lt;&gt;"",
-    SUMIFS([42]FinancingJournal!$E:$E,
-           [42]FinancingJournal!$C:$C,"Capital Injection",
-           [42]FinancingJournal!$A:$A,"&lt;="&amp;A36),
+    SUMIFS([43]FinancingJournal!$E:$E,
+           [43]FinancingJournal!$C:$C,"Capital Injection",
+           [43]FinancingJournal!$A:$A,"&lt;="&amp;A36),
     "")</f>
         <v>#VALUE!</v>
       </c>
       <c r="C36" s="15" t="e">
         <f>IF(A36&lt;&gt;"",
-    SUMIFS([42]InvestingJournal!$F:$F,
-           [42]InvestingJournal!$C:$C,"Izra Advance",
-           [42]InvestingJournal!$A:$A,"&lt;="&amp;A36),
+    SUMIFS([43]InvestingJournal!$F:$F,
+           [43]InvestingJournal!$C:$C,"Izra Advance",
+           [43]InvestingJournal!$A:$A,"&lt;="&amp;A36),
     "")</f>
         <v>#VALUE!</v>
       </c>
       <c r="D36" s="15" t="e">
         <f>IF(A36&lt;&gt;"",
-    SUMIFS([42]InvestingJournal!$F:$F,
-           [42]InvestingJournal!$C:$C,"Loan Advance",
-           [42]InvestingJournal!$A:$A,"&lt;="&amp;A36),
+    SUMIFS([43]InvestingJournal!$F:$F,
+           [43]InvestingJournal!$C:$C,"Loan Advance",
+           [43]InvestingJournal!$A:$A,"&lt;="&amp;A36),
     "")</f>
         <v>#VALUE!</v>
       </c>
       <c r="E36" s="15" t="e">
         <f>IF(A36&lt;&gt;"",
-    SUMIFS([42]FinancingJournal!$E:$E,
-           [42]FinancingJournal!$C:$C,"Borrowing",
-           [42]FinancingJournal!$A:$A,"&lt;="&amp;A36)
+    SUMIFS([43]FinancingJournal!$E:$E,
+           [43]FinancingJournal!$C:$C,"Borrowing",
+           [43]FinancingJournal!$A:$A,"&lt;="&amp;A36)
     +
-    SUMIFS([42]FinancingJournal!$E:$E,
-           [42]FinancingJournal!$C:$C,"Withdrawal",
-           [42]FinancingJournal!$A:$A,"&lt;="&amp;A36),
+    SUMIFS([43]FinancingJournal!$E:$E,
+           [43]FinancingJournal!$C:$C,"Withdrawal",
+           [43]FinancingJournal!$A:$A,"&lt;="&amp;A36),
     "")</f>
         <v>#VALUE!</v>
       </c>
@@ -20909,9 +21210,9 @@
       </c>
       <c r="B37" s="17" t="e">
         <f>IF(A37&lt;&gt;"",
-    SUMIFS([42]FinancingJournal!$E:$E,
-           [42]FinancingJournal!$C:$C,"Capital Injection",
-           [42]FinancingJournal!$A:$A,"&lt;="&amp;A37),
+    SUMIFS([43]FinancingJournal!$E:$E,
+           [43]FinancingJournal!$C:$C,"Capital Injection",
+           [43]FinancingJournal!$A:$A,"&lt;="&amp;A37),
     "")</f>
         <v>#VALUE!</v>
       </c>
@@ -20920,9 +21221,9 @@
       </c>
       <c r="D37" s="18" t="e">
         <f>IF(A37&lt;&gt;"",
-    SUMIFS([42]InvestingJournal!$F:$F,
-           [42]InvestingJournal!$C:$C,"Loan Advance",
-           [42]InvestingJournal!$A:$A,"&lt;="&amp;A37),
+    SUMIFS([43]InvestingJournal!$F:$F,
+           [43]InvestingJournal!$C:$C,"Loan Advance",
+           [43]InvestingJournal!$A:$A,"&lt;="&amp;A37),
     "")</f>
         <v>#VALUE!</v>
       </c>
@@ -20950,9 +21251,9 @@
       </c>
       <c r="B38" s="14" t="e">
         <f>IF(A38&lt;&gt;"",
-    SUMIFS([42]FinancingJournal!$E:$E,
-           [42]FinancingJournal!$C:$C,"Capital Injection",
-           [42]FinancingJournal!$A:$A,"&lt;="&amp;A38),
+    SUMIFS([43]FinancingJournal!$E:$E,
+           [43]FinancingJournal!$C:$C,"Capital Injection",
+           [43]FinancingJournal!$A:$A,"&lt;="&amp;A38),
     "")</f>
         <v>#VALUE!</v>
       </c>
@@ -20961,9 +21262,9 @@
       </c>
       <c r="D38" s="15" t="e">
         <f>IF(A38&lt;&gt;"",
-    SUMIFS([42]InvestingJournal!$F:$F,
-           [42]InvestingJournal!$C:$C,"Loan Advance",
-           [42]InvestingJournal!$A:$A,"&lt;="&amp;A38),
+    SUMIFS([43]InvestingJournal!$F:$F,
+           [43]InvestingJournal!$C:$C,"Loan Advance",
+           [43]InvestingJournal!$A:$A,"&lt;="&amp;A38),
     "")</f>
         <v>#VALUE!</v>
       </c>
@@ -20992,9 +21293,9 @@
       </c>
       <c r="B39" s="17" t="e">
         <f>IF(A39&lt;&gt;"",
-    SUMIFS([42]FinancingJournal!$E:$E,
-           [42]FinancingJournal!$C:$C,"Capital Injection",
-           [42]FinancingJournal!$A:$A,"&lt;="&amp;A39),
+    SUMIFS([43]FinancingJournal!$E:$E,
+           [43]FinancingJournal!$C:$C,"Capital Injection",
+           [43]FinancingJournal!$A:$A,"&lt;="&amp;A39),
     "")</f>
         <v>#VALUE!</v>
       </c>
@@ -21003,9 +21304,9 @@
       </c>
       <c r="D39" s="18" t="e">
         <f>IF(A39&lt;&gt;"",
-    SUMIFS([42]InvestingJournal!$F:$F,
-           [42]InvestingJournal!$C:$C,"Loan Advance",
-           [42]InvestingJournal!$A:$A,"&lt;="&amp;A39),
+    SUMIFS([43]InvestingJournal!$F:$F,
+           [43]InvestingJournal!$C:$C,"Loan Advance",
+           [43]InvestingJournal!$A:$A,"&lt;="&amp;A39),
     "")</f>
         <v>#VALUE!</v>
       </c>
@@ -21035,9 +21336,9 @@
       </c>
       <c r="B40" s="14" t="e">
         <f>IF(A40&lt;&gt;"",
-    SUMIFS([42]FinancingJournal!$E:$E,
-           [42]FinancingJournal!$C:$C,"Capital Injection",
-           [42]FinancingJournal!$A:$A,"&lt;="&amp;A40),
+    SUMIFS([43]FinancingJournal!$E:$E,
+           [43]FinancingJournal!$C:$C,"Capital Injection",
+           [43]FinancingJournal!$A:$A,"&lt;="&amp;A40),
     "")</f>
         <v>#VALUE!</v>
       </c>
@@ -21046,21 +21347,21 @@
       </c>
       <c r="D40" s="15" t="e">
         <f>IF(A40&lt;&gt;"",
-    SUMIFS([42]InvestingJournal!$F:$F,
-           [42]InvestingJournal!$C:$C,"Loan Advance",
-           [42]InvestingJournal!$A:$A,"&lt;="&amp;A40),
+    SUMIFS([43]InvestingJournal!$F:$F,
+           [43]InvestingJournal!$C:$C,"Loan Advance",
+           [43]InvestingJournal!$A:$A,"&lt;="&amp;A40),
     "")</f>
         <v>#VALUE!</v>
       </c>
       <c r="E40" s="15" t="e">
         <f>IF(A40&lt;&gt;"",
-    SUMIFS([42]FinancingJournal!$E:$E,
-           [42]FinancingJournal!$C:$C,"Borrowing",
-           [42]FinancingJournal!$A:$A,"&lt;="&amp;A40)
+    SUMIFS([43]FinancingJournal!$E:$E,
+           [43]FinancingJournal!$C:$C,"Borrowing",
+           [43]FinancingJournal!$A:$A,"&lt;="&amp;A40)
     +
-    SUMIFS([42]FinancingJournal!$E:$E,
-           [42]FinancingJournal!$C:$C,"Withdrawal",
-           [42]FinancingJournal!$A:$A,"&lt;="&amp;A40),
+    SUMIFS([43]FinancingJournal!$E:$E,
+           [43]FinancingJournal!$C:$C,"Withdrawal",
+           [43]FinancingJournal!$A:$A,"&lt;="&amp;A40),
     "")</f>
         <v>#VALUE!</v>
       </c>
@@ -21086,41 +21387,41 @@
       </c>
       <c r="B41" s="17" t="e">
         <f>IF(A41&lt;&gt;"",
-    SUMIFS([42]FinancingJournal!$E:$E,
-           [42]FinancingJournal!$C:$C,"Capital Injection",
-           [42]FinancingJournal!$A:$A,"&lt;="&amp;A41),
+    SUMIFS([43]FinancingJournal!$E:$E,
+           [43]FinancingJournal!$C:$C,"Capital Injection",
+           [43]FinancingJournal!$A:$A,"&lt;="&amp;A41),
     "")</f>
         <v>#VALUE!</v>
       </c>
       <c r="C41" s="18" t="e">
         <f>IF(A41&lt;&gt;"",
-    SUMIFS([42]InvestingJournal!$F:$F,
-           [42]InvestingJournal!$C:$C,"Izra Advance",
-           [42]InvestingJournal!$A:$A,"&lt;="&amp;A41)
+    SUMIFS([43]InvestingJournal!$F:$F,
+           [43]InvestingJournal!$C:$C,"Izra Advance",
+           [43]InvestingJournal!$A:$A,"&lt;="&amp;A41)
     +
-    SUMIFS([42]InvestingJournal!$F:$F,
-           [42]InvestingJournal!$C:$C,"Investment to Unit",
-           [42]InvestingJournal!$A:$A,"&lt;="&amp;A41),
+    SUMIFS([43]InvestingJournal!$F:$F,
+           [43]InvestingJournal!$C:$C,"Investment to Unit",
+           [43]InvestingJournal!$A:$A,"&lt;="&amp;A41),
     "")</f>
         <v>#VALUE!</v>
       </c>
       <c r="D41" s="18" t="e">
         <f>IF(A41&lt;&gt;"",
-    SUMIFS([42]InvestingJournal!$F:$F,
-           [42]InvestingJournal!$C:$C,"Loan Advance",
-           [42]InvestingJournal!$A:$A,"&lt;="&amp;A41),
+    SUMIFS([43]InvestingJournal!$F:$F,
+           [43]InvestingJournal!$C:$C,"Loan Advance",
+           [43]InvestingJournal!$A:$A,"&lt;="&amp;A41),
     "")</f>
         <v>#VALUE!</v>
       </c>
       <c r="E41" s="18" t="e">
         <f>IF(A41&lt;&gt;"",
-    SUMIFS([42]FinancingJournal!$E:$E,
-           [42]FinancingJournal!$C:$C,"Borrowing",
-           [42]FinancingJournal!$A:$A,"&lt;="&amp;A41)
+    SUMIFS([43]FinancingJournal!$E:$E,
+           [43]FinancingJournal!$C:$C,"Borrowing",
+           [43]FinancingJournal!$A:$A,"&lt;="&amp;A41)
     +
-    SUMIFS([42]FinancingJournal!$E:$E,
-           [42]FinancingJournal!$C:$C,"Withdrawal",
-           [42]FinancingJournal!$A:$A,"&lt;="&amp;A41),
+    SUMIFS([43]FinancingJournal!$E:$E,
+           [43]FinancingJournal!$C:$C,"Withdrawal",
+           [43]FinancingJournal!$A:$A,"&lt;="&amp;A41),
     "")</f>
         <v>#VALUE!</v>
       </c>
@@ -21147,41 +21448,41 @@
       </c>
       <c r="B42" s="14" t="e">
         <f>IF(A42&lt;&gt;"",
-    SUMIFS([42]FinancingJournal!$E:$E,
-           [42]FinancingJournal!$C:$C,"Capital Injection",
-           [42]FinancingJournal!$A:$A,"&lt;="&amp;A42),
+    SUMIFS([43]FinancingJournal!$E:$E,
+           [43]FinancingJournal!$C:$C,"Capital Injection",
+           [43]FinancingJournal!$A:$A,"&lt;="&amp;A42),
     "")</f>
         <v>#VALUE!</v>
       </c>
       <c r="C42" s="15" t="e">
         <f>IF(A42&lt;&gt;"",
-    SUMIFS([42]InvestingJournal!$F:$F,
-           [42]InvestingJournal!$C:$C,"Izra Advance",
-           [42]InvestingJournal!$A:$A,"&lt;="&amp;A42)
+    SUMIFS([43]InvestingJournal!$F:$F,
+           [43]InvestingJournal!$C:$C,"Izra Advance",
+           [43]InvestingJournal!$A:$A,"&lt;="&amp;A42)
     +
-    SUMIFS([42]InvestingJournal!$F:$F,
-           [42]InvestingJournal!$C:$C,"Investment to Unit",
-           [42]InvestingJournal!$A:$A,"&lt;="&amp;A42),
+    SUMIFS([43]InvestingJournal!$F:$F,
+           [43]InvestingJournal!$C:$C,"Investment to Unit",
+           [43]InvestingJournal!$A:$A,"&lt;="&amp;A42),
     "")</f>
         <v>#VALUE!</v>
       </c>
       <c r="D42" s="15" t="e">
         <f>IF(A42&lt;&gt;"",
-    SUMIFS([42]InvestingJournal!$F:$F,
-           [42]InvestingJournal!$C:$C,"Loan Advance",
-           [42]InvestingJournal!$A:$A,"&lt;="&amp;A42),
+    SUMIFS([43]InvestingJournal!$F:$F,
+           [43]InvestingJournal!$C:$C,"Loan Advance",
+           [43]InvestingJournal!$A:$A,"&lt;="&amp;A42),
     "")</f>
         <v>#VALUE!</v>
       </c>
       <c r="E42" s="15" t="e">
         <f>IF(A42&lt;&gt;"",
-    SUMIFS([42]FinancingJournal!$E:$E,
-           [42]FinancingJournal!$C:$C,"Borrowing",
-           [42]FinancingJournal!$A:$A,"&lt;="&amp;A42)
+    SUMIFS([43]FinancingJournal!$E:$E,
+           [43]FinancingJournal!$C:$C,"Borrowing",
+           [43]FinancingJournal!$A:$A,"&lt;="&amp;A42)
     +
-    SUMIFS([42]FinancingJournal!$E:$E,
-           [42]FinancingJournal!$C:$C,"Withdrawal",
-           [42]FinancingJournal!$A:$A,"&lt;="&amp;A42),
+    SUMIFS([43]FinancingJournal!$E:$E,
+           [43]FinancingJournal!$C:$C,"Withdrawal",
+           [43]FinancingJournal!$A:$A,"&lt;="&amp;A42),
     "")</f>
         <v>#VALUE!</v>
       </c>
@@ -21207,9 +21508,9 @@
       </c>
       <c r="B43" s="17" t="e">
         <f>IF(A43&lt;&gt;"",
-    SUMIFS([42]FinancingJournal!$E:$E,
-           [42]FinancingJournal!$C:$C,"Capital Injection",
-           [42]FinancingJournal!$A:$A,"&lt;="&amp;A43),
+    SUMIFS([43]FinancingJournal!$E:$E,
+           [43]FinancingJournal!$C:$C,"Capital Injection",
+           [43]FinancingJournal!$A:$A,"&lt;="&amp;A43),
     "")</f>
         <v>#VALUE!</v>
       </c>
@@ -21243,41 +21544,41 @@
       </c>
       <c r="B44" s="14" t="e">
         <f>IF(A44&lt;&gt;"",
-    SUMIFS([42]FinancingJournal!$E:$E,
-           [42]FinancingJournal!$C:$C,"Capital Injection",
-           [42]FinancingJournal!$A:$A,"&lt;="&amp;A44),
+    SUMIFS([43]FinancingJournal!$E:$E,
+           [43]FinancingJournal!$C:$C,"Capital Injection",
+           [43]FinancingJournal!$A:$A,"&lt;="&amp;A44),
     "")</f>
         <v>#VALUE!</v>
       </c>
       <c r="C44" s="15" t="e">
         <f>IF(A44&lt;&gt;"",
-    SUMIFS([42]InvestingJournal!$F:$F,
-           [42]InvestingJournal!$C:$C,"Izra Advance",
-           [42]InvestingJournal!$A:$A,"&lt;="&amp;A44)
+    SUMIFS([43]InvestingJournal!$F:$F,
+           [43]InvestingJournal!$C:$C,"Izra Advance",
+           [43]InvestingJournal!$A:$A,"&lt;="&amp;A44)
     +
-    SUMIFS([42]InvestingJournal!$F:$F,
-           [42]InvestingJournal!$C:$C,"Investment to Unit",
-           [42]InvestingJournal!$A:$A,"&lt;="&amp;A44),
+    SUMIFS([43]InvestingJournal!$F:$F,
+           [43]InvestingJournal!$C:$C,"Investment to Unit",
+           [43]InvestingJournal!$A:$A,"&lt;="&amp;A44),
     "")</f>
         <v>#VALUE!</v>
       </c>
       <c r="D44" s="15" t="e">
         <f>IF(A44&lt;&gt;"",
-    SUMIFS([42]InvestingJournal!$F:$F,
-           [42]InvestingJournal!$C:$C,"Loan Advance",
-           [42]InvestingJournal!$A:$A,"&lt;="&amp;A44),
+    SUMIFS([43]InvestingJournal!$F:$F,
+           [43]InvestingJournal!$C:$C,"Loan Advance",
+           [43]InvestingJournal!$A:$A,"&lt;="&amp;A44),
     "")</f>
         <v>#VALUE!</v>
       </c>
       <c r="E44" s="15" t="e">
         <f>IF(A44&lt;&gt;"",
-    SUMIFS([42]FinancingJournal!$E:$E,
-           [42]FinancingJournal!$C:$C,"Borrowing",
-           [42]FinancingJournal!$A:$A,"&lt;="&amp;A44)
+    SUMIFS([43]FinancingJournal!$E:$E,
+           [43]FinancingJournal!$C:$C,"Borrowing",
+           [43]FinancingJournal!$A:$A,"&lt;="&amp;A44)
     +
-    SUMIFS([42]FinancingJournal!$E:$E,
-           [42]FinancingJournal!$C:$C,"Withdrawal",
-           [42]FinancingJournal!$A:$A,"&lt;="&amp;A44),
+    SUMIFS([43]FinancingJournal!$E:$E,
+           [43]FinancingJournal!$C:$C,"Withdrawal",
+           [43]FinancingJournal!$A:$A,"&lt;="&amp;A44),
     "")</f>
         <v>#VALUE!</v>
       </c>
@@ -21303,9 +21604,9 @@
       </c>
       <c r="B45" s="17" t="e">
         <f>IF(A45&lt;&gt;"",
-    SUMIFS([42]FinancingJournal!$E:$E,
-           [42]FinancingJournal!$C:$C,"Capital Injection",
-           [42]FinancingJournal!$A:$A,"&lt;="&amp;A45),
+    SUMIFS([43]FinancingJournal!$E:$E,
+           [43]FinancingJournal!$C:$C,"Capital Injection",
+           [43]FinancingJournal!$A:$A,"&lt;="&amp;A45),
     "")</f>
         <v>#VALUE!</v>
       </c>
@@ -21339,9 +21640,9 @@
       </c>
       <c r="B46" s="14" t="e">
         <f>IF(A46&lt;&gt;"",
-    SUMIFS([42]FinancingJournal!$E:$E,
-           [42]FinancingJournal!$C:$C,"Capital Injection",
-           [42]FinancingJournal!$A:$A,"&lt;="&amp;A46),
+    SUMIFS([43]FinancingJournal!$E:$E,
+           [43]FinancingJournal!$C:$C,"Capital Injection",
+           [43]FinancingJournal!$A:$A,"&lt;="&amp;A46),
     "")</f>
         <v>#VALUE!</v>
       </c>
@@ -21376,9 +21677,9 @@
       </c>
       <c r="B47" s="17" t="e">
         <f>IF(A47&lt;&gt;"",
-    SUMIFS([42]FinancingJournal!$E:$E,
-           [42]FinancingJournal!$C:$C,"Capital Injection",
-           [42]FinancingJournal!$A:$A,"&lt;="&amp;A47),
+    SUMIFS([43]FinancingJournal!$E:$E,
+           [43]FinancingJournal!$C:$C,"Capital Injection",
+           [43]FinancingJournal!$A:$A,"&lt;="&amp;A47),
     "")</f>
         <v>#VALUE!</v>
       </c>
@@ -21412,9 +21713,9 @@
       </c>
       <c r="B48" s="14" t="e">
         <f>IF(A48&lt;&gt;"",
-    SUMIFS([42]FinancingJournal!$E:$E,
-           [42]FinancingJournal!$C:$C,"Capital Injection",
-           [42]FinancingJournal!$A:$A,"&lt;="&amp;A48),
+    SUMIFS([43]FinancingJournal!$E:$E,
+           [43]FinancingJournal!$C:$C,"Capital Injection",
+           [43]FinancingJournal!$A:$A,"&lt;="&amp;A48),
     "")</f>
         <v>#VALUE!</v>
       </c>
@@ -21449,9 +21750,9 @@
       </c>
       <c r="B49" s="17" t="e">
         <f>IF(A49&lt;&gt;"",
-    SUMIFS([42]FinancingJournal!$E:$E,
-           [42]FinancingJournal!$C:$C,"Capital Injection",
-           [42]FinancingJournal!$A:$A,"&lt;="&amp;A49),
+    SUMIFS([43]FinancingJournal!$E:$E,
+           [43]FinancingJournal!$C:$C,"Capital Injection",
+           [43]FinancingJournal!$A:$A,"&lt;="&amp;A49),
     "")</f>
         <v>#VALUE!</v>
       </c>
@@ -21485,29 +21786,29 @@
       </c>
       <c r="B50" s="14" t="e">
         <f>IF(A50&lt;&gt;"",
-    SUMIFS([42]FinancingJournal!$E:$E,
-           [42]FinancingJournal!$C:$C,"Capital Injection",
-           [42]FinancingJournal!$A:$A,"&lt;="&amp;A50),
+    SUMIFS([43]FinancingJournal!$E:$E,
+           [43]FinancingJournal!$C:$C,"Capital Injection",
+           [43]FinancingJournal!$A:$A,"&lt;="&amp;A50),
     "")</f>
         <v>#VALUE!</v>
       </c>
       <c r="C50" s="15" t="e">
         <f>IF(A50&lt;&gt;"",
-    SUMIFS([42]InvestingJournal!$F:$F,
-           [42]InvestingJournal!$C:$C,"Izra Advance",
-           [42]InvestingJournal!$A:$A,"&lt;="&amp;A50)
+    SUMIFS([43]InvestingJournal!$F:$F,
+           [43]InvestingJournal!$C:$C,"Izra Advance",
+           [43]InvestingJournal!$A:$A,"&lt;="&amp;A50)
     +
-    SUMIFS([42]InvestingJournal!$F:$F,
-           [42]InvestingJournal!$C:$C,"Investment to Unit",
-           [42]InvestingJournal!$A:$A,"&lt;="&amp;A50),
+    SUMIFS([43]InvestingJournal!$F:$F,
+           [43]InvestingJournal!$C:$C,"Investment to Unit",
+           [43]InvestingJournal!$A:$A,"&lt;="&amp;A50),
     "")</f>
         <v>#VALUE!</v>
       </c>
       <c r="D50" s="15" t="e">
         <f>IF(A50&lt;&gt;"",
-    SUMIFS([42]InvestingJournal!$F:$F,
-           [42]InvestingJournal!$C:$C,"Loan Advance",
-           [42]InvestingJournal!$A:$A,"&lt;="&amp;A50),
+    SUMIFS([43]InvestingJournal!$F:$F,
+           [43]InvestingJournal!$C:$C,"Loan Advance",
+           [43]InvestingJournal!$A:$A,"&lt;="&amp;A50),
     "")</f>
         <v>#VALUE!</v>
       </c>
@@ -21536,9 +21837,9 @@
       </c>
       <c r="B51" s="17" t="e">
         <f>IF(A51&lt;&gt;"",
-    SUMIFS([42]FinancingJournal!$E:$E,
-           [42]FinancingJournal!$C:$C,"Capital Injection",
-           [42]FinancingJournal!$A:$A,"&lt;="&amp;A51),
+    SUMIFS([43]FinancingJournal!$E:$E,
+           [43]FinancingJournal!$C:$C,"Capital Injection",
+           [43]FinancingJournal!$A:$A,"&lt;="&amp;A51),
     "")</f>
         <v>#VALUE!</v>
       </c>
@@ -21572,9 +21873,9 @@
       </c>
       <c r="B52" s="14" t="e">
         <f>IF(A52&lt;&gt;"",
-    SUMIFS([42]FinancingJournal!$E:$E,
-           [42]FinancingJournal!$C:$C,"Capital Injection",
-           [42]FinancingJournal!$A:$A,"&lt;="&amp;A52),
+    SUMIFS([43]FinancingJournal!$E:$E,
+           [43]FinancingJournal!$C:$C,"Capital Injection",
+           [43]FinancingJournal!$A:$A,"&lt;="&amp;A52),
     "")</f>
         <v>#VALUE!</v>
       </c>
@@ -21609,9 +21910,9 @@
       </c>
       <c r="B53" s="17" t="e">
         <f>IF(A53&lt;&gt;"",
-    SUMIFS([42]FinancingJournal!$E:$E,
-           [42]FinancingJournal!$C:$C,"Capital Injection",
-           [42]FinancingJournal!$A:$A,"&lt;="&amp;A53),
+    SUMIFS([43]FinancingJournal!$E:$E,
+           [43]FinancingJournal!$C:$C,"Capital Injection",
+           [43]FinancingJournal!$A:$A,"&lt;="&amp;A53),
     "")</f>
         <v>#VALUE!</v>
       </c>
@@ -21647,9 +21948,9 @@
       </c>
       <c r="B54" s="14" t="e">
         <f>IF(A54&lt;&gt;"",
-    SUMIFS([42]FinancingJournal!$E:$E,
-           [42]FinancingJournal!$C:$C,"Capital Injection",
-           [42]FinancingJournal!$A:$A,"&lt;="&amp;A54),
+    SUMIFS([43]FinancingJournal!$E:$E,
+           [43]FinancingJournal!$C:$C,"Capital Injection",
+           [43]FinancingJournal!$A:$A,"&lt;="&amp;A54),
     "")</f>
         <v>#VALUE!</v>
       </c>
@@ -21684,9 +21985,9 @@
       </c>
       <c r="B55" s="17" t="e">
         <f>IF(A55&lt;&gt;"",
-    SUMIFS([42]FinancingJournal!$E:$E,
-           [42]FinancingJournal!$C:$C,"Capital Injection",
-           [42]FinancingJournal!$A:$A,"&lt;="&amp;A55),
+    SUMIFS([43]FinancingJournal!$E:$E,
+           [43]FinancingJournal!$C:$C,"Capital Injection",
+           [43]FinancingJournal!$A:$A,"&lt;="&amp;A55),
     "")</f>
         <v>#VALUE!</v>
       </c>
@@ -21722,9 +22023,9 @@
       </c>
       <c r="B56" s="14" t="e">
         <f>IF(A56&lt;&gt;"",
-    SUMIFS([42]FinancingJournal!$E:$E,
-           [42]FinancingJournal!$C:$C,"Capital Injection",
-           [42]FinancingJournal!$A:$A,"&lt;="&amp;A56),
+    SUMIFS([43]FinancingJournal!$E:$E,
+           [43]FinancingJournal!$C:$C,"Capital Injection",
+           [43]FinancingJournal!$A:$A,"&lt;="&amp;A56),
     "")</f>
         <v>#VALUE!</v>
       </c>
@@ -21759,9 +22060,9 @@
       </c>
       <c r="B57" s="17" t="e">
         <f>IF(A57&lt;&gt;"",
-    SUMIFS([42]FinancingJournal!$E:$E,
-           [42]FinancingJournal!$C:$C,"Capital Injection",
-           [42]FinancingJournal!$A:$A,"&lt;="&amp;A57),
+    SUMIFS([43]FinancingJournal!$E:$E,
+           [43]FinancingJournal!$C:$C,"Capital Injection",
+           [43]FinancingJournal!$A:$A,"&lt;="&amp;A57),
     "")</f>
         <v>#VALUE!</v>
       </c>
@@ -21797,9 +22098,9 @@
       </c>
       <c r="B58" s="14" t="e">
         <f>IF(A58&lt;&gt;"",
-    SUMIFS([42]FinancingJournal!$E:$E,
-           [42]FinancingJournal!$C:$C,"Capital Injection",
-           [42]FinancingJournal!$A:$A,"&lt;="&amp;A58),
+    SUMIFS([43]FinancingJournal!$E:$E,
+           [43]FinancingJournal!$C:$C,"Capital Injection",
+           [43]FinancingJournal!$A:$A,"&lt;="&amp;A58),
     "")</f>
         <v>#VALUE!</v>
       </c>
@@ -21834,9 +22135,9 @@
       </c>
       <c r="B59" s="17" t="e">
         <f>IF(A59&lt;&gt;"",
-    SUMIFS([42]FinancingJournal!$E:$E,
-           [42]FinancingJournal!$C:$C,"Capital Injection",
-           [42]FinancingJournal!$A:$A,"&lt;="&amp;A59),
+    SUMIFS([43]FinancingJournal!$E:$E,
+           [43]FinancingJournal!$C:$C,"Capital Injection",
+           [43]FinancingJournal!$A:$A,"&lt;="&amp;A59),
     "")</f>
         <v>#VALUE!</v>
       </c>
@@ -21870,9 +22171,9 @@
       </c>
       <c r="B60" s="14" t="e">
         <f>IF(A60&lt;&gt;"",
-    SUMIFS([42]FinancingJournal!$E:$E,
-           [42]FinancingJournal!$C:$C,"Capital Injection",
-           [42]FinancingJournal!$A:$A,"&lt;="&amp;A60),
+    SUMIFS([43]FinancingJournal!$E:$E,
+           [43]FinancingJournal!$C:$C,"Capital Injection",
+           [43]FinancingJournal!$A:$A,"&lt;="&amp;A60),
     "")</f>
         <v>#VALUE!</v>
       </c>
@@ -21907,9 +22208,9 @@
       </c>
       <c r="B61" s="17" t="e">
         <f>IF(A61&lt;&gt;"",
-    SUMIFS([42]FinancingJournal!$E:$E,
-           [42]FinancingJournal!$C:$C,"Capital Injection",
-           [42]FinancingJournal!$A:$A,"&lt;="&amp;A61),
+    SUMIFS([43]FinancingJournal!$E:$E,
+           [43]FinancingJournal!$C:$C,"Capital Injection",
+           [43]FinancingJournal!$A:$A,"&lt;="&amp;A61),
     "")</f>
         <v>#VALUE!</v>
       </c>
@@ -21943,9 +22244,9 @@
       </c>
       <c r="B62" s="14" t="e">
         <f>IF(A62&lt;&gt;"",
-    SUMIFS([42]FinancingJournal!$E:$E,
-           [42]FinancingJournal!$C:$C,"Capital Injection",
-           [42]FinancingJournal!$A:$A,"&lt;="&amp;A62),
+    SUMIFS([43]FinancingJournal!$E:$E,
+           [43]FinancingJournal!$C:$C,"Capital Injection",
+           [43]FinancingJournal!$A:$A,"&lt;="&amp;A62),
     "")</f>
         <v>#VALUE!</v>
       </c>
@@ -21980,9 +22281,9 @@
       </c>
       <c r="B63" s="17" t="e">
         <f>IF(A63&lt;&gt;"",
-    SUMIFS([42]FinancingJournal!$E:$E,
-           [42]FinancingJournal!$C:$C,"Capital Injection",
-           [42]FinancingJournal!$A:$A,"&lt;="&amp;A63),
+    SUMIFS([43]FinancingJournal!$E:$E,
+           [43]FinancingJournal!$C:$C,"Capital Injection",
+           [43]FinancingJournal!$A:$A,"&lt;="&amp;A63),
     "")</f>
         <v>#VALUE!</v>
       </c>
@@ -21994,13 +22295,13 @@
       </c>
       <c r="E63" s="18" t="e">
         <f>IF(A63&lt;&gt;"",
-    SUMIFS([42]FinancingJournal!$E:$E,
-           [42]FinancingJournal!$C:$C,"Borrowing",
-           [42]FinancingJournal!$A:$A,"&lt;="&amp;A63)
+    SUMIFS([43]FinancingJournal!$E:$E,
+           [43]FinancingJournal!$C:$C,"Borrowing",
+           [43]FinancingJournal!$A:$A,"&lt;="&amp;A63)
     +
-    SUMIFS([42]FinancingJournal!$E:$E,
-           [42]FinancingJournal!$C:$C,"Withdrawal",
-           [42]FinancingJournal!$A:$A,"&lt;="&amp;A63),
+    SUMIFS([43]FinancingJournal!$E:$E,
+           [43]FinancingJournal!$C:$C,"Withdrawal",
+           [43]FinancingJournal!$A:$A,"&lt;="&amp;A63),
     "")</f>
         <v>#VALUE!</v>
       </c>
@@ -22027,9 +22328,9 @@
       </c>
       <c r="B64" s="14" t="e">
         <f>IF(A64&lt;&gt;"",
-    SUMIFS([42]FinancingJournal!$E:$E,
-           [42]FinancingJournal!$C:$C,"Capital Injection",
-           [42]FinancingJournal!$A:$A,"&lt;="&amp;A64),
+    SUMIFS([43]FinancingJournal!$E:$E,
+           [43]FinancingJournal!$C:$C,"Capital Injection",
+           [43]FinancingJournal!$A:$A,"&lt;="&amp;A64),
     "")</f>
         <v>#VALUE!</v>
       </c>
@@ -22064,9 +22365,9 @@
       </c>
       <c r="B65" s="17" t="e">
         <f>IF(A65&lt;&gt;"",
-    SUMIFS([42]FinancingJournal!$E:$E,
-           [42]FinancingJournal!$C:$C,"Capital Injection",
-           [42]FinancingJournal!$A:$A,"&lt;="&amp;A65),
+    SUMIFS([43]FinancingJournal!$E:$E,
+           [43]FinancingJournal!$C:$C,"Capital Injection",
+           [43]FinancingJournal!$A:$A,"&lt;="&amp;A65),
     "")</f>
         <v>#VALUE!</v>
       </c>
@@ -22100,9 +22401,9 @@
       </c>
       <c r="B66" s="14" t="e">
         <f>IF(A66&lt;&gt;"",
-    SUMIFS([42]FinancingJournal!$E:$E,
-           [42]FinancingJournal!$C:$C,"Capital Injection",
-           [42]FinancingJournal!$A:$A,"&lt;="&amp;A66),
+    SUMIFS([43]FinancingJournal!$E:$E,
+           [43]FinancingJournal!$C:$C,"Capital Injection",
+           [43]FinancingJournal!$A:$A,"&lt;="&amp;A66),
     "")</f>
         <v>#VALUE!</v>
       </c>
@@ -22137,9 +22438,9 @@
       </c>
       <c r="B67" s="17" t="e">
         <f>IF(A67&lt;&gt;"",
-    SUMIFS([42]FinancingJournal!$E:$E,
-           [42]FinancingJournal!$C:$C,"Capital Injection",
-           [42]FinancingJournal!$A:$A,"&lt;="&amp;A67),
+    SUMIFS([43]FinancingJournal!$E:$E,
+           [43]FinancingJournal!$C:$C,"Capital Injection",
+           [43]FinancingJournal!$A:$A,"&lt;="&amp;A67),
     "")</f>
         <v>#VALUE!</v>
       </c>
@@ -22175,41 +22476,41 @@
       </c>
       <c r="B68" s="14" t="e">
         <f>IF(A68&lt;&gt;"",
-    SUMIFS([42]FinancingJournal!$E:$E,
-           [42]FinancingJournal!$C:$C,"Capital Injection",
-           [42]FinancingJournal!$A:$A,"&lt;="&amp;A68),
+    SUMIFS([43]FinancingJournal!$E:$E,
+           [43]FinancingJournal!$C:$C,"Capital Injection",
+           [43]FinancingJournal!$A:$A,"&lt;="&amp;A68),
     "")</f>
         <v>#VALUE!</v>
       </c>
       <c r="C68" s="15" t="e">
         <f>IF(A68&lt;&gt;"",
-    SUMIFS([42]InvestingJournal!$F:$F,
-           [42]InvestingJournal!$C:$C,"Izra Advance",
-           [42]InvestingJournal!$A:$A,"&lt;="&amp;A68)
+    SUMIFS([43]InvestingJournal!$F:$F,
+           [43]InvestingJournal!$C:$C,"Izra Advance",
+           [43]InvestingJournal!$A:$A,"&lt;="&amp;A68)
     +
-    SUMIFS([42]InvestingJournal!$F:$F,
-           [42]InvestingJournal!$C:$C,"Investment to Unit",
-           [42]InvestingJournal!$A:$A,"&lt;="&amp;A68),
+    SUMIFS([43]InvestingJournal!$F:$F,
+           [43]InvestingJournal!$C:$C,"Investment to Unit",
+           [43]InvestingJournal!$A:$A,"&lt;="&amp;A68),
     "")</f>
         <v>#VALUE!</v>
       </c>
       <c r="D68" s="15" t="e">
         <f>IF(A68&lt;&gt;"",
-    SUMIFS([42]InvestingJournal!$F:$F,
-           [42]InvestingJournal!$C:$C,"Loan Advance",
-           [42]InvestingJournal!$A:$A,"&lt;="&amp;A68),
+    SUMIFS([43]InvestingJournal!$F:$F,
+           [43]InvestingJournal!$C:$C,"Loan Advance",
+           [43]InvestingJournal!$A:$A,"&lt;="&amp;A68),
     "")</f>
         <v>#VALUE!</v>
       </c>
       <c r="E68" s="15" t="e">
         <f>IF(A68&lt;&gt;"",
-    SUMIFS([42]FinancingJournal!$E:$E,
-           [42]FinancingJournal!$C:$C,"Borrowing",
-           [42]FinancingJournal!$A:$A,"&lt;="&amp;A68)
+    SUMIFS([43]FinancingJournal!$E:$E,
+           [43]FinancingJournal!$C:$C,"Borrowing",
+           [43]FinancingJournal!$A:$A,"&lt;="&amp;A68)
     +
-    SUMIFS([42]FinancingJournal!$E:$E,
-           [42]FinancingJournal!$C:$C,"Withdrawal",
-           [42]FinancingJournal!$A:$A,"&lt;="&amp;A68),
+    SUMIFS([43]FinancingJournal!$E:$E,
+           [43]FinancingJournal!$C:$C,"Withdrawal",
+           [43]FinancingJournal!$A:$A,"&lt;="&amp;A68),
     "")</f>
         <v>#VALUE!</v>
       </c>
@@ -22235,41 +22536,41 @@
       </c>
       <c r="B69" s="17" t="e">
         <f>IF(A69&lt;&gt;"",
-    SUMIFS([42]FinancingJournal!$E:$E,
-           [42]FinancingJournal!$C:$C,"Capital Injection",
-           [42]FinancingJournal!$A:$A,"&lt;="&amp;A69),
+    SUMIFS([43]FinancingJournal!$E:$E,
+           [43]FinancingJournal!$C:$C,"Capital Injection",
+           [43]FinancingJournal!$A:$A,"&lt;="&amp;A69),
     "")</f>
         <v>#VALUE!</v>
       </c>
       <c r="C69" s="18" t="e">
         <f>IF(A69&lt;&gt;"",
-    SUMIFS([42]InvestingJournal!$F:$F,
-           [42]InvestingJournal!$C:$C,"Izra Advance",
-           [42]InvestingJournal!$A:$A,"&lt;="&amp;A69)
+    SUMIFS([43]InvestingJournal!$F:$F,
+           [43]InvestingJournal!$C:$C,"Izra Advance",
+           [43]InvestingJournal!$A:$A,"&lt;="&amp;A69)
     +
-    SUMIFS([42]InvestingJournal!$F:$F,
-           [42]InvestingJournal!$C:$C,"Investment to Unit",
-           [42]InvestingJournal!$A:$A,"&lt;="&amp;A69),
+    SUMIFS([43]InvestingJournal!$F:$F,
+           [43]InvestingJournal!$C:$C,"Investment to Unit",
+           [43]InvestingJournal!$A:$A,"&lt;="&amp;A69),
     "")</f>
         <v>#VALUE!</v>
       </c>
       <c r="D69" s="18" t="e">
         <f>IF(A69&lt;&gt;"",
-    SUMIFS([42]InvestingJournal!$F:$F,
-           [42]InvestingJournal!$C:$C,"Loan Advance",
-           [42]InvestingJournal!$A:$A,"&lt;="&amp;A69),
+    SUMIFS([43]InvestingJournal!$F:$F,
+           [43]InvestingJournal!$C:$C,"Loan Advance",
+           [43]InvestingJournal!$A:$A,"&lt;="&amp;A69),
     "")</f>
         <v>#VALUE!</v>
       </c>
       <c r="E69" s="18" t="e">
         <f>IF(A69&lt;&gt;"",
-    SUMIFS([42]FinancingJournal!$E:$E,
-           [42]FinancingJournal!$C:$C,"Borrowing",
-           [42]FinancingJournal!$A:$A,"&lt;="&amp;A69)
+    SUMIFS([43]FinancingJournal!$E:$E,
+           [43]FinancingJournal!$C:$C,"Borrowing",
+           [43]FinancingJournal!$A:$A,"&lt;="&amp;A69)
     +
-    SUMIFS([42]FinancingJournal!$E:$E,
-           [42]FinancingJournal!$C:$C,"Withdrawal",
-           [42]FinancingJournal!$A:$A,"&lt;="&amp;A69),
+    SUMIFS([43]FinancingJournal!$E:$E,
+           [43]FinancingJournal!$C:$C,"Withdrawal",
+           [43]FinancingJournal!$A:$A,"&lt;="&amp;A69),
     "")</f>
         <v>#VALUE!</v>
       </c>
@@ -22294,41 +22595,41 @@
       </c>
       <c r="B70" s="14" t="e">
         <f>IF(A70&lt;&gt;"",
-    SUMIFS([42]FinancingJournal!$E:$E,
-           [42]FinancingJournal!$C:$C,"Capital Injection",
-           [42]FinancingJournal!$A:$A,"&lt;="&amp;A70),
+    SUMIFS([43]FinancingJournal!$E:$E,
+           [43]FinancingJournal!$C:$C,"Capital Injection",
+           [43]FinancingJournal!$A:$A,"&lt;="&amp;A70),
     "")</f>
         <v>#VALUE!</v>
       </c>
       <c r="C70" s="15" t="e">
         <f>IF(A70&lt;&gt;"",
-    SUMIFS([42]InvestingJournal!$F:$F,
-           [42]InvestingJournal!$C:$C,"Izra Advance",
-           [42]InvestingJournal!$A:$A,"&lt;="&amp;A70)
+    SUMIFS([43]InvestingJournal!$F:$F,
+           [43]InvestingJournal!$C:$C,"Izra Advance",
+           [43]InvestingJournal!$A:$A,"&lt;="&amp;A70)
     +
-    SUMIFS([42]InvestingJournal!$F:$F,
-           [42]InvestingJournal!$C:$C,"Investment to Unit",
-           [42]InvestingJournal!$A:$A,"&lt;="&amp;A70),
+    SUMIFS([43]InvestingJournal!$F:$F,
+           [43]InvestingJournal!$C:$C,"Investment to Unit",
+           [43]InvestingJournal!$A:$A,"&lt;="&amp;A70),
     "")</f>
         <v>#VALUE!</v>
       </c>
       <c r="D70" s="15" t="e">
         <f>IF(A70&lt;&gt;"",
-    SUMIFS([42]InvestingJournal!$F:$F,
-           [42]InvestingJournal!$C:$C,"Loan Advance",
-           [42]InvestingJournal!$A:$A,"&lt;="&amp;A70),
+    SUMIFS([43]InvestingJournal!$F:$F,
+           [43]InvestingJournal!$C:$C,"Loan Advance",
+           [43]InvestingJournal!$A:$A,"&lt;="&amp;A70),
     "")</f>
         <v>#VALUE!</v>
       </c>
       <c r="E70" s="15" t="e">
         <f>IF(A70&lt;&gt;"",
-    SUMIFS([42]FinancingJournal!$E:$E,
-           [42]FinancingJournal!$C:$C,"Borrowing",
-           [42]FinancingJournal!$A:$A,"&lt;="&amp;A70)
+    SUMIFS([43]FinancingJournal!$E:$E,
+           [43]FinancingJournal!$C:$C,"Borrowing",
+           [43]FinancingJournal!$A:$A,"&lt;="&amp;A70)
     +
-    SUMIFS([42]FinancingJournal!$E:$E,
-           [42]FinancingJournal!$C:$C,"Withdrawal",
-           [42]FinancingJournal!$A:$A,"&lt;="&amp;A70),
+    SUMIFS([43]FinancingJournal!$E:$E,
+           [43]FinancingJournal!$C:$C,"Withdrawal",
+           [43]FinancingJournal!$A:$A,"&lt;="&amp;A70),
     "")</f>
         <v>#VALUE!</v>
       </c>
@@ -22354,41 +22655,41 @@
       </c>
       <c r="B71" s="17" t="e">
         <f>IF(A71&lt;&gt;"",
-    SUMIFS([42]FinancingJournal!$E:$E,
-           [42]FinancingJournal!$C:$C,"Capital Injection",
-           [42]FinancingJournal!$A:$A,"&lt;="&amp;A71),
+    SUMIFS([43]FinancingJournal!$E:$E,
+           [43]FinancingJournal!$C:$C,"Capital Injection",
+           [43]FinancingJournal!$A:$A,"&lt;="&amp;A71),
     "")</f>
         <v>#VALUE!</v>
       </c>
       <c r="C71" s="18" t="e">
         <f>IF(A71&lt;&gt;"",
-    SUMIFS([42]InvestingJournal!$F:$F,
-           [42]InvestingJournal!$C:$C,"Izra Advance",
-           [42]InvestingJournal!$A:$A,"&lt;="&amp;A71)
+    SUMIFS([43]InvestingJournal!$F:$F,
+           [43]InvestingJournal!$C:$C,"Izra Advance",
+           [43]InvestingJournal!$A:$A,"&lt;="&amp;A71)
     +
-    SUMIFS([42]InvestingJournal!$F:$F,
-           [42]InvestingJournal!$C:$C,"Investment to Unit",
-           [42]InvestingJournal!$A:$A,"&lt;="&amp;A71),
+    SUMIFS([43]InvestingJournal!$F:$F,
+           [43]InvestingJournal!$C:$C,"Investment to Unit",
+           [43]InvestingJournal!$A:$A,"&lt;="&amp;A71),
     "")</f>
         <v>#VALUE!</v>
       </c>
       <c r="D71" s="18" t="e">
         <f>IF(A71&lt;&gt;"",
-    SUMIFS([42]InvestingJournal!$F:$F,
-           [42]InvestingJournal!$C:$C,"Loan Advance",
-           [42]InvestingJournal!$A:$A,"&lt;="&amp;A71),
+    SUMIFS([43]InvestingJournal!$F:$F,
+           [43]InvestingJournal!$C:$C,"Loan Advance",
+           [43]InvestingJournal!$A:$A,"&lt;="&amp;A71),
     "")</f>
         <v>#VALUE!</v>
       </c>
       <c r="E71" s="18" t="e">
         <f>IF(A71&lt;&gt;"",
-    SUMIFS([42]FinancingJournal!$E:$E,
-           [42]FinancingJournal!$C:$C,"Borrowing",
-           [42]FinancingJournal!$A:$A,"&lt;="&amp;A71)
+    SUMIFS([43]FinancingJournal!$E:$E,
+           [43]FinancingJournal!$C:$C,"Borrowing",
+           [43]FinancingJournal!$A:$A,"&lt;="&amp;A71)
     +
-    SUMIFS([42]FinancingJournal!$E:$E,
-           [42]FinancingJournal!$C:$C,"Withdrawal",
-           [42]FinancingJournal!$A:$A,"&lt;="&amp;A71),
+    SUMIFS([43]FinancingJournal!$E:$E,
+           [43]FinancingJournal!$C:$C,"Withdrawal",
+           [43]FinancingJournal!$A:$A,"&lt;="&amp;A71),
     "")</f>
         <v>#VALUE!</v>
       </c>
@@ -22413,41 +22714,41 @@
       </c>
       <c r="B72" s="14" t="e">
         <f>IF(A72&lt;&gt;"",
-    SUMIFS([42]FinancingJournal!$E:$E,
-           [42]FinancingJournal!$C:$C,"Capital Injection",
-           [42]FinancingJournal!$A:$A,"&lt;="&amp;A72),
+    SUMIFS([43]FinancingJournal!$E:$E,
+           [43]FinancingJournal!$C:$C,"Capital Injection",
+           [43]FinancingJournal!$A:$A,"&lt;="&amp;A72),
     "")</f>
         <v>#VALUE!</v>
       </c>
       <c r="C72" s="15" t="e">
         <f>IF(A72&lt;&gt;"",
-    SUMIFS([42]InvestingJournal!$F:$F,
-           [42]InvestingJournal!$C:$C,"Izra Advance",
-           [42]InvestingJournal!$A:$A,"&lt;="&amp;A72)
+    SUMIFS([43]InvestingJournal!$F:$F,
+           [43]InvestingJournal!$C:$C,"Izra Advance",
+           [43]InvestingJournal!$A:$A,"&lt;="&amp;A72)
     +
-    SUMIFS([42]InvestingJournal!$F:$F,
-           [42]InvestingJournal!$C:$C,"Investment to Unit",
-           [42]InvestingJournal!$A:$A,"&lt;="&amp;A72),
+    SUMIFS([43]InvestingJournal!$F:$F,
+           [43]InvestingJournal!$C:$C,"Investment to Unit",
+           [43]InvestingJournal!$A:$A,"&lt;="&amp;A72),
     "")</f>
         <v>#VALUE!</v>
       </c>
       <c r="D72" s="15" t="e">
         <f>IF(A72&lt;&gt;"",
-    SUMIFS([42]InvestingJournal!$F:$F,
-           [42]InvestingJournal!$C:$C,"Loan Advance",
-           [42]InvestingJournal!$A:$A,"&lt;="&amp;A72),
+    SUMIFS([43]InvestingJournal!$F:$F,
+           [43]InvestingJournal!$C:$C,"Loan Advance",
+           [43]InvestingJournal!$A:$A,"&lt;="&amp;A72),
     "")</f>
         <v>#VALUE!</v>
       </c>
       <c r="E72" s="15" t="e">
         <f>IF(A72&lt;&gt;"",
-    SUMIFS([42]FinancingJournal!$E:$E,
-           [42]FinancingJournal!$C:$C,"Borrowing",
-           [42]FinancingJournal!$A:$A,"&lt;="&amp;A72)
+    SUMIFS([43]FinancingJournal!$E:$E,
+           [43]FinancingJournal!$C:$C,"Borrowing",
+           [43]FinancingJournal!$A:$A,"&lt;="&amp;A72)
     +
-    SUMIFS([42]FinancingJournal!$E:$E,
-           [42]FinancingJournal!$C:$C,"Withdrawal",
-           [42]FinancingJournal!$A:$A,"&lt;="&amp;A72),
+    SUMIFS([43]FinancingJournal!$E:$E,
+           [43]FinancingJournal!$C:$C,"Withdrawal",
+           [43]FinancingJournal!$A:$A,"&lt;="&amp;A72),
     "")</f>
         <v>#VALUE!</v>
       </c>
@@ -22473,41 +22774,41 @@
       </c>
       <c r="B73" s="17" t="e">
         <f>IF(A73&lt;&gt;"",
-    SUMIFS([42]FinancingJournal!$E:$E,
-           [42]FinancingJournal!$C:$C,"Capital Injection",
-           [42]FinancingJournal!$A:$A,"&lt;="&amp;A73),
+    SUMIFS([43]FinancingJournal!$E:$E,
+           [43]FinancingJournal!$C:$C,"Capital Injection",
+           [43]FinancingJournal!$A:$A,"&lt;="&amp;A73),
     "")</f>
         <v>#VALUE!</v>
       </c>
       <c r="C73" s="18" t="e">
         <f>IF(A73&lt;&gt;"",
-    SUMIFS([42]InvestingJournal!$F:$F,
-           [42]InvestingJournal!$C:$C,"Izra Advance",
-           [42]InvestingJournal!$A:$A,"&lt;="&amp;A73)
+    SUMIFS([43]InvestingJournal!$F:$F,
+           [43]InvestingJournal!$C:$C,"Izra Advance",
+           [43]InvestingJournal!$A:$A,"&lt;="&amp;A73)
     +
-    SUMIFS([42]InvestingJournal!$F:$F,
-           [42]InvestingJournal!$C:$C,"Investment to Unit",
-           [42]InvestingJournal!$A:$A,"&lt;="&amp;A73),
+    SUMIFS([43]InvestingJournal!$F:$F,
+           [43]InvestingJournal!$C:$C,"Investment to Unit",
+           [43]InvestingJournal!$A:$A,"&lt;="&amp;A73),
     "")</f>
         <v>#VALUE!</v>
       </c>
       <c r="D73" s="18" t="e">
         <f>IF(A73&lt;&gt;"",
-    SUMIFS([42]InvestingJournal!$F:$F,
-           [42]InvestingJournal!$C:$C,"Loan Advance",
-           [42]InvestingJournal!$A:$A,"&lt;="&amp;A73),
+    SUMIFS([43]InvestingJournal!$F:$F,
+           [43]InvestingJournal!$C:$C,"Loan Advance",
+           [43]InvestingJournal!$A:$A,"&lt;="&amp;A73),
     "")</f>
         <v>#VALUE!</v>
       </c>
       <c r="E73" s="18" t="e">
         <f>IF(A73&lt;&gt;"",
-    SUMIFS([42]FinancingJournal!$E:$E,
-           [42]FinancingJournal!$C:$C,"Borrowing",
-           [42]FinancingJournal!$A:$A,"&lt;="&amp;A73)
+    SUMIFS([43]FinancingJournal!$E:$E,
+           [43]FinancingJournal!$C:$C,"Borrowing",
+           [43]FinancingJournal!$A:$A,"&lt;="&amp;A73)
     +
-    SUMIFS([42]FinancingJournal!$E:$E,
-           [42]FinancingJournal!$C:$C,"Withdrawal",
-           [42]FinancingJournal!$A:$A,"&lt;="&amp;A73),
+    SUMIFS([43]FinancingJournal!$E:$E,
+           [43]FinancingJournal!$C:$C,"Withdrawal",
+           [43]FinancingJournal!$A:$A,"&lt;="&amp;A73),
     "")</f>
         <v>#VALUE!</v>
       </c>
@@ -22534,41 +22835,41 @@
       </c>
       <c r="B74" s="14" t="e">
         <f>IF(A74&lt;&gt;"",
-    SUMIFS([42]FinancingJournal!$E:$E,
-           [42]FinancingJournal!$C:$C,"Capital Injection",
-           [42]FinancingJournal!$A:$A,"&lt;="&amp;A74),
+    SUMIFS([43]FinancingJournal!$E:$E,
+           [43]FinancingJournal!$C:$C,"Capital Injection",
+           [43]FinancingJournal!$A:$A,"&lt;="&amp;A74),
     "")</f>
         <v>#VALUE!</v>
       </c>
       <c r="C74" s="15" t="e">
         <f>IF(A74&lt;&gt;"",
-    SUMIFS([42]InvestingJournal!$F:$F,
-           [42]InvestingJournal!$C:$C,"Izra Advance",
-           [42]InvestingJournal!$A:$A,"&lt;="&amp;A74)
+    SUMIFS([43]InvestingJournal!$F:$F,
+           [43]InvestingJournal!$C:$C,"Izra Advance",
+           [43]InvestingJournal!$A:$A,"&lt;="&amp;A74)
     +
-    SUMIFS([42]InvestingJournal!$F:$F,
-           [42]InvestingJournal!$C:$C,"Investment to Unit",
-           [42]InvestingJournal!$A:$A,"&lt;="&amp;A74),
+    SUMIFS([43]InvestingJournal!$F:$F,
+           [43]InvestingJournal!$C:$C,"Investment to Unit",
+           [43]InvestingJournal!$A:$A,"&lt;="&amp;A74),
     "")</f>
         <v>#VALUE!</v>
       </c>
       <c r="D74" s="15" t="e">
         <f>IF(A74&lt;&gt;"",
-    SUMIFS([42]InvestingJournal!$F:$F,
-           [42]InvestingJournal!$C:$C,"Loan Advance",
-           [42]InvestingJournal!$A:$A,"&lt;="&amp;A74),
+    SUMIFS([43]InvestingJournal!$F:$F,
+           [43]InvestingJournal!$C:$C,"Loan Advance",
+           [43]InvestingJournal!$A:$A,"&lt;="&amp;A74),
     "")</f>
         <v>#VALUE!</v>
       </c>
       <c r="E74" s="15" t="e">
         <f>IF(A74&lt;&gt;"",
-    SUMIFS([42]FinancingJournal!$E:$E,
-           [42]FinancingJournal!$C:$C,"Borrowing",
-           [42]FinancingJournal!$A:$A,"&lt;="&amp;A74)
+    SUMIFS([43]FinancingJournal!$E:$E,
+           [43]FinancingJournal!$C:$C,"Borrowing",
+           [43]FinancingJournal!$A:$A,"&lt;="&amp;A74)
     +
-    SUMIFS([42]FinancingJournal!$E:$E,
-           [42]FinancingJournal!$C:$C,"Withdrawal",
-           [42]FinancingJournal!$A:$A,"&lt;="&amp;A74),
+    SUMIFS([43]FinancingJournal!$E:$E,
+           [43]FinancingJournal!$C:$C,"Withdrawal",
+           [43]FinancingJournal!$A:$A,"&lt;="&amp;A74),
     "")</f>
         <v>#VALUE!</v>
       </c>
@@ -22594,41 +22895,41 @@
       </c>
       <c r="B75" s="17" t="e">
         <f>IF(A75&lt;&gt;"",
-    SUMIFS([42]FinancingJournal!$E:$E,
-           [42]FinancingJournal!$C:$C,"Capital Injection",
-           [42]FinancingJournal!$A:$A,"&lt;="&amp;A75),
+    SUMIFS([43]FinancingJournal!$E:$E,
+           [43]FinancingJournal!$C:$C,"Capital Injection",
+           [43]FinancingJournal!$A:$A,"&lt;="&amp;A75),
     "")</f>
         <v>#VALUE!</v>
       </c>
       <c r="C75" s="18" t="e">
         <f>IF(A75&lt;&gt;"",
-    SUMIFS([42]InvestingJournal!$F:$F,
-           [42]InvestingJournal!$C:$C,"Izra Advance",
-           [42]InvestingJournal!$A:$A,"&lt;="&amp;A75)
+    SUMIFS([43]InvestingJournal!$F:$F,
+           [43]InvestingJournal!$C:$C,"Izra Advance",
+           [43]InvestingJournal!$A:$A,"&lt;="&amp;A75)
     +
-    SUMIFS([42]InvestingJournal!$F:$F,
-           [42]InvestingJournal!$C:$C,"Investment to Unit",
-           [42]InvestingJournal!$A:$A,"&lt;="&amp;A75),
+    SUMIFS([43]InvestingJournal!$F:$F,
+           [43]InvestingJournal!$C:$C,"Investment to Unit",
+           [43]InvestingJournal!$A:$A,"&lt;="&amp;A75),
     "")</f>
         <v>#VALUE!</v>
       </c>
       <c r="D75" s="18" t="e">
         <f>IF(A75&lt;&gt;"",
-    SUMIFS([42]InvestingJournal!$F:$F,
-           [42]InvestingJournal!$C:$C,"Loan Advance",
-           [42]InvestingJournal!$A:$A,"&lt;="&amp;A75),
+    SUMIFS([43]InvestingJournal!$F:$F,
+           [43]InvestingJournal!$C:$C,"Loan Advance",
+           [43]InvestingJournal!$A:$A,"&lt;="&amp;A75),
     "")</f>
         <v>#VALUE!</v>
       </c>
       <c r="E75" s="18" t="e">
         <f>IF(A75&lt;&gt;"",
-    SUMIFS([42]FinancingJournal!$E:$E,
-           [42]FinancingJournal!$C:$C,"Borrowing",
-           [42]FinancingJournal!$A:$A,"&lt;="&amp;A75)
+    SUMIFS([43]FinancingJournal!$E:$E,
+           [43]FinancingJournal!$C:$C,"Borrowing",
+           [43]FinancingJournal!$A:$A,"&lt;="&amp;A75)
     +
-    SUMIFS([42]FinancingJournal!$E:$E,
-           [42]FinancingJournal!$C:$C,"Withdrawal",
-           [42]FinancingJournal!$A:$A,"&lt;="&amp;A75),
+    SUMIFS([43]FinancingJournal!$E:$E,
+           [43]FinancingJournal!$C:$C,"Withdrawal",
+           [43]FinancingJournal!$A:$A,"&lt;="&amp;A75),
     "")</f>
         <v>#VALUE!</v>
       </c>
@@ -22655,41 +22956,41 @@
       </c>
       <c r="B76" s="14" t="e">
         <f>IF(A76&lt;&gt;"",
-    SUMIFS([42]FinancingJournal!$E:$E,
-           [42]FinancingJournal!$C:$C,"Capital Injection",
-           [42]FinancingJournal!$A:$A,"&lt;="&amp;A76),
+    SUMIFS([43]FinancingJournal!$E:$E,
+           [43]FinancingJournal!$C:$C,"Capital Injection",
+           [43]FinancingJournal!$A:$A,"&lt;="&amp;A76),
     "")</f>
         <v>#VALUE!</v>
       </c>
       <c r="C76" s="15" t="e">
         <f>IF(A76&lt;&gt;"",
-    SUMIFS([42]InvestingJournal!$F:$F,
-           [42]InvestingJournal!$C:$C,"Izra Advance",
-           [42]InvestingJournal!$A:$A,"&lt;="&amp;A76)
+    SUMIFS([43]InvestingJournal!$F:$F,
+           [43]InvestingJournal!$C:$C,"Izra Advance",
+           [43]InvestingJournal!$A:$A,"&lt;="&amp;A76)
     +
-    SUMIFS([42]InvestingJournal!$F:$F,
-           [42]InvestingJournal!$C:$C,"Investment to Unit",
-           [42]InvestingJournal!$A:$A,"&lt;="&amp;A76),
+    SUMIFS([43]InvestingJournal!$F:$F,
+           [43]InvestingJournal!$C:$C,"Investment to Unit",
+           [43]InvestingJournal!$A:$A,"&lt;="&amp;A76),
     "")</f>
         <v>#VALUE!</v>
       </c>
       <c r="D76" s="15" t="e">
         <f>IF(A76&lt;&gt;"",
-    SUMIFS([42]InvestingJournal!$F:$F,
-           [42]InvestingJournal!$C:$C,"Loan Advance",
-           [42]InvestingJournal!$A:$A,"&lt;="&amp;A76),
+    SUMIFS([43]InvestingJournal!$F:$F,
+           [43]InvestingJournal!$C:$C,"Loan Advance",
+           [43]InvestingJournal!$A:$A,"&lt;="&amp;A76),
     "")</f>
         <v>#VALUE!</v>
       </c>
       <c r="E76" s="15" t="e">
         <f>IF(A76&lt;&gt;"",
-    SUMIFS([42]FinancingJournal!$E:$E,
-           [42]FinancingJournal!$C:$C,"Borrowing",
-           [42]FinancingJournal!$A:$A,"&lt;="&amp;A76)
+    SUMIFS([43]FinancingJournal!$E:$E,
+           [43]FinancingJournal!$C:$C,"Borrowing",
+           [43]FinancingJournal!$A:$A,"&lt;="&amp;A76)
     +
-    SUMIFS([42]FinancingJournal!$E:$E,
-           [42]FinancingJournal!$C:$C,"Withdrawal",
-           [42]FinancingJournal!$A:$A,"&lt;="&amp;A76),
+    SUMIFS([43]FinancingJournal!$E:$E,
+           [43]FinancingJournal!$C:$C,"Withdrawal",
+           [43]FinancingJournal!$A:$A,"&lt;="&amp;A76),
     "")</f>
         <v>#VALUE!</v>
       </c>
@@ -22715,41 +23016,41 @@
       </c>
       <c r="B77" s="17" t="e">
         <f>IF(A77&lt;&gt;"",
-    SUMIFS([42]FinancingJournal!$E:$E,
-           [42]FinancingJournal!$C:$C,"Capital Injection",
-           [42]FinancingJournal!$A:$A,"&lt;="&amp;A77),
+    SUMIFS([43]FinancingJournal!$E:$E,
+           [43]FinancingJournal!$C:$C,"Capital Injection",
+           [43]FinancingJournal!$A:$A,"&lt;="&amp;A77),
     "")</f>
         <v>#VALUE!</v>
       </c>
       <c r="C77" s="18" t="e">
         <f>IF(A77&lt;&gt;"",
-    SUMIFS([42]InvestingJournal!$F:$F,
-           [42]InvestingJournal!$C:$C,"Izra Advance",
-           [42]InvestingJournal!$A:$A,"&lt;="&amp;A77)
+    SUMIFS([43]InvestingJournal!$F:$F,
+           [43]InvestingJournal!$C:$C,"Izra Advance",
+           [43]InvestingJournal!$A:$A,"&lt;="&amp;A77)
     +
-    SUMIFS([42]InvestingJournal!$F:$F,
-           [42]InvestingJournal!$C:$C,"Investment to Unit",
-           [42]InvestingJournal!$A:$A,"&lt;="&amp;A77),
+    SUMIFS([43]InvestingJournal!$F:$F,
+           [43]InvestingJournal!$C:$C,"Investment to Unit",
+           [43]InvestingJournal!$A:$A,"&lt;="&amp;A77),
     "")</f>
         <v>#VALUE!</v>
       </c>
       <c r="D77" s="18" t="e">
         <f>IF(A77&lt;&gt;"",
-    SUMIFS([42]InvestingJournal!$F:$F,
-           [42]InvestingJournal!$C:$C,"Loan Advance",
-           [42]InvestingJournal!$A:$A,"&lt;="&amp;A77),
+    SUMIFS([43]InvestingJournal!$F:$F,
+           [43]InvestingJournal!$C:$C,"Loan Advance",
+           [43]InvestingJournal!$A:$A,"&lt;="&amp;A77),
     "")</f>
         <v>#VALUE!</v>
       </c>
       <c r="E77" s="18" t="e">
         <f>IF(A77&lt;&gt;"",
-    SUMIFS([42]FinancingJournal!$E:$E,
-           [42]FinancingJournal!$C:$C,"Borrowing",
-           [42]FinancingJournal!$A:$A,"&lt;="&amp;A77)
+    SUMIFS([43]FinancingJournal!$E:$E,
+           [43]FinancingJournal!$C:$C,"Borrowing",
+           [43]FinancingJournal!$A:$A,"&lt;="&amp;A77)
     +
-    SUMIFS([42]FinancingJournal!$E:$E,
-           [42]FinancingJournal!$C:$C,"Withdrawal",
-           [42]FinancingJournal!$A:$A,"&lt;="&amp;A77),
+    SUMIFS([43]FinancingJournal!$E:$E,
+           [43]FinancingJournal!$C:$C,"Withdrawal",
+           [43]FinancingJournal!$A:$A,"&lt;="&amp;A77),
     "")</f>
         <v>#VALUE!</v>
       </c>
@@ -22771,288 +23072,344 @@
       <c r="P77" s="9"/>
     </row>
     <row r="78" spans="1:16" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A78" s="11"/>
-      <c r="B78" s="14" t="str">
+      <c r="A78" s="11">
+        <v>46290</v>
+      </c>
+      <c r="B78" s="14" t="e">
         <f>IF(A78&lt;&gt;"",
-    SUMIFS([42]FinancingJournal!$E:$E,
-           [42]FinancingJournal!$C:$C,"Capital Injection",
-           [42]FinancingJournal!$A:$A,"&lt;="&amp;A78),
-    "")</f>
-        <v/>
-      </c>
-      <c r="C78" s="15" t="str">
+    SUMIFS([43]FinancingJournal!$E:$E,
+           [43]FinancingJournal!$C:$C,"Capital Injection",
+           [43]FinancingJournal!$A:$A,"&lt;="&amp;A78),
+    "")</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="C78" s="15" t="e">
         <f>IF(A78&lt;&gt;"",
-    SUMIFS([42]InvestingJournal!$F:$F,
-           [42]InvestingJournal!$C:$C,"Izra Advance",
-           [42]InvestingJournal!$A:$A,"&lt;="&amp;A78)
+    SUMIFS([43]InvestingJournal!$F:$F,
+           [43]InvestingJournal!$C:$C,"Izra Advance",
+           [43]InvestingJournal!$A:$A,"&lt;="&amp;A78)
     +
-    SUMIFS([42]InvestingJournal!$F:$F,
-           [42]InvestingJournal!$C:$C,"Investment to Unit",
-           [42]InvestingJournal!$A:$A,"&lt;="&amp;A78),
-    "")</f>
-        <v/>
-      </c>
-      <c r="D78" s="15" t="str">
+    SUMIFS([43]InvestingJournal!$F:$F,
+           [43]InvestingJournal!$C:$C,"Investment to Unit",
+           [43]InvestingJournal!$A:$A,"&lt;="&amp;A78),
+    "")</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="D78" s="15" t="e">
         <f>IF(A78&lt;&gt;"",
-    SUMIFS([42]InvestingJournal!$F:$F,
-           [42]InvestingJournal!$C:$C,"Loan Advance",
-           [42]InvestingJournal!$A:$A,"&lt;="&amp;A78),
-    "")</f>
-        <v/>
-      </c>
-      <c r="E78" s="15" t="str">
+    SUMIFS([43]InvestingJournal!$F:$F,
+           [43]InvestingJournal!$C:$C,"Loan Advance",
+           [43]InvestingJournal!$A:$A,"&lt;="&amp;A78),
+    "")</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="E78" s="15" t="e">
         <f>IF(A78&lt;&gt;"",
-    SUMIFS([42]FinancingJournal!$E:$E,
-           [42]FinancingJournal!$C:$C,"Borrowing",
-           [42]FinancingJournal!$A:$A,"&lt;="&amp;A78)
+    SUMIFS([43]FinancingJournal!$E:$E,
+           [43]FinancingJournal!$C:$C,"Borrowing",
+           [43]FinancingJournal!$A:$A,"&lt;="&amp;A78)
     +
-    SUMIFS([42]FinancingJournal!$E:$E,
-           [42]FinancingJournal!$C:$C,"Withdrawal",
-           [42]FinancingJournal!$A:$A,"&lt;="&amp;A78),
-    "")</f>
-        <v/>
-      </c>
-      <c r="F78" s="26"/>
-      <c r="G78" s="26"/>
-      <c r="H78" s="26"/>
-      <c r="I78" s="26"/>
+    SUMIFS([43]FinancingJournal!$E:$E,
+           [43]FinancingJournal!$C:$C,"Withdrawal",
+           [43]FinancingJournal!$A:$A,"&lt;="&amp;A78),
+    "")</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="F78" s="26">
+        <v>1146496</v>
+      </c>
+      <c r="G78" s="26">
+        <v>131676</v>
+      </c>
+      <c r="H78" s="26">
+        <v>792550</v>
+      </c>
+      <c r="I78" s="26">
+        <v>714836.66219130636</v>
+      </c>
       <c r="J78" s="31" t="s">
         <v>134</v>
       </c>
     </row>
     <row r="79" spans="1:16" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A79" s="16"/>
-      <c r="B79" s="17" t="str">
+      <c r="A79" s="16">
+        <v>46290</v>
+      </c>
+      <c r="B79" s="17" t="e">
         <f>IF(A79&lt;&gt;"",
-    SUMIFS([42]FinancingJournal!$E:$E,
-           [42]FinancingJournal!$C:$C,"Capital Injection",
-           [42]FinancingJournal!$A:$A,"&lt;="&amp;A79),
-    "")</f>
-        <v/>
-      </c>
-      <c r="C79" s="18" t="str">
+    SUMIFS([43]FinancingJournal!$E:$E,
+           [43]FinancingJournal!$C:$C,"Capital Injection",
+           [43]FinancingJournal!$A:$A,"&lt;="&amp;A79),
+    "")</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="C79" s="18" t="e">
         <f>IF(A79&lt;&gt;"",
-    SUMIFS([42]InvestingJournal!$F:$F,
-           [42]InvestingJournal!$C:$C,"Izra Advance",
-           [42]InvestingJournal!$A:$A,"&lt;="&amp;A79)
+    SUMIFS([43]InvestingJournal!$F:$F,
+           [43]InvestingJournal!$C:$C,"Izra Advance",
+           [43]InvestingJournal!$A:$A,"&lt;="&amp;A79)
     +
-    SUMIFS([42]InvestingJournal!$F:$F,
-           [42]InvestingJournal!$C:$C,"Investment to Unit",
-           [42]InvestingJournal!$A:$A,"&lt;="&amp;A79),
-    "")</f>
-        <v/>
-      </c>
-      <c r="D79" s="18" t="str">
+    SUMIFS([43]InvestingJournal!$F:$F,
+           [43]InvestingJournal!$C:$C,"Investment to Unit",
+           [43]InvestingJournal!$A:$A,"&lt;="&amp;A79),
+    "")</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="D79" s="18" t="e">
         <f>IF(A79&lt;&gt;"",
-    SUMIFS([42]InvestingJournal!$F:$F,
-           [42]InvestingJournal!$C:$C,"Loan Advance",
-           [42]InvestingJournal!$A:$A,"&lt;="&amp;A79),
-    "")</f>
-        <v/>
-      </c>
-      <c r="E79" s="18" t="str">
+    SUMIFS([43]InvestingJournal!$F:$F,
+           [43]InvestingJournal!$C:$C,"Loan Advance",
+           [43]InvestingJournal!$A:$A,"&lt;="&amp;A79),
+    "")</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="E79" s="18" t="e">
         <f>IF(A79&lt;&gt;"",
-    SUMIFS([42]FinancingJournal!$E:$E,
-           [42]FinancingJournal!$C:$C,"Borrowing",
-           [42]FinancingJournal!$A:$A,"&lt;="&amp;A79)
+    SUMIFS([43]FinancingJournal!$E:$E,
+           [43]FinancingJournal!$C:$C,"Borrowing",
+           [43]FinancingJournal!$A:$A,"&lt;="&amp;A79)
     +
-    SUMIFS([42]FinancingJournal!$E:$E,
-           [42]FinancingJournal!$C:$C,"Withdrawal",
-           [42]FinancingJournal!$A:$A,"&lt;="&amp;A79),
-    "")</f>
-        <v/>
-      </c>
-      <c r="F79" s="29"/>
-      <c r="G79" s="29"/>
-      <c r="H79" s="29"/>
-      <c r="I79" s="29"/>
-      <c r="J79" s="32"/>
+    SUMIFS([43]FinancingJournal!$E:$E,
+           [43]FinancingJournal!$C:$C,"Withdrawal",
+           [43]FinancingJournal!$A:$A,"&lt;="&amp;A79),
+    "")</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="F79" s="29">
+        <v>1154196</v>
+      </c>
+      <c r="G79" s="29">
+        <v>91676</v>
+      </c>
+      <c r="H79" s="29">
+        <v>840250</v>
+      </c>
+      <c r="I79" s="29">
+        <v>714836.66219130729</v>
+      </c>
+      <c r="J79" s="32" t="s">
+        <v>135</v>
+      </c>
       <c r="P79" s="9"/>
     </row>
     <row r="80" spans="1:16" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A80" s="11"/>
-      <c r="B80" s="14" t="str">
+      <c r="A80" s="11">
+        <v>46293</v>
+      </c>
+      <c r="B80" s="14" t="e">
         <f>IF(A80&lt;&gt;"",
-    SUMIFS([42]FinancingJournal!$E:$E,
-           [42]FinancingJournal!$C:$C,"Capital Injection",
-           [42]FinancingJournal!$A:$A,"&lt;="&amp;A80),
-    "")</f>
-        <v/>
-      </c>
-      <c r="C80" s="15" t="str">
+    SUMIFS([43]FinancingJournal!$E:$E,
+           [43]FinancingJournal!$C:$C,"Capital Injection",
+           [43]FinancingJournal!$A:$A,"&lt;="&amp;A80),
+    "")</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="C80" s="15" t="e">
         <f>IF(A80&lt;&gt;"",
-    SUMIFS([42]InvestingJournal!$F:$F,
-           [42]InvestingJournal!$C:$C,"Izra Advance",
-           [42]InvestingJournal!$A:$A,"&lt;="&amp;A80)
+    SUMIFS([43]InvestingJournal!$F:$F,
+           [43]InvestingJournal!$C:$C,"Izra Advance",
+           [43]InvestingJournal!$A:$A,"&lt;="&amp;A80)
     +
-    SUMIFS([42]InvestingJournal!$F:$F,
-           [42]InvestingJournal!$C:$C,"Investment to Unit",
-           [42]InvestingJournal!$A:$A,"&lt;="&amp;A80),
-    "")</f>
-        <v/>
-      </c>
-      <c r="D80" s="15" t="str">
+    SUMIFS([43]InvestingJournal!$F:$F,
+           [43]InvestingJournal!$C:$C,"Investment to Unit",
+           [43]InvestingJournal!$A:$A,"&lt;="&amp;A80),
+    "")</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="D80" s="15" t="e">
         <f>IF(A80&lt;&gt;"",
-    SUMIFS([42]InvestingJournal!$F:$F,
-           [42]InvestingJournal!$C:$C,"Loan Advance",
-           [42]InvestingJournal!$A:$A,"&lt;="&amp;A80),
-    "")</f>
-        <v/>
-      </c>
-      <c r="E80" s="15" t="str">
+    SUMIFS([43]InvestingJournal!$F:$F,
+           [43]InvestingJournal!$C:$C,"Loan Advance",
+           [43]InvestingJournal!$A:$A,"&lt;="&amp;A80),
+    "")</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="E80" s="15" t="e">
         <f>IF(A80&lt;&gt;"",
-    SUMIFS([42]FinancingJournal!$E:$E,
-           [42]FinancingJournal!$C:$C,"Borrowing",
-           [42]FinancingJournal!$A:$A,"&lt;="&amp;A80)
+    SUMIFS([43]FinancingJournal!$E:$E,
+           [43]FinancingJournal!$C:$C,"Borrowing",
+           [43]FinancingJournal!$A:$A,"&lt;="&amp;A80)
     +
-    SUMIFS([42]FinancingJournal!$E:$E,
-           [42]FinancingJournal!$C:$C,"Withdrawal",
-           [42]FinancingJournal!$A:$A,"&lt;="&amp;A80),
-    "")</f>
-        <v/>
-      </c>
-      <c r="F80" s="26"/>
-      <c r="G80" s="26"/>
-      <c r="H80" s="26"/>
-      <c r="I80" s="26"/>
-      <c r="J80" s="31"/>
+    SUMIFS([43]FinancingJournal!$E:$E,
+           [43]FinancingJournal!$C:$C,"Withdrawal",
+           [43]FinancingJournal!$A:$A,"&lt;="&amp;A80),
+    "")</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="F80" s="26">
+        <v>1150696</v>
+      </c>
+      <c r="G80" s="26">
+        <v>118326</v>
+      </c>
+      <c r="H80" s="26">
+        <v>810100</v>
+      </c>
+      <c r="I80" s="26">
+        <v>687347.36541989387</v>
+      </c>
+      <c r="J80" s="31" t="s">
+        <v>136</v>
+      </c>
     </row>
     <row r="81" spans="1:16" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A81" s="16"/>
-      <c r="B81" s="17" t="str">
+      <c r="A81" s="16">
+        <v>46293</v>
+      </c>
+      <c r="B81" s="17" t="e">
         <f>IF(A81&lt;&gt;"",
-    SUMIFS([42]FinancingJournal!$E:$E,
-           [42]FinancingJournal!$C:$C,"Capital Injection",
-           [42]FinancingJournal!$A:$A,"&lt;="&amp;A81),
-    "")</f>
-        <v/>
-      </c>
-      <c r="C81" s="18" t="str">
+    SUMIFS([43]FinancingJournal!$E:$E,
+           [43]FinancingJournal!$C:$C,"Capital Injection",
+           [43]FinancingJournal!$A:$A,"&lt;="&amp;A81),
+    "")</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="C81" s="18" t="e">
         <f>IF(A81&lt;&gt;"",
-    SUMIFS([42]InvestingJournal!$F:$F,
-           [42]InvestingJournal!$C:$C,"Izra Advance",
-           [42]InvestingJournal!$A:$A,"&lt;="&amp;A81)
+    SUMIFS([43]InvestingJournal!$F:$F,
+           [43]InvestingJournal!$C:$C,"Izra Advance",
+           [43]InvestingJournal!$A:$A,"&lt;="&amp;A81)
     +
-    SUMIFS([42]InvestingJournal!$F:$F,
-           [42]InvestingJournal!$C:$C,"Investment to Unit",
-           [42]InvestingJournal!$A:$A,"&lt;="&amp;A81),
-    "")</f>
-        <v/>
-      </c>
-      <c r="D81" s="18" t="str">
+    SUMIFS([43]InvestingJournal!$F:$F,
+           [43]InvestingJournal!$C:$C,"Investment to Unit",
+           [43]InvestingJournal!$A:$A,"&lt;="&amp;A81),
+    "")</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="D81" s="18" t="e">
         <f>IF(A81&lt;&gt;"",
-    SUMIFS([42]InvestingJournal!$F:$F,
-           [42]InvestingJournal!$C:$C,"Loan Advance",
-           [42]InvestingJournal!$A:$A,"&lt;="&amp;A81),
-    "")</f>
-        <v/>
-      </c>
-      <c r="E81" s="18" t="str">
+    SUMIFS([43]InvestingJournal!$F:$F,
+           [43]InvestingJournal!$C:$C,"Loan Advance",
+           [43]InvestingJournal!$A:$A,"&lt;="&amp;A81),
+    "")</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="E81" s="18" t="e">
         <f>IF(A81&lt;&gt;"",
-    SUMIFS([42]FinancingJournal!$E:$E,
-           [42]FinancingJournal!$C:$C,"Borrowing",
-           [42]FinancingJournal!$A:$A,"&lt;="&amp;A81)
+    SUMIFS([43]FinancingJournal!$E:$E,
+           [43]FinancingJournal!$C:$C,"Borrowing",
+           [43]FinancingJournal!$A:$A,"&lt;="&amp;A81)
     +
-    SUMIFS([42]FinancingJournal!$E:$E,
-           [42]FinancingJournal!$C:$C,"Withdrawal",
-           [42]FinancingJournal!$A:$A,"&lt;="&amp;A81),
-    "")</f>
-        <v/>
-      </c>
-      <c r="F81" s="29"/>
-      <c r="G81" s="29"/>
-      <c r="H81" s="29"/>
-      <c r="I81" s="29"/>
-      <c r="J81" s="32"/>
+    SUMIFS([43]FinancingJournal!$E:$E,
+           [43]FinancingJournal!$C:$C,"Withdrawal",
+           [43]FinancingJournal!$A:$A,"&lt;="&amp;A81),
+    "")</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="F81" s="29">
+        <v>1156396</v>
+      </c>
+      <c r="G81" s="29">
+        <v>88326</v>
+      </c>
+      <c r="H81" s="29">
+        <v>845800</v>
+      </c>
+      <c r="I81" s="29">
+        <v>687347.36541989481</v>
+      </c>
+      <c r="J81" s="32" t="s">
+        <v>137</v>
+      </c>
       <c r="P81" s="9"/>
     </row>
     <row r="82" spans="1:16" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A82" s="11"/>
-      <c r="B82" s="14" t="str">
+      <c r="A82" s="11">
+        <v>46294</v>
+      </c>
+      <c r="B82" s="14" t="e">
         <f>IF(A82&lt;&gt;"",
-    SUMIFS([42]FinancingJournal!$E:$E,
-           [42]FinancingJournal!$C:$C,"Capital Injection",
-           [42]FinancingJournal!$A:$A,"&lt;="&amp;A82),
-    "")</f>
-        <v/>
-      </c>
-      <c r="C82" s="15" t="str">
+    SUMIFS([43]FinancingJournal!$E:$E,
+           [43]FinancingJournal!$C:$C,"Capital Injection",
+           [43]FinancingJournal!$A:$A,"&lt;="&amp;A82),
+    "")</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="C82" s="15" t="e">
         <f>IF(A82&lt;&gt;"",
-    SUMIFS([42]InvestingJournal!$F:$F,
-           [42]InvestingJournal!$C:$C,"Izra Advance",
-           [42]InvestingJournal!$A:$A,"&lt;="&amp;A82)
+    SUMIFS([43]InvestingJournal!$F:$F,
+           [43]InvestingJournal!$C:$C,"Izra Advance",
+           [43]InvestingJournal!$A:$A,"&lt;="&amp;A82)
     +
-    SUMIFS([42]InvestingJournal!$F:$F,
-           [42]InvestingJournal!$C:$C,"Investment to Unit",
-           [42]InvestingJournal!$A:$A,"&lt;="&amp;A82),
-    "")</f>
-        <v/>
-      </c>
-      <c r="D82" s="15" t="str">
+    SUMIFS([43]InvestingJournal!$F:$F,
+           [43]InvestingJournal!$C:$C,"Investment to Unit",
+           [43]InvestingJournal!$A:$A,"&lt;="&amp;A82),
+    "")</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="D82" s="15" t="e">
         <f>IF(A82&lt;&gt;"",
-    SUMIFS([42]InvestingJournal!$F:$F,
-           [42]InvestingJournal!$C:$C,"Loan Advance",
-           [42]InvestingJournal!$A:$A,"&lt;="&amp;A82),
-    "")</f>
-        <v/>
-      </c>
-      <c r="E82" s="15" t="str">
+    SUMIFS([43]InvestingJournal!$F:$F,
+           [43]InvestingJournal!$C:$C,"Loan Advance",
+           [43]InvestingJournal!$A:$A,"&lt;="&amp;A82),
+    "")</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="E82" s="15" t="e">
         <f>IF(A82&lt;&gt;"",
-    SUMIFS([42]FinancingJournal!$E:$E,
-           [42]FinancingJournal!$C:$C,"Borrowing",
-           [42]FinancingJournal!$A:$A,"&lt;="&amp;A82)
+    SUMIFS([43]FinancingJournal!$E:$E,
+           [43]FinancingJournal!$C:$C,"Borrowing",
+           [43]FinancingJournal!$A:$A,"&lt;="&amp;A82)
     +
-    SUMIFS([42]FinancingJournal!$E:$E,
-           [42]FinancingJournal!$C:$C,"Withdrawal",
-           [42]FinancingJournal!$A:$A,"&lt;="&amp;A82),
-    "")</f>
-        <v/>
-      </c>
-      <c r="F82" s="26"/>
-      <c r="G82" s="26"/>
-      <c r="H82" s="26"/>
-      <c r="I82" s="26"/>
+    SUMIFS([43]FinancingJournal!$E:$E,
+           [43]FinancingJournal!$C:$C,"Withdrawal",
+           [43]FinancingJournal!$A:$A,"&lt;="&amp;A82),
+    "")</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="F82" s="26">
+        <v>1156396</v>
+      </c>
+      <c r="G82" s="26">
+        <v>89726</v>
+      </c>
+      <c r="H82" s="26">
+        <v>844400</v>
+      </c>
+      <c r="I82" s="26">
+        <v>686242.6936539209</v>
+      </c>
       <c r="J82" s="31"/>
     </row>
     <row r="83" spans="1:16" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A83" s="16"/>
       <c r="B83" s="17" t="str">
         <f>IF(A83&lt;&gt;"",
-    SUMIFS([42]FinancingJournal!$E:$E,
-           [42]FinancingJournal!$C:$C,"Capital Injection",
-           [42]FinancingJournal!$A:$A,"&lt;="&amp;A83),
+    SUMIFS([43]FinancingJournal!$E:$E,
+           [43]FinancingJournal!$C:$C,"Capital Injection",
+           [43]FinancingJournal!$A:$A,"&lt;="&amp;A83),
     "")</f>
         <v/>
       </c>
       <c r="C83" s="18" t="str">
         <f>IF(A83&lt;&gt;"",
-    SUMIFS([42]InvestingJournal!$F:$F,
-           [42]InvestingJournal!$C:$C,"Izra Advance",
-           [42]InvestingJournal!$A:$A,"&lt;="&amp;A83)
+    SUMIFS([43]InvestingJournal!$F:$F,
+           [43]InvestingJournal!$C:$C,"Izra Advance",
+           [43]InvestingJournal!$A:$A,"&lt;="&amp;A83)
     +
-    SUMIFS([42]InvestingJournal!$F:$F,
-           [42]InvestingJournal!$C:$C,"Investment to Unit",
-           [42]InvestingJournal!$A:$A,"&lt;="&amp;A83),
+    SUMIFS([43]InvestingJournal!$F:$F,
+           [43]InvestingJournal!$C:$C,"Investment to Unit",
+           [43]InvestingJournal!$A:$A,"&lt;="&amp;A83),
     "")</f>
         <v/>
       </c>
       <c r="D83" s="18" t="str">
         <f>IF(A83&lt;&gt;"",
-    SUMIFS([42]InvestingJournal!$F:$F,
-           [42]InvestingJournal!$C:$C,"Loan Advance",
-           [42]InvestingJournal!$A:$A,"&lt;="&amp;A83),
+    SUMIFS([43]InvestingJournal!$F:$F,
+           [43]InvestingJournal!$C:$C,"Loan Advance",
+           [43]InvestingJournal!$A:$A,"&lt;="&amp;A83),
     "")</f>
         <v/>
       </c>
       <c r="E83" s="18" t="str">
         <f>IF(A83&lt;&gt;"",
-    SUMIFS([42]FinancingJournal!$E:$E,
-           [42]FinancingJournal!$C:$C,"Borrowing",
-           [42]FinancingJournal!$A:$A,"&lt;="&amp;A83)
+    SUMIFS([43]FinancingJournal!$E:$E,
+           [43]FinancingJournal!$C:$C,"Borrowing",
+           [43]FinancingJournal!$A:$A,"&lt;="&amp;A83)
     +
-    SUMIFS([42]FinancingJournal!$E:$E,
-           [42]FinancingJournal!$C:$C,"Withdrawal",
-           [42]FinancingJournal!$A:$A,"&lt;="&amp;A83),
+    SUMIFS([43]FinancingJournal!$E:$E,
+           [43]FinancingJournal!$C:$C,"Withdrawal",
+           [43]FinancingJournal!$A:$A,"&lt;="&amp;A83),
     "")</f>
         <v/>
       </c>
@@ -23067,41 +23424,41 @@
       <c r="A84" s="11"/>
       <c r="B84" s="14" t="str">
         <f>IF(A84&lt;&gt;"",
-    SUMIFS([42]FinancingJournal!$E:$E,
-           [42]FinancingJournal!$C:$C,"Capital Injection",
-           [42]FinancingJournal!$A:$A,"&lt;="&amp;A84),
+    SUMIFS([43]FinancingJournal!$E:$E,
+           [43]FinancingJournal!$C:$C,"Capital Injection",
+           [43]FinancingJournal!$A:$A,"&lt;="&amp;A84),
     "")</f>
         <v/>
       </c>
       <c r="C84" s="15" t="str">
         <f>IF(A84&lt;&gt;"",
-    SUMIFS([42]InvestingJournal!$F:$F,
-           [42]InvestingJournal!$C:$C,"Izra Advance",
-           [42]InvestingJournal!$A:$A,"&lt;="&amp;A84)
+    SUMIFS([43]InvestingJournal!$F:$F,
+           [43]InvestingJournal!$C:$C,"Izra Advance",
+           [43]InvestingJournal!$A:$A,"&lt;="&amp;A84)
     +
-    SUMIFS([42]InvestingJournal!$F:$F,
-           [42]InvestingJournal!$C:$C,"Investment to Unit",
-           [42]InvestingJournal!$A:$A,"&lt;="&amp;A84),
+    SUMIFS([43]InvestingJournal!$F:$F,
+           [43]InvestingJournal!$C:$C,"Investment to Unit",
+           [43]InvestingJournal!$A:$A,"&lt;="&amp;A84),
     "")</f>
         <v/>
       </c>
       <c r="D84" s="15" t="str">
         <f>IF(A84&lt;&gt;"",
-    SUMIFS([42]InvestingJournal!$F:$F,
-           [42]InvestingJournal!$C:$C,"Loan Advance",
-           [42]InvestingJournal!$A:$A,"&lt;="&amp;A84),
+    SUMIFS([43]InvestingJournal!$F:$F,
+           [43]InvestingJournal!$C:$C,"Loan Advance",
+           [43]InvestingJournal!$A:$A,"&lt;="&amp;A84),
     "")</f>
         <v/>
       </c>
       <c r="E84" s="15" t="str">
         <f>IF(A84&lt;&gt;"",
-    SUMIFS([42]FinancingJournal!$E:$E,
-           [42]FinancingJournal!$C:$C,"Borrowing",
-           [42]FinancingJournal!$A:$A,"&lt;="&amp;A84)
+    SUMIFS([43]FinancingJournal!$E:$E,
+           [43]FinancingJournal!$C:$C,"Borrowing",
+           [43]FinancingJournal!$A:$A,"&lt;="&amp;A84)
     +
-    SUMIFS([42]FinancingJournal!$E:$E,
-           [42]FinancingJournal!$C:$C,"Withdrawal",
-           [42]FinancingJournal!$A:$A,"&lt;="&amp;A84),
+    SUMIFS([43]FinancingJournal!$E:$E,
+           [43]FinancingJournal!$C:$C,"Withdrawal",
+           [43]FinancingJournal!$A:$A,"&lt;="&amp;A84),
     "")</f>
         <v/>
       </c>
@@ -23115,41 +23472,41 @@
       <c r="A85" s="16"/>
       <c r="B85" s="17" t="str">
         <f>IF(A85&lt;&gt;"",
-    SUMIFS([42]FinancingJournal!$E:$E,
-           [42]FinancingJournal!$C:$C,"Capital Injection",
-           [42]FinancingJournal!$A:$A,"&lt;="&amp;A85),
+    SUMIFS([43]FinancingJournal!$E:$E,
+           [43]FinancingJournal!$C:$C,"Capital Injection",
+           [43]FinancingJournal!$A:$A,"&lt;="&amp;A85),
     "")</f>
         <v/>
       </c>
       <c r="C85" s="18" t="str">
         <f>IF(A85&lt;&gt;"",
-    SUMIFS([42]InvestingJournal!$F:$F,
-           [42]InvestingJournal!$C:$C,"Izra Advance",
-           [42]InvestingJournal!$A:$A,"&lt;="&amp;A85)
+    SUMIFS([43]InvestingJournal!$F:$F,
+           [43]InvestingJournal!$C:$C,"Izra Advance",
+           [43]InvestingJournal!$A:$A,"&lt;="&amp;A85)
     +
-    SUMIFS([42]InvestingJournal!$F:$F,
-           [42]InvestingJournal!$C:$C,"Investment to Unit",
-           [42]InvestingJournal!$A:$A,"&lt;="&amp;A85),
+    SUMIFS([43]InvestingJournal!$F:$F,
+           [43]InvestingJournal!$C:$C,"Investment to Unit",
+           [43]InvestingJournal!$A:$A,"&lt;="&amp;A85),
     "")</f>
         <v/>
       </c>
       <c r="D85" s="18" t="str">
         <f>IF(A85&lt;&gt;"",
-    SUMIFS([42]InvestingJournal!$F:$F,
-           [42]InvestingJournal!$C:$C,"Loan Advance",
-           [42]InvestingJournal!$A:$A,"&lt;="&amp;A85),
+    SUMIFS([43]InvestingJournal!$F:$F,
+           [43]InvestingJournal!$C:$C,"Loan Advance",
+           [43]InvestingJournal!$A:$A,"&lt;="&amp;A85),
     "")</f>
         <v/>
       </c>
       <c r="E85" s="18" t="str">
         <f>IF(A85&lt;&gt;"",
-    SUMIFS([42]FinancingJournal!$E:$E,
-           [42]FinancingJournal!$C:$C,"Borrowing",
-           [42]FinancingJournal!$A:$A,"&lt;="&amp;A85)
+    SUMIFS([43]FinancingJournal!$E:$E,
+           [43]FinancingJournal!$C:$C,"Borrowing",
+           [43]FinancingJournal!$A:$A,"&lt;="&amp;A85)
     +
-    SUMIFS([42]FinancingJournal!$E:$E,
-           [42]FinancingJournal!$C:$C,"Withdrawal",
-           [42]FinancingJournal!$A:$A,"&lt;="&amp;A85),
+    SUMIFS([43]FinancingJournal!$E:$E,
+           [43]FinancingJournal!$C:$C,"Withdrawal",
+           [43]FinancingJournal!$A:$A,"&lt;="&amp;A85),
     "")</f>
         <v/>
       </c>
@@ -23164,41 +23521,41 @@
       <c r="A86" s="11"/>
       <c r="B86" s="14" t="str">
         <f>IF(A86&lt;&gt;"",
-    SUMIFS([42]FinancingJournal!$E:$E,
-           [42]FinancingJournal!$C:$C,"Capital Injection",
-           [42]FinancingJournal!$A:$A,"&lt;="&amp;A86),
+    SUMIFS([43]FinancingJournal!$E:$E,
+           [43]FinancingJournal!$C:$C,"Capital Injection",
+           [43]FinancingJournal!$A:$A,"&lt;="&amp;A86),
     "")</f>
         <v/>
       </c>
       <c r="C86" s="15" t="str">
         <f>IF(A86&lt;&gt;"",
-    SUMIFS([42]InvestingJournal!$F:$F,
-           [42]InvestingJournal!$C:$C,"Izra Advance",
-           [42]InvestingJournal!$A:$A,"&lt;="&amp;A86)
+    SUMIFS([43]InvestingJournal!$F:$F,
+           [43]InvestingJournal!$C:$C,"Izra Advance",
+           [43]InvestingJournal!$A:$A,"&lt;="&amp;A86)
     +
-    SUMIFS([42]InvestingJournal!$F:$F,
-           [42]InvestingJournal!$C:$C,"Investment to Unit",
-           [42]InvestingJournal!$A:$A,"&lt;="&amp;A86),
+    SUMIFS([43]InvestingJournal!$F:$F,
+           [43]InvestingJournal!$C:$C,"Investment to Unit",
+           [43]InvestingJournal!$A:$A,"&lt;="&amp;A86),
     "")</f>
         <v/>
       </c>
       <c r="D86" s="15" t="str">
         <f>IF(A86&lt;&gt;"",
-    SUMIFS([42]InvestingJournal!$F:$F,
-           [42]InvestingJournal!$C:$C,"Loan Advance",
-           [42]InvestingJournal!$A:$A,"&lt;="&amp;A86),
+    SUMIFS([43]InvestingJournal!$F:$F,
+           [43]InvestingJournal!$C:$C,"Loan Advance",
+           [43]InvestingJournal!$A:$A,"&lt;="&amp;A86),
     "")</f>
         <v/>
       </c>
       <c r="E86" s="15" t="str">
         <f>IF(A86&lt;&gt;"",
-    SUMIFS([42]FinancingJournal!$E:$E,
-           [42]FinancingJournal!$C:$C,"Borrowing",
-           [42]FinancingJournal!$A:$A,"&lt;="&amp;A86)
+    SUMIFS([43]FinancingJournal!$E:$E,
+           [43]FinancingJournal!$C:$C,"Borrowing",
+           [43]FinancingJournal!$A:$A,"&lt;="&amp;A86)
     +
-    SUMIFS([42]FinancingJournal!$E:$E,
-           [42]FinancingJournal!$C:$C,"Withdrawal",
-           [42]FinancingJournal!$A:$A,"&lt;="&amp;A86),
+    SUMIFS([43]FinancingJournal!$E:$E,
+           [43]FinancingJournal!$C:$C,"Withdrawal",
+           [43]FinancingJournal!$A:$A,"&lt;="&amp;A86),
     "")</f>
         <v/>
       </c>
@@ -23212,41 +23569,41 @@
       <c r="A87" s="16"/>
       <c r="B87" s="17" t="str">
         <f>IF(A87&lt;&gt;"",
-    SUMIFS([42]FinancingJournal!$E:$E,
-           [42]FinancingJournal!$C:$C,"Capital Injection",
-           [42]FinancingJournal!$A:$A,"&lt;="&amp;A87),
+    SUMIFS([43]FinancingJournal!$E:$E,
+           [43]FinancingJournal!$C:$C,"Capital Injection",
+           [43]FinancingJournal!$A:$A,"&lt;="&amp;A87),
     "")</f>
         <v/>
       </c>
       <c r="C87" s="18" t="str">
         <f>IF(A87&lt;&gt;"",
-    SUMIFS([42]InvestingJournal!$F:$F,
-           [42]InvestingJournal!$C:$C,"Izra Advance",
-           [42]InvestingJournal!$A:$A,"&lt;="&amp;A87)
+    SUMIFS([43]InvestingJournal!$F:$F,
+           [43]InvestingJournal!$C:$C,"Izra Advance",
+           [43]InvestingJournal!$A:$A,"&lt;="&amp;A87)
     +
-    SUMIFS([42]InvestingJournal!$F:$F,
-           [42]InvestingJournal!$C:$C,"Investment to Unit",
-           [42]InvestingJournal!$A:$A,"&lt;="&amp;A87),
+    SUMIFS([43]InvestingJournal!$F:$F,
+           [43]InvestingJournal!$C:$C,"Investment to Unit",
+           [43]InvestingJournal!$A:$A,"&lt;="&amp;A87),
     "")</f>
         <v/>
       </c>
       <c r="D87" s="18" t="str">
         <f>IF(A87&lt;&gt;"",
-    SUMIFS([42]InvestingJournal!$F:$F,
-           [42]InvestingJournal!$C:$C,"Loan Advance",
-           [42]InvestingJournal!$A:$A,"&lt;="&amp;A87),
+    SUMIFS([43]InvestingJournal!$F:$F,
+           [43]InvestingJournal!$C:$C,"Loan Advance",
+           [43]InvestingJournal!$A:$A,"&lt;="&amp;A87),
     "")</f>
         <v/>
       </c>
       <c r="E87" s="18" t="str">
         <f>IF(A87&lt;&gt;"",
-    SUMIFS([42]FinancingJournal!$E:$E,
-           [42]FinancingJournal!$C:$C,"Borrowing",
-           [42]FinancingJournal!$A:$A,"&lt;="&amp;A87)
+    SUMIFS([43]FinancingJournal!$E:$E,
+           [43]FinancingJournal!$C:$C,"Borrowing",
+           [43]FinancingJournal!$A:$A,"&lt;="&amp;A87)
     +
-    SUMIFS([42]FinancingJournal!$E:$E,
-           [42]FinancingJournal!$C:$C,"Withdrawal",
-           [42]FinancingJournal!$A:$A,"&lt;="&amp;A87),
+    SUMIFS([43]FinancingJournal!$E:$E,
+           [43]FinancingJournal!$C:$C,"Withdrawal",
+           [43]FinancingJournal!$A:$A,"&lt;="&amp;A87),
     "")</f>
         <v/>
       </c>
@@ -23261,41 +23618,41 @@
       <c r="A88" s="11"/>
       <c r="B88" s="14" t="str">
         <f>IF(A88&lt;&gt;"",
-    SUMIFS([42]FinancingJournal!$E:$E,
-           [42]FinancingJournal!$C:$C,"Capital Injection",
-           [42]FinancingJournal!$A:$A,"&lt;="&amp;A88),
+    SUMIFS([43]FinancingJournal!$E:$E,
+           [43]FinancingJournal!$C:$C,"Capital Injection",
+           [43]FinancingJournal!$A:$A,"&lt;="&amp;A88),
     "")</f>
         <v/>
       </c>
       <c r="C88" s="15" t="str">
         <f>IF(A88&lt;&gt;"",
-    SUMIFS([42]InvestingJournal!$F:$F,
-           [42]InvestingJournal!$C:$C,"Izra Advance",
-           [42]InvestingJournal!$A:$A,"&lt;="&amp;A88)
+    SUMIFS([43]InvestingJournal!$F:$F,
+           [43]InvestingJournal!$C:$C,"Izra Advance",
+           [43]InvestingJournal!$A:$A,"&lt;="&amp;A88)
     +
-    SUMIFS([42]InvestingJournal!$F:$F,
-           [42]InvestingJournal!$C:$C,"Investment to Unit",
-           [42]InvestingJournal!$A:$A,"&lt;="&amp;A88),
+    SUMIFS([43]InvestingJournal!$F:$F,
+           [43]InvestingJournal!$C:$C,"Investment to Unit",
+           [43]InvestingJournal!$A:$A,"&lt;="&amp;A88),
     "")</f>
         <v/>
       </c>
       <c r="D88" s="15" t="str">
         <f>IF(A88&lt;&gt;"",
-    SUMIFS([42]InvestingJournal!$F:$F,
-           [42]InvestingJournal!$C:$C,"Loan Advance",
-           [42]InvestingJournal!$A:$A,"&lt;="&amp;A88),
+    SUMIFS([43]InvestingJournal!$F:$F,
+           [43]InvestingJournal!$C:$C,"Loan Advance",
+           [43]InvestingJournal!$A:$A,"&lt;="&amp;A88),
     "")</f>
         <v/>
       </c>
       <c r="E88" s="15" t="str">
         <f>IF(A88&lt;&gt;"",
-    SUMIFS([42]FinancingJournal!$E:$E,
-           [42]FinancingJournal!$C:$C,"Borrowing",
-           [42]FinancingJournal!$A:$A,"&lt;="&amp;A88)
+    SUMIFS([43]FinancingJournal!$E:$E,
+           [43]FinancingJournal!$C:$C,"Borrowing",
+           [43]FinancingJournal!$A:$A,"&lt;="&amp;A88)
     +
-    SUMIFS([42]FinancingJournal!$E:$E,
-           [42]FinancingJournal!$C:$C,"Withdrawal",
-           [42]FinancingJournal!$A:$A,"&lt;="&amp;A88),
+    SUMIFS([43]FinancingJournal!$E:$E,
+           [43]FinancingJournal!$C:$C,"Withdrawal",
+           [43]FinancingJournal!$A:$A,"&lt;="&amp;A88),
     "")</f>
         <v/>
       </c>
@@ -23309,41 +23666,41 @@
       <c r="A89" s="16"/>
       <c r="B89" s="17" t="str">
         <f>IF(A89&lt;&gt;"",
-    SUMIFS([42]FinancingJournal!$E:$E,
-           [42]FinancingJournal!$C:$C,"Capital Injection",
-           [42]FinancingJournal!$A:$A,"&lt;="&amp;A89),
+    SUMIFS([43]FinancingJournal!$E:$E,
+           [43]FinancingJournal!$C:$C,"Capital Injection",
+           [43]FinancingJournal!$A:$A,"&lt;="&amp;A89),
     "")</f>
         <v/>
       </c>
       <c r="C89" s="18" t="str">
         <f>IF(A89&lt;&gt;"",
-    SUMIFS([42]InvestingJournal!$F:$F,
-           [42]InvestingJournal!$C:$C,"Izra Advance",
-           [42]InvestingJournal!$A:$A,"&lt;="&amp;A89)
+    SUMIFS([43]InvestingJournal!$F:$F,
+           [43]InvestingJournal!$C:$C,"Izra Advance",
+           [43]InvestingJournal!$A:$A,"&lt;="&amp;A89)
     +
-    SUMIFS([42]InvestingJournal!$F:$F,
-           [42]InvestingJournal!$C:$C,"Investment to Unit",
-           [42]InvestingJournal!$A:$A,"&lt;="&amp;A89),
+    SUMIFS([43]InvestingJournal!$F:$F,
+           [43]InvestingJournal!$C:$C,"Investment to Unit",
+           [43]InvestingJournal!$A:$A,"&lt;="&amp;A89),
     "")</f>
         <v/>
       </c>
       <c r="D89" s="18" t="str">
         <f>IF(A89&lt;&gt;"",
-    SUMIFS([42]InvestingJournal!$F:$F,
-           [42]InvestingJournal!$C:$C,"Loan Advance",
-           [42]InvestingJournal!$A:$A,"&lt;="&amp;A89),
+    SUMIFS([43]InvestingJournal!$F:$F,
+           [43]InvestingJournal!$C:$C,"Loan Advance",
+           [43]InvestingJournal!$A:$A,"&lt;="&amp;A89),
     "")</f>
         <v/>
       </c>
       <c r="E89" s="18" t="str">
         <f>IF(A89&lt;&gt;"",
-    SUMIFS([42]FinancingJournal!$E:$E,
-           [42]FinancingJournal!$C:$C,"Borrowing",
-           [42]FinancingJournal!$A:$A,"&lt;="&amp;A89)
+    SUMIFS([43]FinancingJournal!$E:$E,
+           [43]FinancingJournal!$C:$C,"Borrowing",
+           [43]FinancingJournal!$A:$A,"&lt;="&amp;A89)
     +
-    SUMIFS([42]FinancingJournal!$E:$E,
-           [42]FinancingJournal!$C:$C,"Withdrawal",
-           [42]FinancingJournal!$A:$A,"&lt;="&amp;A89),
+    SUMIFS([43]FinancingJournal!$E:$E,
+           [43]FinancingJournal!$C:$C,"Withdrawal",
+           [43]FinancingJournal!$A:$A,"&lt;="&amp;A89),
     "")</f>
         <v/>
       </c>
@@ -23358,41 +23715,41 @@
       <c r="A90" s="11"/>
       <c r="B90" s="14" t="str">
         <f>IF(A90&lt;&gt;"",
-    SUMIFS([42]FinancingJournal!$E:$E,
-           [42]FinancingJournal!$C:$C,"Capital Injection",
-           [42]FinancingJournal!$A:$A,"&lt;="&amp;A90),
+    SUMIFS([43]FinancingJournal!$E:$E,
+           [43]FinancingJournal!$C:$C,"Capital Injection",
+           [43]FinancingJournal!$A:$A,"&lt;="&amp;A90),
     "")</f>
         <v/>
       </c>
       <c r="C90" s="15" t="str">
         <f>IF(A90&lt;&gt;"",
-    SUMIFS([42]InvestingJournal!$F:$F,
-           [42]InvestingJournal!$C:$C,"Izra Advance",
-           [42]InvestingJournal!$A:$A,"&lt;="&amp;A90)
+    SUMIFS([43]InvestingJournal!$F:$F,
+           [43]InvestingJournal!$C:$C,"Izra Advance",
+           [43]InvestingJournal!$A:$A,"&lt;="&amp;A90)
     +
-    SUMIFS([42]InvestingJournal!$F:$F,
-           [42]InvestingJournal!$C:$C,"Investment to Unit",
-           [42]InvestingJournal!$A:$A,"&lt;="&amp;A90),
+    SUMIFS([43]InvestingJournal!$F:$F,
+           [43]InvestingJournal!$C:$C,"Investment to Unit",
+           [43]InvestingJournal!$A:$A,"&lt;="&amp;A90),
     "")</f>
         <v/>
       </c>
       <c r="D90" s="15" t="str">
         <f>IF(A90&lt;&gt;"",
-    SUMIFS([42]InvestingJournal!$F:$F,
-           [42]InvestingJournal!$C:$C,"Loan Advance",
-           [42]InvestingJournal!$A:$A,"&lt;="&amp;A90),
+    SUMIFS([43]InvestingJournal!$F:$F,
+           [43]InvestingJournal!$C:$C,"Loan Advance",
+           [43]InvestingJournal!$A:$A,"&lt;="&amp;A90),
     "")</f>
         <v/>
       </c>
       <c r="E90" s="15" t="str">
         <f>IF(A90&lt;&gt;"",
-    SUMIFS([42]FinancingJournal!$E:$E,
-           [42]FinancingJournal!$C:$C,"Borrowing",
-           [42]FinancingJournal!$A:$A,"&lt;="&amp;A90)
+    SUMIFS([43]FinancingJournal!$E:$E,
+           [43]FinancingJournal!$C:$C,"Borrowing",
+           [43]FinancingJournal!$A:$A,"&lt;="&amp;A90)
     +
-    SUMIFS([42]FinancingJournal!$E:$E,
-           [42]FinancingJournal!$C:$C,"Withdrawal",
-           [42]FinancingJournal!$A:$A,"&lt;="&amp;A90),
+    SUMIFS([43]FinancingJournal!$E:$E,
+           [43]FinancingJournal!$C:$C,"Withdrawal",
+           [43]FinancingJournal!$A:$A,"&lt;="&amp;A90),
     "")</f>
         <v/>
       </c>
@@ -23406,41 +23763,41 @@
       <c r="A91" s="16"/>
       <c r="B91" s="17" t="str">
         <f>IF(A91&lt;&gt;"",
-    SUMIFS([42]FinancingJournal!$E:$E,
-           [42]FinancingJournal!$C:$C,"Capital Injection",
-           [42]FinancingJournal!$A:$A,"&lt;="&amp;A91),
+    SUMIFS([43]FinancingJournal!$E:$E,
+           [43]FinancingJournal!$C:$C,"Capital Injection",
+           [43]FinancingJournal!$A:$A,"&lt;="&amp;A91),
     "")</f>
         <v/>
       </c>
       <c r="C91" s="18" t="str">
         <f>IF(A91&lt;&gt;"",
-    SUMIFS([42]InvestingJournal!$F:$F,
-           [42]InvestingJournal!$C:$C,"Izra Advance",
-           [42]InvestingJournal!$A:$A,"&lt;="&amp;A91)
+    SUMIFS([43]InvestingJournal!$F:$F,
+           [43]InvestingJournal!$C:$C,"Izra Advance",
+           [43]InvestingJournal!$A:$A,"&lt;="&amp;A91)
     +
-    SUMIFS([42]InvestingJournal!$F:$F,
-           [42]InvestingJournal!$C:$C,"Investment to Unit",
-           [42]InvestingJournal!$A:$A,"&lt;="&amp;A91),
+    SUMIFS([43]InvestingJournal!$F:$F,
+           [43]InvestingJournal!$C:$C,"Investment to Unit",
+           [43]InvestingJournal!$A:$A,"&lt;="&amp;A91),
     "")</f>
         <v/>
       </c>
       <c r="D91" s="18" t="str">
         <f>IF(A91&lt;&gt;"",
-    SUMIFS([42]InvestingJournal!$F:$F,
-           [42]InvestingJournal!$C:$C,"Loan Advance",
-           [42]InvestingJournal!$A:$A,"&lt;="&amp;A91),
+    SUMIFS([43]InvestingJournal!$F:$F,
+           [43]InvestingJournal!$C:$C,"Loan Advance",
+           [43]InvestingJournal!$A:$A,"&lt;="&amp;A91),
     "")</f>
         <v/>
       </c>
       <c r="E91" s="18" t="str">
         <f>IF(A91&lt;&gt;"",
-    SUMIFS([42]FinancingJournal!$E:$E,
-           [42]FinancingJournal!$C:$C,"Borrowing",
-           [42]FinancingJournal!$A:$A,"&lt;="&amp;A91)
+    SUMIFS([43]FinancingJournal!$E:$E,
+           [43]FinancingJournal!$C:$C,"Borrowing",
+           [43]FinancingJournal!$A:$A,"&lt;="&amp;A91)
     +
-    SUMIFS([42]FinancingJournal!$E:$E,
-           [42]FinancingJournal!$C:$C,"Withdrawal",
-           [42]FinancingJournal!$A:$A,"&lt;="&amp;A91),
+    SUMIFS([43]FinancingJournal!$E:$E,
+           [43]FinancingJournal!$C:$C,"Withdrawal",
+           [43]FinancingJournal!$A:$A,"&lt;="&amp;A91),
     "")</f>
         <v/>
       </c>
@@ -23455,41 +23812,41 @@
       <c r="A92" s="11"/>
       <c r="B92" s="14" t="str">
         <f>IF(A92&lt;&gt;"",
-    SUMIFS([42]FinancingJournal!$E:$E,
-           [42]FinancingJournal!$C:$C,"Capital Injection",
-           [42]FinancingJournal!$A:$A,"&lt;="&amp;A92),
+    SUMIFS([43]FinancingJournal!$E:$E,
+           [43]FinancingJournal!$C:$C,"Capital Injection",
+           [43]FinancingJournal!$A:$A,"&lt;="&amp;A92),
     "")</f>
         <v/>
       </c>
       <c r="C92" s="15" t="str">
         <f>IF(A92&lt;&gt;"",
-    SUMIFS([42]InvestingJournal!$F:$F,
-           [42]InvestingJournal!$C:$C,"Izra Advance",
-           [42]InvestingJournal!$A:$A,"&lt;="&amp;A92)
+    SUMIFS([43]InvestingJournal!$F:$F,
+           [43]InvestingJournal!$C:$C,"Izra Advance",
+           [43]InvestingJournal!$A:$A,"&lt;="&amp;A92)
     +
-    SUMIFS([42]InvestingJournal!$F:$F,
-           [42]InvestingJournal!$C:$C,"Investment to Unit",
-           [42]InvestingJournal!$A:$A,"&lt;="&amp;A92),
+    SUMIFS([43]InvestingJournal!$F:$F,
+           [43]InvestingJournal!$C:$C,"Investment to Unit",
+           [43]InvestingJournal!$A:$A,"&lt;="&amp;A92),
     "")</f>
         <v/>
       </c>
       <c r="D92" s="15" t="str">
         <f>IF(A92&lt;&gt;"",
-    SUMIFS([42]InvestingJournal!$F:$F,
-           [42]InvestingJournal!$C:$C,"Loan Advance",
-           [42]InvestingJournal!$A:$A,"&lt;="&amp;A92),
+    SUMIFS([43]InvestingJournal!$F:$F,
+           [43]InvestingJournal!$C:$C,"Loan Advance",
+           [43]InvestingJournal!$A:$A,"&lt;="&amp;A92),
     "")</f>
         <v/>
       </c>
       <c r="E92" s="15" t="str">
         <f>IF(A92&lt;&gt;"",
-    SUMIFS([42]FinancingJournal!$E:$E,
-           [42]FinancingJournal!$C:$C,"Borrowing",
-           [42]FinancingJournal!$A:$A,"&lt;="&amp;A92)
+    SUMIFS([43]FinancingJournal!$E:$E,
+           [43]FinancingJournal!$C:$C,"Borrowing",
+           [43]FinancingJournal!$A:$A,"&lt;="&amp;A92)
     +
-    SUMIFS([42]FinancingJournal!$E:$E,
-           [42]FinancingJournal!$C:$C,"Withdrawal",
-           [42]FinancingJournal!$A:$A,"&lt;="&amp;A92),
+    SUMIFS([43]FinancingJournal!$E:$E,
+           [43]FinancingJournal!$C:$C,"Withdrawal",
+           [43]FinancingJournal!$A:$A,"&lt;="&amp;A92),
     "")</f>
         <v/>
       </c>
@@ -23503,41 +23860,41 @@
       <c r="A93" s="16"/>
       <c r="B93" s="17" t="str">
         <f>IF(A93&lt;&gt;"",
-    SUMIFS([42]FinancingJournal!$E:$E,
-           [42]FinancingJournal!$C:$C,"Capital Injection",
-           [42]FinancingJournal!$A:$A,"&lt;="&amp;A93),
+    SUMIFS([43]FinancingJournal!$E:$E,
+           [43]FinancingJournal!$C:$C,"Capital Injection",
+           [43]FinancingJournal!$A:$A,"&lt;="&amp;A93),
     "")</f>
         <v/>
       </c>
       <c r="C93" s="18" t="str">
         <f>IF(A93&lt;&gt;"",
-    SUMIFS([42]InvestingJournal!$F:$F,
-           [42]InvestingJournal!$C:$C,"Izra Advance",
-           [42]InvestingJournal!$A:$A,"&lt;="&amp;A93)
+    SUMIFS([43]InvestingJournal!$F:$F,
+           [43]InvestingJournal!$C:$C,"Izra Advance",
+           [43]InvestingJournal!$A:$A,"&lt;="&amp;A93)
     +
-    SUMIFS([42]InvestingJournal!$F:$F,
-           [42]InvestingJournal!$C:$C,"Investment to Unit",
-           [42]InvestingJournal!$A:$A,"&lt;="&amp;A93),
+    SUMIFS([43]InvestingJournal!$F:$F,
+           [43]InvestingJournal!$C:$C,"Investment to Unit",
+           [43]InvestingJournal!$A:$A,"&lt;="&amp;A93),
     "")</f>
         <v/>
       </c>
       <c r="D93" s="18" t="str">
         <f>IF(A93&lt;&gt;"",
-    SUMIFS([42]InvestingJournal!$F:$F,
-           [42]InvestingJournal!$C:$C,"Loan Advance",
-           [42]InvestingJournal!$A:$A,"&lt;="&amp;A93),
+    SUMIFS([43]InvestingJournal!$F:$F,
+           [43]InvestingJournal!$C:$C,"Loan Advance",
+           [43]InvestingJournal!$A:$A,"&lt;="&amp;A93),
     "")</f>
         <v/>
       </c>
       <c r="E93" s="18" t="str">
         <f>IF(A93&lt;&gt;"",
-    SUMIFS([42]FinancingJournal!$E:$E,
-           [42]FinancingJournal!$C:$C,"Borrowing",
-           [42]FinancingJournal!$A:$A,"&lt;="&amp;A93)
+    SUMIFS([43]FinancingJournal!$E:$E,
+           [43]FinancingJournal!$C:$C,"Borrowing",
+           [43]FinancingJournal!$A:$A,"&lt;="&amp;A93)
     +
-    SUMIFS([42]FinancingJournal!$E:$E,
-           [42]FinancingJournal!$C:$C,"Withdrawal",
-           [42]FinancingJournal!$A:$A,"&lt;="&amp;A93),
+    SUMIFS([43]FinancingJournal!$E:$E,
+           [43]FinancingJournal!$C:$C,"Withdrawal",
+           [43]FinancingJournal!$A:$A,"&lt;="&amp;A93),
     "")</f>
         <v/>
       </c>
@@ -23552,41 +23909,41 @@
       <c r="A94" s="11"/>
       <c r="B94" s="14" t="str">
         <f>IF(A94&lt;&gt;"",
-    SUMIFS([42]FinancingJournal!$E:$E,
-           [42]FinancingJournal!$C:$C,"Capital Injection",
-           [42]FinancingJournal!$A:$A,"&lt;="&amp;A94),
+    SUMIFS([43]FinancingJournal!$E:$E,
+           [43]FinancingJournal!$C:$C,"Capital Injection",
+           [43]FinancingJournal!$A:$A,"&lt;="&amp;A94),
     "")</f>
         <v/>
       </c>
       <c r="C94" s="15" t="str">
         <f>IF(A94&lt;&gt;"",
-    SUMIFS([42]InvestingJournal!$F:$F,
-           [42]InvestingJournal!$C:$C,"Izra Advance",
-           [42]InvestingJournal!$A:$A,"&lt;="&amp;A94)
+    SUMIFS([43]InvestingJournal!$F:$F,
+           [43]InvestingJournal!$C:$C,"Izra Advance",
+           [43]InvestingJournal!$A:$A,"&lt;="&amp;A94)
     +
-    SUMIFS([42]InvestingJournal!$F:$F,
-           [42]InvestingJournal!$C:$C,"Investment to Unit",
-           [42]InvestingJournal!$A:$A,"&lt;="&amp;A94),
+    SUMIFS([43]InvestingJournal!$F:$F,
+           [43]InvestingJournal!$C:$C,"Investment to Unit",
+           [43]InvestingJournal!$A:$A,"&lt;="&amp;A94),
     "")</f>
         <v/>
       </c>
       <c r="D94" s="15" t="str">
         <f>IF(A94&lt;&gt;"",
-    SUMIFS([42]InvestingJournal!$F:$F,
-           [42]InvestingJournal!$C:$C,"Loan Advance",
-           [42]InvestingJournal!$A:$A,"&lt;="&amp;A94),
+    SUMIFS([43]InvestingJournal!$F:$F,
+           [43]InvestingJournal!$C:$C,"Loan Advance",
+           [43]InvestingJournal!$A:$A,"&lt;="&amp;A94),
     "")</f>
         <v/>
       </c>
       <c r="E94" s="15" t="str">
         <f>IF(A94&lt;&gt;"",
-    SUMIFS([42]FinancingJournal!$E:$E,
-           [42]FinancingJournal!$C:$C,"Borrowing",
-           [42]FinancingJournal!$A:$A,"&lt;="&amp;A94)
+    SUMIFS([43]FinancingJournal!$E:$E,
+           [43]FinancingJournal!$C:$C,"Borrowing",
+           [43]FinancingJournal!$A:$A,"&lt;="&amp;A94)
     +
-    SUMIFS([42]FinancingJournal!$E:$E,
-           [42]FinancingJournal!$C:$C,"Withdrawal",
-           [42]FinancingJournal!$A:$A,"&lt;="&amp;A94),
+    SUMIFS([43]FinancingJournal!$E:$E,
+           [43]FinancingJournal!$C:$C,"Withdrawal",
+           [43]FinancingJournal!$A:$A,"&lt;="&amp;A94),
     "")</f>
         <v/>
       </c>
@@ -23600,41 +23957,41 @@
       <c r="A95" s="16"/>
       <c r="B95" s="17" t="str">
         <f>IF(A95&lt;&gt;"",
-    SUMIFS([42]FinancingJournal!$E:$E,
-           [42]FinancingJournal!$C:$C,"Capital Injection",
-           [42]FinancingJournal!$A:$A,"&lt;="&amp;A95),
+    SUMIFS([43]FinancingJournal!$E:$E,
+           [43]FinancingJournal!$C:$C,"Capital Injection",
+           [43]FinancingJournal!$A:$A,"&lt;="&amp;A95),
     "")</f>
         <v/>
       </c>
       <c r="C95" s="18" t="str">
         <f>IF(A95&lt;&gt;"",
-    SUMIFS([42]InvestingJournal!$F:$F,
-           [42]InvestingJournal!$C:$C,"Izra Advance",
-           [42]InvestingJournal!$A:$A,"&lt;="&amp;A95)
+    SUMIFS([43]InvestingJournal!$F:$F,
+           [43]InvestingJournal!$C:$C,"Izra Advance",
+           [43]InvestingJournal!$A:$A,"&lt;="&amp;A95)
     +
-    SUMIFS([42]InvestingJournal!$F:$F,
-           [42]InvestingJournal!$C:$C,"Investment to Unit",
-           [42]InvestingJournal!$A:$A,"&lt;="&amp;A95),
+    SUMIFS([43]InvestingJournal!$F:$F,
+           [43]InvestingJournal!$C:$C,"Investment to Unit",
+           [43]InvestingJournal!$A:$A,"&lt;="&amp;A95),
     "")</f>
         <v/>
       </c>
       <c r="D95" s="18" t="str">
         <f>IF(A95&lt;&gt;"",
-    SUMIFS([42]InvestingJournal!$F:$F,
-           [42]InvestingJournal!$C:$C,"Loan Advance",
-           [42]InvestingJournal!$A:$A,"&lt;="&amp;A95),
+    SUMIFS([43]InvestingJournal!$F:$F,
+           [43]InvestingJournal!$C:$C,"Loan Advance",
+           [43]InvestingJournal!$A:$A,"&lt;="&amp;A95),
     "")</f>
         <v/>
       </c>
       <c r="E95" s="18" t="str">
         <f>IF(A95&lt;&gt;"",
-    SUMIFS([42]FinancingJournal!$E:$E,
-           [42]FinancingJournal!$C:$C,"Borrowing",
-           [42]FinancingJournal!$A:$A,"&lt;="&amp;A95)
+    SUMIFS([43]FinancingJournal!$E:$E,
+           [43]FinancingJournal!$C:$C,"Borrowing",
+           [43]FinancingJournal!$A:$A,"&lt;="&amp;A95)
     +
-    SUMIFS([42]FinancingJournal!$E:$E,
-           [42]FinancingJournal!$C:$C,"Withdrawal",
-           [42]FinancingJournal!$A:$A,"&lt;="&amp;A95),
+    SUMIFS([43]FinancingJournal!$E:$E,
+           [43]FinancingJournal!$C:$C,"Withdrawal",
+           [43]FinancingJournal!$A:$A,"&lt;="&amp;A95),
     "")</f>
         <v/>
       </c>
@@ -23649,41 +24006,41 @@
       <c r="A96" s="11"/>
       <c r="B96" s="14" t="str">
         <f>IF(A96&lt;&gt;"",
-    SUMIFS([42]FinancingJournal!$E:$E,
-           [42]FinancingJournal!$C:$C,"Capital Injection",
-           [42]FinancingJournal!$A:$A,"&lt;="&amp;A96),
+    SUMIFS([43]FinancingJournal!$E:$E,
+           [43]FinancingJournal!$C:$C,"Capital Injection",
+           [43]FinancingJournal!$A:$A,"&lt;="&amp;A96),
     "")</f>
         <v/>
       </c>
       <c r="C96" s="15" t="str">
         <f>IF(A96&lt;&gt;"",
-    SUMIFS([42]InvestingJournal!$F:$F,
-           [42]InvestingJournal!$C:$C,"Izra Advance",
-           [42]InvestingJournal!$A:$A,"&lt;="&amp;A96)
+    SUMIFS([43]InvestingJournal!$F:$F,
+           [43]InvestingJournal!$C:$C,"Izra Advance",
+           [43]InvestingJournal!$A:$A,"&lt;="&amp;A96)
     +
-    SUMIFS([42]InvestingJournal!$F:$F,
-           [42]InvestingJournal!$C:$C,"Investment to Unit",
-           [42]InvestingJournal!$A:$A,"&lt;="&amp;A96),
+    SUMIFS([43]InvestingJournal!$F:$F,
+           [43]InvestingJournal!$C:$C,"Investment to Unit",
+           [43]InvestingJournal!$A:$A,"&lt;="&amp;A96),
     "")</f>
         <v/>
       </c>
       <c r="D96" s="15" t="str">
         <f>IF(A96&lt;&gt;"",
-    SUMIFS([42]InvestingJournal!$F:$F,
-           [42]InvestingJournal!$C:$C,"Loan Advance",
-           [42]InvestingJournal!$A:$A,"&lt;="&amp;A96),
+    SUMIFS([43]InvestingJournal!$F:$F,
+           [43]InvestingJournal!$C:$C,"Loan Advance",
+           [43]InvestingJournal!$A:$A,"&lt;="&amp;A96),
     "")</f>
         <v/>
       </c>
       <c r="E96" s="15" t="str">
         <f>IF(A96&lt;&gt;"",
-    SUMIFS([42]FinancingJournal!$E:$E,
-           [42]FinancingJournal!$C:$C,"Borrowing",
-           [42]FinancingJournal!$A:$A,"&lt;="&amp;A96)
+    SUMIFS([43]FinancingJournal!$E:$E,
+           [43]FinancingJournal!$C:$C,"Borrowing",
+           [43]FinancingJournal!$A:$A,"&lt;="&amp;A96)
     +
-    SUMIFS([42]FinancingJournal!$E:$E,
-           [42]FinancingJournal!$C:$C,"Withdrawal",
-           [42]FinancingJournal!$A:$A,"&lt;="&amp;A96),
+    SUMIFS([43]FinancingJournal!$E:$E,
+           [43]FinancingJournal!$C:$C,"Withdrawal",
+           [43]FinancingJournal!$A:$A,"&lt;="&amp;A96),
     "")</f>
         <v/>
       </c>
@@ -23697,41 +24054,41 @@
       <c r="A97" s="16"/>
       <c r="B97" s="17" t="str">
         <f>IF(A97&lt;&gt;"",
-    SUMIFS([42]FinancingJournal!$E:$E,
-           [42]FinancingJournal!$C:$C,"Capital Injection",
-           [42]FinancingJournal!$A:$A,"&lt;="&amp;A97),
+    SUMIFS([43]FinancingJournal!$E:$E,
+           [43]FinancingJournal!$C:$C,"Capital Injection",
+           [43]FinancingJournal!$A:$A,"&lt;="&amp;A97),
     "")</f>
         <v/>
       </c>
       <c r="C97" s="18" t="str">
         <f>IF(A97&lt;&gt;"",
-    SUMIFS([42]InvestingJournal!$F:$F,
-           [42]InvestingJournal!$C:$C,"Izra Advance",
-           [42]InvestingJournal!$A:$A,"&lt;="&amp;A97)
+    SUMIFS([43]InvestingJournal!$F:$F,
+           [43]InvestingJournal!$C:$C,"Izra Advance",
+           [43]InvestingJournal!$A:$A,"&lt;="&amp;A97)
     +
-    SUMIFS([42]InvestingJournal!$F:$F,
-           [42]InvestingJournal!$C:$C,"Investment to Unit",
-           [42]InvestingJournal!$A:$A,"&lt;="&amp;A97),
+    SUMIFS([43]InvestingJournal!$F:$F,
+           [43]InvestingJournal!$C:$C,"Investment to Unit",
+           [43]InvestingJournal!$A:$A,"&lt;="&amp;A97),
     "")</f>
         <v/>
       </c>
       <c r="D97" s="18" t="str">
         <f>IF(A97&lt;&gt;"",
-    SUMIFS([42]InvestingJournal!$F:$F,
-           [42]InvestingJournal!$C:$C,"Loan Advance",
-           [42]InvestingJournal!$A:$A,"&lt;="&amp;A97),
+    SUMIFS([43]InvestingJournal!$F:$F,
+           [43]InvestingJournal!$C:$C,"Loan Advance",
+           [43]InvestingJournal!$A:$A,"&lt;="&amp;A97),
     "")</f>
         <v/>
       </c>
       <c r="E97" s="18" t="str">
         <f>IF(A97&lt;&gt;"",
-    SUMIFS([42]FinancingJournal!$E:$E,
-           [42]FinancingJournal!$C:$C,"Borrowing",
-           [42]FinancingJournal!$A:$A,"&lt;="&amp;A97)
+    SUMIFS([43]FinancingJournal!$E:$E,
+           [43]FinancingJournal!$C:$C,"Borrowing",
+           [43]FinancingJournal!$A:$A,"&lt;="&amp;A97)
     +
-    SUMIFS([42]FinancingJournal!$E:$E,
-           [42]FinancingJournal!$C:$C,"Withdrawal",
-           [42]FinancingJournal!$A:$A,"&lt;="&amp;A97),
+    SUMIFS([43]FinancingJournal!$E:$E,
+           [43]FinancingJournal!$C:$C,"Withdrawal",
+           [43]FinancingJournal!$A:$A,"&lt;="&amp;A97),
     "")</f>
         <v/>
       </c>
@@ -23746,41 +24103,41 @@
       <c r="A98" s="11"/>
       <c r="B98" s="14" t="str">
         <f>IF(A98&lt;&gt;"",
-    SUMIFS([42]FinancingJournal!$E:$E,
-           [42]FinancingJournal!$C:$C,"Capital Injection",
-           [42]FinancingJournal!$A:$A,"&lt;="&amp;A98),
+    SUMIFS([43]FinancingJournal!$E:$E,
+           [43]FinancingJournal!$C:$C,"Capital Injection",
+           [43]FinancingJournal!$A:$A,"&lt;="&amp;A98),
     "")</f>
         <v/>
       </c>
       <c r="C98" s="15" t="str">
         <f>IF(A98&lt;&gt;"",
-    SUMIFS([42]InvestingJournal!$F:$F,
-           [42]InvestingJournal!$C:$C,"Izra Advance",
-           [42]InvestingJournal!$A:$A,"&lt;="&amp;A98)
+    SUMIFS([43]InvestingJournal!$F:$F,
+           [43]InvestingJournal!$C:$C,"Izra Advance",
+           [43]InvestingJournal!$A:$A,"&lt;="&amp;A98)
     +
-    SUMIFS([42]InvestingJournal!$F:$F,
-           [42]InvestingJournal!$C:$C,"Investment to Unit",
-           [42]InvestingJournal!$A:$A,"&lt;="&amp;A98),
+    SUMIFS([43]InvestingJournal!$F:$F,
+           [43]InvestingJournal!$C:$C,"Investment to Unit",
+           [43]InvestingJournal!$A:$A,"&lt;="&amp;A98),
     "")</f>
         <v/>
       </c>
       <c r="D98" s="15" t="str">
         <f>IF(A98&lt;&gt;"",
-    SUMIFS([42]InvestingJournal!$F:$F,
-           [42]InvestingJournal!$C:$C,"Loan Advance",
-           [42]InvestingJournal!$A:$A,"&lt;="&amp;A98),
+    SUMIFS([43]InvestingJournal!$F:$F,
+           [43]InvestingJournal!$C:$C,"Loan Advance",
+           [43]InvestingJournal!$A:$A,"&lt;="&amp;A98),
     "")</f>
         <v/>
       </c>
       <c r="E98" s="15" t="str">
         <f>IF(A98&lt;&gt;"",
-    SUMIFS([42]FinancingJournal!$E:$E,
-           [42]FinancingJournal!$C:$C,"Borrowing",
-           [42]FinancingJournal!$A:$A,"&lt;="&amp;A98)
+    SUMIFS([43]FinancingJournal!$E:$E,
+           [43]FinancingJournal!$C:$C,"Borrowing",
+           [43]FinancingJournal!$A:$A,"&lt;="&amp;A98)
     +
-    SUMIFS([42]FinancingJournal!$E:$E,
-           [42]FinancingJournal!$C:$C,"Withdrawal",
-           [42]FinancingJournal!$A:$A,"&lt;="&amp;A98),
+    SUMIFS([43]FinancingJournal!$E:$E,
+           [43]FinancingJournal!$C:$C,"Withdrawal",
+           [43]FinancingJournal!$A:$A,"&lt;="&amp;A98),
     "")</f>
         <v/>
       </c>
@@ -23794,41 +24151,41 @@
       <c r="A99" s="16"/>
       <c r="B99" s="17" t="str">
         <f>IF(A99&lt;&gt;"",
-    SUMIFS([42]FinancingJournal!$E:$E,
-           [42]FinancingJournal!$C:$C,"Capital Injection",
-           [42]FinancingJournal!$A:$A,"&lt;="&amp;A99),
+    SUMIFS([43]FinancingJournal!$E:$E,
+           [43]FinancingJournal!$C:$C,"Capital Injection",
+           [43]FinancingJournal!$A:$A,"&lt;="&amp;A99),
     "")</f>
         <v/>
       </c>
       <c r="C99" s="18" t="str">
         <f>IF(A99&lt;&gt;"",
-    SUMIFS([42]InvestingJournal!$F:$F,
-           [42]InvestingJournal!$C:$C,"Izra Advance",
-           [42]InvestingJournal!$A:$A,"&lt;="&amp;A99)
+    SUMIFS([43]InvestingJournal!$F:$F,
+           [43]InvestingJournal!$C:$C,"Izra Advance",
+           [43]InvestingJournal!$A:$A,"&lt;="&amp;A99)
     +
-    SUMIFS([42]InvestingJournal!$F:$F,
-           [42]InvestingJournal!$C:$C,"Investment to Unit",
-           [42]InvestingJournal!$A:$A,"&lt;="&amp;A99),
+    SUMIFS([43]InvestingJournal!$F:$F,
+           [43]InvestingJournal!$C:$C,"Investment to Unit",
+           [43]InvestingJournal!$A:$A,"&lt;="&amp;A99),
     "")</f>
         <v/>
       </c>
       <c r="D99" s="18" t="str">
         <f>IF(A99&lt;&gt;"",
-    SUMIFS([42]InvestingJournal!$F:$F,
-           [42]InvestingJournal!$C:$C,"Loan Advance",
-           [42]InvestingJournal!$A:$A,"&lt;="&amp;A99),
+    SUMIFS([43]InvestingJournal!$F:$F,
+           [43]InvestingJournal!$C:$C,"Loan Advance",
+           [43]InvestingJournal!$A:$A,"&lt;="&amp;A99),
     "")</f>
         <v/>
       </c>
       <c r="E99" s="18" t="str">
         <f>IF(A99&lt;&gt;"",
-    SUMIFS([42]FinancingJournal!$E:$E,
-           [42]FinancingJournal!$C:$C,"Borrowing",
-           [42]FinancingJournal!$A:$A,"&lt;="&amp;A99)
+    SUMIFS([43]FinancingJournal!$E:$E,
+           [43]FinancingJournal!$C:$C,"Borrowing",
+           [43]FinancingJournal!$A:$A,"&lt;="&amp;A99)
     +
-    SUMIFS([42]FinancingJournal!$E:$E,
-           [42]FinancingJournal!$C:$C,"Withdrawal",
-           [42]FinancingJournal!$A:$A,"&lt;="&amp;A99),
+    SUMIFS([43]FinancingJournal!$E:$E,
+           [43]FinancingJournal!$C:$C,"Withdrawal",
+           [43]FinancingJournal!$A:$A,"&lt;="&amp;A99),
     "")</f>
         <v/>
       </c>
@@ -23843,41 +24200,41 @@
       <c r="A100" s="11"/>
       <c r="B100" s="14" t="str">
         <f>IF(A100&lt;&gt;"",
-    SUMIFS([42]FinancingJournal!$E:$E,
-           [42]FinancingJournal!$C:$C,"Capital Injection",
-           [42]FinancingJournal!$A:$A,"&lt;="&amp;A100),
+    SUMIFS([43]FinancingJournal!$E:$E,
+           [43]FinancingJournal!$C:$C,"Capital Injection",
+           [43]FinancingJournal!$A:$A,"&lt;="&amp;A100),
     "")</f>
         <v/>
       </c>
       <c r="C100" s="15" t="str">
         <f>IF(A100&lt;&gt;"",
-    SUMIFS([42]InvestingJournal!$F:$F,
-           [42]InvestingJournal!$C:$C,"Izra Advance",
-           [42]InvestingJournal!$A:$A,"&lt;="&amp;A100)
+    SUMIFS([43]InvestingJournal!$F:$F,
+           [43]InvestingJournal!$C:$C,"Izra Advance",
+           [43]InvestingJournal!$A:$A,"&lt;="&amp;A100)
     +
-    SUMIFS([42]InvestingJournal!$F:$F,
-           [42]InvestingJournal!$C:$C,"Investment to Unit",
-           [42]InvestingJournal!$A:$A,"&lt;="&amp;A100),
+    SUMIFS([43]InvestingJournal!$F:$F,
+           [43]InvestingJournal!$C:$C,"Investment to Unit",
+           [43]InvestingJournal!$A:$A,"&lt;="&amp;A100),
     "")</f>
         <v/>
       </c>
       <c r="D100" s="15" t="str">
         <f>IF(A100&lt;&gt;"",
-    SUMIFS([42]InvestingJournal!$F:$F,
-           [42]InvestingJournal!$C:$C,"Loan Advance",
-           [42]InvestingJournal!$A:$A,"&lt;="&amp;A100),
+    SUMIFS([43]InvestingJournal!$F:$F,
+           [43]InvestingJournal!$C:$C,"Loan Advance",
+           [43]InvestingJournal!$A:$A,"&lt;="&amp;A100),
     "")</f>
         <v/>
       </c>
       <c r="E100" s="15" t="str">
         <f>IF(A100&lt;&gt;"",
-    SUMIFS([42]FinancingJournal!$E:$E,
-           [42]FinancingJournal!$C:$C,"Borrowing",
-           [42]FinancingJournal!$A:$A,"&lt;="&amp;A100)
+    SUMIFS([43]FinancingJournal!$E:$E,
+           [43]FinancingJournal!$C:$C,"Borrowing",
+           [43]FinancingJournal!$A:$A,"&lt;="&amp;A100)
     +
-    SUMIFS([42]FinancingJournal!$E:$E,
-           [42]FinancingJournal!$C:$C,"Withdrawal",
-           [42]FinancingJournal!$A:$A,"&lt;="&amp;A100),
+    SUMIFS([43]FinancingJournal!$E:$E,
+           [43]FinancingJournal!$C:$C,"Withdrawal",
+           [43]FinancingJournal!$A:$A,"&lt;="&amp;A100),
     "")</f>
         <v/>
       </c>
@@ -23891,9 +24248,9 @@
       <c r="A101" s="16"/>
       <c r="B101" s="17" t="str">
         <f>IF(A101&lt;&gt;"",
-    SUMIFS([42]FinancingJournal!$E:$E,
-           [42]FinancingJournal!$C:$C,"Capital Injection",
-           [42]FinancingJournal!$A:$A,"&lt;="&amp;A101),
+    SUMIFS([43]FinancingJournal!$E:$E,
+           [43]FinancingJournal!$C:$C,"Capital Injection",
+           [43]FinancingJournal!$A:$A,"&lt;="&amp;A101),
     "")</f>
         <v/>
       </c>
@@ -23911,41 +24268,41 @@
       <c r="A102" s="11"/>
       <c r="B102" s="14" t="str">
         <f>IF(A102&lt;&gt;"",
-    SUMIFS([42]FinancingJournal!$E:$E,
-           [42]FinancingJournal!$C:$C,"Capital Injection",
-           [42]FinancingJournal!$A:$A,"&lt;="&amp;A102),
+    SUMIFS([43]FinancingJournal!$E:$E,
+           [43]FinancingJournal!$C:$C,"Capital Injection",
+           [43]FinancingJournal!$A:$A,"&lt;="&amp;A102),
     "")</f>
         <v/>
       </c>
       <c r="C102" s="15" t="str">
         <f>IF(A102&lt;&gt;"",
-    SUMIFS([42]InvestingJournal!$F:$F,
-           [42]InvestingJournal!$C:$C,"Izra Advance",
-           [42]InvestingJournal!$A:$A,"&lt;="&amp;A102)
+    SUMIFS([43]InvestingJournal!$F:$F,
+           [43]InvestingJournal!$C:$C,"Izra Advance",
+           [43]InvestingJournal!$A:$A,"&lt;="&amp;A102)
     +
-    SUMIFS([42]InvestingJournal!$F:$F,
-           [42]InvestingJournal!$C:$C,"Investment to Unit",
-           [42]InvestingJournal!$A:$A,"&lt;="&amp;A102),
+    SUMIFS([43]InvestingJournal!$F:$F,
+           [43]InvestingJournal!$C:$C,"Investment to Unit",
+           [43]InvestingJournal!$A:$A,"&lt;="&amp;A102),
     "")</f>
         <v/>
       </c>
       <c r="D102" s="15" t="str">
         <f>IF(A102&lt;&gt;"",
-    SUMIFS([42]InvestingJournal!$F:$F,
-           [42]InvestingJournal!$C:$C,"Loan Advance",
-           [42]InvestingJournal!$A:$A,"&lt;="&amp;A102),
+    SUMIFS([43]InvestingJournal!$F:$F,
+           [43]InvestingJournal!$C:$C,"Loan Advance",
+           [43]InvestingJournal!$A:$A,"&lt;="&amp;A102),
     "")</f>
         <v/>
       </c>
       <c r="E102" s="15" t="str">
         <f>IF(A102&lt;&gt;"",
-    SUMIFS([42]FinancingJournal!$E:$E,
-           [42]FinancingJournal!$C:$C,"Borrowing",
-           [42]FinancingJournal!$A:$A,"&lt;="&amp;A102)
+    SUMIFS([43]FinancingJournal!$E:$E,
+           [43]FinancingJournal!$C:$C,"Borrowing",
+           [43]FinancingJournal!$A:$A,"&lt;="&amp;A102)
     +
-    SUMIFS([42]FinancingJournal!$E:$E,
-           [42]FinancingJournal!$C:$C,"Withdrawal",
-           [42]FinancingJournal!$A:$A,"&lt;="&amp;A102),
+    SUMIFS([43]FinancingJournal!$E:$E,
+           [43]FinancingJournal!$C:$C,"Withdrawal",
+           [43]FinancingJournal!$A:$A,"&lt;="&amp;A102),
     "")</f>
         <v/>
       </c>
@@ -23959,41 +24316,41 @@
       <c r="A103" s="16"/>
       <c r="B103" s="17" t="str">
         <f>IF(A103&lt;&gt;"",
-    SUMIFS([42]FinancingJournal!$E:$E,
-           [42]FinancingJournal!$C:$C,"Capital Injection",
-           [42]FinancingJournal!$A:$A,"&lt;="&amp;A103),
+    SUMIFS([43]FinancingJournal!$E:$E,
+           [43]FinancingJournal!$C:$C,"Capital Injection",
+           [43]FinancingJournal!$A:$A,"&lt;="&amp;A103),
     "")</f>
         <v/>
       </c>
       <c r="C103" s="18" t="str">
         <f>IF(A103&lt;&gt;"",
-    SUMIFS([42]InvestingJournal!$F:$F,
-           [42]InvestingJournal!$C:$C,"Izra Advance",
-           [42]InvestingJournal!$A:$A,"&lt;="&amp;A103)
+    SUMIFS([43]InvestingJournal!$F:$F,
+           [43]InvestingJournal!$C:$C,"Izra Advance",
+           [43]InvestingJournal!$A:$A,"&lt;="&amp;A103)
     +
-    SUMIFS([42]InvestingJournal!$F:$F,
-           [42]InvestingJournal!$C:$C,"Investment to Unit",
-           [42]InvestingJournal!$A:$A,"&lt;="&amp;A103),
+    SUMIFS([43]InvestingJournal!$F:$F,
+           [43]InvestingJournal!$C:$C,"Investment to Unit",
+           [43]InvestingJournal!$A:$A,"&lt;="&amp;A103),
     "")</f>
         <v/>
       </c>
       <c r="D103" s="18" t="str">
         <f>IF(A103&lt;&gt;"",
-    SUMIFS([42]InvestingJournal!$F:$F,
-           [42]InvestingJournal!$C:$C,"Loan Advance",
-           [42]InvestingJournal!$A:$A,"&lt;="&amp;A103),
+    SUMIFS([43]InvestingJournal!$F:$F,
+           [43]InvestingJournal!$C:$C,"Loan Advance",
+           [43]InvestingJournal!$A:$A,"&lt;="&amp;A103),
     "")</f>
         <v/>
       </c>
       <c r="E103" s="18" t="str">
         <f>IF(A103&lt;&gt;"",
-    SUMIFS([42]FinancingJournal!$E:$E,
-           [42]FinancingJournal!$C:$C,"Borrowing",
-           [42]FinancingJournal!$A:$A,"&lt;="&amp;A103)
+    SUMIFS([43]FinancingJournal!$E:$E,
+           [43]FinancingJournal!$C:$C,"Borrowing",
+           [43]FinancingJournal!$A:$A,"&lt;="&amp;A103)
     +
-    SUMIFS([42]FinancingJournal!$E:$E,
-           [42]FinancingJournal!$C:$C,"Withdrawal",
-           [42]FinancingJournal!$A:$A,"&lt;="&amp;A103),
+    SUMIFS([43]FinancingJournal!$E:$E,
+           [43]FinancingJournal!$C:$C,"Withdrawal",
+           [43]FinancingJournal!$A:$A,"&lt;="&amp;A103),
     "")</f>
         <v/>
       </c>
@@ -24008,41 +24365,41 @@
       <c r="A104" s="11"/>
       <c r="B104" s="14" t="str">
         <f>IF(A104&lt;&gt;"",
-    SUMIFS([42]FinancingJournal!$E:$E,
-           [42]FinancingJournal!$C:$C,"Capital Injection",
-           [42]FinancingJournal!$A:$A,"&lt;="&amp;A104),
+    SUMIFS([43]FinancingJournal!$E:$E,
+           [43]FinancingJournal!$C:$C,"Capital Injection",
+           [43]FinancingJournal!$A:$A,"&lt;="&amp;A104),
     "")</f>
         <v/>
       </c>
       <c r="C104" s="15" t="str">
         <f>IF(A104&lt;&gt;"",
-    SUMIFS([42]InvestingJournal!$F:$F,
-           [42]InvestingJournal!$C:$C,"Izra Advance",
-           [42]InvestingJournal!$A:$A,"&lt;="&amp;A104)
+    SUMIFS([43]InvestingJournal!$F:$F,
+           [43]InvestingJournal!$C:$C,"Izra Advance",
+           [43]InvestingJournal!$A:$A,"&lt;="&amp;A104)
     +
-    SUMIFS([42]InvestingJournal!$F:$F,
-           [42]InvestingJournal!$C:$C,"Investment to Unit",
-           [42]InvestingJournal!$A:$A,"&lt;="&amp;A104),
+    SUMIFS([43]InvestingJournal!$F:$F,
+           [43]InvestingJournal!$C:$C,"Investment to Unit",
+           [43]InvestingJournal!$A:$A,"&lt;="&amp;A104),
     "")</f>
         <v/>
       </c>
       <c r="D104" s="15" t="str">
         <f>IF(A104&lt;&gt;"",
-    SUMIFS([42]InvestingJournal!$F:$F,
-           [42]InvestingJournal!$C:$C,"Loan Advance",
-           [42]InvestingJournal!$A:$A,"&lt;="&amp;A104),
+    SUMIFS([43]InvestingJournal!$F:$F,
+           [43]InvestingJournal!$C:$C,"Loan Advance",
+           [43]InvestingJournal!$A:$A,"&lt;="&amp;A104),
     "")</f>
         <v/>
       </c>
       <c r="E104" s="15" t="str">
         <f>IF(A104&lt;&gt;"",
-    SUMIFS([42]FinancingJournal!$E:$E,
-           [42]FinancingJournal!$C:$C,"Borrowing",
-           [42]FinancingJournal!$A:$A,"&lt;="&amp;A104)
+    SUMIFS([43]FinancingJournal!$E:$E,
+           [43]FinancingJournal!$C:$C,"Borrowing",
+           [43]FinancingJournal!$A:$A,"&lt;="&amp;A104)
     +
-    SUMIFS([42]FinancingJournal!$E:$E,
-           [42]FinancingJournal!$C:$C,"Withdrawal",
-           [42]FinancingJournal!$A:$A,"&lt;="&amp;A104),
+    SUMIFS([43]FinancingJournal!$E:$E,
+           [43]FinancingJournal!$C:$C,"Withdrawal",
+           [43]FinancingJournal!$A:$A,"&lt;="&amp;A104),
     "")</f>
         <v/>
       </c>
@@ -24056,41 +24413,41 @@
       <c r="A105" s="16"/>
       <c r="B105" s="17" t="str">
         <f>IF(A105&lt;&gt;"",
-    SUMIFS([42]FinancingJournal!$E:$E,
-           [42]FinancingJournal!$C:$C,"Capital Injection",
-           [42]FinancingJournal!$A:$A,"&lt;="&amp;A105),
+    SUMIFS([43]FinancingJournal!$E:$E,
+           [43]FinancingJournal!$C:$C,"Capital Injection",
+           [43]FinancingJournal!$A:$A,"&lt;="&amp;A105),
     "")</f>
         <v/>
       </c>
       <c r="C105" s="18" t="str">
         <f>IF(A105&lt;&gt;"",
-    SUMIFS([42]InvestingJournal!$F:$F,
-           [42]InvestingJournal!$C:$C,"Izra Advance",
-           [42]InvestingJournal!$A:$A,"&lt;="&amp;A105)
+    SUMIFS([43]InvestingJournal!$F:$F,
+           [43]InvestingJournal!$C:$C,"Izra Advance",
+           [43]InvestingJournal!$A:$A,"&lt;="&amp;A105)
     +
-    SUMIFS([42]InvestingJournal!$F:$F,
-           [42]InvestingJournal!$C:$C,"Investment to Unit",
-           [42]InvestingJournal!$A:$A,"&lt;="&amp;A105),
+    SUMIFS([43]InvestingJournal!$F:$F,
+           [43]InvestingJournal!$C:$C,"Investment to Unit",
+           [43]InvestingJournal!$A:$A,"&lt;="&amp;A105),
     "")</f>
         <v/>
       </c>
       <c r="D105" s="18" t="str">
         <f>IF(A105&lt;&gt;"",
-    SUMIFS([42]InvestingJournal!$F:$F,
-           [42]InvestingJournal!$C:$C,"Loan Advance",
-           [42]InvestingJournal!$A:$A,"&lt;="&amp;A105),
+    SUMIFS([43]InvestingJournal!$F:$F,
+           [43]InvestingJournal!$C:$C,"Loan Advance",
+           [43]InvestingJournal!$A:$A,"&lt;="&amp;A105),
     "")</f>
         <v/>
       </c>
       <c r="E105" s="18" t="str">
         <f>IF(A105&lt;&gt;"",
-    SUMIFS([42]FinancingJournal!$E:$E,
-           [42]FinancingJournal!$C:$C,"Borrowing",
-           [42]FinancingJournal!$A:$A,"&lt;="&amp;A105)
+    SUMIFS([43]FinancingJournal!$E:$E,
+           [43]FinancingJournal!$C:$C,"Borrowing",
+           [43]FinancingJournal!$A:$A,"&lt;="&amp;A105)
     +
-    SUMIFS([42]FinancingJournal!$E:$E,
-           [42]FinancingJournal!$C:$C,"Withdrawal",
-           [42]FinancingJournal!$A:$A,"&lt;="&amp;A105),
+    SUMIFS([43]FinancingJournal!$E:$E,
+           [43]FinancingJournal!$C:$C,"Withdrawal",
+           [43]FinancingJournal!$A:$A,"&lt;="&amp;A105),
     "")</f>
         <v/>
       </c>
@@ -24105,41 +24462,41 @@
       <c r="A106" s="11"/>
       <c r="B106" s="14" t="str">
         <f>IF(A106&lt;&gt;"",
-    SUMIFS([42]FinancingJournal!$E:$E,
-           [42]FinancingJournal!$C:$C,"Capital Injection",
-           [42]FinancingJournal!$A:$A,"&lt;="&amp;A106),
+    SUMIFS([43]FinancingJournal!$E:$E,
+           [43]FinancingJournal!$C:$C,"Capital Injection",
+           [43]FinancingJournal!$A:$A,"&lt;="&amp;A106),
     "")</f>
         <v/>
       </c>
       <c r="C106" s="15" t="str">
         <f>IF(A106&lt;&gt;"",
-    SUMIFS([42]InvestingJournal!$F:$F,
-           [42]InvestingJournal!$C:$C,"Izra Advance",
-           [42]InvestingJournal!$A:$A,"&lt;="&amp;A106)
+    SUMIFS([43]InvestingJournal!$F:$F,
+           [43]InvestingJournal!$C:$C,"Izra Advance",
+           [43]InvestingJournal!$A:$A,"&lt;="&amp;A106)
     +
-    SUMIFS([42]InvestingJournal!$F:$F,
-           [42]InvestingJournal!$C:$C,"Investment to Unit",
-           [42]InvestingJournal!$A:$A,"&lt;="&amp;A106),
+    SUMIFS([43]InvestingJournal!$F:$F,
+           [43]InvestingJournal!$C:$C,"Investment to Unit",
+           [43]InvestingJournal!$A:$A,"&lt;="&amp;A106),
     "")</f>
         <v/>
       </c>
       <c r="D106" s="15" t="str">
         <f>IF(A106&lt;&gt;"",
-    SUMIFS([42]InvestingJournal!$F:$F,
-           [42]InvestingJournal!$C:$C,"Loan Advance",
-           [42]InvestingJournal!$A:$A,"&lt;="&amp;A106),
+    SUMIFS([43]InvestingJournal!$F:$F,
+           [43]InvestingJournal!$C:$C,"Loan Advance",
+           [43]InvestingJournal!$A:$A,"&lt;="&amp;A106),
     "")</f>
         <v/>
       </c>
       <c r="E106" s="15" t="str">
         <f>IF(A106&lt;&gt;"",
-    SUMIFS([42]FinancingJournal!$E:$E,
-           [42]FinancingJournal!$C:$C,"Borrowing",
-           [42]FinancingJournal!$A:$A,"&lt;="&amp;A106)
+    SUMIFS([43]FinancingJournal!$E:$E,
+           [43]FinancingJournal!$C:$C,"Borrowing",
+           [43]FinancingJournal!$A:$A,"&lt;="&amp;A106)
     +
-    SUMIFS([42]FinancingJournal!$E:$E,
-           [42]FinancingJournal!$C:$C,"Withdrawal",
-           [42]FinancingJournal!$A:$A,"&lt;="&amp;A106),
+    SUMIFS([43]FinancingJournal!$E:$E,
+           [43]FinancingJournal!$C:$C,"Withdrawal",
+           [43]FinancingJournal!$A:$A,"&lt;="&amp;A106),
     "")</f>
         <v/>
       </c>
@@ -24153,41 +24510,41 @@
       <c r="A107" s="16"/>
       <c r="B107" s="17" t="str">
         <f>IF(A107&lt;&gt;"",
-    SUMIFS([42]FinancingJournal!$E:$E,
-           [42]FinancingJournal!$C:$C,"Capital Injection",
-           [42]FinancingJournal!$A:$A,"&lt;="&amp;A107),
+    SUMIFS([43]FinancingJournal!$E:$E,
+           [43]FinancingJournal!$C:$C,"Capital Injection",
+           [43]FinancingJournal!$A:$A,"&lt;="&amp;A107),
     "")</f>
         <v/>
       </c>
       <c r="C107" s="18" t="str">
         <f>IF(A107&lt;&gt;"",
-    SUMIFS([42]InvestingJournal!$F:$F,
-           [42]InvestingJournal!$C:$C,"Izra Advance",
-           [42]InvestingJournal!$A:$A,"&lt;="&amp;A107)
+    SUMIFS([43]InvestingJournal!$F:$F,
+           [43]InvestingJournal!$C:$C,"Izra Advance",
+           [43]InvestingJournal!$A:$A,"&lt;="&amp;A107)
     +
-    SUMIFS([42]InvestingJournal!$F:$F,
-           [42]InvestingJournal!$C:$C,"Investment to Unit",
-           [42]InvestingJournal!$A:$A,"&lt;="&amp;A107),
+    SUMIFS([43]InvestingJournal!$F:$F,
+           [43]InvestingJournal!$C:$C,"Investment to Unit",
+           [43]InvestingJournal!$A:$A,"&lt;="&amp;A107),
     "")</f>
         <v/>
       </c>
       <c r="D107" s="18" t="str">
         <f>IF(A107&lt;&gt;"",
-    SUMIFS([42]InvestingJournal!$F:$F,
-           [42]InvestingJournal!$C:$C,"Loan Advance",
-           [42]InvestingJournal!$A:$A,"&lt;="&amp;A107),
+    SUMIFS([43]InvestingJournal!$F:$F,
+           [43]InvestingJournal!$C:$C,"Loan Advance",
+           [43]InvestingJournal!$A:$A,"&lt;="&amp;A107),
     "")</f>
         <v/>
       </c>
       <c r="E107" s="18" t="str">
         <f>IF(A107&lt;&gt;"",
-    SUMIFS([42]FinancingJournal!$E:$E,
-           [42]FinancingJournal!$C:$C,"Borrowing",
-           [42]FinancingJournal!$A:$A,"&lt;="&amp;A107)
+    SUMIFS([43]FinancingJournal!$E:$E,
+           [43]FinancingJournal!$C:$C,"Borrowing",
+           [43]FinancingJournal!$A:$A,"&lt;="&amp;A107)
     +
-    SUMIFS([42]FinancingJournal!$E:$E,
-           [42]FinancingJournal!$C:$C,"Withdrawal",
-           [42]FinancingJournal!$A:$A,"&lt;="&amp;A107),
+    SUMIFS([43]FinancingJournal!$E:$E,
+           [43]FinancingJournal!$C:$C,"Withdrawal",
+           [43]FinancingJournal!$A:$A,"&lt;="&amp;A107),
     "")</f>
         <v/>
       </c>
@@ -24202,41 +24559,41 @@
       <c r="A108" s="11"/>
       <c r="B108" s="14" t="str">
         <f>IF(A108&lt;&gt;"",
-    SUMIFS([42]FinancingJournal!$E:$E,
-           [42]FinancingJournal!$C:$C,"Capital Injection",
-           [42]FinancingJournal!$A:$A,"&lt;="&amp;A108),
+    SUMIFS([43]FinancingJournal!$E:$E,
+           [43]FinancingJournal!$C:$C,"Capital Injection",
+           [43]FinancingJournal!$A:$A,"&lt;="&amp;A108),
     "")</f>
         <v/>
       </c>
       <c r="C108" s="15" t="str">
         <f>IF(A108&lt;&gt;"",
-    SUMIFS([42]InvestingJournal!$F:$F,
-           [42]InvestingJournal!$C:$C,"Izra Advance",
-           [42]InvestingJournal!$A:$A,"&lt;="&amp;A108)
+    SUMIFS([43]InvestingJournal!$F:$F,
+           [43]InvestingJournal!$C:$C,"Izra Advance",
+           [43]InvestingJournal!$A:$A,"&lt;="&amp;A108)
     +
-    SUMIFS([42]InvestingJournal!$F:$F,
-           [42]InvestingJournal!$C:$C,"Investment to Unit",
-           [42]InvestingJournal!$A:$A,"&lt;="&amp;A108),
+    SUMIFS([43]InvestingJournal!$F:$F,
+           [43]InvestingJournal!$C:$C,"Investment to Unit",
+           [43]InvestingJournal!$A:$A,"&lt;="&amp;A108),
     "")</f>
         <v/>
       </c>
       <c r="D108" s="15" t="str">
         <f>IF(A108&lt;&gt;"",
-    SUMIFS([42]InvestingJournal!$F:$F,
-           [42]InvestingJournal!$C:$C,"Loan Advance",
-           [42]InvestingJournal!$A:$A,"&lt;="&amp;A108),
+    SUMIFS([43]InvestingJournal!$F:$F,
+           [43]InvestingJournal!$C:$C,"Loan Advance",
+           [43]InvestingJournal!$A:$A,"&lt;="&amp;A108),
     "")</f>
         <v/>
       </c>
       <c r="E108" s="15" t="str">
         <f>IF(A108&lt;&gt;"",
-    SUMIFS([42]FinancingJournal!$E:$E,
-           [42]FinancingJournal!$C:$C,"Borrowing",
-           [42]FinancingJournal!$A:$A,"&lt;="&amp;A108)
+    SUMIFS([43]FinancingJournal!$E:$E,
+           [43]FinancingJournal!$C:$C,"Borrowing",
+           [43]FinancingJournal!$A:$A,"&lt;="&amp;A108)
     +
-    SUMIFS([42]FinancingJournal!$E:$E,
-           [42]FinancingJournal!$C:$C,"Withdrawal",
-           [42]FinancingJournal!$A:$A,"&lt;="&amp;A108),
+    SUMIFS([43]FinancingJournal!$E:$E,
+           [43]FinancingJournal!$C:$C,"Withdrawal",
+           [43]FinancingJournal!$A:$A,"&lt;="&amp;A108),
     "")</f>
         <v/>
       </c>
@@ -24250,41 +24607,41 @@
       <c r="A109" s="16"/>
       <c r="B109" s="17" t="str">
         <f>IF(A109&lt;&gt;"",
-    SUMIFS([42]FinancingJournal!$E:$E,
-           [42]FinancingJournal!$C:$C,"Capital Injection",
-           [42]FinancingJournal!$A:$A,"&lt;="&amp;A109),
+    SUMIFS([43]FinancingJournal!$E:$E,
+           [43]FinancingJournal!$C:$C,"Capital Injection",
+           [43]FinancingJournal!$A:$A,"&lt;="&amp;A109),
     "")</f>
         <v/>
       </c>
       <c r="C109" s="18" t="str">
         <f>IF(A109&lt;&gt;"",
-    SUMIFS([42]InvestingJournal!$F:$F,
-           [42]InvestingJournal!$C:$C,"Izra Advance",
-           [42]InvestingJournal!$A:$A,"&lt;="&amp;A109)
+    SUMIFS([43]InvestingJournal!$F:$F,
+           [43]InvestingJournal!$C:$C,"Izra Advance",
+           [43]InvestingJournal!$A:$A,"&lt;="&amp;A109)
     +
-    SUMIFS([42]InvestingJournal!$F:$F,
-           [42]InvestingJournal!$C:$C,"Investment to Unit",
-           [42]InvestingJournal!$A:$A,"&lt;="&amp;A109),
+    SUMIFS([43]InvestingJournal!$F:$F,
+           [43]InvestingJournal!$C:$C,"Investment to Unit",
+           [43]InvestingJournal!$A:$A,"&lt;="&amp;A109),
     "")</f>
         <v/>
       </c>
       <c r="D109" s="18" t="str">
         <f>IF(A109&lt;&gt;"",
-    SUMIFS([42]InvestingJournal!$F:$F,
-           [42]InvestingJournal!$C:$C,"Loan Advance",
-           [42]InvestingJournal!$A:$A,"&lt;="&amp;A109),
+    SUMIFS([43]InvestingJournal!$F:$F,
+           [43]InvestingJournal!$C:$C,"Loan Advance",
+           [43]InvestingJournal!$A:$A,"&lt;="&amp;A109),
     "")</f>
         <v/>
       </c>
       <c r="E109" s="18" t="str">
         <f>IF(A109&lt;&gt;"",
-    SUMIFS([42]FinancingJournal!$E:$E,
-           [42]FinancingJournal!$C:$C,"Borrowing",
-           [42]FinancingJournal!$A:$A,"&lt;="&amp;A109)
+    SUMIFS([43]FinancingJournal!$E:$E,
+           [43]FinancingJournal!$C:$C,"Borrowing",
+           [43]FinancingJournal!$A:$A,"&lt;="&amp;A109)
     +
-    SUMIFS([42]FinancingJournal!$E:$E,
-           [42]FinancingJournal!$C:$C,"Withdrawal",
-           [42]FinancingJournal!$A:$A,"&lt;="&amp;A109),
+    SUMIFS([43]FinancingJournal!$E:$E,
+           [43]FinancingJournal!$C:$C,"Withdrawal",
+           [43]FinancingJournal!$A:$A,"&lt;="&amp;A109),
     "")</f>
         <v/>
       </c>
@@ -24299,41 +24656,41 @@
       <c r="A110" s="11"/>
       <c r="B110" s="14" t="str">
         <f>IF(A110&lt;&gt;"",
-    SUMIFS([42]FinancingJournal!$E:$E,
-           [42]FinancingJournal!$C:$C,"Capital Injection",
-           [42]FinancingJournal!$A:$A,"&lt;="&amp;A110),
+    SUMIFS([43]FinancingJournal!$E:$E,
+           [43]FinancingJournal!$C:$C,"Capital Injection",
+           [43]FinancingJournal!$A:$A,"&lt;="&amp;A110),
     "")</f>
         <v/>
       </c>
       <c r="C110" s="15" t="str">
         <f>IF(A110&lt;&gt;"",
-    SUMIFS([42]InvestingJournal!$F:$F,
-           [42]InvestingJournal!$C:$C,"Izra Advance",
-           [42]InvestingJournal!$A:$A,"&lt;="&amp;A110)
+    SUMIFS([43]InvestingJournal!$F:$F,
+           [43]InvestingJournal!$C:$C,"Izra Advance",
+           [43]InvestingJournal!$A:$A,"&lt;="&amp;A110)
     +
-    SUMIFS([42]InvestingJournal!$F:$F,
-           [42]InvestingJournal!$C:$C,"Investment to Unit",
-           [42]InvestingJournal!$A:$A,"&lt;="&amp;A110),
+    SUMIFS([43]InvestingJournal!$F:$F,
+           [43]InvestingJournal!$C:$C,"Investment to Unit",
+           [43]InvestingJournal!$A:$A,"&lt;="&amp;A110),
     "")</f>
         <v/>
       </c>
       <c r="D110" s="15" t="str">
         <f>IF(A110&lt;&gt;"",
-    SUMIFS([42]InvestingJournal!$F:$F,
-           [42]InvestingJournal!$C:$C,"Loan Advance",
-           [42]InvestingJournal!$A:$A,"&lt;="&amp;A110),
+    SUMIFS([43]InvestingJournal!$F:$F,
+           [43]InvestingJournal!$C:$C,"Loan Advance",
+           [43]InvestingJournal!$A:$A,"&lt;="&amp;A110),
     "")</f>
         <v/>
       </c>
       <c r="E110" s="15" t="str">
         <f>IF(A110&lt;&gt;"",
-    SUMIFS([42]FinancingJournal!$E:$E,
-           [42]FinancingJournal!$C:$C,"Borrowing",
-           [42]FinancingJournal!$A:$A,"&lt;="&amp;A110)
+    SUMIFS([43]FinancingJournal!$E:$E,
+           [43]FinancingJournal!$C:$C,"Borrowing",
+           [43]FinancingJournal!$A:$A,"&lt;="&amp;A110)
     +
-    SUMIFS([42]FinancingJournal!$E:$E,
-           [42]FinancingJournal!$C:$C,"Withdrawal",
-           [42]FinancingJournal!$A:$A,"&lt;="&amp;A110),
+    SUMIFS([43]FinancingJournal!$E:$E,
+           [43]FinancingJournal!$C:$C,"Withdrawal",
+           [43]FinancingJournal!$A:$A,"&lt;="&amp;A110),
     "")</f>
         <v/>
       </c>
@@ -24347,41 +24704,41 @@
       <c r="A111" s="16"/>
       <c r="B111" s="17" t="str">
         <f>IF(A111&lt;&gt;"",
-    SUMIFS([42]FinancingJournal!$E:$E,
-           [42]FinancingJournal!$C:$C,"Capital Injection",
-           [42]FinancingJournal!$A:$A,"&lt;="&amp;A111),
+    SUMIFS([43]FinancingJournal!$E:$E,
+           [43]FinancingJournal!$C:$C,"Capital Injection",
+           [43]FinancingJournal!$A:$A,"&lt;="&amp;A111),
     "")</f>
         <v/>
       </c>
       <c r="C111" s="18" t="str">
         <f>IF(A111&lt;&gt;"",
-    SUMIFS([42]InvestingJournal!$F:$F,
-           [42]InvestingJournal!$C:$C,"Izra Advance",
-           [42]InvestingJournal!$A:$A,"&lt;="&amp;A111)
+    SUMIFS([43]InvestingJournal!$F:$F,
+           [43]InvestingJournal!$C:$C,"Izra Advance",
+           [43]InvestingJournal!$A:$A,"&lt;="&amp;A111)
     +
-    SUMIFS([42]InvestingJournal!$F:$F,
-           [42]InvestingJournal!$C:$C,"Investment to Unit",
-           [42]InvestingJournal!$A:$A,"&lt;="&amp;A111),
+    SUMIFS([43]InvestingJournal!$F:$F,
+           [43]InvestingJournal!$C:$C,"Investment to Unit",
+           [43]InvestingJournal!$A:$A,"&lt;="&amp;A111),
     "")</f>
         <v/>
       </c>
       <c r="D111" s="18" t="str">
         <f>IF(A111&lt;&gt;"",
-    SUMIFS([42]InvestingJournal!$F:$F,
-           [42]InvestingJournal!$C:$C,"Loan Advance",
-           [42]InvestingJournal!$A:$A,"&lt;="&amp;A111),
+    SUMIFS([43]InvestingJournal!$F:$F,
+           [43]InvestingJournal!$C:$C,"Loan Advance",
+           [43]InvestingJournal!$A:$A,"&lt;="&amp;A111),
     "")</f>
         <v/>
       </c>
       <c r="E111" s="18" t="str">
         <f>IF(A111&lt;&gt;"",
-    SUMIFS([42]FinancingJournal!$E:$E,
-           [42]FinancingJournal!$C:$C,"Borrowing",
-           [42]FinancingJournal!$A:$A,"&lt;="&amp;A111)
+    SUMIFS([43]FinancingJournal!$E:$E,
+           [43]FinancingJournal!$C:$C,"Borrowing",
+           [43]FinancingJournal!$A:$A,"&lt;="&amp;A111)
     +
-    SUMIFS([42]FinancingJournal!$E:$E,
-           [42]FinancingJournal!$C:$C,"Withdrawal",
-           [42]FinancingJournal!$A:$A,"&lt;="&amp;A111),
+    SUMIFS([43]FinancingJournal!$E:$E,
+           [43]FinancingJournal!$C:$C,"Withdrawal",
+           [43]FinancingJournal!$A:$A,"&lt;="&amp;A111),
     "")</f>
         <v/>
       </c>
